--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -21783,7 +21783,7 @@
         <v>526</v>
       </c>
       <c r="G140" t="n">
-        <v>501.52</v>
+        <v>481.38</v>
       </c>
       <c r="H140" t="n">
         <v>1218000</v>
@@ -21795,7 +21795,7 @@
         <v>573</v>
       </c>
       <c r="K140" t="n">
-        <v>448.5</v>
+        <v>365</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1810500</v>
+        <v>1984500</v>
       </c>
       <c r="N2" t="n">
-        <v>2034493</v>
+        <v>2208493</v>
       </c>
       <c r="O2" t="n">
-        <v>2924527</v>
+        <v>3098527</v>
       </c>
       <c r="P2" t="n">
-        <v>2970912</v>
+        <v>3144912</v>
       </c>
       <c r="Q2" t="n">
         <v>1498076</v>
@@ -713,16 +713,16 @@
         <v>1953524</v>
       </c>
       <c r="U2" t="n">
-        <v>179000</v>
+        <v>353000</v>
       </c>
       <c r="V2" t="n">
-        <v>904000</v>
+        <v>1078000</v>
       </c>
       <c r="W2" t="n">
-        <v>946000</v>
+        <v>1120000</v>
       </c>
       <c r="X2" t="n">
-        <v>782000</v>
+        <v>956000</v>
       </c>
       <c r="Y2" t="n">
         <v>133424</v>
@@ -3137,16 +3137,16 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>75025</v>
+        <v>69025</v>
       </c>
       <c r="N18" t="n">
-        <v>18835</v>
+        <v>12835</v>
       </c>
       <c r="O18" t="n">
-        <v>110010</v>
+        <v>104010</v>
       </c>
       <c r="P18" t="n">
-        <v>484271</v>
+        <v>478271</v>
       </c>
       <c r="Q18" t="n">
         <v>43119</v>
@@ -3161,16 +3161,16 @@
         <v>-53625</v>
       </c>
       <c r="U18" t="n">
-        <v>-16000</v>
+        <v>-22000</v>
       </c>
       <c r="V18" t="n">
-        <v>107921</v>
+        <v>101921</v>
       </c>
       <c r="W18" t="n">
-        <v>158172</v>
+        <v>152172</v>
       </c>
       <c r="X18" t="n">
-        <v>498612</v>
+        <v>492612</v>
       </c>
       <c r="Y18" t="n">
         <v>47906</v>
@@ -5126,16 +5126,16 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>6473824</v>
+        <v>6304723</v>
       </c>
       <c r="N31" t="n">
-        <v>6244792</v>
+        <v>6075691</v>
       </c>
       <c r="O31" t="n">
-        <v>19367738</v>
+        <v>19198637</v>
       </c>
       <c r="P31" t="n">
-        <v>-14122065</v>
+        <v>-14291166</v>
       </c>
       <c r="Q31" t="n">
         <v>7123363</v>
@@ -5150,16 +5150,16 @@
         <v>-18040671</v>
       </c>
       <c r="U31" t="n">
-        <v>-973707</v>
+        <v>-1142808</v>
       </c>
       <c r="V31" t="n">
-        <v>-644735</v>
+        <v>-813836</v>
       </c>
       <c r="W31" t="n">
-        <v>-225924</v>
+        <v>-395025</v>
       </c>
       <c r="X31" t="n">
-        <v>-169448</v>
+        <v>-338549</v>
       </c>
       <c r="Y31" t="n">
         <v>324168</v>
@@ -6919,42 +6919,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00940.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>元大台灣價值高息</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.12</v>
+        <v>515</v>
       </c>
       <c r="E43" t="n">
-        <v>13.09</v>
+        <v>508.2</v>
       </c>
       <c r="F43" t="n">
-        <v>12.96</v>
+        <v>498</v>
       </c>
       <c r="G43" t="n">
-        <v>12.9</v>
+        <v>509.23</v>
       </c>
       <c r="H43" t="n">
-        <v>6904249</v>
+        <v>62507257</v>
       </c>
       <c r="I43" t="n">
-        <v>16148427</v>
+        <v>56959501</v>
       </c>
       <c r="J43" t="n">
-        <v>13.21</v>
+        <v>569</v>
       </c>
       <c r="K43" t="n">
-        <v>12.61</v>
+        <v>465.5</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -6962,52 +6962,52 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>1761010</v>
+        <v>29607502</v>
       </c>
       <c r="N43" t="n">
-        <v>17507854</v>
+        <v>1598314</v>
       </c>
       <c r="O43" t="n">
-        <v>56857757</v>
+        <v>39915979</v>
       </c>
       <c r="P43" t="n">
-        <v>81857784</v>
+        <v>10467833</v>
       </c>
       <c r="Q43" t="n">
-        <v>-1350990</v>
+        <v>29196171</v>
       </c>
       <c r="R43" t="n">
-        <v>1744048</v>
+        <v>2628770</v>
       </c>
       <c r="S43" t="n">
-        <v>4634431</v>
+        <v>35170358</v>
       </c>
       <c r="T43" t="n">
-        <v>3254642</v>
+        <v>10873298</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>-180000</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>-321212</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>4210362</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>-469218</v>
       </c>
       <c r="Y43" t="n">
-        <v>3112000</v>
+        <v>591331</v>
       </c>
       <c r="Z43" t="n">
-        <v>15763806</v>
+        <v>-709244</v>
       </c>
       <c r="AA43" t="n">
-        <v>52223326</v>
+        <v>535259</v>
       </c>
       <c r="AB43" t="n">
-        <v>78603142</v>
+        <v>63753</v>
       </c>
       <c r="AC43" t="n">
         <v>44</v>
@@ -7016,10 +7016,10 @@
         <v>44</v>
       </c>
       <c r="AE43" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AF43" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -7028,19 +7028,19 @@
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="AL43" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -7055,17 +7055,17 @@
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -7531,12 +7531,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>6531.TW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>愛普</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7545,28 +7545,28 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>515</v>
+        <v>987</v>
       </c>
       <c r="E47" t="n">
-        <v>508.2</v>
+        <v>951.4</v>
       </c>
       <c r="F47" t="n">
-        <v>498</v>
+        <v>957.6</v>
       </c>
       <c r="G47" t="n">
-        <v>509.23</v>
+        <v>947.15</v>
       </c>
       <c r="H47" t="n">
-        <v>62507257</v>
+        <v>3924896</v>
       </c>
       <c r="I47" t="n">
-        <v>56959501</v>
+        <v>2698994</v>
       </c>
       <c r="J47" t="n">
-        <v>569</v>
+        <v>1065</v>
       </c>
       <c r="K47" t="n">
-        <v>465.5</v>
+        <v>879</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -7574,52 +7574,52 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>29624502</v>
+        <v>1216190</v>
       </c>
       <c r="N47" t="n">
-        <v>1615314</v>
+        <v>737400</v>
       </c>
       <c r="O47" t="n">
-        <v>39932979</v>
+        <v>1154055</v>
       </c>
       <c r="P47" t="n">
-        <v>10484833</v>
+        <v>1730764</v>
       </c>
       <c r="Q47" t="n">
-        <v>29196171</v>
+        <v>1032914</v>
       </c>
       <c r="R47" t="n">
-        <v>2628770</v>
+        <v>515112</v>
       </c>
       <c r="S47" t="n">
-        <v>35170358</v>
+        <v>1026173</v>
       </c>
       <c r="T47" t="n">
-        <v>10873298</v>
+        <v>594337</v>
       </c>
       <c r="U47" t="n">
-        <v>-163000</v>
+        <v>139620</v>
       </c>
       <c r="V47" t="n">
-        <v>-304212</v>
+        <v>206620</v>
       </c>
       <c r="W47" t="n">
-        <v>4227362</v>
+        <v>77620</v>
       </c>
       <c r="X47" t="n">
-        <v>-452218</v>
+        <v>1124620</v>
       </c>
       <c r="Y47" t="n">
-        <v>591331</v>
+        <v>43656</v>
       </c>
       <c r="Z47" t="n">
-        <v>-709244</v>
+        <v>15668</v>
       </c>
       <c r="AA47" t="n">
-        <v>535259</v>
+        <v>50262</v>
       </c>
       <c r="AB47" t="n">
-        <v>63753</v>
+        <v>11807</v>
       </c>
       <c r="AC47" t="n">
         <v>44</v>
@@ -7640,10 +7640,10 @@
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AL47" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣</t>
+          <t>DT進入觀察區、5MA乖離尚可、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7990,42 +7990,42 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3443.TW</t>
+          <t>00940.TW</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>元大台灣價值高息</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8385</v>
+        <v>13.12</v>
       </c>
       <c r="E50" t="n">
-        <v>7605</v>
+        <v>13.09</v>
       </c>
       <c r="F50" t="n">
-        <v>6897.5</v>
+        <v>12.96</v>
       </c>
       <c r="G50" t="n">
-        <v>6416.5</v>
+        <v>12.9</v>
       </c>
       <c r="H50" t="n">
-        <v>2107816</v>
+        <v>6904249</v>
       </c>
       <c r="I50" t="n">
-        <v>2215346</v>
+        <v>16148427</v>
       </c>
       <c r="J50" t="n">
-        <v>8540</v>
+        <v>13.21</v>
       </c>
       <c r="K50" t="n">
-        <v>5680</v>
+        <v>12.61</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -8033,52 +8033,52 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>421404</v>
+        <v>1761010</v>
       </c>
       <c r="N50" t="n">
-        <v>581151</v>
+        <v>17507854</v>
       </c>
       <c r="O50" t="n">
-        <v>209383</v>
+        <v>56857757</v>
       </c>
       <c r="P50" t="n">
-        <v>387419</v>
+        <v>81857784</v>
       </c>
       <c r="Q50" t="n">
-        <v>452245</v>
+        <v>-1350990</v>
       </c>
       <c r="R50" t="n">
-        <v>644185</v>
+        <v>1744048</v>
       </c>
       <c r="S50" t="n">
-        <v>-281720</v>
+        <v>4634431</v>
       </c>
       <c r="T50" t="n">
-        <v>-564810</v>
+        <v>3254642</v>
       </c>
       <c r="U50" t="n">
-        <v>-29000</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>-86005</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>434742</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1025839</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>-1841</v>
+        <v>3112000</v>
       </c>
       <c r="Z50" t="n">
-        <v>22971</v>
+        <v>15763806</v>
       </c>
       <c r="AA50" t="n">
-        <v>56361</v>
+        <v>52223326</v>
       </c>
       <c r="AB50" t="n">
-        <v>-73610</v>
+        <v>78603142</v>
       </c>
       <c r="AC50" t="n">
         <v>44</v>
@@ -8087,10 +8087,10 @@
         <v>44</v>
       </c>
       <c r="AE50" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF50" t="n">
         <v>60</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>50</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -8099,19 +8099,19 @@
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="n">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="AL50" t="n">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>DT進入觀察區、離5MA偏遠、均線多頭排列</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8126,29 +8126,29 @@
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2409.TW</t>
+          <t>3443.TW</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -8157,28 +8157,28 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>34.7</v>
+        <v>8385</v>
       </c>
       <c r="E51" t="n">
-        <v>33.01</v>
+        <v>7605</v>
       </c>
       <c r="F51" t="n">
-        <v>31.25</v>
+        <v>6897.5</v>
       </c>
       <c r="G51" t="n">
-        <v>29.26</v>
+        <v>6416.5</v>
       </c>
       <c r="H51" t="n">
-        <v>948644349</v>
+        <v>2107816</v>
       </c>
       <c r="I51" t="n">
-        <v>730333889</v>
+        <v>2215346</v>
       </c>
       <c r="J51" t="n">
-        <v>36.65</v>
+        <v>8540</v>
       </c>
       <c r="K51" t="n">
-        <v>25.2</v>
+        <v>5680</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -8186,61 +8186,61 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>-162137606</v>
+        <v>421404</v>
       </c>
       <c r="N51" t="n">
-        <v>346625837</v>
+        <v>581151</v>
       </c>
       <c r="O51" t="n">
-        <v>357087476</v>
+        <v>209383</v>
       </c>
       <c r="P51" t="n">
-        <v>188187454</v>
+        <v>387419</v>
       </c>
       <c r="Q51" t="n">
-        <v>-153888176</v>
+        <v>452245</v>
       </c>
       <c r="R51" t="n">
-        <v>327319249</v>
+        <v>644185</v>
       </c>
       <c r="S51" t="n">
-        <v>328379369</v>
+        <v>-281720</v>
       </c>
       <c r="T51" t="n">
-        <v>171759561</v>
+        <v>-564810</v>
       </c>
       <c r="U51" t="n">
-        <v>229000</v>
+        <v>-29000</v>
       </c>
       <c r="V51" t="n">
-        <v>158808</v>
+        <v>-86005</v>
       </c>
       <c r="W51" t="n">
-        <v>3768119</v>
+        <v>434742</v>
       </c>
       <c r="X51" t="n">
-        <v>3698865</v>
+        <v>1025839</v>
       </c>
       <c r="Y51" t="n">
-        <v>-8478430</v>
+        <v>-1841</v>
       </c>
       <c r="Z51" t="n">
-        <v>19147780</v>
+        <v>22971</v>
       </c>
       <c r="AA51" t="n">
-        <v>24939988</v>
+        <v>56361</v>
       </c>
       <c r="AB51" t="n">
-        <v>12729028</v>
+        <v>-73610</v>
       </c>
       <c r="AC51" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD51" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE51" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF51" t="n">
         <v>50</v>
@@ -8252,19 +8252,19 @@
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="AL51" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT進入觀察區、離5MA偏遠、均線多頭排列</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8279,17 +8279,17 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -8798,16 +8798,16 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>1858179</v>
+        <v>1907819</v>
       </c>
       <c r="N55" t="n">
-        <v>19302682</v>
+        <v>19352322</v>
       </c>
       <c r="O55" t="n">
-        <v>30008552</v>
+        <v>30058192</v>
       </c>
       <c r="P55" t="n">
-        <v>21942789</v>
+        <v>21992429</v>
       </c>
       <c r="Q55" t="n">
         <v>4008437</v>
@@ -8822,16 +8822,16 @@
         <v>21508691</v>
       </c>
       <c r="U55" t="n">
-        <v>-2326000</v>
+        <v>-2276360</v>
       </c>
       <c r="V55" t="n">
-        <v>-621200</v>
+        <v>-571560</v>
       </c>
       <c r="W55" t="n">
-        <v>-806798</v>
+        <v>-757158</v>
       </c>
       <c r="X55" t="n">
-        <v>-2136203</v>
+        <v>-2086563</v>
       </c>
       <c r="Y55" t="n">
         <v>175742</v>
@@ -9367,12 +9367,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2006.TW</t>
+          <t>2409.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9381,28 +9381,28 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>85.8</v>
+        <v>34.7</v>
       </c>
       <c r="E59" t="n">
-        <v>85.5</v>
+        <v>33.01</v>
       </c>
       <c r="F59" t="n">
-        <v>83.53</v>
+        <v>31.25</v>
       </c>
       <c r="G59" t="n">
-        <v>82.52</v>
+        <v>29.26</v>
       </c>
       <c r="H59" t="n">
-        <v>1864183</v>
+        <v>948644349</v>
       </c>
       <c r="I59" t="n">
-        <v>2848358</v>
+        <v>730333889</v>
       </c>
       <c r="J59" t="n">
-        <v>89</v>
+        <v>36.65</v>
       </c>
       <c r="K59" t="n">
-        <v>79.5</v>
+        <v>25.2</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -9410,52 +9410,52 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>119703</v>
+        <v>-162137606</v>
       </c>
       <c r="N59" t="n">
-        <v>286607</v>
+        <v>346625837</v>
       </c>
       <c r="O59" t="n">
-        <v>4145661</v>
+        <v>357087476</v>
       </c>
       <c r="P59" t="n">
-        <v>4331584</v>
+        <v>188187454</v>
       </c>
       <c r="Q59" t="n">
-        <v>-496171</v>
+        <v>-153888176</v>
       </c>
       <c r="R59" t="n">
-        <v>-360390</v>
+        <v>327319249</v>
       </c>
       <c r="S59" t="n">
-        <v>4494020</v>
+        <v>328379369</v>
       </c>
       <c r="T59" t="n">
-        <v>5336968</v>
+        <v>171759561</v>
       </c>
       <c r="U59" t="n">
-        <v>630000</v>
+        <v>229000</v>
       </c>
       <c r="V59" t="n">
-        <v>631000</v>
+        <v>158808</v>
       </c>
       <c r="W59" t="n">
-        <v>-379257</v>
+        <v>3768119</v>
       </c>
       <c r="X59" t="n">
-        <v>-1111982</v>
+        <v>3698865</v>
       </c>
       <c r="Y59" t="n">
-        <v>-14126</v>
+        <v>-8478430</v>
       </c>
       <c r="Z59" t="n">
-        <v>15997</v>
+        <v>19147780</v>
       </c>
       <c r="AA59" t="n">
-        <v>30898</v>
+        <v>24939988</v>
       </c>
       <c r="AB59" t="n">
-        <v>106598</v>
+        <v>12729028</v>
       </c>
       <c r="AC59" t="n">
         <v>42</v>
@@ -9464,10 +9464,10 @@
         <v>42</v>
       </c>
       <c r="AE59" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AF59" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -9476,10 +9476,10 @@
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AL59" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9503,29 +9503,29 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2376.TW</t>
+          <t>2006.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9534,28 +9534,28 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>365</v>
+        <v>85.8</v>
       </c>
       <c r="E60" t="n">
-        <v>362.1</v>
+        <v>85.5</v>
       </c>
       <c r="F60" t="n">
-        <v>354.8</v>
+        <v>83.53</v>
       </c>
       <c r="G60" t="n">
-        <v>355.15</v>
+        <v>82.52</v>
       </c>
       <c r="H60" t="n">
-        <v>3929451</v>
+        <v>1864183</v>
       </c>
       <c r="I60" t="n">
-        <v>6771598</v>
+        <v>2848358</v>
       </c>
       <c r="J60" t="n">
-        <v>376</v>
+        <v>89</v>
       </c>
       <c r="K60" t="n">
-        <v>341</v>
+        <v>79.5</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -9563,64 +9563,64 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>341771</v>
+        <v>119703</v>
       </c>
       <c r="N60" t="n">
-        <v>1289292</v>
+        <v>286607</v>
       </c>
       <c r="O60" t="n">
-        <v>2498828</v>
+        <v>4145661</v>
       </c>
       <c r="P60" t="n">
-        <v>-538990</v>
+        <v>4331584</v>
       </c>
       <c r="Q60" t="n">
-        <v>441507</v>
+        <v>-496171</v>
       </c>
       <c r="R60" t="n">
-        <v>1669447</v>
+        <v>-360390</v>
       </c>
       <c r="S60" t="n">
-        <v>991108</v>
+        <v>4494020</v>
       </c>
       <c r="T60" t="n">
-        <v>-5031548</v>
+        <v>5336968</v>
       </c>
       <c r="U60" t="n">
-        <v>-13000</v>
+        <v>630000</v>
       </c>
       <c r="V60" t="n">
-        <v>17996</v>
+        <v>631000</v>
       </c>
       <c r="W60" t="n">
-        <v>1662237</v>
+        <v>-379257</v>
       </c>
       <c r="X60" t="n">
-        <v>4492480</v>
+        <v>-1111982</v>
       </c>
       <c r="Y60" t="n">
-        <v>-86736</v>
+        <v>-14126</v>
       </c>
       <c r="Z60" t="n">
-        <v>-398151</v>
+        <v>15997</v>
       </c>
       <c r="AA60" t="n">
-        <v>-154517</v>
+        <v>30898</v>
       </c>
       <c r="AB60" t="n">
-        <v>78</v>
+        <v>106598</v>
       </c>
       <c r="AC60" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AD60" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE60" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AF60" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -9629,19 +9629,19 @@
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AL60" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣</t>
+          <t>DT進入觀察區、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9656,17 +9656,17 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -9716,16 +9716,16 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>114287</v>
+        <v>135287</v>
       </c>
       <c r="N61" t="n">
-        <v>6992138</v>
+        <v>7013138</v>
       </c>
       <c r="O61" t="n">
-        <v>9987275</v>
+        <v>10008275</v>
       </c>
       <c r="P61" t="n">
-        <v>-4207664</v>
+        <v>-4186664</v>
       </c>
       <c r="Q61" t="n">
         <v>-139009</v>
@@ -9740,16 +9740,16 @@
         <v>-7990653</v>
       </c>
       <c r="U61" t="n">
-        <v>190002</v>
+        <v>211002</v>
       </c>
       <c r="V61" t="n">
-        <v>5224620</v>
+        <v>5245620</v>
       </c>
       <c r="W61" t="n">
-        <v>5457972</v>
+        <v>5478972</v>
       </c>
       <c r="X61" t="n">
-        <v>2768529</v>
+        <v>2789529</v>
       </c>
       <c r="Y61" t="n">
         <v>63294</v>
@@ -10132,12 +10132,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4904.TW</t>
+          <t>2376.TW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -10146,28 +10146,28 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>105.5</v>
+        <v>365</v>
       </c>
       <c r="E64" t="n">
-        <v>106.1</v>
+        <v>362.1</v>
       </c>
       <c r="F64" t="n">
-        <v>105.8</v>
+        <v>354.8</v>
       </c>
       <c r="G64" t="n">
-        <v>104.1</v>
+        <v>355.15</v>
       </c>
       <c r="H64" t="n">
-        <v>3732583</v>
+        <v>3929451</v>
       </c>
       <c r="I64" t="n">
-        <v>5938127</v>
+        <v>6771598</v>
       </c>
       <c r="J64" t="n">
-        <v>107.5</v>
+        <v>376</v>
       </c>
       <c r="K64" t="n">
-        <v>99.8</v>
+        <v>341</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -10175,52 +10175,52 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>737992</v>
+        <v>341771</v>
       </c>
       <c r="N64" t="n">
-        <v>1378035</v>
+        <v>1289292</v>
       </c>
       <c r="O64" t="n">
-        <v>2444089</v>
+        <v>2498828</v>
       </c>
       <c r="P64" t="n">
-        <v>6362721</v>
+        <v>-538990</v>
       </c>
       <c r="Q64" t="n">
-        <v>-361557</v>
+        <v>441507</v>
       </c>
       <c r="R64" t="n">
-        <v>-261903</v>
+        <v>1669447</v>
       </c>
       <c r="S64" t="n">
-        <v>1132718</v>
+        <v>991108</v>
       </c>
       <c r="T64" t="n">
-        <v>4553123</v>
+        <v>-5031548</v>
       </c>
       <c r="U64" t="n">
-        <v>946000</v>
+        <v>-13000</v>
       </c>
       <c r="V64" t="n">
-        <v>1370389</v>
+        <v>17996</v>
       </c>
       <c r="W64" t="n">
-        <v>731822</v>
+        <v>1662237</v>
       </c>
       <c r="X64" t="n">
-        <v>1066592</v>
+        <v>4492480</v>
       </c>
       <c r="Y64" t="n">
-        <v>153549</v>
+        <v>-86736</v>
       </c>
       <c r="Z64" t="n">
-        <v>269549</v>
+        <v>-398151</v>
       </c>
       <c r="AA64" t="n">
-        <v>579549</v>
+        <v>-154517</v>
       </c>
       <c r="AB64" t="n">
-        <v>743006</v>
+        <v>78</v>
       </c>
       <c r="AC64" t="n">
         <v>40</v>
@@ -10241,19 +10241,19 @@
       <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="AL64" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>DT進入觀察區、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
@@ -10278,19 +10278,19 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3045.TW</t>
+          <t>4904.TW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10299,28 +10299,28 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>123</v>
+        <v>105.5</v>
       </c>
       <c r="E65" t="n">
-        <v>123.7</v>
+        <v>106.1</v>
       </c>
       <c r="F65" t="n">
-        <v>122.95</v>
+        <v>105.8</v>
       </c>
       <c r="G65" t="n">
-        <v>119.92</v>
+        <v>104.1</v>
       </c>
       <c r="H65" t="n">
-        <v>6840892</v>
+        <v>3732583</v>
       </c>
       <c r="I65" t="n">
-        <v>10426378</v>
+        <v>5938127</v>
       </c>
       <c r="J65" t="n">
-        <v>125.5</v>
+        <v>107.5</v>
       </c>
       <c r="K65" t="n">
-        <v>113.5</v>
+        <v>99.8</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -10328,52 +10328,52 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>1451386</v>
+        <v>737992</v>
       </c>
       <c r="N65" t="n">
-        <v>7839545</v>
+        <v>1378035</v>
       </c>
       <c r="O65" t="n">
-        <v>10488757</v>
+        <v>2444089</v>
       </c>
       <c r="P65" t="n">
-        <v>20779256</v>
+        <v>6362721</v>
       </c>
       <c r="Q65" t="n">
-        <v>1316372</v>
+        <v>-361557</v>
       </c>
       <c r="R65" t="n">
-        <v>7547541</v>
+        <v>-261903</v>
       </c>
       <c r="S65" t="n">
-        <v>7976018</v>
+        <v>1132718</v>
       </c>
       <c r="T65" t="n">
-        <v>18939499</v>
+        <v>4553123</v>
       </c>
       <c r="U65" t="n">
-        <v>-15000</v>
+        <v>946000</v>
       </c>
       <c r="V65" t="n">
-        <v>-192969</v>
+        <v>1370389</v>
       </c>
       <c r="W65" t="n">
-        <v>2006523</v>
+        <v>731822</v>
       </c>
       <c r="X65" t="n">
-        <v>2348788</v>
+        <v>1066592</v>
       </c>
       <c r="Y65" t="n">
-        <v>150014</v>
+        <v>153549</v>
       </c>
       <c r="Z65" t="n">
-        <v>484973</v>
+        <v>269549</v>
       </c>
       <c r="AA65" t="n">
-        <v>506216</v>
+        <v>579549</v>
       </c>
       <c r="AB65" t="n">
-        <v>-509031</v>
+        <v>743006</v>
       </c>
       <c r="AC65" t="n">
         <v>40</v>
@@ -10438,12 +10438,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6426.TW</t>
+          <t>3045.TW</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10452,28 +10452,28 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>391.5</v>
+        <v>123</v>
       </c>
       <c r="E66" t="n">
-        <v>371.6</v>
+        <v>123.7</v>
       </c>
       <c r="F66" t="n">
-        <v>342.4</v>
+        <v>122.95</v>
       </c>
       <c r="G66" t="n">
-        <v>309.7</v>
+        <v>119.92</v>
       </c>
       <c r="H66" t="n">
-        <v>3158672</v>
+        <v>6840892</v>
       </c>
       <c r="I66" t="n">
-        <v>3484432</v>
+        <v>10426378</v>
       </c>
       <c r="J66" t="n">
-        <v>391.5</v>
+        <v>125.5</v>
       </c>
       <c r="K66" t="n">
-        <v>249</v>
+        <v>113.5</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -10481,52 +10481,52 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>109331</v>
+        <v>1451386</v>
       </c>
       <c r="N66" t="n">
-        <v>-639136</v>
+        <v>7839545</v>
       </c>
       <c r="O66" t="n">
-        <v>673682</v>
+        <v>10488757</v>
       </c>
       <c r="P66" t="n">
-        <v>71367</v>
+        <v>20779256</v>
       </c>
       <c r="Q66" t="n">
-        <v>92285</v>
+        <v>1316372</v>
       </c>
       <c r="R66" t="n">
-        <v>-664460</v>
+        <v>7547541</v>
       </c>
       <c r="S66" t="n">
-        <v>662051</v>
+        <v>7976018</v>
       </c>
       <c r="T66" t="n">
-        <v>117479</v>
+        <v>18939499</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>-15000</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>-192969</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>2006523</v>
       </c>
       <c r="X66" t="n">
-        <v>-33000</v>
+        <v>2348788</v>
       </c>
       <c r="Y66" t="n">
-        <v>17046</v>
+        <v>150014</v>
       </c>
       <c r="Z66" t="n">
-        <v>25324</v>
+        <v>484973</v>
       </c>
       <c r="AA66" t="n">
-        <v>11631</v>
+        <v>506216</v>
       </c>
       <c r="AB66" t="n">
-        <v>-13112</v>
+        <v>-509031</v>
       </c>
       <c r="AC66" t="n">
         <v>40</v>
@@ -10535,10 +10535,10 @@
         <v>40</v>
       </c>
       <c r="AE66" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="AF66" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -10547,10 +10547,10 @@
       <c r="AI66" t="inlineStr"/>
       <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL66" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、接近20日高位</t>
+          <t>DT進入觀察區、尚未站上5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10574,29 +10574,29 @@
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2449.TW</t>
+          <t>6426.TW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10605,28 +10605,28 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>304</v>
+        <v>391.5</v>
       </c>
       <c r="E67" t="n">
-        <v>295.8</v>
+        <v>371.6</v>
       </c>
       <c r="F67" t="n">
-        <v>279.35</v>
+        <v>342.4</v>
       </c>
       <c r="G67" t="n">
-        <v>272.6</v>
+        <v>309.7</v>
       </c>
       <c r="H67" t="n">
-        <v>37725251</v>
+        <v>3158672</v>
       </c>
       <c r="I67" t="n">
-        <v>48674444</v>
+        <v>3484432</v>
       </c>
       <c r="J67" t="n">
-        <v>330</v>
+        <v>391.5</v>
       </c>
       <c r="K67" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -10634,64 +10634,64 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>-4893406</v>
+        <v>109331</v>
       </c>
       <c r="N67" t="n">
-        <v>22963703</v>
+        <v>-639136</v>
       </c>
       <c r="O67" t="n">
-        <v>50204223</v>
+        <v>673682</v>
       </c>
       <c r="P67" t="n">
-        <v>49999042</v>
+        <v>71367</v>
       </c>
       <c r="Q67" t="n">
-        <v>-3966715</v>
+        <v>92285</v>
       </c>
       <c r="R67" t="n">
-        <v>14228057</v>
+        <v>-664460</v>
       </c>
       <c r="S67" t="n">
-        <v>38277697</v>
+        <v>662051</v>
       </c>
       <c r="T67" t="n">
-        <v>39052562</v>
+        <v>117479</v>
       </c>
       <c r="U67" t="n">
-        <v>-162000</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>7375513</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>7227478</v>
+        <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>6721581</v>
+        <v>-33000</v>
       </c>
       <c r="Y67" t="n">
-        <v>-764691</v>
+        <v>17046</v>
       </c>
       <c r="Z67" t="n">
-        <v>1360133</v>
+        <v>25324</v>
       </c>
       <c r="AA67" t="n">
-        <v>4699048</v>
+        <v>11631</v>
       </c>
       <c r="AB67" t="n">
-        <v>4224899</v>
+        <v>-13112</v>
       </c>
       <c r="AC67" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AD67" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE67" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="AF67" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -10700,19 +10700,19 @@
       <c r="AI67" t="inlineStr"/>
       <c r="AJ67" t="inlineStr"/>
       <c r="AK67" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AL67" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT進入觀察區、5MA乖離尚可、均線多頭排列、接近20日高位</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10727,17 +10727,17 @@
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、突破20日高點</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、突破20日高點、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -10897,12 +10897,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6214.TW</t>
+          <t>2449.TW</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10911,28 +10911,28 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>190</v>
+        <v>304</v>
       </c>
       <c r="E69" t="n">
-        <v>191.9</v>
+        <v>295.8</v>
       </c>
       <c r="F69" t="n">
-        <v>190.4</v>
+        <v>279.35</v>
       </c>
       <c r="G69" t="n">
-        <v>187.12</v>
+        <v>272.6</v>
       </c>
       <c r="H69" t="n">
-        <v>2530287</v>
+        <v>37725251</v>
       </c>
       <c r="I69" t="n">
-        <v>1954658</v>
+        <v>48674444</v>
       </c>
       <c r="J69" t="n">
-        <v>195</v>
+        <v>330</v>
       </c>
       <c r="K69" t="n">
-        <v>179</v>
+        <v>243</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -10940,52 +10940,52 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>299823</v>
+        <v>-4893406</v>
       </c>
       <c r="N69" t="n">
-        <v>307355</v>
+        <v>22963703</v>
       </c>
       <c r="O69" t="n">
-        <v>1388608</v>
+        <v>50204223</v>
       </c>
       <c r="P69" t="n">
-        <v>2843688</v>
+        <v>49999042</v>
       </c>
       <c r="Q69" t="n">
-        <v>304823</v>
+        <v>-3966715</v>
       </c>
       <c r="R69" t="n">
-        <v>306522</v>
+        <v>14228057</v>
       </c>
       <c r="S69" t="n">
-        <v>1349775</v>
+        <v>38277697</v>
       </c>
       <c r="T69" t="n">
-        <v>3189114</v>
+        <v>39052562</v>
       </c>
       <c r="U69" t="n">
-        <v>1000</v>
+        <v>-162000</v>
       </c>
       <c r="V69" t="n">
-        <v>2000</v>
+        <v>7375513</v>
       </c>
       <c r="W69" t="n">
-        <v>2000</v>
+        <v>7227478</v>
       </c>
       <c r="X69" t="n">
-        <v>-206211</v>
+        <v>6721581</v>
       </c>
       <c r="Y69" t="n">
-        <v>-6000</v>
+        <v>-764691</v>
       </c>
       <c r="Z69" t="n">
-        <v>-1167</v>
+        <v>1360133</v>
       </c>
       <c r="AA69" t="n">
-        <v>36833</v>
+        <v>4699048</v>
       </c>
       <c r="AB69" t="n">
-        <v>-139215</v>
+        <v>4224899</v>
       </c>
       <c r="AC69" t="n">
         <v>38</v>
@@ -10994,10 +10994,10 @@
         <v>38</v>
       </c>
       <c r="AE69" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="AF69" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -11006,19 +11006,19 @@
       <c r="AI69" t="inlineStr"/>
       <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AL69" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11033,29 +11033,29 @@
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3047.TW</t>
+          <t>2360.TW</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>訊舟</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -11064,28 +11064,28 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.7</v>
+        <v>2325</v>
       </c>
       <c r="E70" t="n">
-        <v>14.48</v>
+        <v>2303</v>
       </c>
       <c r="F70" t="n">
-        <v>14.01</v>
+        <v>2216.5</v>
       </c>
       <c r="G70" t="n">
-        <v>13.84</v>
+        <v>2150.25</v>
       </c>
       <c r="H70" t="n">
-        <v>1112910</v>
+        <v>2628143</v>
       </c>
       <c r="I70" t="n">
-        <v>2167088</v>
+        <v>2664419</v>
       </c>
       <c r="J70" t="n">
-        <v>15.3</v>
+        <v>2540</v>
       </c>
       <c r="K70" t="n">
-        <v>13.25</v>
+        <v>1905</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -11093,52 +11093,52 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>125523</v>
+        <v>61781</v>
       </c>
       <c r="N70" t="n">
-        <v>59471</v>
+        <v>291284</v>
       </c>
       <c r="O70" t="n">
-        <v>465727</v>
+        <v>371034</v>
       </c>
       <c r="P70" t="n">
-        <v>891328</v>
+        <v>-137917</v>
       </c>
       <c r="Q70" t="n">
-        <v>125000</v>
+        <v>251314</v>
       </c>
       <c r="R70" t="n">
-        <v>56000</v>
+        <v>832306</v>
       </c>
       <c r="S70" t="n">
-        <v>458256</v>
+        <v>736713</v>
       </c>
       <c r="T70" t="n">
-        <v>883406</v>
+        <v>113545</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>-276000</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>-614369</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>-552688</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>-469726</v>
       </c>
       <c r="Y70" t="n">
-        <v>523</v>
+        <v>86467</v>
       </c>
       <c r="Z70" t="n">
-        <v>3471</v>
+        <v>73347</v>
       </c>
       <c r="AA70" t="n">
-        <v>7471</v>
+        <v>187009</v>
       </c>
       <c r="AB70" t="n">
-        <v>7922</v>
+        <v>218264</v>
       </c>
       <c r="AC70" t="n">
         <v>38</v>
@@ -11191,24 +11191,24 @@
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2360.TW</t>
+          <t>3047.TW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>訊舟</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11217,28 +11217,28 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2325</v>
+        <v>14.7</v>
       </c>
       <c r="E71" t="n">
-        <v>2303</v>
+        <v>14.48</v>
       </c>
       <c r="F71" t="n">
-        <v>2216.5</v>
+        <v>14.01</v>
       </c>
       <c r="G71" t="n">
-        <v>2150.25</v>
+        <v>13.84</v>
       </c>
       <c r="H71" t="n">
-        <v>2628143</v>
+        <v>1112910</v>
       </c>
       <c r="I71" t="n">
-        <v>2664419</v>
+        <v>2167088</v>
       </c>
       <c r="J71" t="n">
-        <v>2540</v>
+        <v>15.3</v>
       </c>
       <c r="K71" t="n">
-        <v>1905</v>
+        <v>13.25</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -11246,52 +11246,52 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>61781</v>
+        <v>125523</v>
       </c>
       <c r="N71" t="n">
-        <v>291284</v>
+        <v>59471</v>
       </c>
       <c r="O71" t="n">
-        <v>371034</v>
+        <v>465727</v>
       </c>
       <c r="P71" t="n">
-        <v>-137917</v>
+        <v>891328</v>
       </c>
       <c r="Q71" t="n">
-        <v>251314</v>
+        <v>125000</v>
       </c>
       <c r="R71" t="n">
-        <v>832306</v>
+        <v>56000</v>
       </c>
       <c r="S71" t="n">
-        <v>736713</v>
+        <v>458256</v>
       </c>
       <c r="T71" t="n">
-        <v>113545</v>
+        <v>883406</v>
       </c>
       <c r="U71" t="n">
-        <v>-276000</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>-614369</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>-552688</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>-469726</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>86467</v>
+        <v>523</v>
       </c>
       <c r="Z71" t="n">
-        <v>73347</v>
+        <v>3471</v>
       </c>
       <c r="AA71" t="n">
-        <v>187009</v>
+        <v>7471</v>
       </c>
       <c r="AB71" t="n">
-        <v>218264</v>
+        <v>7922</v>
       </c>
       <c r="AC71" t="n">
         <v>38</v>
@@ -11344,12 +11344,12 @@
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -11662,12 +11662,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2303.TW</t>
+          <t>6214.TW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -11676,28 +11676,28 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="E74" t="n">
-        <v>156.1</v>
+        <v>191.9</v>
       </c>
       <c r="F74" t="n">
-        <v>148.65</v>
+        <v>190.4</v>
       </c>
       <c r="G74" t="n">
-        <v>139.95</v>
+        <v>187.12</v>
       </c>
       <c r="H74" t="n">
-        <v>124757294</v>
+        <v>2530287</v>
       </c>
       <c r="I74" t="n">
-        <v>226712095</v>
+        <v>1954658</v>
       </c>
       <c r="J74" t="n">
-        <v>168.5</v>
+        <v>195</v>
       </c>
       <c r="K74" t="n">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -11705,52 +11705,52 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-10134633</v>
+        <v>299823</v>
       </c>
       <c r="N74" t="n">
-        <v>55751253</v>
+        <v>307355</v>
       </c>
       <c r="O74" t="n">
-        <v>141750949</v>
+        <v>1388608</v>
       </c>
       <c r="P74" t="n">
-        <v>158879811</v>
+        <v>2843688</v>
       </c>
       <c r="Q74" t="n">
-        <v>-10353990</v>
+        <v>304823</v>
       </c>
       <c r="R74" t="n">
-        <v>34465647</v>
+        <v>306522</v>
       </c>
       <c r="S74" t="n">
-        <v>71783037</v>
+        <v>1349775</v>
       </c>
       <c r="T74" t="n">
-        <v>54771937</v>
+        <v>3189114</v>
       </c>
       <c r="U74" t="n">
-        <v>1374000</v>
+        <v>1000</v>
       </c>
       <c r="V74" t="n">
-        <v>17132684</v>
+        <v>2000</v>
       </c>
       <c r="W74" t="n">
-        <v>58671872</v>
+        <v>2000</v>
       </c>
       <c r="X74" t="n">
-        <v>90606382</v>
+        <v>-206211</v>
       </c>
       <c r="Y74" t="n">
-        <v>-1154643</v>
+        <v>-6000</v>
       </c>
       <c r="Z74" t="n">
-        <v>4152922</v>
+        <v>-1167</v>
       </c>
       <c r="AA74" t="n">
-        <v>11296040</v>
+        <v>36833</v>
       </c>
       <c r="AB74" t="n">
-        <v>13501492</v>
+        <v>-139215</v>
       </c>
       <c r="AC74" t="n">
         <v>38</v>
@@ -11759,10 +11759,10 @@
         <v>38</v>
       </c>
       <c r="AE74" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AF74" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -11771,19 +11771,19 @@
       <c r="AI74" t="inlineStr"/>
       <c r="AJ74" t="inlineStr"/>
       <c r="AK74" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AL74" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -11798,59 +11798,59 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0050.TW</t>
+          <t>2303.TW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>元大台灣50</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>112.45</v>
+        <v>160</v>
       </c>
       <c r="E75" t="n">
-        <v>110.71</v>
+        <v>156.1</v>
       </c>
       <c r="F75" t="n">
-        <v>109.05</v>
+        <v>148.65</v>
       </c>
       <c r="G75" t="n">
-        <v>108.41</v>
+        <v>139.95</v>
       </c>
       <c r="H75" t="n">
-        <v>58059253</v>
+        <v>124757294</v>
       </c>
       <c r="I75" t="n">
-        <v>79725344</v>
+        <v>226712095</v>
       </c>
       <c r="J75" t="n">
-        <v>113.75</v>
+        <v>168.5</v>
       </c>
       <c r="K75" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -11858,64 +11858,64 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>-2215320</v>
+        <v>-10134633</v>
       </c>
       <c r="N75" t="n">
-        <v>10178025</v>
+        <v>55751253</v>
       </c>
       <c r="O75" t="n">
-        <v>37586717</v>
+        <v>141750949</v>
       </c>
       <c r="P75" t="n">
-        <v>-144121776</v>
+        <v>158879811</v>
       </c>
       <c r="Q75" t="n">
-        <v>-11051231</v>
+        <v>-10353990</v>
       </c>
       <c r="R75" t="n">
-        <v>-18953328</v>
+        <v>34465647</v>
       </c>
       <c r="S75" t="n">
-        <v>-27257266</v>
+        <v>71783037</v>
       </c>
       <c r="T75" t="n">
-        <v>-179107133</v>
+        <v>54771937</v>
       </c>
       <c r="U75" t="n">
-        <v>2200000</v>
+        <v>1374000</v>
       </c>
       <c r="V75" t="n">
-        <v>5391000</v>
+        <v>17132684</v>
       </c>
       <c r="W75" t="n">
-        <v>7811000</v>
+        <v>58671872</v>
       </c>
       <c r="X75" t="n">
-        <v>15249000</v>
+        <v>90606382</v>
       </c>
       <c r="Y75" t="n">
-        <v>6635911</v>
+        <v>-1154643</v>
       </c>
       <c r="Z75" t="n">
-        <v>23740353</v>
+        <v>4152922</v>
       </c>
       <c r="AA75" t="n">
-        <v>57032983</v>
+        <v>11296040</v>
       </c>
       <c r="AB75" t="n">
-        <v>19736357</v>
+        <v>13501492</v>
       </c>
       <c r="AC75" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AD75" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE75" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AF75" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -11924,19 +11924,19 @@
       <c r="AI75" t="inlineStr"/>
       <c r="AJ75" t="inlineStr"/>
       <c r="AK75" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AL75" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -11951,17 +11951,17 @@
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -12121,42 +12121,42 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3094.TW</t>
+          <t>0050.TW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>聯傑</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>54.3</v>
+        <v>112.45</v>
       </c>
       <c r="E77" t="n">
-        <v>52.48</v>
+        <v>110.71</v>
       </c>
       <c r="F77" t="n">
-        <v>47.6</v>
+        <v>109.05</v>
       </c>
       <c r="G77" t="n">
-        <v>44.67</v>
+        <v>108.41</v>
       </c>
       <c r="H77" t="n">
-        <v>27139876</v>
+        <v>58059253</v>
       </c>
       <c r="I77" t="n">
-        <v>15937039</v>
+        <v>79725344</v>
       </c>
       <c r="J77" t="n">
-        <v>57.8</v>
+        <v>113.75</v>
       </c>
       <c r="K77" t="n">
-        <v>37.5</v>
+        <v>105</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -12164,52 +12164,52 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-116004</v>
+        <v>-2215320</v>
       </c>
       <c r="N77" t="n">
-        <v>1246968</v>
+        <v>10178025</v>
       </c>
       <c r="O77" t="n">
-        <v>4526986</v>
+        <v>37586717</v>
       </c>
       <c r="P77" t="n">
-        <v>5548956</v>
+        <v>-144121776</v>
       </c>
       <c r="Q77" t="n">
-        <v>-110853</v>
+        <v>-11051231</v>
       </c>
       <c r="R77" t="n">
-        <v>1233961</v>
+        <v>-18953328</v>
       </c>
       <c r="S77" t="n">
-        <v>4495545</v>
+        <v>-27257266</v>
       </c>
       <c r="T77" t="n">
-        <v>5514607</v>
+        <v>-179107133</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>2200000</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>5391000</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>7811000</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>15249000</v>
       </c>
       <c r="Y77" t="n">
-        <v>-5151</v>
+        <v>6635911</v>
       </c>
       <c r="Z77" t="n">
-        <v>13007</v>
+        <v>23740353</v>
       </c>
       <c r="AA77" t="n">
-        <v>31441</v>
+        <v>57032983</v>
       </c>
       <c r="AB77" t="n">
-        <v>34349</v>
+        <v>19736357</v>
       </c>
       <c r="AC77" t="n">
         <v>36</v>
@@ -12230,19 +12230,19 @@
       <c r="AI77" t="inlineStr"/>
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AL77" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -12257,17 +12257,17 @@
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -12427,12 +12427,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6531.TW</t>
+          <t>2103.TW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>愛普</t>
+          <t>台橡</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12441,28 +12441,28 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>987</v>
+        <v>27.9</v>
       </c>
       <c r="E79" t="n">
-        <v>951.4</v>
+        <v>27.77</v>
       </c>
       <c r="F79" t="n">
-        <v>957.6</v>
+        <v>26.85</v>
       </c>
       <c r="G79" t="n">
-        <v>947.15</v>
+        <v>27.29</v>
       </c>
       <c r="H79" t="n">
-        <v>3924896</v>
+        <v>4459016</v>
       </c>
       <c r="I79" t="n">
-        <v>2698994</v>
+        <v>4152015</v>
       </c>
       <c r="J79" t="n">
-        <v>1065</v>
+        <v>29.45</v>
       </c>
       <c r="K79" t="n">
-        <v>879</v>
+        <v>25.15</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -12470,52 +12470,52 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>1089970</v>
+        <v>1686670</v>
       </c>
       <c r="N79" t="n">
-        <v>611180</v>
+        <v>1346841</v>
       </c>
       <c r="O79" t="n">
-        <v>1027835</v>
+        <v>3831577</v>
       </c>
       <c r="P79" t="n">
-        <v>1604544</v>
+        <v>5859183</v>
       </c>
       <c r="Q79" t="n">
-        <v>1032914</v>
+        <v>1663717</v>
       </c>
       <c r="R79" t="n">
-        <v>515112</v>
+        <v>1486383</v>
       </c>
       <c r="S79" t="n">
-        <v>1026173</v>
+        <v>3945395</v>
       </c>
       <c r="T79" t="n">
-        <v>594337</v>
+        <v>5801020</v>
       </c>
       <c r="U79" t="n">
-        <v>13400</v>
+        <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>80400</v>
+        <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>-48600</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>998400</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>43656</v>
+        <v>22953</v>
       </c>
       <c r="Z79" t="n">
-        <v>15668</v>
+        <v>-139542</v>
       </c>
       <c r="AA79" t="n">
-        <v>50262</v>
+        <v>-113818</v>
       </c>
       <c r="AB79" t="n">
-        <v>11807</v>
+        <v>58163</v>
       </c>
       <c r="AC79" t="n">
         <v>36</v>
@@ -12536,19 +12536,19 @@
       <c r="AI79" t="inlineStr"/>
       <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AL79" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -12568,24 +12568,24 @@
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2103.TW</t>
+          <t>3094.TW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>台橡</t>
+          <t>聯傑</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -12594,28 +12594,28 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>27.9</v>
+        <v>54.3</v>
       </c>
       <c r="E80" t="n">
-        <v>27.77</v>
+        <v>52.48</v>
       </c>
       <c r="F80" t="n">
-        <v>26.85</v>
+        <v>47.6</v>
       </c>
       <c r="G80" t="n">
-        <v>27.29</v>
+        <v>44.67</v>
       </c>
       <c r="H80" t="n">
-        <v>4459016</v>
+        <v>27139876</v>
       </c>
       <c r="I80" t="n">
-        <v>4152015</v>
+        <v>15937039</v>
       </c>
       <c r="J80" t="n">
-        <v>29.45</v>
+        <v>57.8</v>
       </c>
       <c r="K80" t="n">
-        <v>25.15</v>
+        <v>37.5</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -12623,28 +12623,28 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>1686670</v>
+        <v>-116004</v>
       </c>
       <c r="N80" t="n">
-        <v>1346841</v>
+        <v>1246968</v>
       </c>
       <c r="O80" t="n">
-        <v>3831577</v>
+        <v>4526986</v>
       </c>
       <c r="P80" t="n">
-        <v>5859183</v>
+        <v>5548956</v>
       </c>
       <c r="Q80" t="n">
-        <v>1663717</v>
+        <v>-110853</v>
       </c>
       <c r="R80" t="n">
-        <v>1486383</v>
+        <v>1233961</v>
       </c>
       <c r="S80" t="n">
-        <v>3945395</v>
+        <v>4495545</v>
       </c>
       <c r="T80" t="n">
-        <v>5801020</v>
+        <v>5514607</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -12659,16 +12659,16 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>22953</v>
+        <v>-5151</v>
       </c>
       <c r="Z80" t="n">
-        <v>-139542</v>
+        <v>13007</v>
       </c>
       <c r="AA80" t="n">
-        <v>-113818</v>
+        <v>31441</v>
       </c>
       <c r="AB80" t="n">
-        <v>58163</v>
+        <v>34349</v>
       </c>
       <c r="AC80" t="n">
         <v>36</v>
@@ -12677,10 +12677,10 @@
         <v>36</v>
       </c>
       <c r="AE80" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF80" t="n">
         <v>30</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>60</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -12689,19 +12689,19 @@
       <c r="AI80" t="inlineStr"/>
       <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AL80" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -12716,17 +12716,17 @@
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -34043,16 +34043,16 @@
         </is>
       </c>
       <c r="M220" t="n">
-        <v>6976172</v>
+        <v>6946172</v>
       </c>
       <c r="N220" t="n">
-        <v>-26378707</v>
+        <v>-26408707</v>
       </c>
       <c r="O220" t="n">
-        <v>10438136</v>
+        <v>10408136</v>
       </c>
       <c r="P220" t="n">
-        <v>-70414336</v>
+        <v>-70444336</v>
       </c>
       <c r="Q220" t="n">
         <v>10124159</v>
@@ -34067,16 +34067,16 @@
         <v>-37429578</v>
       </c>
       <c r="U220" t="n">
-        <v>-3242000</v>
+        <v>-3272000</v>
       </c>
       <c r="V220" t="n">
-        <v>-19591793</v>
+        <v>-19621793</v>
       </c>
       <c r="W220" t="n">
-        <v>-19851679</v>
+        <v>-19881679</v>
       </c>
       <c r="X220" t="n">
-        <v>-35636976</v>
+        <v>-35666976</v>
       </c>
       <c r="Y220" t="n">
         <v>94013</v>
@@ -40928,16 +40928,16 @@
         </is>
       </c>
       <c r="M265" t="n">
-        <v>-54090692</v>
+        <v>-57815692</v>
       </c>
       <c r="N265" t="n">
-        <v>7787557</v>
+        <v>4062557</v>
       </c>
       <c r="O265" t="n">
-        <v>-23873892</v>
+        <v>-27598892</v>
       </c>
       <c r="P265" t="n">
-        <v>-59282158</v>
+        <v>-63007158</v>
       </c>
       <c r="Q265" t="n">
         <v>-47830253</v>
@@ -40952,16 +40952,16 @@
         <v>-50974512</v>
       </c>
       <c r="U265" t="n">
-        <v>-9900</v>
+        <v>-3734900</v>
       </c>
       <c r="V265" t="n">
-        <v>-4952304</v>
+        <v>-8677304</v>
       </c>
       <c r="W265" t="n">
-        <v>-7988597</v>
+        <v>-11713597</v>
       </c>
       <c r="X265" t="n">
-        <v>-8099625</v>
+        <v>-11824625</v>
       </c>
       <c r="Y265" t="n">
         <v>-6250539</v>
@@ -46107,7 +46107,7 @@
         <v>49.14</v>
       </c>
       <c r="F299" t="n">
-        <v>49.39</v>
+        <v>49.38</v>
       </c>
       <c r="G299" t="n">
         <v>49.71</v>
@@ -46895,16 +46895,16 @@
         </is>
       </c>
       <c r="M304" t="n">
-        <v>-659128</v>
+        <v>-663128</v>
       </c>
       <c r="N304" t="n">
-        <v>-602149</v>
+        <v>-606149</v>
       </c>
       <c r="O304" t="n">
-        <v>-713314</v>
+        <v>-717314</v>
       </c>
       <c r="P304" t="n">
-        <v>-1598114</v>
+        <v>-1602114</v>
       </c>
       <c r="Q304" t="n">
         <v>-662709</v>
@@ -46919,16 +46919,16 @@
         <v>-1366491</v>
       </c>
       <c r="U304" t="n">
-        <v>120000</v>
+        <v>116000</v>
       </c>
       <c r="V304" t="n">
-        <v>48000</v>
+        <v>44000</v>
       </c>
       <c r="W304" t="n">
-        <v>-50995</v>
+        <v>-54995</v>
       </c>
       <c r="X304" t="n">
-        <v>-173445</v>
+        <v>-177445</v>
       </c>
       <c r="Y304" t="n">
         <v>-116419</v>
@@ -53933,16 +53933,16 @@
         </is>
       </c>
       <c r="M350" t="n">
-        <v>-1118010</v>
+        <v>-1143010</v>
       </c>
       <c r="N350" t="n">
-        <v>-1876687</v>
+        <v>-1901687</v>
       </c>
       <c r="O350" t="n">
-        <v>-3326950</v>
+        <v>-3351950</v>
       </c>
       <c r="P350" t="n">
-        <v>-4583667</v>
+        <v>-4608667</v>
       </c>
       <c r="Q350" t="n">
         <v>-594803</v>
@@ -53957,16 +53957,16 @@
         <v>-172267</v>
       </c>
       <c r="U350" t="n">
-        <v>-507000</v>
+        <v>-532000</v>
       </c>
       <c r="V350" t="n">
-        <v>-1465004</v>
+        <v>-1490004</v>
       </c>
       <c r="W350" t="n">
-        <v>-3345788</v>
+        <v>-3370788</v>
       </c>
       <c r="X350" t="n">
-        <v>-4715322</v>
+        <v>-4740322</v>
       </c>
       <c r="Y350" t="n">
         <v>-16207</v>
@@ -58523,16 +58523,16 @@
         </is>
       </c>
       <c r="M380" t="n">
-        <v>-286826</v>
+        <v>-313826</v>
       </c>
       <c r="N380" t="n">
-        <v>-933404</v>
+        <v>-960404</v>
       </c>
       <c r="O380" t="n">
-        <v>-1021221</v>
+        <v>-1048221</v>
       </c>
       <c r="P380" t="n">
-        <v>-796043</v>
+        <v>-823043</v>
       </c>
       <c r="Q380" t="n">
         <v>-311896</v>
@@ -58547,16 +58547,16 @@
         <v>-1315285</v>
       </c>
       <c r="U380" t="n">
-        <v>-2000</v>
+        <v>-29000</v>
       </c>
       <c r="V380" t="n">
-        <v>299915</v>
+        <v>272915</v>
       </c>
       <c r="W380" t="n">
-        <v>465391</v>
+        <v>438391</v>
       </c>
       <c r="X380" t="n">
-        <v>358967</v>
+        <v>331967</v>
       </c>
       <c r="Y380" t="n">
         <v>27070</v>
@@ -60665,16 +60665,16 @@
         </is>
       </c>
       <c r="M394" t="n">
-        <v>-220272</v>
+        <v>-221272</v>
       </c>
       <c r="N394" t="n">
-        <v>-837807</v>
+        <v>-838807</v>
       </c>
       <c r="O394" t="n">
-        <v>-701321</v>
+        <v>-702321</v>
       </c>
       <c r="P394" t="n">
-        <v>-991487</v>
+        <v>-992487</v>
       </c>
       <c r="Q394" t="n">
         <v>-134405</v>
@@ -60689,16 +60689,16 @@
         <v>-215386</v>
       </c>
       <c r="U394" t="n">
-        <v>-83320</v>
+        <v>-84320</v>
       </c>
       <c r="V394" t="n">
-        <v>-726491</v>
+        <v>-727491</v>
       </c>
       <c r="W394" t="n">
-        <v>-725140</v>
+        <v>-726140</v>
       </c>
       <c r="X394" t="n">
-        <v>-803010</v>
+        <v>-804010</v>
       </c>
       <c r="Y394" t="n">
         <v>-2547</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -46107,7 +46107,7 @@
         <v>49.14</v>
       </c>
       <c r="F299" t="n">
-        <v>49.38</v>
+        <v>49.39</v>
       </c>
       <c r="G299" t="n">
         <v>49.71</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -15103,12 +15103,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2605.TW</t>
+          <t>3030.TW</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>新興</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -15127,28 +15127,28 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>36.7</v>
+        <v>313.5</v>
       </c>
       <c r="G85" t="n">
-        <v>36.23</v>
+        <v>308.1</v>
       </c>
       <c r="H85" t="n">
-        <v>36.11</v>
+        <v>291.9</v>
       </c>
       <c r="I85" t="n">
-        <v>36.28</v>
+        <v>278.35</v>
       </c>
       <c r="J85" t="n">
-        <v>5360639</v>
+        <v>2226309</v>
       </c>
       <c r="K85" t="n">
-        <v>8834578</v>
+        <v>3568084</v>
       </c>
       <c r="L85" t="n">
-        <v>38.65</v>
+        <v>318</v>
       </c>
       <c r="M85" t="n">
-        <v>34.85</v>
+        <v>258</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -15156,52 +15156,52 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>641094</v>
+        <v>113660</v>
       </c>
       <c r="P85" t="n">
-        <v>10268287</v>
+        <v>-48025</v>
       </c>
       <c r="Q85" t="n">
-        <v>7494079</v>
+        <v>254674</v>
       </c>
       <c r="R85" t="n">
-        <v>-3231651</v>
+        <v>1064953</v>
       </c>
       <c r="S85" t="n">
-        <v>534950</v>
+        <v>111578</v>
       </c>
       <c r="T85" t="n">
-        <v>9471008</v>
+        <v>-169323</v>
       </c>
       <c r="U85" t="n">
-        <v>6783394</v>
+        <v>-8769</v>
       </c>
       <c r="V85" t="n">
-        <v>-3024550</v>
+        <v>632625</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X85" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>-201000</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>106144</v>
+        <v>1082</v>
       </c>
       <c r="AB85" t="n">
-        <v>798279</v>
+        <v>121298</v>
       </c>
       <c r="AC85" t="n">
-        <v>711685</v>
+        <v>263443</v>
       </c>
       <c r="AD85" t="n">
-        <v>-6101</v>
+        <v>432328</v>
       </c>
       <c r="AE85" t="n">
         <v>32</v>
@@ -15210,16 +15210,16 @@
         <v>32</v>
       </c>
       <c r="AG85" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH85" t="n">
         <v>20</v>
       </c>
-      <c r="AH85" t="n">
-        <v>60</v>
-      </c>
       <c r="AI85" t="n">
         <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
@@ -15227,16 +15227,16 @@
         </is>
       </c>
       <c r="AL85" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AM85" t="n">
-        <v>220</v>
+        <v>33.33</v>
       </c>
       <c r="AN85" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO85" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數剛升溫</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
@@ -15260,17 +15260,17 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -15799,12 +15799,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4766.TW</t>
+          <t>6485.TWO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -15823,28 +15823,28 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>354.5</v>
+        <v>77</v>
       </c>
       <c r="G89" t="n">
-        <v>353.4</v>
+        <v>70.78</v>
       </c>
       <c r="H89" t="n">
-        <v>347.6</v>
+        <v>66.87</v>
       </c>
       <c r="I89" t="n">
-        <v>343.45</v>
+        <v>63.8</v>
       </c>
       <c r="J89" t="n">
-        <v>109770</v>
+        <v>2165000</v>
       </c>
       <c r="K89" t="n">
-        <v>224357</v>
+        <v>1010600</v>
       </c>
       <c r="L89" t="n">
-        <v>360</v>
+        <v>77.3</v>
       </c>
       <c r="M89" t="n">
-        <v>330.5</v>
+        <v>58.5</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -15852,28 +15852,28 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>-14458</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>228837</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>417295</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>508223</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>-14458</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>232307</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>417934</v>
+        <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>508122</v>
+        <v>0</v>
       </c>
       <c r="W89" t="n">
         <v>0</v>
@@ -15891,13 +15891,13 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>-3470</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
-        <v>-639</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
         <v>32</v>
@@ -15906,42 +15906,32 @@
         <v>32</v>
       </c>
       <c r="AG89" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AH89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr"/>
+      <c r="AN89" t="n">
         <v>20</v>
       </c>
-      <c r="AI89" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ89" t="n">
-        <v>52</v>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AL89" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AM89" t="n">
-        <v>-38.46</v>
-      </c>
-      <c r="AN89" t="n">
-        <v>45</v>
-      </c>
       <c r="AO89" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、接近20日高位、量能偏強</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
@@ -15956,29 +15946,29 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、爆量、接近20日高點</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、爆量、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3030.TW</t>
+          <t>4766.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -15997,28 +15987,28 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>313.5</v>
+        <v>354.5</v>
       </c>
       <c r="G90" t="n">
-        <v>308.1</v>
+        <v>353.4</v>
       </c>
       <c r="H90" t="n">
-        <v>291.9</v>
+        <v>347.6</v>
       </c>
       <c r="I90" t="n">
-        <v>278.35</v>
+        <v>343.45</v>
       </c>
       <c r="J90" t="n">
-        <v>2226309</v>
+        <v>109770</v>
       </c>
       <c r="K90" t="n">
-        <v>3568084</v>
+        <v>224357</v>
       </c>
       <c r="L90" t="n">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="M90" t="n">
-        <v>258</v>
+        <v>330.5</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -16026,31 +16016,31 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>113660</v>
+        <v>-14458</v>
       </c>
       <c r="P90" t="n">
-        <v>-48025</v>
+        <v>228837</v>
       </c>
       <c r="Q90" t="n">
-        <v>254674</v>
+        <v>417295</v>
       </c>
       <c r="R90" t="n">
-        <v>1064953</v>
+        <v>508223</v>
       </c>
       <c r="S90" t="n">
-        <v>111578</v>
+        <v>-14458</v>
       </c>
       <c r="T90" t="n">
-        <v>-169323</v>
+        <v>232307</v>
       </c>
       <c r="U90" t="n">
-        <v>-8769</v>
+        <v>417934</v>
       </c>
       <c r="V90" t="n">
-        <v>632625</v>
+        <v>508122</v>
       </c>
       <c r="W90" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X90" t="n">
         <v>0</v>
@@ -16062,16 +16052,16 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1082</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>121298</v>
+        <v>-3470</v>
       </c>
       <c r="AC90" t="n">
-        <v>263443</v>
+        <v>-639</v>
       </c>
       <c r="AD90" t="n">
-        <v>432328</v>
+        <v>101</v>
       </c>
       <c r="AE90" t="n">
         <v>32</v>
@@ -16089,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
@@ -16097,16 +16087,16 @@
         </is>
       </c>
       <c r="AL90" t="n">
-        <v>8</v>
+        <v>-20</v>
       </c>
       <c r="AM90" t="n">
-        <v>33.33</v>
+        <v>-38.46</v>
       </c>
       <c r="AN90" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AO90" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
@@ -16115,7 +16105,7 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
@@ -16495,12 +16485,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2816.TW</t>
+          <t>2605.TW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>旺旺保</t>
+          <t>新興</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -16519,28 +16509,28 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>40.8</v>
+        <v>36.7</v>
       </c>
       <c r="G93" t="n">
-        <v>40.07</v>
+        <v>36.23</v>
       </c>
       <c r="H93" t="n">
-        <v>40.08</v>
+        <v>36.11</v>
       </c>
       <c r="I93" t="n">
-        <v>39.92</v>
+        <v>36.28</v>
       </c>
       <c r="J93" t="n">
-        <v>230213</v>
+        <v>5360639</v>
       </c>
       <c r="K93" t="n">
-        <v>233755</v>
+        <v>8834578</v>
       </c>
       <c r="L93" t="n">
-        <v>41.4</v>
+        <v>38.65</v>
       </c>
       <c r="M93" t="n">
-        <v>38.5</v>
+        <v>34.85</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -16548,52 +16538,52 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>-19932</v>
+        <v>641094</v>
       </c>
       <c r="P93" t="n">
-        <v>239255</v>
+        <v>10268287</v>
       </c>
       <c r="Q93" t="n">
-        <v>234376</v>
+        <v>7494079</v>
       </c>
       <c r="R93" t="n">
-        <v>78395</v>
+        <v>-3231651</v>
       </c>
       <c r="S93" t="n">
-        <v>-19932</v>
+        <v>534950</v>
       </c>
       <c r="T93" t="n">
-        <v>239255</v>
+        <v>9471008</v>
       </c>
       <c r="U93" t="n">
-        <v>234376</v>
+        <v>6783394</v>
       </c>
       <c r="V93" t="n">
-        <v>78395</v>
+        <v>-3024550</v>
       </c>
       <c r="W93" t="n">
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>-201000</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>106144</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>798279</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>711685</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>-6101</v>
       </c>
       <c r="AE93" t="n">
         <v>32</v>
@@ -16602,16 +16592,16 @@
         <v>32</v>
       </c>
       <c r="AG93" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH93" t="n">
         <v>60</v>
       </c>
-      <c r="AH93" t="n">
-        <v>20</v>
-      </c>
       <c r="AI93" t="n">
         <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
@@ -16619,25 +16609,25 @@
         </is>
       </c>
       <c r="AL93" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AM93" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AN93" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AO93" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
@@ -16652,29 +16642,29 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能未放大、接近20日高點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能未放大、接近20日高點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2402.TW</t>
+          <t>2816.TW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>毅嘉</t>
+          <t>旺旺保</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16693,28 +16683,28 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>61</v>
+        <v>40.8</v>
       </c>
       <c r="G94" t="n">
-        <v>60.04</v>
+        <v>40.07</v>
       </c>
       <c r="H94" t="n">
-        <v>58.12</v>
+        <v>40.08</v>
       </c>
       <c r="I94" t="n">
-        <v>56.14</v>
+        <v>39.92</v>
       </c>
       <c r="J94" t="n">
-        <v>2515996</v>
+        <v>230213</v>
       </c>
       <c r="K94" t="n">
-        <v>3246488</v>
+        <v>233755</v>
       </c>
       <c r="L94" t="n">
-        <v>63.6</v>
+        <v>41.4</v>
       </c>
       <c r="M94" t="n">
-        <v>53</v>
+        <v>38.5</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -16722,28 +16712,28 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>-203444</v>
+        <v>-19932</v>
       </c>
       <c r="P94" t="n">
-        <v>2227023</v>
+        <v>239255</v>
       </c>
       <c r="Q94" t="n">
-        <v>2608128</v>
+        <v>234376</v>
       </c>
       <c r="R94" t="n">
-        <v>3380772</v>
+        <v>78395</v>
       </c>
       <c r="S94" t="n">
-        <v>-63205</v>
+        <v>-19932</v>
       </c>
       <c r="T94" t="n">
-        <v>1950411</v>
+        <v>239255</v>
       </c>
       <c r="U94" t="n">
-        <v>2344206</v>
+        <v>234376</v>
       </c>
       <c r="V94" t="n">
-        <v>2998465</v>
+        <v>78395</v>
       </c>
       <c r="W94" t="n">
         <v>0</v>
@@ -16758,34 +16748,34 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>-140239</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>276612</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>263922</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>382307</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF94" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG94" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="AH94" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
       </c>
       <c r="AJ94" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
@@ -16793,25 +16783,25 @@
         </is>
       </c>
       <c r="AL94" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="AM94" t="n">
-        <v>-45.45</v>
+        <v>0</v>
       </c>
       <c r="AN94" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AO94" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
@@ -16826,17 +16816,17 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、黃金交叉、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、黃金交叉、量能未放大、接近20日高點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -17017,12 +17007,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2301.TW</t>
+          <t>2360.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17041,28 +17031,28 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>297.5</v>
+        <v>2330</v>
       </c>
       <c r="G96" t="n">
-        <v>295.2</v>
+        <v>2319</v>
       </c>
       <c r="H96" t="n">
-        <v>289.15</v>
+        <v>2261.5</v>
       </c>
       <c r="I96" t="n">
-        <v>285.68</v>
+        <v>2239.5</v>
       </c>
       <c r="J96" t="n">
-        <v>13602817</v>
+        <v>1763765</v>
       </c>
       <c r="K96" t="n">
-        <v>16886819</v>
+        <v>3088197</v>
       </c>
       <c r="L96" t="n">
-        <v>304.5</v>
+        <v>2560</v>
       </c>
       <c r="M96" t="n">
-        <v>271</v>
+        <v>2025</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -17070,52 +17060,52 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>-2219183</v>
+        <v>-50914</v>
       </c>
       <c r="P96" t="n">
-        <v>-1032441</v>
+        <v>677959</v>
       </c>
       <c r="Q96" t="n">
-        <v>9085450</v>
+        <v>1734466</v>
       </c>
       <c r="R96" t="n">
-        <v>644210</v>
+        <v>569730</v>
       </c>
       <c r="S96" t="n">
-        <v>-2343867</v>
+        <v>-51489</v>
       </c>
       <c r="T96" t="n">
-        <v>-1604904</v>
+        <v>904278</v>
       </c>
       <c r="U96" t="n">
-        <v>7998501</v>
+        <v>2489090</v>
       </c>
       <c r="V96" t="n">
-        <v>30542</v>
+        <v>3772789</v>
       </c>
       <c r="W96" t="n">
-        <v>7383</v>
+        <v>22865</v>
       </c>
       <c r="X96" t="n">
-        <v>200968</v>
+        <v>-4913</v>
       </c>
       <c r="Y96" t="n">
-        <v>-94175</v>
+        <v>-481599</v>
       </c>
       <c r="Z96" t="n">
-        <v>-938175</v>
+        <v>-3184599</v>
       </c>
       <c r="AA96" t="n">
-        <v>117301</v>
+        <v>-22290</v>
       </c>
       <c r="AB96" t="n">
-        <v>371495</v>
+        <v>-221406</v>
       </c>
       <c r="AC96" t="n">
-        <v>1181124</v>
+        <v>-273025</v>
       </c>
       <c r="AD96" t="n">
-        <v>1551843</v>
+        <v>-18460</v>
       </c>
       <c r="AE96" t="n">
         <v>30</v>
@@ -17133,7 +17123,7 @@
         <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
@@ -17141,10 +17131,10 @@
         </is>
       </c>
       <c r="AL96" t="n">
-        <v>-22</v>
+        <v>-18</v>
       </c>
       <c r="AM96" t="n">
-        <v>-42.31</v>
+        <v>-37.5</v>
       </c>
       <c r="AN96" t="n">
         <v>45</v>
@@ -17191,12 +17181,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2360.TW</t>
+          <t>2301.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17215,28 +17205,28 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2330</v>
+        <v>297.5</v>
       </c>
       <c r="G97" t="n">
-        <v>2319</v>
+        <v>295.2</v>
       </c>
       <c r="H97" t="n">
-        <v>2261.5</v>
+        <v>289.15</v>
       </c>
       <c r="I97" t="n">
-        <v>2239.5</v>
+        <v>285.68</v>
       </c>
       <c r="J97" t="n">
-        <v>1763765</v>
+        <v>13602817</v>
       </c>
       <c r="K97" t="n">
-        <v>3088197</v>
+        <v>16886819</v>
       </c>
       <c r="L97" t="n">
-        <v>2560</v>
+        <v>304.5</v>
       </c>
       <c r="M97" t="n">
-        <v>2025</v>
+        <v>271</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -17244,52 +17234,52 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>-50914</v>
+        <v>-2219183</v>
       </c>
       <c r="P97" t="n">
-        <v>677959</v>
+        <v>-1032441</v>
       </c>
       <c r="Q97" t="n">
-        <v>1734466</v>
+        <v>9085450</v>
       </c>
       <c r="R97" t="n">
-        <v>569730</v>
+        <v>644210</v>
       </c>
       <c r="S97" t="n">
-        <v>-51489</v>
+        <v>-2343867</v>
       </c>
       <c r="T97" t="n">
-        <v>904278</v>
+        <v>-1604904</v>
       </c>
       <c r="U97" t="n">
-        <v>2489090</v>
+        <v>7998501</v>
       </c>
       <c r="V97" t="n">
-        <v>3772789</v>
+        <v>30542</v>
       </c>
       <c r="W97" t="n">
-        <v>22865</v>
+        <v>7383</v>
       </c>
       <c r="X97" t="n">
-        <v>-4913</v>
+        <v>200968</v>
       </c>
       <c r="Y97" t="n">
-        <v>-481599</v>
+        <v>-94175</v>
       </c>
       <c r="Z97" t="n">
-        <v>-3184599</v>
+        <v>-938175</v>
       </c>
       <c r="AA97" t="n">
-        <v>-22290</v>
+        <v>117301</v>
       </c>
       <c r="AB97" t="n">
-        <v>-221406</v>
+        <v>371495</v>
       </c>
       <c r="AC97" t="n">
-        <v>-273025</v>
+        <v>1181124</v>
       </c>
       <c r="AD97" t="n">
-        <v>-18460</v>
+        <v>1551843</v>
       </c>
       <c r="AE97" t="n">
         <v>30</v>
@@ -17307,7 +17297,7 @@
         <v>0</v>
       </c>
       <c r="AJ97" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
@@ -17315,10 +17305,10 @@
         </is>
       </c>
       <c r="AL97" t="n">
-        <v>-18</v>
+        <v>-22</v>
       </c>
       <c r="AM97" t="n">
-        <v>-37.5</v>
+        <v>-42.31</v>
       </c>
       <c r="AN97" t="n">
         <v>45</v>
@@ -17365,12 +17355,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1504.TW</t>
+          <t>2402.TW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>毅嘉</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -17389,28 +17379,28 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>71.7</v>
+        <v>61</v>
       </c>
       <c r="G98" t="n">
-        <v>70.95999999999999</v>
+        <v>60.04</v>
       </c>
       <c r="H98" t="n">
-        <v>69.86</v>
+        <v>58.12</v>
       </c>
       <c r="I98" t="n">
-        <v>69.86</v>
+        <v>56.14</v>
       </c>
       <c r="J98" t="n">
-        <v>10635881</v>
+        <v>2515996</v>
       </c>
       <c r="K98" t="n">
-        <v>11165380</v>
+        <v>3246488</v>
       </c>
       <c r="L98" t="n">
-        <v>73.90000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="M98" t="n">
-        <v>67.59999999999999</v>
+        <v>53</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -17418,70 +17408,70 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>-4946995</v>
+        <v>-203444</v>
       </c>
       <c r="P98" t="n">
-        <v>1978993</v>
+        <v>2227023</v>
       </c>
       <c r="Q98" t="n">
-        <v>3411315</v>
+        <v>2608128</v>
       </c>
       <c r="R98" t="n">
-        <v>3607018</v>
+        <v>3380772</v>
       </c>
       <c r="S98" t="n">
-        <v>-4647471</v>
+        <v>-63205</v>
       </c>
       <c r="T98" t="n">
-        <v>1917752</v>
+        <v>1950411</v>
       </c>
       <c r="U98" t="n">
-        <v>3289152</v>
+        <v>2344206</v>
       </c>
       <c r="V98" t="n">
-        <v>4289186</v>
+        <v>2998465</v>
       </c>
       <c r="W98" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>-19889</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>14114</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>-737886</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>-312524</v>
+        <v>-140239</v>
       </c>
       <c r="AB98" t="n">
-        <v>81130</v>
+        <v>276612</v>
       </c>
       <c r="AC98" t="n">
-        <v>108049</v>
+        <v>263922</v>
       </c>
       <c r="AD98" t="n">
-        <v>55718</v>
+        <v>382307</v>
       </c>
       <c r="AE98" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AF98" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG98" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AH98" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
       </c>
       <c r="AJ98" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
@@ -17489,25 +17479,25 @@
         </is>
       </c>
       <c r="AL98" t="n">
-        <v>-41</v>
+        <v>-25</v>
       </c>
       <c r="AM98" t="n">
-        <v>-59.42</v>
+        <v>-45.45</v>
       </c>
       <c r="AN98" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AO98" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
@@ -17522,17 +17512,17 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -18409,12 +18399,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1522.TW</t>
+          <t>1504.TW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -18433,28 +18423,28 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>26.4</v>
+        <v>71.7</v>
       </c>
       <c r="G104" t="n">
-        <v>25.94</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="H104" t="n">
-        <v>26.25</v>
+        <v>69.86</v>
       </c>
       <c r="I104" t="n">
-        <v>26.05</v>
+        <v>69.86</v>
       </c>
       <c r="J104" t="n">
-        <v>354738</v>
+        <v>10635881</v>
       </c>
       <c r="K104" t="n">
-        <v>366677</v>
+        <v>11165380</v>
       </c>
       <c r="L104" t="n">
-        <v>27</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M104" t="n">
-        <v>24.9</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -18462,52 +18452,52 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>204320</v>
+        <v>-4946995</v>
       </c>
       <c r="P104" t="n">
-        <v>310514</v>
+        <v>1978993</v>
       </c>
       <c r="Q104" t="n">
-        <v>360494</v>
+        <v>3411315</v>
       </c>
       <c r="R104" t="n">
-        <v>715649</v>
+        <v>3607018</v>
       </c>
       <c r="S104" t="n">
-        <v>205320</v>
+        <v>-4647471</v>
       </c>
       <c r="T104" t="n">
-        <v>311514</v>
+        <v>1917752</v>
       </c>
       <c r="U104" t="n">
-        <v>361494</v>
+        <v>3289152</v>
       </c>
       <c r="V104" t="n">
-        <v>738668</v>
+        <v>4289186</v>
       </c>
       <c r="W104" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>-19889</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>14114</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>-737886</v>
       </c>
       <c r="AA104" t="n">
-        <v>-1000</v>
+        <v>-312524</v>
       </c>
       <c r="AB104" t="n">
-        <v>-1000</v>
+        <v>81130</v>
       </c>
       <c r="AC104" t="n">
-        <v>-1000</v>
+        <v>108049</v>
       </c>
       <c r="AD104" t="n">
-        <v>-23019</v>
+        <v>55718</v>
       </c>
       <c r="AE104" t="n">
         <v>28</v>
@@ -18525,7 +18515,7 @@
         <v>0</v>
       </c>
       <c r="AJ104" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
@@ -18533,25 +18523,25 @@
         </is>
       </c>
       <c r="AL104" t="n">
-        <v>16</v>
+        <v>-41</v>
       </c>
       <c r="AM104" t="n">
-        <v>133.33</v>
+        <v>-59.42</v>
       </c>
       <c r="AN104" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AO104" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
@@ -18571,12 +18561,12 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -19105,12 +19095,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2881.TW</t>
+          <t>1522.TW</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -19129,28 +19119,28 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>153</v>
+        <v>26.4</v>
       </c>
       <c r="G108" t="n">
-        <v>153.1</v>
+        <v>25.94</v>
       </c>
       <c r="H108" t="n">
-        <v>152.15</v>
+        <v>26.25</v>
       </c>
       <c r="I108" t="n">
-        <v>151.72</v>
+        <v>26.05</v>
       </c>
       <c r="J108" t="n">
-        <v>14629239</v>
+        <v>354738</v>
       </c>
       <c r="K108" t="n">
-        <v>13038962</v>
+        <v>366677</v>
       </c>
       <c r="L108" t="n">
-        <v>156.5</v>
+        <v>27</v>
       </c>
       <c r="M108" t="n">
-        <v>144</v>
+        <v>24.9</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -19158,61 +19148,61 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>-1788918</v>
+        <v>204320</v>
       </c>
       <c r="P108" t="n">
-        <v>2944027</v>
+        <v>310514</v>
       </c>
       <c r="Q108" t="n">
-        <v>7486577</v>
+        <v>360494</v>
       </c>
       <c r="R108" t="n">
-        <v>1954670</v>
+        <v>715649</v>
       </c>
       <c r="S108" t="n">
-        <v>-4764493</v>
+        <v>205320</v>
       </c>
       <c r="T108" t="n">
-        <v>-672087</v>
+        <v>311514</v>
       </c>
       <c r="U108" t="n">
-        <v>2502422</v>
+        <v>361494</v>
       </c>
       <c r="V108" t="n">
-        <v>-3946852</v>
+        <v>738668</v>
       </c>
       <c r="W108" t="n">
-        <v>2844942</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>3401983</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>4852177</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>5837177</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>130633</v>
+        <v>-1000</v>
       </c>
       <c r="AB108" t="n">
-        <v>214131</v>
+        <v>-1000</v>
       </c>
       <c r="AC108" t="n">
-        <v>131978</v>
+        <v>-1000</v>
       </c>
       <c r="AD108" t="n">
-        <v>64345</v>
+        <v>-23019</v>
       </c>
       <c r="AE108" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF108" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG108" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AH108" t="n">
         <v>50</v>
@@ -19221,7 +19211,7 @@
         <v>0</v>
       </c>
       <c r="AJ108" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
@@ -19229,25 +19219,25 @@
         </is>
       </c>
       <c r="AL108" t="n">
-        <v>-30</v>
+        <v>16</v>
       </c>
       <c r="AM108" t="n">
-        <v>-53.57</v>
+        <v>133.33</v>
       </c>
       <c r="AN108" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AO108" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
@@ -19262,17 +19252,17 @@
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -19453,12 +19443,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>2881.TW</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19477,28 +19467,28 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>22.2</v>
+        <v>153</v>
       </c>
       <c r="G110" t="n">
-        <v>22.44</v>
+        <v>153.1</v>
       </c>
       <c r="H110" t="n">
-        <v>22.35</v>
+        <v>152.15</v>
       </c>
       <c r="I110" t="n">
-        <v>21.7</v>
+        <v>151.72</v>
       </c>
       <c r="J110" t="n">
-        <v>955361</v>
+        <v>14629239</v>
       </c>
       <c r="K110" t="n">
-        <v>1373880</v>
+        <v>13038962</v>
       </c>
       <c r="L110" t="n">
-        <v>23.2</v>
+        <v>156.5</v>
       </c>
       <c r="M110" t="n">
-        <v>20.1</v>
+        <v>144</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -19506,52 +19496,52 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>49512</v>
+        <v>-1788918</v>
       </c>
       <c r="P110" t="n">
-        <v>221687</v>
+        <v>2944027</v>
       </c>
       <c r="Q110" t="n">
-        <v>735376</v>
+        <v>7486577</v>
       </c>
       <c r="R110" t="n">
-        <v>316160</v>
+        <v>1954670</v>
       </c>
       <c r="S110" t="n">
-        <v>125000</v>
+        <v>-4764493</v>
       </c>
       <c r="T110" t="n">
-        <v>357558</v>
+        <v>-672087</v>
       </c>
       <c r="U110" t="n">
-        <v>778076</v>
+        <v>2502422</v>
       </c>
       <c r="V110" t="n">
-        <v>356730</v>
+        <v>-3946852</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>2844942</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>3401983</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>4852177</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>5837177</v>
       </c>
       <c r="AA110" t="n">
-        <v>-75488</v>
+        <v>130633</v>
       </c>
       <c r="AB110" t="n">
-        <v>-135871</v>
+        <v>214131</v>
       </c>
       <c r="AC110" t="n">
-        <v>-42700</v>
+        <v>131978</v>
       </c>
       <c r="AD110" t="n">
-        <v>-40570</v>
+        <v>64345</v>
       </c>
       <c r="AE110" t="n">
         <v>26</v>
@@ -19560,16 +19550,16 @@
         <v>26</v>
       </c>
       <c r="AG110" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AH110" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
       </c>
       <c r="AJ110" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
@@ -19577,16 +19567,16 @@
         </is>
       </c>
       <c r="AL110" t="n">
-        <v>4</v>
+        <v>-30</v>
       </c>
       <c r="AM110" t="n">
-        <v>18.18</v>
+        <v>-53.57</v>
       </c>
       <c r="AN110" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AO110" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
@@ -19595,7 +19585,7 @@
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
@@ -19610,17 +19600,17 @@
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -19801,12 +19791,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>2377.TW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -19825,28 +19815,28 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>23.8</v>
+        <v>154.5</v>
       </c>
       <c r="G112" t="n">
-        <v>24.12</v>
+        <v>155.1</v>
       </c>
       <c r="H112" t="n">
-        <v>23.76</v>
+        <v>153.25</v>
       </c>
       <c r="I112" t="n">
-        <v>22.52</v>
+        <v>152.68</v>
       </c>
       <c r="J112" t="n">
-        <v>2386573</v>
+        <v>3266008</v>
       </c>
       <c r="K112" t="n">
-        <v>3427521</v>
+        <v>4750295</v>
       </c>
       <c r="L112" t="n">
-        <v>24.95</v>
+        <v>159</v>
       </c>
       <c r="M112" t="n">
-        <v>19.5</v>
+        <v>144.5</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -19854,52 +19844,52 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>443097</v>
+        <v>245065</v>
       </c>
       <c r="P112" t="n">
-        <v>1556373</v>
+        <v>1080788</v>
       </c>
       <c r="Q112" t="n">
-        <v>1617983</v>
+        <v>4455439</v>
       </c>
       <c r="R112" t="n">
-        <v>1731432</v>
+        <v>5307986</v>
       </c>
       <c r="S112" t="n">
-        <v>431287</v>
+        <v>674547</v>
       </c>
       <c r="T112" t="n">
-        <v>1537360</v>
+        <v>2339887</v>
       </c>
       <c r="U112" t="n">
-        <v>1616185</v>
+        <v>4422245</v>
       </c>
       <c r="V112" t="n">
-        <v>1825757</v>
+        <v>4681529</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>-497000</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>-1318146</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>-318576</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>162424</v>
       </c>
       <c r="AA112" t="n">
-        <v>11810</v>
+        <v>67518</v>
       </c>
       <c r="AB112" t="n">
-        <v>19013</v>
+        <v>59047</v>
       </c>
       <c r="AC112" t="n">
-        <v>1798</v>
+        <v>351770</v>
       </c>
       <c r="AD112" t="n">
-        <v>-94325</v>
+        <v>464033</v>
       </c>
       <c r="AE112" t="n">
         <v>26</v>
@@ -19917,7 +19907,7 @@
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
@@ -19925,14 +19915,16 @@
         </is>
       </c>
       <c r="AL112" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM112" t="inlineStr"/>
+        <v>-30</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>-53.57</v>
+      </c>
       <c r="AN112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AO112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
@@ -19941,7 +19933,7 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -19961,12 +19953,12 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -20843,12 +20835,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2328.TW</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>廣宇</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -20867,28 +20859,28 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>48.05</v>
+        <v>22.2</v>
       </c>
       <c r="G118" t="n">
-        <v>48.12</v>
+        <v>22.44</v>
       </c>
       <c r="H118" t="n">
-        <v>47.7</v>
+        <v>22.35</v>
       </c>
       <c r="I118" t="n">
-        <v>46.95</v>
+        <v>21.71</v>
       </c>
       <c r="J118" t="n">
-        <v>878176</v>
+        <v>955361</v>
       </c>
       <c r="K118" t="n">
-        <v>1618983</v>
+        <v>1373880</v>
       </c>
       <c r="L118" t="n">
-        <v>49.6</v>
+        <v>23.2</v>
       </c>
       <c r="M118" t="n">
-        <v>44.85</v>
+        <v>20.1</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -20896,28 +20888,28 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>308114</v>
+        <v>49512</v>
       </c>
       <c r="P118" t="n">
-        <v>456040</v>
+        <v>221687</v>
       </c>
       <c r="Q118" t="n">
-        <v>1569129</v>
+        <v>735376</v>
       </c>
       <c r="R118" t="n">
-        <v>2778526</v>
+        <v>316160</v>
       </c>
       <c r="S118" t="n">
-        <v>269066</v>
+        <v>125000</v>
       </c>
       <c r="T118" t="n">
-        <v>633992</v>
+        <v>357558</v>
       </c>
       <c r="U118" t="n">
-        <v>1480207</v>
+        <v>778076</v>
       </c>
       <c r="V118" t="n">
-        <v>2743529</v>
+        <v>356730</v>
       </c>
       <c r="W118" t="n">
         <v>0</v>
@@ -20932,16 +20924,16 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>39048</v>
+        <v>-75488</v>
       </c>
       <c r="AB118" t="n">
-        <v>-177952</v>
+        <v>-135871</v>
       </c>
       <c r="AC118" t="n">
-        <v>88922</v>
+        <v>-42700</v>
       </c>
       <c r="AD118" t="n">
-        <v>34997</v>
+        <v>-40570</v>
       </c>
       <c r="AE118" t="n">
         <v>26</v>
@@ -20959,7 +20951,7 @@
         <v>0</v>
       </c>
       <c r="AJ118" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
@@ -20967,16 +20959,16 @@
         </is>
       </c>
       <c r="AL118" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="AM118" t="n">
-        <v>-38.1</v>
+        <v>18.18</v>
       </c>
       <c r="AN118" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AO118" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
@@ -20985,7 +20977,7 @@
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
@@ -21017,12 +21009,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2377.TW</t>
+          <t>2328.TW</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>廣宇</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -21041,28 +21033,28 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>154.5</v>
+        <v>48.05</v>
       </c>
       <c r="G119" t="n">
-        <v>155.1</v>
+        <v>48.12</v>
       </c>
       <c r="H119" t="n">
-        <v>153.25</v>
+        <v>47.7</v>
       </c>
       <c r="I119" t="n">
-        <v>152.68</v>
+        <v>46.95</v>
       </c>
       <c r="J119" t="n">
-        <v>3266008</v>
+        <v>878176</v>
       </c>
       <c r="K119" t="n">
-        <v>4750295</v>
+        <v>1618983</v>
       </c>
       <c r="L119" t="n">
-        <v>159</v>
+        <v>49.6</v>
       </c>
       <c r="M119" t="n">
-        <v>144.5</v>
+        <v>44.85</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -21070,52 +21062,52 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>245065</v>
+        <v>308114</v>
       </c>
       <c r="P119" t="n">
-        <v>1080788</v>
+        <v>456040</v>
       </c>
       <c r="Q119" t="n">
-        <v>4455439</v>
+        <v>1569129</v>
       </c>
       <c r="R119" t="n">
-        <v>5307986</v>
+        <v>2778526</v>
       </c>
       <c r="S119" t="n">
-        <v>674547</v>
+        <v>269066</v>
       </c>
       <c r="T119" t="n">
-        <v>2339887</v>
+        <v>633992</v>
       </c>
       <c r="U119" t="n">
-        <v>4422245</v>
+        <v>1480207</v>
       </c>
       <c r="V119" t="n">
-        <v>4681529</v>
+        <v>2743529</v>
       </c>
       <c r="W119" t="n">
-        <v>-497000</v>
+        <v>0</v>
       </c>
       <c r="X119" t="n">
-        <v>-1318146</v>
+        <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>-318576</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>162424</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>67518</v>
+        <v>39048</v>
       </c>
       <c r="AB119" t="n">
-        <v>59047</v>
+        <v>-177952</v>
       </c>
       <c r="AC119" t="n">
-        <v>351770</v>
+        <v>88922</v>
       </c>
       <c r="AD119" t="n">
-        <v>464033</v>
+        <v>34997</v>
       </c>
       <c r="AE119" t="n">
         <v>26</v>
@@ -21133,7 +21125,7 @@
         <v>0</v>
       </c>
       <c r="AJ119" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
@@ -21141,10 +21133,10 @@
         </is>
       </c>
       <c r="AL119" t="n">
-        <v>-30</v>
+        <v>-16</v>
       </c>
       <c r="AM119" t="n">
-        <v>-53.57</v>
+        <v>-38.1</v>
       </c>
       <c r="AN119" t="n">
         <v>10</v>
@@ -21179,24 +21171,24 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2347.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -21215,28 +21207,28 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>96.40000000000001</v>
+        <v>23.8</v>
       </c>
       <c r="G120" t="n">
-        <v>96.62</v>
+        <v>24.12</v>
       </c>
       <c r="H120" t="n">
-        <v>95.69</v>
+        <v>23.76</v>
       </c>
       <c r="I120" t="n">
-        <v>92.5</v>
+        <v>22.52</v>
       </c>
       <c r="J120" t="n">
-        <v>1894748</v>
+        <v>2386573</v>
       </c>
       <c r="K120" t="n">
-        <v>2647895</v>
+        <v>3427521</v>
       </c>
       <c r="L120" t="n">
-        <v>100</v>
+        <v>24.95</v>
       </c>
       <c r="M120" t="n">
-        <v>87.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -21244,52 +21236,52 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>476019</v>
+        <v>443097</v>
       </c>
       <c r="P120" t="n">
-        <v>2136290</v>
+        <v>1556373</v>
       </c>
       <c r="Q120" t="n">
-        <v>5344563</v>
+        <v>1617983</v>
       </c>
       <c r="R120" t="n">
-        <v>13711783</v>
+        <v>1731432</v>
       </c>
       <c r="S120" t="n">
-        <v>508992</v>
+        <v>431287</v>
       </c>
       <c r="T120" t="n">
-        <v>2916152</v>
+        <v>1537360</v>
       </c>
       <c r="U120" t="n">
-        <v>6328142</v>
+        <v>1616185</v>
       </c>
       <c r="V120" t="n">
-        <v>13019958</v>
+        <v>1825757</v>
       </c>
       <c r="W120" t="n">
-        <v>-182000</v>
+        <v>0</v>
       </c>
       <c r="X120" t="n">
-        <v>-1049899</v>
+        <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>-1460760</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>-132781</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>149027</v>
+        <v>11810</v>
       </c>
       <c r="AB120" t="n">
-        <v>270037</v>
+        <v>19013</v>
       </c>
       <c r="AC120" t="n">
-        <v>477181</v>
+        <v>1798</v>
       </c>
       <c r="AD120" t="n">
-        <v>824606</v>
+        <v>-94325</v>
       </c>
       <c r="AE120" t="n">
         <v>26</v>
@@ -21307,7 +21299,7 @@
         <v>0</v>
       </c>
       <c r="AJ120" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
@@ -21315,16 +21307,14 @@
         </is>
       </c>
       <c r="AL120" t="n">
-        <v>-16</v>
-      </c>
-      <c r="AM120" t="n">
-        <v>-38.1</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="AM120" t="inlineStr"/>
       <c r="AN120" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AO120" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
@@ -21333,7 +21323,7 @@
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
@@ -21353,24 +21343,24 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2637.TW</t>
+          <t>2347.TW</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -21389,28 +21379,28 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>98.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G121" t="n">
-        <v>98.34</v>
+        <v>96.62</v>
       </c>
       <c r="H121" t="n">
-        <v>97.94</v>
+        <v>95.69</v>
       </c>
       <c r="I121" t="n">
-        <v>99.44</v>
+        <v>92.5</v>
       </c>
       <c r="J121" t="n">
-        <v>1706603</v>
+        <v>1894748</v>
       </c>
       <c r="K121" t="n">
-        <v>2162301</v>
+        <v>2647895</v>
       </c>
       <c r="L121" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M121" t="n">
-        <v>95</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -21418,96 +21408,96 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>495472</v>
+        <v>476019</v>
       </c>
       <c r="P121" t="n">
-        <v>-50659</v>
+        <v>2136290</v>
       </c>
       <c r="Q121" t="n">
-        <v>559188</v>
+        <v>5344563</v>
       </c>
       <c r="R121" t="n">
-        <v>-377210</v>
+        <v>13711783</v>
       </c>
       <c r="S121" t="n">
-        <v>465620</v>
+        <v>508992</v>
       </c>
       <c r="T121" t="n">
-        <v>-78807</v>
+        <v>2916152</v>
       </c>
       <c r="U121" t="n">
-        <v>466278</v>
+        <v>6328142</v>
       </c>
       <c r="V121" t="n">
-        <v>-717842</v>
+        <v>13019958</v>
       </c>
       <c r="W121" t="n">
-        <v>19000</v>
+        <v>-182000</v>
       </c>
       <c r="X121" t="n">
-        <v>6719</v>
+        <v>-1049899</v>
       </c>
       <c r="Y121" t="n">
-        <v>84439</v>
+        <v>-1460760</v>
       </c>
       <c r="Z121" t="n">
-        <v>335878</v>
+        <v>-132781</v>
       </c>
       <c r="AA121" t="n">
-        <v>10852</v>
+        <v>149027</v>
       </c>
       <c r="AB121" t="n">
-        <v>21429</v>
+        <v>270037</v>
       </c>
       <c r="AC121" t="n">
-        <v>8471</v>
+        <v>477181</v>
       </c>
       <c r="AD121" t="n">
-        <v>4754</v>
+        <v>824606</v>
       </c>
       <c r="AE121" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF121" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AG121" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AL121" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>-38.1</v>
+      </c>
+      <c r="AN121" t="n">
         <v>10</v>
       </c>
-      <c r="AH121" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>-36</v>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AL121" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM121" t="n">
-        <v>166.67</v>
-      </c>
-      <c r="AN121" t="n">
-        <v>35</v>
-      </c>
       <c r="AO121" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
@@ -21522,17 +21512,17 @@
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -22409,12 +22399,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2535.TW</t>
+          <t>2637.TW</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -22433,28 +22423,28 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>91.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="G127" t="n">
-        <v>89.31999999999999</v>
+        <v>98.34</v>
       </c>
       <c r="H127" t="n">
-        <v>89.34999999999999</v>
+        <v>97.94</v>
       </c>
       <c r="I127" t="n">
-        <v>89.44</v>
+        <v>99.44</v>
       </c>
       <c r="J127" t="n">
-        <v>379048</v>
+        <v>1706603</v>
       </c>
       <c r="K127" t="n">
-        <v>285835</v>
+        <v>2162301</v>
       </c>
       <c r="L127" t="n">
-        <v>91.90000000000001</v>
+        <v>105</v>
       </c>
       <c r="M127" t="n">
-        <v>87.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -22462,52 +22452,52 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>269183</v>
+        <v>495472</v>
       </c>
       <c r="P127" t="n">
-        <v>471875</v>
+        <v>-50659</v>
       </c>
       <c r="Q127" t="n">
-        <v>305092</v>
+        <v>559188</v>
       </c>
       <c r="R127" t="n">
-        <v>334647</v>
+        <v>-377210</v>
       </c>
       <c r="S127" t="n">
-        <v>268411</v>
+        <v>465620</v>
       </c>
       <c r="T127" t="n">
-        <v>467103</v>
+        <v>-78807</v>
       </c>
       <c r="U127" t="n">
-        <v>299375</v>
+        <v>466278</v>
       </c>
       <c r="V127" t="n">
-        <v>328813</v>
+        <v>-717842</v>
       </c>
       <c r="W127" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="X127" t="n">
-        <v>0</v>
+        <v>6719</v>
       </c>
       <c r="Y127" t="n">
-        <v>-1000</v>
+        <v>84439</v>
       </c>
       <c r="Z127" t="n">
-        <v>-1000</v>
+        <v>335878</v>
       </c>
       <c r="AA127" t="n">
-        <v>772</v>
+        <v>10852</v>
       </c>
       <c r="AB127" t="n">
-        <v>4772</v>
+        <v>21429</v>
       </c>
       <c r="AC127" t="n">
-        <v>6717</v>
+        <v>8471</v>
       </c>
       <c r="AD127" t="n">
-        <v>6834</v>
+        <v>4754</v>
       </c>
       <c r="AE127" t="n">
         <v>24</v>
@@ -22525,7 +22515,7 @@
         <v>0</v>
       </c>
       <c r="AJ127" t="n">
-        <v>-10</v>
+        <v>-36</v>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
@@ -22533,25 +22523,25 @@
         </is>
       </c>
       <c r="AL127" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AM127" t="n">
-        <v>340</v>
+        <v>166.67</v>
       </c>
       <c r="AN127" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AO127" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
@@ -22566,29 +22556,29 @@
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2912.TW</t>
+          <t>2535.TW</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -22607,28 +22597,28 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>213</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G128" t="n">
-        <v>211.7</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="H128" t="n">
-        <v>212.1</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="I128" t="n">
-        <v>214.18</v>
+        <v>89.44</v>
       </c>
       <c r="J128" t="n">
-        <v>1914231</v>
+        <v>379048</v>
       </c>
       <c r="K128" t="n">
-        <v>1906044</v>
+        <v>285835</v>
       </c>
       <c r="L128" t="n">
-        <v>219</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="M128" t="n">
-        <v>210</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -22636,70 +22626,70 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>750317</v>
+        <v>269183</v>
       </c>
       <c r="P128" t="n">
-        <v>2029597</v>
+        <v>471875</v>
       </c>
       <c r="Q128" t="n">
-        <v>879411</v>
+        <v>305092</v>
       </c>
       <c r="R128" t="n">
-        <v>275070</v>
+        <v>334647</v>
       </c>
       <c r="S128" t="n">
-        <v>726685</v>
+        <v>268411</v>
       </c>
       <c r="T128" t="n">
-        <v>1874750</v>
+        <v>467103</v>
       </c>
       <c r="U128" t="n">
-        <v>1555506</v>
+        <v>299375</v>
       </c>
       <c r="V128" t="n">
-        <v>710165</v>
+        <v>328813</v>
       </c>
       <c r="W128" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="X128" t="n">
-        <v>146000</v>
+        <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>-691000</v>
+        <v>-1000</v>
       </c>
       <c r="Z128" t="n">
-        <v>-557000</v>
+        <v>-1000</v>
       </c>
       <c r="AA128" t="n">
-        <v>2632</v>
+        <v>772</v>
       </c>
       <c r="AB128" t="n">
-        <v>8847</v>
+        <v>4772</v>
       </c>
       <c r="AC128" t="n">
-        <v>14905</v>
+        <v>6717</v>
       </c>
       <c r="AD128" t="n">
-        <v>121905</v>
+        <v>6834</v>
       </c>
       <c r="AE128" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF128" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG128" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="AH128" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
       </c>
       <c r="AJ128" t="n">
-        <v>14</v>
+        <v>-10</v>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
@@ -22707,25 +22697,25 @@
         </is>
       </c>
       <c r="AL128" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="AM128" t="n">
-        <v>57.14</v>
+        <v>340</v>
       </c>
       <c r="AN128" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AO128" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
@@ -22740,29 +22730,29 @@
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2892.TW</t>
+          <t>2912.TW</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -22781,28 +22771,28 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>38.65</v>
+        <v>213</v>
       </c>
       <c r="G129" t="n">
-        <v>38.54</v>
+        <v>211.7</v>
       </c>
       <c r="H129" t="n">
-        <v>38.8</v>
+        <v>212.1</v>
       </c>
       <c r="I129" t="n">
-        <v>39.11</v>
+        <v>214.18</v>
       </c>
       <c r="J129" t="n">
-        <v>14704600</v>
+        <v>1914231</v>
       </c>
       <c r="K129" t="n">
-        <v>13952892</v>
+        <v>1906044</v>
       </c>
       <c r="L129" t="n">
-        <v>40.95</v>
+        <v>219</v>
       </c>
       <c r="M129" t="n">
-        <v>37.15</v>
+        <v>210</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -22810,52 +22800,52 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>213631</v>
+        <v>750317</v>
       </c>
       <c r="P129" t="n">
-        <v>3348609</v>
+        <v>2029597</v>
       </c>
       <c r="Q129" t="n">
-        <v>3346311</v>
+        <v>879411</v>
       </c>
       <c r="R129" t="n">
-        <v>13584604</v>
+        <v>275070</v>
       </c>
       <c r="S129" t="n">
-        <v>85897</v>
+        <v>726685</v>
       </c>
       <c r="T129" t="n">
-        <v>5207101</v>
+        <v>1874750</v>
       </c>
       <c r="U129" t="n">
-        <v>-192087</v>
+        <v>1555506</v>
       </c>
       <c r="V129" t="n">
-        <v>-2890074</v>
+        <v>710165</v>
       </c>
       <c r="W129" t="n">
-        <v>129893</v>
+        <v>21000</v>
       </c>
       <c r="X129" t="n">
-        <v>-1941243</v>
+        <v>146000</v>
       </c>
       <c r="Y129" t="n">
-        <v>3503517</v>
+        <v>-691000</v>
       </c>
       <c r="Z129" t="n">
-        <v>16116517</v>
+        <v>-557000</v>
       </c>
       <c r="AA129" t="n">
-        <v>-2159</v>
+        <v>2632</v>
       </c>
       <c r="AB129" t="n">
-        <v>82751</v>
+        <v>8847</v>
       </c>
       <c r="AC129" t="n">
-        <v>34881</v>
+        <v>14905</v>
       </c>
       <c r="AD129" t="n">
-        <v>358161</v>
+        <v>121905</v>
       </c>
       <c r="AE129" t="n">
         <v>22</v>
@@ -22873,7 +22863,7 @@
         <v>0</v>
       </c>
       <c r="AJ129" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
@@ -22881,16 +22871,16 @@
         </is>
       </c>
       <c r="AL129" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AM129" t="n">
-        <v>120</v>
+        <v>57.14</v>
       </c>
       <c r="AN129" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO129" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
@@ -22899,7 +22889,7 @@
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
@@ -22919,24 +22909,24 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3653.TW</t>
+          <t>2323.TW</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>中環</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -22946,7 +22936,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -22955,28 +22945,28 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>7165</v>
+        <v>11</v>
       </c>
       <c r="G130" t="n">
-        <v>7011</v>
+        <v>10.83</v>
       </c>
       <c r="H130" t="n">
-        <v>6895.5</v>
+        <v>10.74</v>
       </c>
       <c r="I130" t="n">
-        <v>6257</v>
+        <v>10.75</v>
       </c>
       <c r="J130" t="n">
-        <v>1628778</v>
+        <v>14064496</v>
       </c>
       <c r="K130" t="n">
-        <v>1085614</v>
+        <v>6377380</v>
       </c>
       <c r="L130" t="n">
-        <v>7440</v>
+        <v>11.15</v>
       </c>
       <c r="M130" t="n">
-        <v>5210</v>
+        <v>10.4</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -22984,52 +22974,52 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>145617</v>
+        <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>106999</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>-129036</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>-488780</v>
+        <v>5058704</v>
       </c>
       <c r="S130" t="n">
-        <v>247986</v>
+        <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>380920</v>
+        <v>0</v>
       </c>
       <c r="U130" t="n">
-        <v>62355</v>
+        <v>0</v>
       </c>
       <c r="V130" t="n">
-        <v>-780733</v>
+        <v>4973551</v>
       </c>
       <c r="W130" t="n">
-        <v>-52932</v>
+        <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>-226553</v>
+        <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>-144585</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>294153</v>
+        <v>100</v>
       </c>
       <c r="AA130" t="n">
-        <v>-49437</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>-47368</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>-46806</v>
+        <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>-2200</v>
+        <v>85053</v>
       </c>
       <c r="AE130" t="n">
         <v>22</v>
@@ -23038,42 +23028,42 @@
         <v>22</v>
       </c>
       <c r="AG130" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AH130" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI130" t="n">
         <v>0</v>
       </c>
       <c r="AJ130" t="n">
-        <v>-20</v>
+        <v>-34</v>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AL130" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="AM130" t="n">
-        <v>210</v>
+        <v>164.71</v>
       </c>
       <c r="AN130" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AO130" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
@@ -23088,29 +23078,29 @@
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、爆量、接近20日高點</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、短線籌碼止穩、5日法人賣超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、爆量、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>6147.TWO</t>
+          <t>2892.TW</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -23129,28 +23119,28 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>226</v>
+        <v>38.65</v>
       </c>
       <c r="G131" t="n">
-        <v>222.6</v>
+        <v>38.54</v>
       </c>
       <c r="H131" t="n">
-        <v>218.45</v>
+        <v>38.8</v>
       </c>
       <c r="I131" t="n">
-        <v>211.6</v>
+        <v>39.11</v>
       </c>
       <c r="J131" t="n">
-        <v>48534000</v>
+        <v>14704600</v>
       </c>
       <c r="K131" t="n">
-        <v>42631000</v>
+        <v>13952892</v>
       </c>
       <c r="L131" t="n">
-        <v>238</v>
+        <v>40.95</v>
       </c>
       <c r="M131" t="n">
-        <v>171</v>
+        <v>37.15</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -23158,52 +23148,52 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>213631</v>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>3348609</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3346311</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>13584604</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>85897</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>5207101</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>-192087</v>
       </c>
       <c r="V131" t="n">
-        <v>0</v>
+        <v>-2890074</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>129893</v>
       </c>
       <c r="X131" t="n">
-        <v>0</v>
+        <v>-1941243</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>3503517</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>16116517</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>-2159</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>82751</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>34881</v>
       </c>
       <c r="AD131" t="n">
-        <v>0</v>
+        <v>358161</v>
       </c>
       <c r="AE131" t="n">
         <v>22</v>
@@ -23212,16 +23202,16 @@
         <v>22</v>
       </c>
       <c r="AG131" t="n">
-        <v>55</v>
+        <v>-5</v>
       </c>
       <c r="AH131" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AI131" t="n">
         <v>0</v>
       </c>
       <c r="AJ131" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
@@ -23229,25 +23219,25 @@
         </is>
       </c>
       <c r="AL131" t="n">
-        <v>-2</v>
+        <v>12</v>
       </c>
       <c r="AM131" t="n">
-        <v>-8.33</v>
+        <v>120</v>
       </c>
       <c r="AN131" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AO131" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
@@ -23262,17 +23252,17 @@
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -23801,12 +23791,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2323.TW</t>
+          <t>3653.TW</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>中環</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -23816,7 +23806,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -23825,28 +23815,28 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>11</v>
+        <v>7165</v>
       </c>
       <c r="G135" t="n">
-        <v>10.83</v>
+        <v>7011</v>
       </c>
       <c r="H135" t="n">
-        <v>10.74</v>
+        <v>6895.5</v>
       </c>
       <c r="I135" t="n">
-        <v>10.75</v>
+        <v>6257</v>
       </c>
       <c r="J135" t="n">
-        <v>14064496</v>
+        <v>1628778</v>
       </c>
       <c r="K135" t="n">
-        <v>6377380</v>
+        <v>1085614</v>
       </c>
       <c r="L135" t="n">
-        <v>11.15</v>
+        <v>7440</v>
       </c>
       <c r="M135" t="n">
-        <v>10.4</v>
+        <v>5210</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -23854,52 +23844,52 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>145617</v>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>106999</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>-129036</v>
       </c>
       <c r="R135" t="n">
-        <v>5058704</v>
+        <v>-488780</v>
       </c>
       <c r="S135" t="n">
-        <v>0</v>
+        <v>247986</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>380920</v>
       </c>
       <c r="U135" t="n">
-        <v>0</v>
+        <v>62355</v>
       </c>
       <c r="V135" t="n">
-        <v>4973551</v>
+        <v>-780733</v>
       </c>
       <c r="W135" t="n">
-        <v>0</v>
+        <v>-52932</v>
       </c>
       <c r="X135" t="n">
-        <v>0</v>
+        <v>-226553</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>-144585</v>
       </c>
       <c r="Z135" t="n">
-        <v>100</v>
+        <v>294153</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>-49437</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>-47368</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>-46806</v>
       </c>
       <c r="AD135" t="n">
-        <v>85053</v>
+        <v>-2200</v>
       </c>
       <c r="AE135" t="n">
         <v>22</v>
@@ -23908,42 +23898,42 @@
         <v>22</v>
       </c>
       <c r="AG135" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AH135" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
       </c>
       <c r="AJ135" t="n">
-        <v>-34</v>
+        <v>-20</v>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AL135" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="AM135" t="n">
-        <v>164.71</v>
+        <v>210</v>
       </c>
       <c r="AN135" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AO135" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
@@ -23958,29 +23948,29 @@
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>站上5日線、爆量、接近20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、爆量、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、短線籌碼止穩、5日法人賣超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1736.TW</t>
+          <t>6147.TWO</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>喬山</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -23999,28 +23989,28 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="G136" t="n">
-        <v>122.6</v>
+        <v>222.6</v>
       </c>
       <c r="H136" t="n">
-        <v>125.05</v>
+        <v>218.45</v>
       </c>
       <c r="I136" t="n">
-        <v>125.33</v>
+        <v>211.6</v>
       </c>
       <c r="J136" t="n">
-        <v>460026</v>
+        <v>48534000</v>
       </c>
       <c r="K136" t="n">
-        <v>697276</v>
+        <v>42631000</v>
       </c>
       <c r="L136" t="n">
-        <v>133.5</v>
+        <v>238</v>
       </c>
       <c r="M136" t="n">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -24028,52 +24018,52 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>183265</v>
+        <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>182377</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>120259</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>593937</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
-        <v>181858</v>
+        <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>183858</v>
+        <v>0</v>
       </c>
       <c r="U136" t="n">
-        <v>128988</v>
+        <v>0</v>
       </c>
       <c r="V136" t="n">
-        <v>598915</v>
+        <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X136" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>-2481</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
-        <v>-9729</v>
+        <v>0</v>
       </c>
       <c r="AD136" t="n">
-        <v>-5978</v>
+        <v>0</v>
       </c>
       <c r="AE136" t="n">
         <v>22</v>
@@ -24082,16 +24072,16 @@
         <v>22</v>
       </c>
       <c r="AG136" t="n">
-        <v>-15</v>
+        <v>55</v>
       </c>
       <c r="AH136" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AI136" t="n">
         <v>0</v>
       </c>
       <c r="AJ136" t="n">
-        <v>-20</v>
+        <v>24</v>
       </c>
       <c r="AK136" t="inlineStr">
         <is>
@@ -24099,25 +24089,25 @@
         </is>
       </c>
       <c r="AL136" t="n">
-        <v>42</v>
+        <v>-2</v>
       </c>
       <c r="AM136" t="n">
-        <v>210</v>
+        <v>-8.33</v>
       </c>
       <c r="AN136" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AO136" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
@@ -24132,29 +24122,29 @@
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>1736.TW</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -24173,81 +24163,81 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>45.95</v>
+        <v>123</v>
       </c>
       <c r="G137" t="n">
-        <v>44.86</v>
+        <v>122.6</v>
       </c>
       <c r="H137" t="n">
-        <v>43.95</v>
+        <v>125.05</v>
       </c>
       <c r="I137" t="n">
-        <v>40.18</v>
+        <v>125.33</v>
       </c>
       <c r="J137" t="n">
-        <v>19354000</v>
+        <v>460026</v>
       </c>
       <c r="K137" t="n">
-        <v>8237000</v>
+        <v>697276</v>
       </c>
       <c r="L137" t="n">
-        <v>50.7</v>
+        <v>133.5</v>
       </c>
       <c r="M137" t="n">
-        <v>33.15</v>
+        <v>119</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>183265</v>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>182377</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>120259</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>593937</v>
       </c>
       <c r="S137" t="n">
-        <v>0</v>
+        <v>181858</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>183858</v>
       </c>
       <c r="U137" t="n">
-        <v>0</v>
+        <v>128988</v>
       </c>
       <c r="V137" t="n">
-        <v>0</v>
+        <v>598915</v>
       </c>
       <c r="W137" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X137" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y137" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z137" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>-2481</v>
       </c>
       <c r="AC137" t="n">
-        <v>0</v>
+        <v>-9729</v>
       </c>
       <c r="AD137" t="n">
-        <v>0</v>
+        <v>-5978</v>
       </c>
       <c r="AE137" t="n">
         <v>22</v>
@@ -24256,42 +24246,42 @@
         <v>22</v>
       </c>
       <c r="AG137" t="n">
-        <v>65</v>
+        <v>-15</v>
       </c>
       <c r="AH137" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="n">
         <v>-20</v>
       </c>
-      <c r="AJ137" t="n">
-        <v>28</v>
-      </c>
       <c r="AK137" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
       <c r="AL137" t="n">
-        <v>-6</v>
+        <v>42</v>
       </c>
       <c r="AM137" t="n">
-        <v>-21.43</v>
+        <v>210</v>
       </c>
       <c r="AN137" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="AO137" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -24306,17 +24296,17 @@
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、爆量、爆量價未漲、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -24845,17 +24835,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>00692.TW</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>富邦公司治理</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -24869,57 +24859,57 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>99</v>
+        <v>45.95</v>
       </c>
       <c r="G141" t="n">
-        <v>99.13</v>
+        <v>44.86</v>
       </c>
       <c r="H141" t="n">
-        <v>97.88</v>
+        <v>43.95</v>
       </c>
       <c r="I141" t="n">
-        <v>95.62</v>
+        <v>40.18</v>
       </c>
       <c r="J141" t="n">
-        <v>621175</v>
+        <v>19354000</v>
       </c>
       <c r="K141" t="n">
-        <v>782490</v>
+        <v>8237000</v>
       </c>
       <c r="L141" t="n">
-        <v>100.1</v>
+        <v>50.7</v>
       </c>
       <c r="M141" t="n">
-        <v>90.90000000000001</v>
+        <v>33.15</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="O141" t="n">
-        <v>-90933</v>
+        <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>511477</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>777074</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>2112826</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>-15042</v>
+        <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>-225118</v>
+        <v>0</v>
       </c>
       <c r="U141" t="n">
-        <v>74909</v>
+        <v>0</v>
       </c>
       <c r="V141" t="n">
-        <v>-59064</v>
+        <v>0</v>
       </c>
       <c r="W141" t="n">
         <v>0</v>
@@ -24934,34 +24924,34 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>-75891</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>736595</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
-        <v>702165</v>
+        <v>0</v>
       </c>
       <c r="AD141" t="n">
-        <v>2171890</v>
+        <v>0</v>
       </c>
       <c r="AE141" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF141" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG141" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AH141" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI141" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ141" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
@@ -24969,25 +24959,25 @@
         </is>
       </c>
       <c r="AL141" t="n">
-        <v>-28</v>
+        <v>-6</v>
       </c>
       <c r="AM141" t="n">
-        <v>-58.33</v>
+        <v>-21.43</v>
       </c>
       <c r="AN141" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AO141" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
@@ -25002,17 +24992,17 @@
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、爆量、爆量價未漲、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -25193,12 +25183,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1789.TW</t>
+          <t>2207.TW</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>神隆</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -25217,28 +25207,28 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>19.1</v>
+        <v>518</v>
       </c>
       <c r="G143" t="n">
-        <v>18.76</v>
+        <v>516.4</v>
       </c>
       <c r="H143" t="n">
-        <v>18.76</v>
+        <v>514.2</v>
       </c>
       <c r="I143" t="n">
-        <v>18.73</v>
+        <v>521.55</v>
       </c>
       <c r="J143" t="n">
-        <v>445648</v>
+        <v>229795</v>
       </c>
       <c r="K143" t="n">
-        <v>353517</v>
+        <v>267493</v>
       </c>
       <c r="L143" t="n">
-        <v>19.85</v>
+        <v>541</v>
       </c>
       <c r="M143" t="n">
-        <v>17.9</v>
+        <v>506</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -25246,52 +25236,52 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>90038</v>
+        <v>-9970</v>
       </c>
       <c r="P143" t="n">
-        <v>179227</v>
+        <v>206456</v>
       </c>
       <c r="Q143" t="n">
-        <v>-234383</v>
+        <v>302021</v>
       </c>
       <c r="R143" t="n">
-        <v>-183593</v>
+        <v>99038</v>
       </c>
       <c r="S143" t="n">
-        <v>90038</v>
+        <v>-12443</v>
       </c>
       <c r="T143" t="n">
-        <v>180227</v>
+        <v>203875</v>
       </c>
       <c r="U143" t="n">
-        <v>-229106</v>
+        <v>298065</v>
       </c>
       <c r="V143" t="n">
-        <v>-189407</v>
+        <v>38231</v>
       </c>
       <c r="W143" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="X143" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>-527</v>
       </c>
       <c r="AB143" t="n">
-        <v>-1000</v>
+        <v>-1419</v>
       </c>
       <c r="AC143" t="n">
-        <v>-5277</v>
+        <v>-44</v>
       </c>
       <c r="AD143" t="n">
-        <v>5814</v>
+        <v>6807</v>
       </c>
       <c r="AE143" t="n">
         <v>20</v>
@@ -25300,16 +25290,16 @@
         <v>20</v>
       </c>
       <c r="AG143" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="AH143" t="n">
-        <v>-5</v>
+        <v>40</v>
       </c>
       <c r="AI143" t="n">
         <v>0</v>
       </c>
       <c r="AJ143" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
@@ -25317,25 +25307,25 @@
         </is>
       </c>
       <c r="AL143" t="n">
-        <v>16</v>
+        <v>-16</v>
       </c>
       <c r="AM143" t="n">
-        <v>400</v>
+        <v>-44.44</v>
       </c>
       <c r="AN143" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="AO143" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
@@ -25350,17 +25340,17 @@
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、短線籌碼止穩、5日法人賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -25541,17 +25531,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2207.TW</t>
+          <t>00692.TW</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>富邦公司治理</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -25565,28 +25555,28 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>518</v>
+        <v>99</v>
       </c>
       <c r="G145" t="n">
-        <v>516.4</v>
+        <v>99.13</v>
       </c>
       <c r="H145" t="n">
-        <v>514.2</v>
+        <v>97.88</v>
       </c>
       <c r="I145" t="n">
-        <v>521.55</v>
+        <v>95.62</v>
       </c>
       <c r="J145" t="n">
-        <v>229795</v>
+        <v>621175</v>
       </c>
       <c r="K145" t="n">
-        <v>267493</v>
+        <v>782490</v>
       </c>
       <c r="L145" t="n">
-        <v>541</v>
+        <v>100.1</v>
       </c>
       <c r="M145" t="n">
-        <v>506</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -25594,52 +25584,52 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>-9970</v>
+        <v>-90933</v>
       </c>
       <c r="P145" t="n">
-        <v>206456</v>
+        <v>511477</v>
       </c>
       <c r="Q145" t="n">
-        <v>302021</v>
+        <v>777074</v>
       </c>
       <c r="R145" t="n">
-        <v>99038</v>
+        <v>2112826</v>
       </c>
       <c r="S145" t="n">
-        <v>-12443</v>
+        <v>-15042</v>
       </c>
       <c r="T145" t="n">
-        <v>203875</v>
+        <v>-225118</v>
       </c>
       <c r="U145" t="n">
-        <v>298065</v>
+        <v>74909</v>
       </c>
       <c r="V145" t="n">
-        <v>38231</v>
+        <v>-59064</v>
       </c>
       <c r="W145" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="X145" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>54000</v>
+        <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>-527</v>
+        <v>-75891</v>
       </c>
       <c r="AB145" t="n">
-        <v>-1419</v>
+        <v>736595</v>
       </c>
       <c r="AC145" t="n">
-        <v>-44</v>
+        <v>702165</v>
       </c>
       <c r="AD145" t="n">
-        <v>6807</v>
+        <v>2171890</v>
       </c>
       <c r="AE145" t="n">
         <v>20</v>
@@ -25648,16 +25638,16 @@
         <v>20</v>
       </c>
       <c r="AG145" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AH145" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AI145" t="n">
         <v>0</v>
       </c>
       <c r="AJ145" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
@@ -25665,16 +25655,16 @@
         </is>
       </c>
       <c r="AL145" t="n">
-        <v>-16</v>
+        <v>-28</v>
       </c>
       <c r="AM145" t="n">
-        <v>-44.44</v>
+        <v>-58.33</v>
       </c>
       <c r="AN145" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO145" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
@@ -25683,7 +25673,7 @@
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
@@ -25698,29 +25688,29 @@
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3680.TWO</t>
+          <t>1789.TW</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>神隆</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -25739,28 +25729,28 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>571</v>
+        <v>19.1</v>
       </c>
       <c r="G146" t="n">
-        <v>562.8</v>
+        <v>18.76</v>
       </c>
       <c r="H146" t="n">
-        <v>553.8</v>
+        <v>18.76</v>
       </c>
       <c r="I146" t="n">
-        <v>540.08</v>
+        <v>18.73</v>
       </c>
       <c r="J146" t="n">
-        <v>1165000</v>
+        <v>445648</v>
       </c>
       <c r="K146" t="n">
-        <v>1561400</v>
+        <v>353517</v>
       </c>
       <c r="L146" t="n">
-        <v>594</v>
+        <v>19.85</v>
       </c>
       <c r="M146" t="n">
-        <v>488.5</v>
+        <v>17.9</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
@@ -25768,28 +25758,28 @@
         </is>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>90038</v>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>179227</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>-234383</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>-183593</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>90038</v>
       </c>
       <c r="T146" t="n">
-        <v>0</v>
+        <v>180227</v>
       </c>
       <c r="U146" t="n">
-        <v>0</v>
+        <v>-229106</v>
       </c>
       <c r="V146" t="n">
-        <v>0</v>
+        <v>-189407</v>
       </c>
       <c r="W146" t="n">
         <v>0</v>
@@ -25807,31 +25797,31 @@
         <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AC146" t="n">
-        <v>0</v>
+        <v>-5277</v>
       </c>
       <c r="AD146" t="n">
-        <v>0</v>
+        <v>5814</v>
       </c>
       <c r="AE146" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF146" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG146" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AH146" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI146" t="n">
         <v>0</v>
       </c>
       <c r="AJ146" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
@@ -25839,50 +25829,50 @@
         </is>
       </c>
       <c r="AL146" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AM146" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AN146" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AO146" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>❌避開</t>
+          <t>⚠️整理</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>觀望</t>
+          <t>整理觀察</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人賣超</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、短線籌碼止穩、5日法人賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -26063,12 +26053,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3293.TWO</t>
+          <t>3680.TWO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -26087,28 +26077,28 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>788</v>
+        <v>571</v>
       </c>
       <c r="G148" t="n">
-        <v>786.6</v>
+        <v>562.8</v>
       </c>
       <c r="H148" t="n">
-        <v>780.4</v>
+        <v>553.8</v>
       </c>
       <c r="I148" t="n">
-        <v>745.85</v>
+        <v>540.08</v>
       </c>
       <c r="J148" t="n">
-        <v>1068000</v>
+        <v>1165000</v>
       </c>
       <c r="K148" t="n">
-        <v>1524600</v>
+        <v>1561400</v>
       </c>
       <c r="L148" t="n">
-        <v>819</v>
+        <v>594</v>
       </c>
       <c r="M148" t="n">
-        <v>687</v>
+        <v>488.5</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
@@ -26179,7 +26169,7 @@
         <v>0</v>
       </c>
       <c r="AJ148" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
@@ -26187,25 +26177,25 @@
         </is>
       </c>
       <c r="AL148" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AM148" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="AN148" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AO148" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
@@ -27455,12 +27445,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1514.TW</t>
+          <t>3293.TWO</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -27479,28 +27469,28 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>102.5</v>
+        <v>788</v>
       </c>
       <c r="G156" t="n">
-        <v>102.8</v>
+        <v>786.6</v>
       </c>
       <c r="H156" t="n">
-        <v>102.75</v>
+        <v>780.4</v>
       </c>
       <c r="I156" t="n">
-        <v>101.99</v>
+        <v>745.85</v>
       </c>
       <c r="J156" t="n">
-        <v>790867</v>
+        <v>1068000</v>
       </c>
       <c r="K156" t="n">
-        <v>1092443</v>
+        <v>1524600</v>
       </c>
       <c r="L156" t="n">
-        <v>105.5</v>
+        <v>819</v>
       </c>
       <c r="M156" t="n">
-        <v>99.40000000000001</v>
+        <v>687</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
@@ -27508,52 +27498,52 @@
         </is>
       </c>
       <c r="O156" t="n">
-        <v>-27667</v>
+        <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>412208</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>906576</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>1490858</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>-27550</v>
+        <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>403859</v>
+        <v>0</v>
       </c>
       <c r="U156" t="n">
-        <v>879850</v>
+        <v>0</v>
       </c>
       <c r="V156" t="n">
-        <v>1470510</v>
+        <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X156" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>-2117</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>-1651</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
-        <v>-3274</v>
+        <v>0</v>
       </c>
       <c r="AD156" t="n">
-        <v>-13652</v>
+        <v>0</v>
       </c>
       <c r="AE156" t="n">
         <v>18</v>
@@ -27562,16 +27552,16 @@
         <v>18</v>
       </c>
       <c r="AG156" t="n">
-        <v>-5</v>
+        <v>45</v>
       </c>
       <c r="AH156" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
       </c>
       <c r="AJ156" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
@@ -27579,25 +27569,25 @@
         </is>
       </c>
       <c r="AL156" t="n">
-        <v>-18</v>
+        <v>16</v>
       </c>
       <c r="AM156" t="n">
-        <v>-50</v>
+        <v>800</v>
       </c>
       <c r="AN156" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="AO156" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
@@ -27612,29 +27602,29 @@
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2880.TW</t>
+          <t>1514.TW</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -27653,28 +27643,28 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>45.8</v>
+        <v>102.5</v>
       </c>
       <c r="G157" t="n">
-        <v>45.52</v>
+        <v>102.8</v>
       </c>
       <c r="H157" t="n">
-        <v>45.46</v>
+        <v>102.75</v>
       </c>
       <c r="I157" t="n">
-        <v>45.95</v>
+        <v>101.99</v>
       </c>
       <c r="J157" t="n">
-        <v>8913162</v>
+        <v>790867</v>
       </c>
       <c r="K157" t="n">
-        <v>9425825</v>
+        <v>1092443</v>
       </c>
       <c r="L157" t="n">
-        <v>48.3</v>
+        <v>105.5</v>
       </c>
       <c r="M157" t="n">
-        <v>44</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
@@ -27682,87 +27672,87 @@
         </is>
       </c>
       <c r="O157" t="n">
-        <v>-1994441</v>
+        <v>-27667</v>
       </c>
       <c r="P157" t="n">
-        <v>4045062</v>
+        <v>412208</v>
       </c>
       <c r="Q157" t="n">
-        <v>4910286</v>
+        <v>906576</v>
       </c>
       <c r="R157" t="n">
-        <v>3992612</v>
+        <v>1490858</v>
       </c>
       <c r="S157" t="n">
-        <v>-3423755</v>
+        <v>-27550</v>
       </c>
       <c r="T157" t="n">
-        <v>1401733</v>
+        <v>403859</v>
       </c>
       <c r="U157" t="n">
-        <v>-1833174</v>
+        <v>879850</v>
       </c>
       <c r="V157" t="n">
-        <v>-10693226</v>
+        <v>1470510</v>
       </c>
       <c r="W157" t="n">
-        <v>21595</v>
+        <v>2000</v>
       </c>
       <c r="X157" t="n">
-        <v>-61150</v>
+        <v>10000</v>
       </c>
       <c r="Y157" t="n">
-        <v>1781445</v>
+        <v>30000</v>
       </c>
       <c r="Z157" t="n">
-        <v>4707445</v>
+        <v>34000</v>
       </c>
       <c r="AA157" t="n">
-        <v>1407719</v>
+        <v>-2117</v>
       </c>
       <c r="AB157" t="n">
-        <v>2704479</v>
+        <v>-1651</v>
       </c>
       <c r="AC157" t="n">
-        <v>4962015</v>
+        <v>-3274</v>
       </c>
       <c r="AD157" t="n">
-        <v>9978393</v>
+        <v>-13652</v>
       </c>
       <c r="AE157" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF157" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AG157" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AL157" t="n">
+        <v>-18</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AN157" t="n">
         <v>10</v>
       </c>
-      <c r="AH157" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ157" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AL157" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AM157" t="n">
-        <v>-38.46</v>
-      </c>
-      <c r="AN157" t="n">
-        <v>15</v>
-      </c>
       <c r="AO157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
@@ -27771,7 +27761,7 @@
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
@@ -27786,17 +27776,17 @@
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -27977,12 +27967,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2880.TW</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -28001,28 +27991,28 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>202</v>
+        <v>45.8</v>
       </c>
       <c r="G159" t="n">
-        <v>210.6</v>
+        <v>45.52</v>
       </c>
       <c r="H159" t="n">
-        <v>209.7</v>
+        <v>45.46</v>
       </c>
       <c r="I159" t="n">
-        <v>195.07</v>
+        <v>45.95</v>
       </c>
       <c r="J159" t="n">
-        <v>3361860</v>
+        <v>8913162</v>
       </c>
       <c r="K159" t="n">
-        <v>4379258</v>
+        <v>9425825</v>
       </c>
       <c r="L159" t="n">
-        <v>223.5</v>
+        <v>48.3</v>
       </c>
       <c r="M159" t="n">
-        <v>165</v>
+        <v>44</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
@@ -28030,61 +28020,61 @@
         </is>
       </c>
       <c r="O159" t="n">
-        <v>-353007</v>
+        <v>-1994441</v>
       </c>
       <c r="P159" t="n">
-        <v>1142596</v>
+        <v>4045062</v>
       </c>
       <c r="Q159" t="n">
-        <v>4129551</v>
+        <v>4910286</v>
       </c>
       <c r="R159" t="n">
-        <v>8237526</v>
+        <v>3992612</v>
       </c>
       <c r="S159" t="n">
-        <v>-225985</v>
+        <v>-3423755</v>
       </c>
       <c r="T159" t="n">
-        <v>1261253</v>
+        <v>1401733</v>
       </c>
       <c r="U159" t="n">
-        <v>4021309</v>
+        <v>-1833174</v>
       </c>
       <c r="V159" t="n">
-        <v>7950434</v>
+        <v>-10693226</v>
       </c>
       <c r="W159" t="n">
-        <v>0</v>
+        <v>21595</v>
       </c>
       <c r="X159" t="n">
-        <v>0</v>
+        <v>-61150</v>
       </c>
       <c r="Y159" t="n">
-        <v>0</v>
+        <v>1781445</v>
       </c>
       <c r="Z159" t="n">
-        <v>-8000</v>
+        <v>4707445</v>
       </c>
       <c r="AA159" t="n">
-        <v>-127022</v>
+        <v>1407719</v>
       </c>
       <c r="AB159" t="n">
-        <v>-118657</v>
+        <v>2704479</v>
       </c>
       <c r="AC159" t="n">
-        <v>108242</v>
+        <v>4962015</v>
       </c>
       <c r="AD159" t="n">
-        <v>295092</v>
+        <v>9978393</v>
       </c>
       <c r="AE159" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF159" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG159" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AH159" t="n">
         <v>30</v>
@@ -28101,16 +28091,16 @@
         </is>
       </c>
       <c r="AL159" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AM159" t="n">
-        <v>-46.15</v>
+        <v>-38.46</v>
       </c>
       <c r="AN159" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AO159" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
@@ -28119,7 +28109,7 @@
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
@@ -28134,17 +28124,17 @@
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -28673,12 +28663,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2534.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>宏盛</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -28697,28 +28687,28 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>16.65</v>
+        <v>202</v>
       </c>
       <c r="G163" t="n">
-        <v>16.62</v>
+        <v>210.6</v>
       </c>
       <c r="H163" t="n">
-        <v>16.74</v>
+        <v>209.7</v>
       </c>
       <c r="I163" t="n">
-        <v>16.81</v>
+        <v>195.07</v>
       </c>
       <c r="J163" t="n">
-        <v>137378</v>
+        <v>3361860</v>
       </c>
       <c r="K163" t="n">
-        <v>222456</v>
+        <v>4379258</v>
       </c>
       <c r="L163" t="n">
-        <v>17.35</v>
+        <v>223.5</v>
       </c>
       <c r="M163" t="n">
-        <v>16.5</v>
+        <v>165</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
@@ -28726,28 +28716,28 @@
         </is>
       </c>
       <c r="O163" t="n">
-        <v>45000</v>
+        <v>-353007</v>
       </c>
       <c r="P163" t="n">
-        <v>17013</v>
+        <v>1142596</v>
       </c>
       <c r="Q163" t="n">
-        <v>148113</v>
+        <v>4129551</v>
       </c>
       <c r="R163" t="n">
-        <v>411693</v>
+        <v>8237526</v>
       </c>
       <c r="S163" t="n">
-        <v>45000</v>
+        <v>-225985</v>
       </c>
       <c r="T163" t="n">
-        <v>17013</v>
+        <v>1261253</v>
       </c>
       <c r="U163" t="n">
-        <v>148113</v>
+        <v>4021309</v>
       </c>
       <c r="V163" t="n">
-        <v>411051</v>
+        <v>7950434</v>
       </c>
       <c r="W163" t="n">
         <v>0</v>
@@ -28759,19 +28749,19 @@
         <v>0</v>
       </c>
       <c r="Z163" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>-127022</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>-118657</v>
       </c>
       <c r="AC163" t="n">
-        <v>0</v>
+        <v>108242</v>
       </c>
       <c r="AD163" t="n">
-        <v>642</v>
+        <v>295092</v>
       </c>
       <c r="AE163" t="n">
         <v>14</v>
@@ -28780,16 +28770,16 @@
         <v>14</v>
       </c>
       <c r="AG163" t="n">
-        <v>-15</v>
+        <v>5</v>
       </c>
       <c r="AH163" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>
       </c>
       <c r="AJ163" t="n">
-        <v>-2</v>
+        <v>26</v>
       </c>
       <c r="AK163" t="inlineStr">
         <is>
@@ -28797,25 +28787,25 @@
         </is>
       </c>
       <c r="AL163" t="n">
-        <v>16</v>
+        <v>-12</v>
       </c>
       <c r="AM163" t="n">
-        <v>800</v>
+        <v>-46.15</v>
       </c>
       <c r="AN163" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="AO163" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
@@ -28830,29 +28820,29 @@
       </c>
       <c r="AT163" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>2534.TW</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>宏盛</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -28871,28 +28861,28 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>44.5</v>
+        <v>16.65</v>
       </c>
       <c r="G164" t="n">
-        <v>45.05</v>
+        <v>16.62</v>
       </c>
       <c r="H164" t="n">
-        <v>44.7</v>
+        <v>16.74</v>
       </c>
       <c r="I164" t="n">
-        <v>43.69</v>
+        <v>16.81</v>
       </c>
       <c r="J164" t="n">
-        <v>4606023</v>
+        <v>137378</v>
       </c>
       <c r="K164" t="n">
-        <v>3258705</v>
+        <v>222456</v>
       </c>
       <c r="L164" t="n">
-        <v>46.25</v>
+        <v>17.35</v>
       </c>
       <c r="M164" t="n">
-        <v>40.9</v>
+        <v>16.5</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
@@ -28900,28 +28890,28 @@
         </is>
       </c>
       <c r="O164" t="n">
-        <v>-1417282</v>
+        <v>45000</v>
       </c>
       <c r="P164" t="n">
-        <v>220038</v>
+        <v>17013</v>
       </c>
       <c r="Q164" t="n">
-        <v>295456</v>
+        <v>148113</v>
       </c>
       <c r="R164" t="n">
-        <v>1198593</v>
+        <v>411693</v>
       </c>
       <c r="S164" t="n">
-        <v>-1376396</v>
+        <v>45000</v>
       </c>
       <c r="T164" t="n">
-        <v>276091</v>
+        <v>17013</v>
       </c>
       <c r="U164" t="n">
-        <v>365036</v>
+        <v>148113</v>
       </c>
       <c r="V164" t="n">
-        <v>1279950</v>
+        <v>411051</v>
       </c>
       <c r="W164" t="n">
         <v>0</v>
@@ -28936,16 +28926,16 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>-40886</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>-56053</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
-        <v>-69580</v>
+        <v>0</v>
       </c>
       <c r="AD164" t="n">
-        <v>-81357</v>
+        <v>642</v>
       </c>
       <c r="AE164" t="n">
         <v>14</v>
@@ -28954,16 +28944,16 @@
         <v>14</v>
       </c>
       <c r="AG164" t="n">
-        <v>15</v>
+        <v>-15</v>
       </c>
       <c r="AH164" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AI164" t="n">
         <v>0</v>
       </c>
       <c r="AJ164" t="n">
-        <v>48</v>
+        <v>-2</v>
       </c>
       <c r="AK164" t="inlineStr">
         <is>
@@ -28971,25 +28961,25 @@
         </is>
       </c>
       <c r="AL164" t="n">
-        <v>-34</v>
+        <v>16</v>
       </c>
       <c r="AM164" t="n">
-        <v>-70.83</v>
+        <v>800</v>
       </c>
       <c r="AN164" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AO164" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
@@ -29004,17 +28994,17 @@
       </c>
       <c r="AT164" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -29195,12 +29185,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>6202.TW</t>
+          <t>4123.TWO</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>晟德</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -29219,28 +29209,28 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>58.9</v>
+        <v>31.35</v>
       </c>
       <c r="G166" t="n">
-        <v>60.88</v>
+        <v>31.06</v>
       </c>
       <c r="H166" t="n">
-        <v>59.87</v>
+        <v>31.13</v>
       </c>
       <c r="I166" t="n">
-        <v>57.8</v>
+        <v>30.87</v>
       </c>
       <c r="J166" t="n">
-        <v>1845781</v>
+        <v>1334000</v>
       </c>
       <c r="K166" t="n">
-        <v>2779674</v>
+        <v>1170800</v>
       </c>
       <c r="L166" t="n">
-        <v>64.09999999999999</v>
+        <v>31.5</v>
       </c>
       <c r="M166" t="n">
-        <v>53.5</v>
+        <v>30</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
@@ -29248,28 +29238,28 @@
         </is>
       </c>
       <c r="O166" t="n">
-        <v>-542874</v>
+        <v>0</v>
       </c>
       <c r="P166" t="n">
-        <v>100494</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>715158</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>652773</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>-531428</v>
+        <v>0</v>
       </c>
       <c r="T166" t="n">
-        <v>141161</v>
+        <v>0</v>
       </c>
       <c r="U166" t="n">
-        <v>694345</v>
+        <v>0</v>
       </c>
       <c r="V166" t="n">
-        <v>567457</v>
+        <v>0</v>
       </c>
       <c r="W166" t="n">
         <v>0</v>
@@ -29281,19 +29271,19 @@
         <v>0</v>
       </c>
       <c r="Z166" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>-11446</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>-40667</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
-        <v>20813</v>
+        <v>0</v>
       </c>
       <c r="AD166" t="n">
-        <v>35316</v>
+        <v>0</v>
       </c>
       <c r="AE166" t="n">
         <v>14</v>
@@ -29302,16 +29292,16 @@
         <v>14</v>
       </c>
       <c r="AG166" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="AH166" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI166" t="n">
         <v>0</v>
       </c>
       <c r="AJ166" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AK166" t="inlineStr">
         <is>
@@ -29319,16 +29309,16 @@
         </is>
       </c>
       <c r="AL166" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AM166" t="n">
-        <v>-46.15</v>
+        <v>0</v>
       </c>
       <c r="AN166" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AO166" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
@@ -29337,7 +29327,7 @@
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
@@ -29352,17 +29342,17 @@
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、接近20日高點、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -29543,12 +29533,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>4123.TWO</t>
+          <t>2329.TW</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -29567,28 +29557,28 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>31.35</v>
+        <v>44.5</v>
       </c>
       <c r="G168" t="n">
-        <v>31.06</v>
+        <v>45.05</v>
       </c>
       <c r="H168" t="n">
-        <v>31.13</v>
+        <v>44.7</v>
       </c>
       <c r="I168" t="n">
-        <v>30.87</v>
+        <v>43.69</v>
       </c>
       <c r="J168" t="n">
-        <v>1334000</v>
+        <v>4606023</v>
       </c>
       <c r="K168" t="n">
-        <v>1170800</v>
+        <v>3258705</v>
       </c>
       <c r="L168" t="n">
-        <v>31.5</v>
+        <v>46.25</v>
       </c>
       <c r="M168" t="n">
-        <v>30</v>
+        <v>40.9</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -29596,28 +29586,28 @@
         </is>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>-1417282</v>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>220038</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>295456</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>1198593</v>
       </c>
       <c r="S168" t="n">
-        <v>0</v>
+        <v>-1376396</v>
       </c>
       <c r="T168" t="n">
-        <v>0</v>
+        <v>276091</v>
       </c>
       <c r="U168" t="n">
-        <v>0</v>
+        <v>365036</v>
       </c>
       <c r="V168" t="n">
-        <v>0</v>
+        <v>1279950</v>
       </c>
       <c r="W168" t="n">
         <v>0</v>
@@ -29632,16 +29622,16 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>-40886</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>-56053</v>
       </c>
       <c r="AC168" t="n">
-        <v>0</v>
+        <v>-69580</v>
       </c>
       <c r="AD168" t="n">
-        <v>0</v>
+        <v>-81357</v>
       </c>
       <c r="AE168" t="n">
         <v>14</v>
@@ -29650,16 +29640,16 @@
         <v>14</v>
       </c>
       <c r="AG168" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AH168" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI168" t="n">
         <v>0</v>
       </c>
       <c r="AJ168" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="AK168" t="inlineStr">
         <is>
@@ -29667,10 +29657,10 @@
         </is>
       </c>
       <c r="AL168" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="AM168" t="n">
-        <v>0</v>
+        <v>-70.83</v>
       </c>
       <c r="AN168" t="n">
         <v>25</v>
@@ -29685,7 +29675,7 @@
       </c>
       <c r="AQ168" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR168" t="inlineStr">
@@ -29700,17 +29690,17 @@
       </c>
       <c r="AT168" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、接近20日高點、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -30239,12 +30229,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>6202.TW</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -30263,28 +30253,28 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>177</v>
+        <v>58.9</v>
       </c>
       <c r="G172" t="n">
-        <v>178.8</v>
+        <v>60.88</v>
       </c>
       <c r="H172" t="n">
-        <v>177.15</v>
+        <v>59.87</v>
       </c>
       <c r="I172" t="n">
-        <v>174.43</v>
+        <v>57.8</v>
       </c>
       <c r="J172" t="n">
-        <v>70323153</v>
+        <v>1845781</v>
       </c>
       <c r="K172" t="n">
-        <v>71564064</v>
+        <v>2779674</v>
       </c>
       <c r="L172" t="n">
-        <v>190.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M172" t="n">
-        <v>158.5</v>
+        <v>53.5</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
@@ -30292,52 +30282,52 @@
         </is>
       </c>
       <c r="O172" t="n">
-        <v>-14590377</v>
+        <v>-542874</v>
       </c>
       <c r="P172" t="n">
-        <v>-5500799</v>
+        <v>100494</v>
       </c>
       <c r="Q172" t="n">
-        <v>8208577</v>
+        <v>715158</v>
       </c>
       <c r="R172" t="n">
-        <v>59770154</v>
+        <v>652773</v>
       </c>
       <c r="S172" t="n">
-        <v>-14220689</v>
+        <v>-531428</v>
       </c>
       <c r="T172" t="n">
-        <v>13596778</v>
+        <v>141161</v>
       </c>
       <c r="U172" t="n">
-        <v>37785539</v>
+        <v>694345</v>
       </c>
       <c r="V172" t="n">
-        <v>91976442</v>
+        <v>567457</v>
       </c>
       <c r="W172" t="n">
-        <v>-250134</v>
+        <v>0</v>
       </c>
       <c r="X172" t="n">
-        <v>-18344140</v>
+        <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>-30416415</v>
+        <v>0</v>
       </c>
       <c r="Z172" t="n">
-        <v>-36352416</v>
+        <v>50000</v>
       </c>
       <c r="AA172" t="n">
-        <v>-119554</v>
+        <v>-11446</v>
       </c>
       <c r="AB172" t="n">
-        <v>-753437</v>
+        <v>-40667</v>
       </c>
       <c r="AC172" t="n">
-        <v>839453</v>
+        <v>20813</v>
       </c>
       <c r="AD172" t="n">
-        <v>4146128</v>
+        <v>35316</v>
       </c>
       <c r="AE172" t="n">
         <v>14</v>
@@ -30355,7 +30345,7 @@
         <v>0</v>
       </c>
       <c r="AJ172" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AK172" t="inlineStr">
         <is>
@@ -30363,10 +30353,10 @@
         </is>
       </c>
       <c r="AL172" t="n">
-        <v>-28</v>
+        <v>-12</v>
       </c>
       <c r="AM172" t="n">
-        <v>-66.67</v>
+        <v>-46.15</v>
       </c>
       <c r="AN172" t="n">
         <v>10</v>
@@ -30401,12 +30391,12 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -30587,12 +30577,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>3047.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>訊舟</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -30611,28 +30601,28 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>14.35</v>
+        <v>177</v>
       </c>
       <c r="G174" t="n">
-        <v>14.45</v>
+        <v>178.8</v>
       </c>
       <c r="H174" t="n">
-        <v>14.53</v>
+        <v>177.15</v>
       </c>
       <c r="I174" t="n">
-        <v>14.22</v>
+        <v>174.43</v>
       </c>
       <c r="J174" t="n">
-        <v>323561</v>
+        <v>70323153</v>
       </c>
       <c r="K174" t="n">
-        <v>453484</v>
+        <v>71564064</v>
       </c>
       <c r="L174" t="n">
-        <v>15.3</v>
+        <v>190.5</v>
       </c>
       <c r="M174" t="n">
-        <v>13.3</v>
+        <v>158.5</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
@@ -30640,70 +30630,70 @@
         </is>
       </c>
       <c r="O174" t="n">
-        <v>56314</v>
+        <v>-14590377</v>
       </c>
       <c r="P174" t="n">
-        <v>188880</v>
+        <v>-5500799</v>
       </c>
       <c r="Q174" t="n">
-        <v>160403</v>
+        <v>8208577</v>
       </c>
       <c r="R174" t="n">
-        <v>478373</v>
+        <v>59770154</v>
       </c>
       <c r="S174" t="n">
-        <v>56270</v>
+        <v>-14220689</v>
       </c>
       <c r="T174" t="n">
-        <v>191836</v>
+        <v>13596778</v>
       </c>
       <c r="U174" t="n">
-        <v>163836</v>
+        <v>37785539</v>
       </c>
       <c r="V174" t="n">
-        <v>467288</v>
+        <v>91976442</v>
       </c>
       <c r="W174" t="n">
-        <v>0</v>
+        <v>-250134</v>
       </c>
       <c r="X174" t="n">
-        <v>0</v>
+        <v>-18344140</v>
       </c>
       <c r="Y174" t="n">
-        <v>0</v>
+        <v>-30416415</v>
       </c>
       <c r="Z174" t="n">
-        <v>0</v>
+        <v>-36352416</v>
       </c>
       <c r="AA174" t="n">
-        <v>44</v>
+        <v>-119554</v>
       </c>
       <c r="AB174" t="n">
-        <v>-2956</v>
+        <v>-753437</v>
       </c>
       <c r="AC174" t="n">
-        <v>-3433</v>
+        <v>839453</v>
       </c>
       <c r="AD174" t="n">
-        <v>11085</v>
+        <v>4146128</v>
       </c>
       <c r="AE174" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF174" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG174" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="AH174" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI174" t="n">
         <v>0</v>
       </c>
       <c r="AJ174" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
@@ -30711,16 +30701,16 @@
         </is>
       </c>
       <c r="AL174" t="n">
-        <v>4</v>
+        <v>-28</v>
       </c>
       <c r="AM174" t="n">
-        <v>50</v>
+        <v>-66.67</v>
       </c>
       <c r="AN174" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AO174" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
@@ -30729,7 +30719,7 @@
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
@@ -30744,17 +30734,17 @@
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -31457,17 +31447,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>00900.TW</t>
+          <t>3047.TW</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>富邦特選高股息30</t>
+          <t>訊舟</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -31481,28 +31471,28 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>19.52</v>
+        <v>14.35</v>
       </c>
       <c r="G179" t="n">
-        <v>19.54</v>
+        <v>14.45</v>
       </c>
       <c r="H179" t="n">
-        <v>19.5</v>
+        <v>14.53</v>
       </c>
       <c r="I179" t="n">
-        <v>19.58</v>
+        <v>14.22</v>
       </c>
       <c r="J179" t="n">
-        <v>1903209</v>
+        <v>323561</v>
       </c>
       <c r="K179" t="n">
-        <v>5191611</v>
+        <v>453484</v>
       </c>
       <c r="L179" t="n">
-        <v>19.93</v>
+        <v>15.3</v>
       </c>
       <c r="M179" t="n">
-        <v>19.19</v>
+        <v>13.3</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
@@ -31510,28 +31500,28 @@
         </is>
       </c>
       <c r="O179" t="n">
-        <v>465457</v>
+        <v>56314</v>
       </c>
       <c r="P179" t="n">
-        <v>11553952</v>
+        <v>188880</v>
       </c>
       <c r="Q179" t="n">
-        <v>19730399</v>
+        <v>160403</v>
       </c>
       <c r="R179" t="n">
-        <v>28711947</v>
+        <v>478373</v>
       </c>
       <c r="S179" t="n">
-        <v>470000</v>
+        <v>56270</v>
       </c>
       <c r="T179" t="n">
-        <v>4461000</v>
+        <v>191836</v>
       </c>
       <c r="U179" t="n">
-        <v>9251215</v>
+        <v>163836</v>
       </c>
       <c r="V179" t="n">
-        <v>13887326</v>
+        <v>467288</v>
       </c>
       <c r="W179" t="n">
         <v>0</v>
@@ -31546,16 +31536,16 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>-4543</v>
+        <v>44</v>
       </c>
       <c r="AB179" t="n">
-        <v>7092952</v>
+        <v>-2956</v>
       </c>
       <c r="AC179" t="n">
-        <v>10479184</v>
+        <v>-3433</v>
       </c>
       <c r="AD179" t="n">
-        <v>14824621</v>
+        <v>11085</v>
       </c>
       <c r="AE179" t="n">
         <v>12</v>
@@ -31564,16 +31554,16 @@
         <v>12</v>
       </c>
       <c r="AG179" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="AH179" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI179" t="n">
         <v>0</v>
       </c>
       <c r="AJ179" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
@@ -31581,16 +31571,16 @@
         </is>
       </c>
       <c r="AL179" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="AM179" t="n">
-        <v>-57.14</v>
+        <v>50</v>
       </c>
       <c r="AN179" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO179" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
@@ -31599,7 +31589,7 @@
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
@@ -31614,17 +31604,17 @@
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -32153,17 +32143,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2379.TW</t>
+          <t>00900.TW</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>富邦特選高股息30</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -32177,28 +32167,28 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>749</v>
+        <v>19.52</v>
       </c>
       <c r="G183" t="n">
-        <v>750.8</v>
+        <v>19.54</v>
       </c>
       <c r="H183" t="n">
-        <v>754.6</v>
+        <v>19.5</v>
       </c>
       <c r="I183" t="n">
-        <v>736.2</v>
+        <v>19.58</v>
       </c>
       <c r="J183" t="n">
-        <v>1176621</v>
+        <v>1903209</v>
       </c>
       <c r="K183" t="n">
-        <v>1578286</v>
+        <v>5191611</v>
       </c>
       <c r="L183" t="n">
-        <v>794</v>
+        <v>19.93</v>
       </c>
       <c r="M183" t="n">
-        <v>686</v>
+        <v>19.19</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
@@ -32206,52 +32196,52 @@
         </is>
       </c>
       <c r="O183" t="n">
-        <v>267564</v>
+        <v>465457</v>
       </c>
       <c r="P183" t="n">
-        <v>327556</v>
+        <v>11553952</v>
       </c>
       <c r="Q183" t="n">
-        <v>366836</v>
+        <v>19730399</v>
       </c>
       <c r="R183" t="n">
-        <v>3533426</v>
+        <v>28711947</v>
       </c>
       <c r="S183" t="n">
-        <v>95044</v>
+        <v>470000</v>
       </c>
       <c r="T183" t="n">
-        <v>-90262</v>
+        <v>4461000</v>
       </c>
       <c r="U183" t="n">
-        <v>-357986</v>
+        <v>9251215</v>
       </c>
       <c r="V183" t="n">
-        <v>1508664</v>
+        <v>13887326</v>
       </c>
       <c r="W183" t="n">
-        <v>127000</v>
+        <v>0</v>
       </c>
       <c r="X183" t="n">
-        <v>338000</v>
+        <v>0</v>
       </c>
       <c r="Y183" t="n">
-        <v>547228</v>
+        <v>0</v>
       </c>
       <c r="Z183" t="n">
-        <v>1746228</v>
+        <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>45520</v>
+        <v>-4543</v>
       </c>
       <c r="AB183" t="n">
-        <v>79818</v>
+        <v>7092952</v>
       </c>
       <c r="AC183" t="n">
-        <v>177594</v>
+        <v>10479184</v>
       </c>
       <c r="AD183" t="n">
-        <v>278534</v>
+        <v>14824621</v>
       </c>
       <c r="AE183" t="n">
         <v>12</v>
@@ -32260,16 +32250,16 @@
         <v>12</v>
       </c>
       <c r="AG183" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="AH183" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AI183" t="n">
         <v>0</v>
       </c>
       <c r="AJ183" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AK183" t="inlineStr">
         <is>
@@ -32277,16 +32267,16 @@
         </is>
       </c>
       <c r="AL183" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AM183" t="n">
-        <v>0</v>
+        <v>-57.14</v>
       </c>
       <c r="AN183" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AO183" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
@@ -32295,7 +32285,7 @@
       </c>
       <c r="AQ183" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR183" t="inlineStr">
@@ -32310,17 +32300,17 @@
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -32501,12 +32491,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3019.TW</t>
+          <t>2379.TW</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -32525,28 +32515,28 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>137</v>
+        <v>749</v>
       </c>
       <c r="G185" t="n">
-        <v>139.3</v>
+        <v>750.8</v>
       </c>
       <c r="H185" t="n">
-        <v>137.55</v>
+        <v>754.6</v>
       </c>
       <c r="I185" t="n">
-        <v>137.12</v>
+        <v>736.2</v>
       </c>
       <c r="J185" t="n">
-        <v>1612834</v>
+        <v>1176621</v>
       </c>
       <c r="K185" t="n">
-        <v>2779824</v>
+        <v>1578286</v>
       </c>
       <c r="L185" t="n">
-        <v>143.5</v>
+        <v>794</v>
       </c>
       <c r="M185" t="n">
-        <v>131</v>
+        <v>686</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
@@ -32554,70 +32544,70 @@
         </is>
       </c>
       <c r="O185" t="n">
-        <v>-110141</v>
+        <v>267564</v>
       </c>
       <c r="P185" t="n">
-        <v>542047</v>
+        <v>327556</v>
       </c>
       <c r="Q185" t="n">
-        <v>2484485</v>
+        <v>366836</v>
       </c>
       <c r="R185" t="n">
-        <v>-166408</v>
+        <v>3533426</v>
       </c>
       <c r="S185" t="n">
-        <v>41453</v>
+        <v>95044</v>
       </c>
       <c r="T185" t="n">
-        <v>702911</v>
+        <v>-90262</v>
       </c>
       <c r="U185" t="n">
-        <v>2349418</v>
+        <v>-357986</v>
       </c>
       <c r="V185" t="n">
-        <v>-289093</v>
+        <v>1508664</v>
       </c>
       <c r="W185" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="X185" t="n">
-        <v>0</v>
+        <v>338000</v>
       </c>
       <c r="Y185" t="n">
-        <v>0</v>
+        <v>547228</v>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>1746228</v>
       </c>
       <c r="AA185" t="n">
-        <v>-151594</v>
+        <v>45520</v>
       </c>
       <c r="AB185" t="n">
-        <v>-160864</v>
+        <v>79818</v>
       </c>
       <c r="AC185" t="n">
-        <v>135067</v>
+        <v>177594</v>
       </c>
       <c r="AD185" t="n">
-        <v>122685</v>
+        <v>278534</v>
       </c>
       <c r="AE185" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF185" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG185" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="AH185" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI185" t="n">
         <v>0</v>
       </c>
       <c r="AJ185" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
@@ -32625,16 +32615,16 @@
         </is>
       </c>
       <c r="AL185" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AM185" t="n">
-        <v>-66.67</v>
+        <v>0</v>
       </c>
       <c r="AN185" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AO185" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
@@ -32643,7 +32633,7 @@
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
@@ -32658,17 +32648,17 @@
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -33371,12 +33361,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2006.TW</t>
+          <t>3019.TW</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>亞光</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -33395,28 +33385,28 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>85.3</v>
+        <v>137</v>
       </c>
       <c r="G190" t="n">
-        <v>86.04000000000001</v>
+        <v>139.3</v>
       </c>
       <c r="H190" t="n">
-        <v>85.92</v>
+        <v>137.55</v>
       </c>
       <c r="I190" t="n">
-        <v>84.53</v>
+        <v>137.12</v>
       </c>
       <c r="J190" t="n">
-        <v>761729</v>
+        <v>1612834</v>
       </c>
       <c r="K190" t="n">
-        <v>1016472</v>
+        <v>2779824</v>
       </c>
       <c r="L190" t="n">
-        <v>89</v>
+        <v>143.5</v>
       </c>
       <c r="M190" t="n">
-        <v>80.59999999999999</v>
+        <v>131</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
@@ -33424,52 +33414,52 @@
         </is>
       </c>
       <c r="O190" t="n">
-        <v>-152663</v>
+        <v>-110141</v>
       </c>
       <c r="P190" t="n">
-        <v>-106587</v>
+        <v>542047</v>
       </c>
       <c r="Q190" t="n">
-        <v>244906</v>
+        <v>2484485</v>
       </c>
       <c r="R190" t="n">
-        <v>107984</v>
+        <v>-166408</v>
       </c>
       <c r="S190" t="n">
-        <v>-181652</v>
+        <v>41453</v>
       </c>
       <c r="T190" t="n">
-        <v>517016</v>
+        <v>702911</v>
       </c>
       <c r="U190" t="n">
-        <v>838195</v>
+        <v>2349418</v>
       </c>
       <c r="V190" t="n">
-        <v>567823</v>
+        <v>-289093</v>
       </c>
       <c r="W190" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="X190" t="n">
-        <v>-698259</v>
+        <v>0</v>
       </c>
       <c r="Y190" t="n">
-        <v>-702517</v>
+        <v>0</v>
       </c>
       <c r="Z190" t="n">
-        <v>-581033</v>
+        <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>24989</v>
+        <v>-151594</v>
       </c>
       <c r="AB190" t="n">
-        <v>74656</v>
+        <v>-160864</v>
       </c>
       <c r="AC190" t="n">
-        <v>109228</v>
+        <v>135067</v>
       </c>
       <c r="AD190" t="n">
-        <v>121194</v>
+        <v>122685</v>
       </c>
       <c r="AE190" t="n">
         <v>10</v>
@@ -33478,16 +33468,16 @@
         <v>10</v>
       </c>
       <c r="AG190" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AH190" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AI190" t="n">
         <v>0</v>
       </c>
       <c r="AJ190" t="n">
-        <v>-8</v>
+        <v>30</v>
       </c>
       <c r="AK190" t="inlineStr">
         <is>
@@ -33495,25 +33485,25 @@
         </is>
       </c>
       <c r="AL190" t="n">
-        <v>18</v>
+        <v>-20</v>
       </c>
       <c r="AM190" t="n">
-        <v>225</v>
+        <v>-66.67</v>
       </c>
       <c r="AN190" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AO190" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
@@ -33528,29 +33518,29 @@
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3048.TW</t>
+          <t>2006.TW</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>益登</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -33569,99 +33559,99 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>57</v>
+        <v>85.3</v>
       </c>
       <c r="G191" t="n">
-        <v>54.2</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="H191" t="n">
-        <v>52.89</v>
+        <v>85.92</v>
       </c>
       <c r="I191" t="n">
-        <v>51.75</v>
+        <v>84.53</v>
       </c>
       <c r="J191" t="n">
-        <v>12195758</v>
+        <v>761729</v>
       </c>
       <c r="K191" t="n">
-        <v>4430341</v>
+        <v>1016472</v>
       </c>
       <c r="L191" t="n">
-        <v>58.3</v>
+        <v>89</v>
       </c>
       <c r="M191" t="n">
-        <v>49.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O191" t="n">
-        <v>-1681590</v>
+        <v>-152663</v>
       </c>
       <c r="P191" t="n">
-        <v>-1667794</v>
+        <v>-106587</v>
       </c>
       <c r="Q191" t="n">
-        <v>-3002370</v>
+        <v>244906</v>
       </c>
       <c r="R191" t="n">
-        <v>-3370707</v>
+        <v>107984</v>
       </c>
       <c r="S191" t="n">
-        <v>-1845911</v>
+        <v>-181652</v>
       </c>
       <c r="T191" t="n">
-        <v>-1921114</v>
+        <v>517016</v>
       </c>
       <c r="U191" t="n">
-        <v>-3413893</v>
+        <v>838195</v>
       </c>
       <c r="V191" t="n">
-        <v>-3775830</v>
+        <v>567823</v>
       </c>
       <c r="W191" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="X191" t="n">
-        <v>0</v>
+        <v>-698259</v>
       </c>
       <c r="Y191" t="n">
-        <v>0</v>
+        <v>-702517</v>
       </c>
       <c r="Z191" t="n">
-        <v>0</v>
+        <v>-581033</v>
       </c>
       <c r="AA191" t="n">
-        <v>164321</v>
+        <v>24989</v>
       </c>
       <c r="AB191" t="n">
-        <v>253320</v>
+        <v>74656</v>
       </c>
       <c r="AC191" t="n">
-        <v>411523</v>
+        <v>109228</v>
       </c>
       <c r="AD191" t="n">
-        <v>405123</v>
+        <v>121194</v>
       </c>
       <c r="AE191" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF191" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG191" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="AH191" t="n">
-        <v>-55</v>
+        <v>20</v>
       </c>
       <c r="AI191" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AJ191" t="n">
-        <v>12</v>
+        <v>-8</v>
       </c>
       <c r="AK191" t="inlineStr">
         <is>
@@ -33669,25 +33659,25 @@
         </is>
       </c>
       <c r="AL191" t="n">
-        <v>-3</v>
+        <v>18</v>
       </c>
       <c r="AM191" t="n">
-        <v>-25</v>
+        <v>225</v>
       </c>
       <c r="AN191" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AO191" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、爆量後不追價、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
@@ -33702,29 +33692,29 @@
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1810.TW</t>
+          <t>3048.TW</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>和成</t>
+          <t>益登</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -33743,57 +33733,57 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>23.4</v>
+        <v>57</v>
       </c>
       <c r="G192" t="n">
-        <v>23.59</v>
+        <v>54.2</v>
       </c>
       <c r="H192" t="n">
-        <v>23.79</v>
+        <v>52.89</v>
       </c>
       <c r="I192" t="n">
-        <v>23.77</v>
+        <v>51.75</v>
       </c>
       <c r="J192" t="n">
-        <v>939503</v>
+        <v>12195758</v>
       </c>
       <c r="K192" t="n">
-        <v>1154906</v>
+        <v>4430341</v>
       </c>
       <c r="L192" t="n">
-        <v>24.6</v>
+        <v>58.3</v>
       </c>
       <c r="M192" t="n">
-        <v>23.2</v>
+        <v>49.3</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="O192" t="n">
-        <v>282188</v>
+        <v>-1681590</v>
       </c>
       <c r="P192" t="n">
-        <v>248412</v>
+        <v>-1667794</v>
       </c>
       <c r="Q192" t="n">
-        <v>306494</v>
+        <v>-3002370</v>
       </c>
       <c r="R192" t="n">
-        <v>1646608</v>
+        <v>-3370707</v>
       </c>
       <c r="S192" t="n">
-        <v>270187</v>
+        <v>-1845911</v>
       </c>
       <c r="T192" t="n">
-        <v>242579</v>
+        <v>-1921114</v>
       </c>
       <c r="U192" t="n">
-        <v>303726</v>
+        <v>-3413893</v>
       </c>
       <c r="V192" t="n">
-        <v>1636083</v>
+        <v>-3775830</v>
       </c>
       <c r="W192" t="n">
         <v>0</v>
@@ -33808,34 +33798,34 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>12001</v>
+        <v>164321</v>
       </c>
       <c r="AB192" t="n">
-        <v>5833</v>
+        <v>253320</v>
       </c>
       <c r="AC192" t="n">
-        <v>2768</v>
+        <v>411523</v>
       </c>
       <c r="AD192" t="n">
-        <v>10525</v>
+        <v>405123</v>
       </c>
       <c r="AE192" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF192" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG192" t="n">
-        <v>-30</v>
+        <v>65</v>
       </c>
       <c r="AH192" t="n">
-        <v>50</v>
+        <v>-55</v>
       </c>
       <c r="AI192" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AJ192" t="n">
-        <v>-20</v>
+        <v>12</v>
       </c>
       <c r="AK192" t="inlineStr">
         <is>
@@ -33843,16 +33833,16 @@
         </is>
       </c>
       <c r="AL192" t="n">
-        <v>28</v>
+        <v>-3</v>
       </c>
       <c r="AM192" t="n">
-        <v>140</v>
+        <v>-25</v>
       </c>
       <c r="AN192" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO192" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
@@ -33861,7 +33851,7 @@
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、爆量後不追價、分數轉弱</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
@@ -33876,17 +33866,17 @@
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -34241,12 +34231,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2014.TW</t>
+          <t>1810.TW</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>中鴻</t>
+          <t>和成</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -34265,28 +34255,28 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>16.95</v>
+        <v>23.4</v>
       </c>
       <c r="G195" t="n">
-        <v>16.95</v>
+        <v>23.59</v>
       </c>
       <c r="H195" t="n">
-        <v>16.96</v>
+        <v>23.79</v>
       </c>
       <c r="I195" t="n">
-        <v>16.78</v>
+        <v>23.77</v>
       </c>
       <c r="J195" t="n">
-        <v>1025766</v>
+        <v>939503</v>
       </c>
       <c r="K195" t="n">
-        <v>1337417</v>
+        <v>1154906</v>
       </c>
       <c r="L195" t="n">
-        <v>17.45</v>
+        <v>24.6</v>
       </c>
       <c r="M195" t="n">
-        <v>16.2</v>
+        <v>23.2</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
@@ -34294,28 +34284,28 @@
         </is>
       </c>
       <c r="O195" t="n">
-        <v>441429</v>
+        <v>282188</v>
       </c>
       <c r="P195" t="n">
-        <v>772378</v>
+        <v>248412</v>
       </c>
       <c r="Q195" t="n">
-        <v>244404</v>
+        <v>306494</v>
       </c>
       <c r="R195" t="n">
-        <v>5464793</v>
+        <v>1646608</v>
       </c>
       <c r="S195" t="n">
-        <v>378429</v>
+        <v>270187</v>
       </c>
       <c r="T195" t="n">
-        <v>709378</v>
+        <v>242579</v>
       </c>
       <c r="U195" t="n">
-        <v>194404</v>
+        <v>303726</v>
       </c>
       <c r="V195" t="n">
-        <v>5401793</v>
+        <v>1636083</v>
       </c>
       <c r="W195" t="n">
         <v>0</v>
@@ -34330,16 +34320,16 @@
         <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>63000</v>
+        <v>12001</v>
       </c>
       <c r="AB195" t="n">
-        <v>63000</v>
+        <v>5833</v>
       </c>
       <c r="AC195" t="n">
-        <v>50000</v>
+        <v>2768</v>
       </c>
       <c r="AD195" t="n">
-        <v>63000</v>
+        <v>10525</v>
       </c>
       <c r="AE195" t="n">
         <v>8</v>
@@ -34357,7 +34347,7 @@
         <v>0</v>
       </c>
       <c r="AJ195" t="n">
-        <v>-34</v>
+        <v>-20</v>
       </c>
       <c r="AK195" t="inlineStr">
         <is>
@@ -34365,16 +34355,16 @@
         </is>
       </c>
       <c r="AL195" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AM195" t="n">
-        <v>123.53</v>
+        <v>140</v>
       </c>
       <c r="AN195" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO195" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
@@ -34383,7 +34373,7 @@
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR195" t="inlineStr">
@@ -34937,12 +34927,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3406.TW</t>
+          <t>2014.TW</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -34961,28 +34951,28 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>1060</v>
+        <v>16.95</v>
       </c>
       <c r="G199" t="n">
-        <v>1041.2</v>
+        <v>16.95</v>
       </c>
       <c r="H199" t="n">
-        <v>973.4</v>
+        <v>16.96</v>
       </c>
       <c r="I199" t="n">
-        <v>983</v>
+        <v>16.78</v>
       </c>
       <c r="J199" t="n">
-        <v>3077733</v>
+        <v>1025766</v>
       </c>
       <c r="K199" t="n">
-        <v>5460443</v>
+        <v>1337417</v>
       </c>
       <c r="L199" t="n">
-        <v>1140</v>
+        <v>17.45</v>
       </c>
       <c r="M199" t="n">
-        <v>869</v>
+        <v>16.2</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
@@ -34990,70 +34980,70 @@
         </is>
       </c>
       <c r="O199" t="n">
-        <v>-122448</v>
+        <v>441429</v>
       </c>
       <c r="P199" t="n">
-        <v>128048</v>
+        <v>772378</v>
       </c>
       <c r="Q199" t="n">
-        <v>-112331</v>
+        <v>244404</v>
       </c>
       <c r="R199" t="n">
-        <v>-728752</v>
+        <v>5464793</v>
       </c>
       <c r="S199" t="n">
-        <v>-384724</v>
+        <v>378429</v>
       </c>
       <c r="T199" t="n">
-        <v>-927780</v>
+        <v>709378</v>
       </c>
       <c r="U199" t="n">
-        <v>-1635106</v>
+        <v>194404</v>
       </c>
       <c r="V199" t="n">
-        <v>-2144094</v>
+        <v>5401793</v>
       </c>
       <c r="W199" t="n">
-        <v>276000</v>
+        <v>0</v>
       </c>
       <c r="X199" t="n">
-        <v>1072000</v>
+        <v>0</v>
       </c>
       <c r="Y199" t="n">
-        <v>1531500</v>
+        <v>0</v>
       </c>
       <c r="Z199" t="n">
-        <v>1472500</v>
+        <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>-13724</v>
+        <v>63000</v>
       </c>
       <c r="AB199" t="n">
-        <v>-16172</v>
+        <v>63000</v>
       </c>
       <c r="AC199" t="n">
-        <v>-8725</v>
+        <v>50000</v>
       </c>
       <c r="AD199" t="n">
-        <v>-57158</v>
+        <v>63000</v>
       </c>
       <c r="AE199" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF199" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG199" t="n">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="AH199" t="n">
-        <v>-5</v>
+        <v>50</v>
       </c>
       <c r="AI199" t="n">
         <v>0</v>
       </c>
       <c r="AJ199" t="n">
-        <v>6</v>
+        <v>-34</v>
       </c>
       <c r="AK199" t="inlineStr">
         <is>
@@ -35061,25 +35051,25 @@
         </is>
       </c>
       <c r="AL199" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM199" t="n">
-        <v>0</v>
+        <v>123.53</v>
       </c>
       <c r="AN199" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AO199" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
@@ -35094,17 +35084,17 @@
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -35285,12 +35275,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3013.TW</t>
+          <t>3406.TW</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>晟銘電</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -35309,28 +35299,28 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>97.90000000000001</v>
+        <v>1060</v>
       </c>
       <c r="G201" t="n">
-        <v>94.98</v>
+        <v>1041.2</v>
       </c>
       <c r="H201" t="n">
-        <v>90.84999999999999</v>
+        <v>973.4</v>
       </c>
       <c r="I201" t="n">
-        <v>87.31</v>
+        <v>983</v>
       </c>
       <c r="J201" t="n">
-        <v>6377587</v>
+        <v>3077733</v>
       </c>
       <c r="K201" t="n">
-        <v>4857340</v>
+        <v>5460443</v>
       </c>
       <c r="L201" t="n">
-        <v>98.8</v>
+        <v>1140</v>
       </c>
       <c r="M201" t="n">
-        <v>81.5</v>
+        <v>869</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
@@ -35338,52 +35328,52 @@
         </is>
       </c>
       <c r="O201" t="n">
-        <v>-1014019</v>
+        <v>-122448</v>
       </c>
       <c r="P201" t="n">
-        <v>-1257133</v>
+        <v>128048</v>
       </c>
       <c r="Q201" t="n">
-        <v>-3270892</v>
+        <v>-112331</v>
       </c>
       <c r="R201" t="n">
-        <v>-3252078</v>
+        <v>-728752</v>
       </c>
       <c r="S201" t="n">
-        <v>-1036201</v>
+        <v>-384724</v>
       </c>
       <c r="T201" t="n">
-        <v>-1375601</v>
+        <v>-927780</v>
       </c>
       <c r="U201" t="n">
-        <v>-3221506</v>
+        <v>-1635106</v>
       </c>
       <c r="V201" t="n">
-        <v>-3460184</v>
+        <v>-2144094</v>
       </c>
       <c r="W201" t="n">
-        <v>1000</v>
+        <v>276000</v>
       </c>
       <c r="X201" t="n">
-        <v>1000</v>
+        <v>1072000</v>
       </c>
       <c r="Y201" t="n">
-        <v>1000</v>
+        <v>1531500</v>
       </c>
       <c r="Z201" t="n">
-        <v>2022</v>
+        <v>1472500</v>
       </c>
       <c r="AA201" t="n">
-        <v>21182</v>
+        <v>-13724</v>
       </c>
       <c r="AB201" t="n">
-        <v>117468</v>
+        <v>-16172</v>
       </c>
       <c r="AC201" t="n">
-        <v>-50386</v>
+        <v>-8725</v>
       </c>
       <c r="AD201" t="n">
-        <v>206084</v>
+        <v>-57158</v>
       </c>
       <c r="AE201" t="n">
         <v>6</v>
@@ -35392,16 +35382,16 @@
         <v>6</v>
       </c>
       <c r="AG201" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="AH201" t="n">
-        <v>-55</v>
+        <v>-5</v>
       </c>
       <c r="AI201" t="n">
         <v>0</v>
       </c>
       <c r="AJ201" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK201" t="inlineStr">
         <is>
@@ -35409,25 +35399,25 @@
         </is>
       </c>
       <c r="AL201" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM201" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AN201" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="AO201" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
@@ -35442,17 +35432,17 @@
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -36319,12 +36309,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3617.TW</t>
+          <t>3013.TW</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>晟銘電</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -36343,28 +36333,28 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>241.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="G207" t="n">
-        <v>243.4</v>
+        <v>94.98</v>
       </c>
       <c r="H207" t="n">
-        <v>242.8</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="I207" t="n">
-        <v>242.65</v>
+        <v>87.31</v>
       </c>
       <c r="J207" t="n">
-        <v>219126</v>
+        <v>6377587</v>
       </c>
       <c r="K207" t="n">
-        <v>254684</v>
+        <v>4857340</v>
       </c>
       <c r="L207" t="n">
-        <v>253.5</v>
+        <v>98.8</v>
       </c>
       <c r="M207" t="n">
-        <v>234</v>
+        <v>81.5</v>
       </c>
       <c r="N207" t="inlineStr">
         <is>
@@ -36372,52 +36362,52 @@
         </is>
       </c>
       <c r="O207" t="n">
-        <v>-13733</v>
+        <v>-1014019</v>
       </c>
       <c r="P207" t="n">
-        <v>20335</v>
+        <v>-1257133</v>
       </c>
       <c r="Q207" t="n">
-        <v>33002</v>
+        <v>-3270892</v>
       </c>
       <c r="R207" t="n">
-        <v>238168</v>
+        <v>-3252078</v>
       </c>
       <c r="S207" t="n">
-        <v>-16976</v>
+        <v>-1036201</v>
       </c>
       <c r="T207" t="n">
-        <v>59149</v>
+        <v>-1375601</v>
       </c>
       <c r="U207" t="n">
-        <v>72818</v>
+        <v>-3221506</v>
       </c>
       <c r="V207" t="n">
-        <v>292891</v>
+        <v>-3460184</v>
       </c>
       <c r="W207" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X207" t="n">
-        <v>2115</v>
+        <v>1000</v>
       </c>
       <c r="Y207" t="n">
-        <v>2115</v>
+        <v>1000</v>
       </c>
       <c r="Z207" t="n">
-        <v>2115</v>
+        <v>2022</v>
       </c>
       <c r="AA207" t="n">
-        <v>3243</v>
+        <v>21182</v>
       </c>
       <c r="AB207" t="n">
-        <v>-40929</v>
+        <v>117468</v>
       </c>
       <c r="AC207" t="n">
-        <v>-41931</v>
+        <v>-50386</v>
       </c>
       <c r="AD207" t="n">
-        <v>-56838</v>
+        <v>206084</v>
       </c>
       <c r="AE207" t="n">
         <v>6</v>
@@ -36426,16 +36416,16 @@
         <v>6</v>
       </c>
       <c r="AG207" t="n">
-        <v>-5</v>
+        <v>70</v>
       </c>
       <c r="AH207" t="n">
-        <v>20</v>
+        <v>-55</v>
       </c>
       <c r="AI207" t="n">
         <v>0</v>
       </c>
       <c r="AJ207" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
@@ -36443,25 +36433,25 @@
         </is>
       </c>
       <c r="AL207" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
       <c r="AM207" t="n">
-        <v>-76.92</v>
+        <v>200</v>
       </c>
       <c r="AN207" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AO207" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
@@ -36476,17 +36466,17 @@
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>籌碼中性、外資投信同步買超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、籌碼中性、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -36667,12 +36657,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>6485.TWO</t>
+          <t>3617.TW</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -36691,28 +36681,28 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>81.2</v>
+        <v>241.5</v>
       </c>
       <c r="G209" t="n">
-        <v>81.45999999999999</v>
+        <v>243.4</v>
       </c>
       <c r="H209" t="n">
-        <v>77.69</v>
+        <v>242.8</v>
       </c>
       <c r="I209" t="n">
-        <v>70.06999999999999</v>
+        <v>242.65</v>
       </c>
       <c r="J209" t="n">
-        <v>2001000</v>
+        <v>219126</v>
       </c>
       <c r="K209" t="n">
-        <v>1879400</v>
+        <v>254684</v>
       </c>
       <c r="L209" t="n">
-        <v>87.2</v>
+        <v>253.5</v>
       </c>
       <c r="M209" t="n">
-        <v>58.5</v>
+        <v>234</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
@@ -36720,52 +36710,52 @@
         </is>
       </c>
       <c r="O209" t="n">
-        <v>0</v>
+        <v>-13733</v>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>20335</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>33002</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>238168</v>
       </c>
       <c r="S209" t="n">
-        <v>0</v>
+        <v>-16976</v>
       </c>
       <c r="T209" t="n">
-        <v>0</v>
+        <v>59149</v>
       </c>
       <c r="U209" t="n">
-        <v>0</v>
+        <v>72818</v>
       </c>
       <c r="V209" t="n">
-        <v>0</v>
+        <v>292891</v>
       </c>
       <c r="W209" t="n">
         <v>0</v>
       </c>
       <c r="X209" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="Y209" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="Z209" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="AA209" t="n">
-        <v>0</v>
+        <v>3243</v>
       </c>
       <c r="AB209" t="n">
-        <v>0</v>
+        <v>-40929</v>
       </c>
       <c r="AC209" t="n">
-        <v>0</v>
+        <v>-41931</v>
       </c>
       <c r="AD209" t="n">
-        <v>0</v>
+        <v>-56838</v>
       </c>
       <c r="AE209" t="n">
         <v>6</v>
@@ -36774,16 +36764,16 @@
         <v>6</v>
       </c>
       <c r="AG209" t="n">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="AH209" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI209" t="n">
         <v>0</v>
       </c>
       <c r="AJ209" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK209" t="inlineStr">
         <is>
@@ -36791,16 +36781,16 @@
         </is>
       </c>
       <c r="AL209" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="AM209" t="n">
-        <v>-75</v>
+        <v>-76.92</v>
       </c>
       <c r="AN209" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO209" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
@@ -36809,7 +36799,7 @@
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
@@ -36824,17 +36814,17 @@
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>籌碼中性、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、籌碼中性、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -15103,12 +15103,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3030.TW</t>
+          <t>2605.TW</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>新興</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -15127,28 +15127,28 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>313.5</v>
+        <v>36.7</v>
       </c>
       <c r="G85" t="n">
-        <v>308.1</v>
+        <v>36.23</v>
       </c>
       <c r="H85" t="n">
-        <v>291.9</v>
+        <v>36.11</v>
       </c>
       <c r="I85" t="n">
-        <v>278.35</v>
+        <v>36.28</v>
       </c>
       <c r="J85" t="n">
-        <v>2226309</v>
+        <v>5360639</v>
       </c>
       <c r="K85" t="n">
-        <v>3568084</v>
+        <v>8834578</v>
       </c>
       <c r="L85" t="n">
-        <v>318</v>
+        <v>38.65</v>
       </c>
       <c r="M85" t="n">
-        <v>258</v>
+        <v>34.85</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -15156,52 +15156,52 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>113660</v>
+        <v>641094</v>
       </c>
       <c r="P85" t="n">
-        <v>-48025</v>
+        <v>10268287</v>
       </c>
       <c r="Q85" t="n">
-        <v>254674</v>
+        <v>7494079</v>
       </c>
       <c r="R85" t="n">
-        <v>1064953</v>
+        <v>-3231651</v>
       </c>
       <c r="S85" t="n">
-        <v>111578</v>
+        <v>534950</v>
       </c>
       <c r="T85" t="n">
-        <v>-169323</v>
+        <v>9471008</v>
       </c>
       <c r="U85" t="n">
-        <v>-8769</v>
+        <v>6783394</v>
       </c>
       <c r="V85" t="n">
-        <v>632625</v>
+        <v>-3024550</v>
       </c>
       <c r="W85" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>-201000</v>
       </c>
       <c r="AA85" t="n">
-        <v>1082</v>
+        <v>106144</v>
       </c>
       <c r="AB85" t="n">
-        <v>121298</v>
+        <v>798279</v>
       </c>
       <c r="AC85" t="n">
-        <v>263443</v>
+        <v>711685</v>
       </c>
       <c r="AD85" t="n">
-        <v>432328</v>
+        <v>-6101</v>
       </c>
       <c r="AE85" t="n">
         <v>32</v>
@@ -15210,16 +15210,16 @@
         <v>32</v>
       </c>
       <c r="AG85" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH85" t="n">
         <v>60</v>
       </c>
-      <c r="AH85" t="n">
-        <v>20</v>
-      </c>
       <c r="AI85" t="n">
         <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
@@ -15227,16 +15227,16 @@
         </is>
       </c>
       <c r="AL85" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AM85" t="n">
-        <v>33.33</v>
+        <v>220</v>
       </c>
       <c r="AN85" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AO85" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
@@ -15245,7 +15245,7 @@
       </c>
       <c r="AQ85" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
@@ -15260,17 +15260,17 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -15799,12 +15799,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6485.TWO</t>
+          <t>4766.TW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -15823,28 +15823,28 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>77</v>
+        <v>354.5</v>
       </c>
       <c r="G89" t="n">
-        <v>70.78</v>
+        <v>353.4</v>
       </c>
       <c r="H89" t="n">
-        <v>66.87</v>
+        <v>347.6</v>
       </c>
       <c r="I89" t="n">
-        <v>63.8</v>
+        <v>343.45</v>
       </c>
       <c r="J89" t="n">
-        <v>2165000</v>
+        <v>109770</v>
       </c>
       <c r="K89" t="n">
-        <v>1010600</v>
+        <v>224357</v>
       </c>
       <c r="L89" t="n">
-        <v>77.3</v>
+        <v>360</v>
       </c>
       <c r="M89" t="n">
-        <v>58.5</v>
+        <v>330.5</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -15852,28 +15852,28 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>-14458</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>228837</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>417295</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>508223</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>-14458</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>232307</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>417934</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>508122</v>
       </c>
       <c r="W89" t="n">
         <v>0</v>
@@ -15891,13 +15891,13 @@
         <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>-3470</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>-639</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="AE89" t="n">
         <v>32</v>
@@ -15906,32 +15906,42 @@
         <v>32</v>
       </c>
       <c r="AG89" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
       </c>
-      <c r="AJ89" t="inlineStr"/>
-      <c r="AK89" t="inlineStr"/>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89" t="inlineStr"/>
+      <c r="AJ89" t="n">
+        <v>52</v>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AL89" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>-38.46</v>
+      </c>
       <c r="AN89" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AO89" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>DT尚未轉強、離5MA偏遠、均線多頭排列、接近20日高位、量能偏強</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
@@ -15946,29 +15956,29 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、爆量、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4766.TW</t>
+          <t>3030.TW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -15987,28 +15997,28 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>354.5</v>
+        <v>313.5</v>
       </c>
       <c r="G90" t="n">
-        <v>353.4</v>
+        <v>308.1</v>
       </c>
       <c r="H90" t="n">
-        <v>347.6</v>
+        <v>291.9</v>
       </c>
       <c r="I90" t="n">
-        <v>343.45</v>
+        <v>278.35</v>
       </c>
       <c r="J90" t="n">
-        <v>109770</v>
+        <v>2226309</v>
       </c>
       <c r="K90" t="n">
-        <v>224357</v>
+        <v>3568084</v>
       </c>
       <c r="L90" t="n">
-        <v>360</v>
+        <v>318</v>
       </c>
       <c r="M90" t="n">
-        <v>330.5</v>
+        <v>258</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -16016,31 +16026,31 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>-14458</v>
+        <v>113660</v>
       </c>
       <c r="P90" t="n">
-        <v>228837</v>
+        <v>-48025</v>
       </c>
       <c r="Q90" t="n">
-        <v>417295</v>
+        <v>254674</v>
       </c>
       <c r="R90" t="n">
-        <v>508223</v>
+        <v>1064953</v>
       </c>
       <c r="S90" t="n">
-        <v>-14458</v>
+        <v>111578</v>
       </c>
       <c r="T90" t="n">
-        <v>232307</v>
+        <v>-169323</v>
       </c>
       <c r="U90" t="n">
-        <v>417934</v>
+        <v>-8769</v>
       </c>
       <c r="V90" t="n">
-        <v>508122</v>
+        <v>632625</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X90" t="n">
         <v>0</v>
@@ -16052,16 +16062,16 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1082</v>
       </c>
       <c r="AB90" t="n">
-        <v>-3470</v>
+        <v>121298</v>
       </c>
       <c r="AC90" t="n">
-        <v>-639</v>
+        <v>263443</v>
       </c>
       <c r="AD90" t="n">
-        <v>101</v>
+        <v>432328</v>
       </c>
       <c r="AE90" t="n">
         <v>32</v>
@@ -16079,7 +16089,7 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
@@ -16087,16 +16097,16 @@
         </is>
       </c>
       <c r="AL90" t="n">
-        <v>-20</v>
+        <v>8</v>
       </c>
       <c r="AM90" t="n">
-        <v>-38.46</v>
+        <v>33.33</v>
       </c>
       <c r="AN90" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AO90" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
@@ -16105,7 +16115,7 @@
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、分數剛升溫</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
@@ -16485,12 +16495,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2605.TW</t>
+          <t>2816.TW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>新興</t>
+          <t>旺旺保</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -16509,28 +16519,28 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>36.7</v>
+        <v>40.8</v>
       </c>
       <c r="G93" t="n">
-        <v>36.23</v>
+        <v>40.07</v>
       </c>
       <c r="H93" t="n">
-        <v>36.11</v>
+        <v>40.08</v>
       </c>
       <c r="I93" t="n">
-        <v>36.28</v>
+        <v>39.92</v>
       </c>
       <c r="J93" t="n">
-        <v>5360639</v>
+        <v>230213</v>
       </c>
       <c r="K93" t="n">
-        <v>8834578</v>
+        <v>233755</v>
       </c>
       <c r="L93" t="n">
-        <v>38.65</v>
+        <v>41.4</v>
       </c>
       <c r="M93" t="n">
-        <v>34.85</v>
+        <v>38.5</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -16538,52 +16548,52 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>641094</v>
+        <v>-19932</v>
       </c>
       <c r="P93" t="n">
-        <v>10268287</v>
+        <v>239255</v>
       </c>
       <c r="Q93" t="n">
-        <v>7494079</v>
+        <v>234376</v>
       </c>
       <c r="R93" t="n">
-        <v>-3231651</v>
+        <v>78395</v>
       </c>
       <c r="S93" t="n">
-        <v>534950</v>
+        <v>-19932</v>
       </c>
       <c r="T93" t="n">
-        <v>9471008</v>
+        <v>239255</v>
       </c>
       <c r="U93" t="n">
-        <v>6783394</v>
+        <v>234376</v>
       </c>
       <c r="V93" t="n">
-        <v>-3024550</v>
+        <v>78395</v>
       </c>
       <c r="W93" t="n">
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>-201000</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>106144</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>798279</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>711685</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>-6101</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
         <v>32</v>
@@ -16592,16 +16602,16 @@
         <v>32</v>
       </c>
       <c r="AG93" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH93" t="n">
         <v>20</v>
       </c>
-      <c r="AH93" t="n">
-        <v>60</v>
-      </c>
       <c r="AI93" t="n">
         <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
@@ -16609,25 +16619,25 @@
         </is>
       </c>
       <c r="AL93" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AM93" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="AN93" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AO93" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
@@ -16642,29 +16652,29 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、黃金交叉、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、黃金交叉、量能未放大、接近20日高點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2816.TW</t>
+          <t>2402.TW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>旺旺保</t>
+          <t>毅嘉</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16683,28 +16693,28 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>40.8</v>
+        <v>61</v>
       </c>
       <c r="G94" t="n">
-        <v>40.07</v>
+        <v>60.04</v>
       </c>
       <c r="H94" t="n">
-        <v>40.08</v>
+        <v>58.12</v>
       </c>
       <c r="I94" t="n">
-        <v>39.92</v>
+        <v>56.14</v>
       </c>
       <c r="J94" t="n">
-        <v>230213</v>
+        <v>2515996</v>
       </c>
       <c r="K94" t="n">
-        <v>233755</v>
+        <v>3246488</v>
       </c>
       <c r="L94" t="n">
-        <v>41.4</v>
+        <v>63.6</v>
       </c>
       <c r="M94" t="n">
-        <v>38.5</v>
+        <v>53</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -16712,28 +16722,28 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>-19932</v>
+        <v>-203444</v>
       </c>
       <c r="P94" t="n">
-        <v>239255</v>
+        <v>2227023</v>
       </c>
       <c r="Q94" t="n">
-        <v>234376</v>
+        <v>2608128</v>
       </c>
       <c r="R94" t="n">
-        <v>78395</v>
+        <v>3380772</v>
       </c>
       <c r="S94" t="n">
-        <v>-19932</v>
+        <v>-63205</v>
       </c>
       <c r="T94" t="n">
-        <v>239255</v>
+        <v>1950411</v>
       </c>
       <c r="U94" t="n">
-        <v>234376</v>
+        <v>2344206</v>
       </c>
       <c r="V94" t="n">
-        <v>78395</v>
+        <v>2998465</v>
       </c>
       <c r="W94" t="n">
         <v>0</v>
@@ -16748,34 +16758,34 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>-140239</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>276612</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>263922</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>382307</v>
       </c>
       <c r="AE94" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF94" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG94" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="AH94" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
       </c>
       <c r="AJ94" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
@@ -16783,25 +16793,25 @@
         </is>
       </c>
       <c r="AL94" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="AM94" t="n">
-        <v>0</v>
+        <v>-45.45</v>
       </c>
       <c r="AN94" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AO94" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
@@ -16816,17 +16826,17 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能未放大、接近20日高點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能未放大、接近20日高點、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -17007,12 +17017,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2360.TW</t>
+          <t>2301.TW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -17031,28 +17041,28 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2330</v>
+        <v>297.5</v>
       </c>
       <c r="G96" t="n">
-        <v>2319</v>
+        <v>295.2</v>
       </c>
       <c r="H96" t="n">
-        <v>2261.5</v>
+        <v>289.15</v>
       </c>
       <c r="I96" t="n">
-        <v>2239.5</v>
+        <v>285.68</v>
       </c>
       <c r="J96" t="n">
-        <v>1763765</v>
+        <v>13602817</v>
       </c>
       <c r="K96" t="n">
-        <v>3088197</v>
+        <v>16886819</v>
       </c>
       <c r="L96" t="n">
-        <v>2560</v>
+        <v>304.5</v>
       </c>
       <c r="M96" t="n">
-        <v>2025</v>
+        <v>271</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -17060,52 +17070,52 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>-50914</v>
+        <v>-2219183</v>
       </c>
       <c r="P96" t="n">
-        <v>677959</v>
+        <v>-1032441</v>
       </c>
       <c r="Q96" t="n">
-        <v>1734466</v>
+        <v>9085450</v>
       </c>
       <c r="R96" t="n">
-        <v>569730</v>
+        <v>644210</v>
       </c>
       <c r="S96" t="n">
-        <v>-51489</v>
+        <v>-2343867</v>
       </c>
       <c r="T96" t="n">
-        <v>904278</v>
+        <v>-1604904</v>
       </c>
       <c r="U96" t="n">
-        <v>2489090</v>
+        <v>7998501</v>
       </c>
       <c r="V96" t="n">
-        <v>3772789</v>
+        <v>30542</v>
       </c>
       <c r="W96" t="n">
-        <v>22865</v>
+        <v>7383</v>
       </c>
       <c r="X96" t="n">
-        <v>-4913</v>
+        <v>200968</v>
       </c>
       <c r="Y96" t="n">
-        <v>-481599</v>
+        <v>-94175</v>
       </c>
       <c r="Z96" t="n">
-        <v>-3184599</v>
+        <v>-938175</v>
       </c>
       <c r="AA96" t="n">
-        <v>-22290</v>
+        <v>117301</v>
       </c>
       <c r="AB96" t="n">
-        <v>-221406</v>
+        <v>371495</v>
       </c>
       <c r="AC96" t="n">
-        <v>-273025</v>
+        <v>1181124</v>
       </c>
       <c r="AD96" t="n">
-        <v>-18460</v>
+        <v>1551843</v>
       </c>
       <c r="AE96" t="n">
         <v>30</v>
@@ -17123,7 +17133,7 @@
         <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
@@ -17131,10 +17141,10 @@
         </is>
       </c>
       <c r="AL96" t="n">
-        <v>-18</v>
+        <v>-22</v>
       </c>
       <c r="AM96" t="n">
-        <v>-37.5</v>
+        <v>-42.31</v>
       </c>
       <c r="AN96" t="n">
         <v>45</v>
@@ -17181,12 +17191,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2301.TW</t>
+          <t>2360.TW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -17205,28 +17215,28 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>297.5</v>
+        <v>2330</v>
       </c>
       <c r="G97" t="n">
-        <v>295.2</v>
+        <v>2319</v>
       </c>
       <c r="H97" t="n">
-        <v>289.15</v>
+        <v>2261.5</v>
       </c>
       <c r="I97" t="n">
-        <v>285.68</v>
+        <v>2239.5</v>
       </c>
       <c r="J97" t="n">
-        <v>13602817</v>
+        <v>1763765</v>
       </c>
       <c r="K97" t="n">
-        <v>16886819</v>
+        <v>3088197</v>
       </c>
       <c r="L97" t="n">
-        <v>304.5</v>
+        <v>2560</v>
       </c>
       <c r="M97" t="n">
-        <v>271</v>
+        <v>2025</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -17234,52 +17244,52 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>-2219183</v>
+        <v>-50914</v>
       </c>
       <c r="P97" t="n">
-        <v>-1032441</v>
+        <v>677959</v>
       </c>
       <c r="Q97" t="n">
-        <v>9085450</v>
+        <v>1734466</v>
       </c>
       <c r="R97" t="n">
-        <v>644210</v>
+        <v>569730</v>
       </c>
       <c r="S97" t="n">
-        <v>-2343867</v>
+        <v>-51489</v>
       </c>
       <c r="T97" t="n">
-        <v>-1604904</v>
+        <v>904278</v>
       </c>
       <c r="U97" t="n">
-        <v>7998501</v>
+        <v>2489090</v>
       </c>
       <c r="V97" t="n">
-        <v>30542</v>
+        <v>3772789</v>
       </c>
       <c r="W97" t="n">
-        <v>7383</v>
+        <v>22865</v>
       </c>
       <c r="X97" t="n">
-        <v>200968</v>
+        <v>-4913</v>
       </c>
       <c r="Y97" t="n">
-        <v>-94175</v>
+        <v>-481599</v>
       </c>
       <c r="Z97" t="n">
-        <v>-938175</v>
+        <v>-3184599</v>
       </c>
       <c r="AA97" t="n">
-        <v>117301</v>
+        <v>-22290</v>
       </c>
       <c r="AB97" t="n">
-        <v>371495</v>
+        <v>-221406</v>
       </c>
       <c r="AC97" t="n">
-        <v>1181124</v>
+        <v>-273025</v>
       </c>
       <c r="AD97" t="n">
-        <v>1551843</v>
+        <v>-18460</v>
       </c>
       <c r="AE97" t="n">
         <v>30</v>
@@ -17297,7 +17307,7 @@
         <v>0</v>
       </c>
       <c r="AJ97" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
@@ -17305,10 +17315,10 @@
         </is>
       </c>
       <c r="AL97" t="n">
-        <v>-22</v>
+        <v>-18</v>
       </c>
       <c r="AM97" t="n">
-        <v>-42.31</v>
+        <v>-37.5</v>
       </c>
       <c r="AN97" t="n">
         <v>45</v>
@@ -17355,12 +17365,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2402.TW</t>
+          <t>1504.TW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>毅嘉</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -17379,28 +17389,28 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>61</v>
+        <v>71.7</v>
       </c>
       <c r="G98" t="n">
-        <v>60.04</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>58.12</v>
+        <v>69.86</v>
       </c>
       <c r="I98" t="n">
-        <v>56.14</v>
+        <v>69.86</v>
       </c>
       <c r="J98" t="n">
-        <v>2515996</v>
+        <v>10635881</v>
       </c>
       <c r="K98" t="n">
-        <v>3246488</v>
+        <v>11165380</v>
       </c>
       <c r="L98" t="n">
-        <v>63.6</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M98" t="n">
-        <v>53</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -17408,96 +17418,96 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>-203444</v>
+        <v>-4946995</v>
       </c>
       <c r="P98" t="n">
-        <v>2227023</v>
+        <v>1978993</v>
       </c>
       <c r="Q98" t="n">
-        <v>2608128</v>
+        <v>3411315</v>
       </c>
       <c r="R98" t="n">
-        <v>3380772</v>
+        <v>3607018</v>
       </c>
       <c r="S98" t="n">
-        <v>-63205</v>
+        <v>-4647471</v>
       </c>
       <c r="T98" t="n">
-        <v>1950411</v>
+        <v>1917752</v>
       </c>
       <c r="U98" t="n">
-        <v>2344206</v>
+        <v>3289152</v>
       </c>
       <c r="V98" t="n">
-        <v>2998465</v>
+        <v>4289186</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>-19889</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>14114</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>-737886</v>
       </c>
       <c r="AA98" t="n">
-        <v>-140239</v>
+        <v>-312524</v>
       </c>
       <c r="AB98" t="n">
-        <v>276612</v>
+        <v>81130</v>
       </c>
       <c r="AC98" t="n">
-        <v>263922</v>
+        <v>108049</v>
       </c>
       <c r="AD98" t="n">
-        <v>382307</v>
+        <v>55718</v>
       </c>
       <c r="AE98" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>69</v>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AL98" t="n">
+        <v>-41</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>-59.42</v>
+      </c>
+      <c r="AN98" t="n">
         <v>30</v>
       </c>
-      <c r="AF98" t="n">
+      <c r="AO98" t="n">
         <v>30</v>
       </c>
-      <c r="AG98" t="n">
-        <v>45</v>
-      </c>
-      <c r="AH98" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ98" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AL98" t="n">
-        <v>-25</v>
-      </c>
-      <c r="AM98" t="n">
-        <v>-45.45</v>
-      </c>
-      <c r="AN98" t="n">
-        <v>45</v>
-      </c>
-      <c r="AO98" t="n">
-        <v>45</v>
-      </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
@@ -17512,17 +17522,17 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -18399,12 +18409,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1504.TW</t>
+          <t>1522.TW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -18423,28 +18433,28 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>71.7</v>
+        <v>26.4</v>
       </c>
       <c r="G104" t="n">
-        <v>70.95999999999999</v>
+        <v>25.94</v>
       </c>
       <c r="H104" t="n">
-        <v>69.86</v>
+        <v>26.25</v>
       </c>
       <c r="I104" t="n">
-        <v>69.86</v>
+        <v>26.05</v>
       </c>
       <c r="J104" t="n">
-        <v>10635881</v>
+        <v>354738</v>
       </c>
       <c r="K104" t="n">
-        <v>11165380</v>
+        <v>366677</v>
       </c>
       <c r="L104" t="n">
-        <v>73.90000000000001</v>
+        <v>27</v>
       </c>
       <c r="M104" t="n">
-        <v>67.59999999999999</v>
+        <v>24.9</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -18452,52 +18462,52 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>-4946995</v>
+        <v>204320</v>
       </c>
       <c r="P104" t="n">
-        <v>1978993</v>
+        <v>310514</v>
       </c>
       <c r="Q104" t="n">
-        <v>3411315</v>
+        <v>360494</v>
       </c>
       <c r="R104" t="n">
-        <v>3607018</v>
+        <v>715649</v>
       </c>
       <c r="S104" t="n">
-        <v>-4647471</v>
+        <v>205320</v>
       </c>
       <c r="T104" t="n">
-        <v>1917752</v>
+        <v>311514</v>
       </c>
       <c r="U104" t="n">
-        <v>3289152</v>
+        <v>361494</v>
       </c>
       <c r="V104" t="n">
-        <v>4289186</v>
+        <v>738668</v>
       </c>
       <c r="W104" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>-19889</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>14114</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>-737886</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>-312524</v>
+        <v>-1000</v>
       </c>
       <c r="AB104" t="n">
-        <v>81130</v>
+        <v>-1000</v>
       </c>
       <c r="AC104" t="n">
-        <v>108049</v>
+        <v>-1000</v>
       </c>
       <c r="AD104" t="n">
-        <v>55718</v>
+        <v>-23019</v>
       </c>
       <c r="AE104" t="n">
         <v>28</v>
@@ -18515,7 +18525,7 @@
         <v>0</v>
       </c>
       <c r="AJ104" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
@@ -18523,25 +18533,25 @@
         </is>
       </c>
       <c r="AL104" t="n">
-        <v>-41</v>
+        <v>16</v>
       </c>
       <c r="AM104" t="n">
-        <v>-59.42</v>
+        <v>133.33</v>
       </c>
       <c r="AN104" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AO104" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
@@ -18561,12 +18571,12 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -19095,12 +19105,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1522.TW</t>
+          <t>2881.TW</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -19119,28 +19129,28 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>26.4</v>
+        <v>153</v>
       </c>
       <c r="G108" t="n">
-        <v>25.94</v>
+        <v>153.1</v>
       </c>
       <c r="H108" t="n">
-        <v>26.25</v>
+        <v>152.15</v>
       </c>
       <c r="I108" t="n">
-        <v>26.05</v>
+        <v>151.72</v>
       </c>
       <c r="J108" t="n">
-        <v>354738</v>
+        <v>14629239</v>
       </c>
       <c r="K108" t="n">
-        <v>366677</v>
+        <v>13038962</v>
       </c>
       <c r="L108" t="n">
-        <v>27</v>
+        <v>156.5</v>
       </c>
       <c r="M108" t="n">
-        <v>24.9</v>
+        <v>144</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -19148,61 +19158,61 @@
         </is>
       </c>
       <c r="O108" t="n">
-        <v>204320</v>
+        <v>-1788918</v>
       </c>
       <c r="P108" t="n">
-        <v>310514</v>
+        <v>2944027</v>
       </c>
       <c r="Q108" t="n">
-        <v>360494</v>
+        <v>7486577</v>
       </c>
       <c r="R108" t="n">
-        <v>715649</v>
+        <v>1954670</v>
       </c>
       <c r="S108" t="n">
-        <v>205320</v>
+        <v>-4764493</v>
       </c>
       <c r="T108" t="n">
-        <v>311514</v>
+        <v>-672087</v>
       </c>
       <c r="U108" t="n">
-        <v>361494</v>
+        <v>2502422</v>
       </c>
       <c r="V108" t="n">
-        <v>738668</v>
+        <v>-3946852</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>2844942</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>3401983</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>4852177</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>5837177</v>
       </c>
       <c r="AA108" t="n">
-        <v>-1000</v>
+        <v>130633</v>
       </c>
       <c r="AB108" t="n">
-        <v>-1000</v>
+        <v>214131</v>
       </c>
       <c r="AC108" t="n">
-        <v>-1000</v>
+        <v>131978</v>
       </c>
       <c r="AD108" t="n">
-        <v>-23019</v>
+        <v>64345</v>
       </c>
       <c r="AE108" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF108" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG108" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AH108" t="n">
         <v>50</v>
@@ -19211,7 +19221,7 @@
         <v>0</v>
       </c>
       <c r="AJ108" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
@@ -19219,25 +19229,25 @@
         </is>
       </c>
       <c r="AL108" t="n">
-        <v>16</v>
+        <v>-30</v>
       </c>
       <c r="AM108" t="n">
-        <v>133.33</v>
+        <v>-53.57</v>
       </c>
       <c r="AN108" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="AO108" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
@@ -19252,17 +19262,17 @@
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -19443,12 +19453,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2881.TW</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -19467,28 +19477,28 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>153</v>
+        <v>22.2</v>
       </c>
       <c r="G110" t="n">
-        <v>153.1</v>
+        <v>22.44</v>
       </c>
       <c r="H110" t="n">
-        <v>152.15</v>
+        <v>22.35</v>
       </c>
       <c r="I110" t="n">
-        <v>151.72</v>
+        <v>21.7</v>
       </c>
       <c r="J110" t="n">
-        <v>14629239</v>
+        <v>955361</v>
       </c>
       <c r="K110" t="n">
-        <v>13038962</v>
+        <v>1373880</v>
       </c>
       <c r="L110" t="n">
-        <v>156.5</v>
+        <v>23.2</v>
       </c>
       <c r="M110" t="n">
-        <v>144</v>
+        <v>20.1</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -19496,52 +19506,52 @@
         </is>
       </c>
       <c r="O110" t="n">
-        <v>-1788918</v>
+        <v>49512</v>
       </c>
       <c r="P110" t="n">
-        <v>2944027</v>
+        <v>221687</v>
       </c>
       <c r="Q110" t="n">
-        <v>7486577</v>
+        <v>735376</v>
       </c>
       <c r="R110" t="n">
-        <v>1954670</v>
+        <v>316160</v>
       </c>
       <c r="S110" t="n">
-        <v>-4764493</v>
+        <v>125000</v>
       </c>
       <c r="T110" t="n">
-        <v>-672087</v>
+        <v>357558</v>
       </c>
       <c r="U110" t="n">
-        <v>2502422</v>
+        <v>778076</v>
       </c>
       <c r="V110" t="n">
-        <v>-3946852</v>
+        <v>356730</v>
       </c>
       <c r="W110" t="n">
-        <v>2844942</v>
+        <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>3401983</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>4852177</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>5837177</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>130633</v>
+        <v>-75488</v>
       </c>
       <c r="AB110" t="n">
-        <v>214131</v>
+        <v>-135871</v>
       </c>
       <c r="AC110" t="n">
-        <v>131978</v>
+        <v>-42700</v>
       </c>
       <c r="AD110" t="n">
-        <v>64345</v>
+        <v>-40570</v>
       </c>
       <c r="AE110" t="n">
         <v>26</v>
@@ -19550,16 +19560,16 @@
         <v>26</v>
       </c>
       <c r="AG110" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AH110" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
       </c>
       <c r="AJ110" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
@@ -19567,16 +19577,16 @@
         </is>
       </c>
       <c r="AL110" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
       <c r="AM110" t="n">
-        <v>-53.57</v>
+        <v>18.18</v>
       </c>
       <c r="AN110" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AO110" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
@@ -19585,7 +19595,7 @@
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
@@ -19600,17 +19610,17 @@
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -19791,12 +19801,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2377.TW</t>
+          <t>4960.TW</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>誠美材</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -19815,28 +19825,28 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>154.5</v>
+        <v>23.8</v>
       </c>
       <c r="G112" t="n">
-        <v>155.1</v>
+        <v>24.12</v>
       </c>
       <c r="H112" t="n">
-        <v>153.25</v>
+        <v>23.76</v>
       </c>
       <c r="I112" t="n">
-        <v>152.68</v>
+        <v>22.52</v>
       </c>
       <c r="J112" t="n">
-        <v>3266008</v>
+        <v>2386573</v>
       </c>
       <c r="K112" t="n">
-        <v>4750295</v>
+        <v>3427521</v>
       </c>
       <c r="L112" t="n">
-        <v>159</v>
+        <v>24.95</v>
       </c>
       <c r="M112" t="n">
-        <v>144.5</v>
+        <v>19.5</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -19844,52 +19854,52 @@
         </is>
       </c>
       <c r="O112" t="n">
-        <v>245065</v>
+        <v>443097</v>
       </c>
       <c r="P112" t="n">
-        <v>1080788</v>
+        <v>1556373</v>
       </c>
       <c r="Q112" t="n">
-        <v>4455439</v>
+        <v>1617983</v>
       </c>
       <c r="R112" t="n">
-        <v>5307986</v>
+        <v>1731432</v>
       </c>
       <c r="S112" t="n">
-        <v>674547</v>
+        <v>431287</v>
       </c>
       <c r="T112" t="n">
-        <v>2339887</v>
+        <v>1537360</v>
       </c>
       <c r="U112" t="n">
-        <v>4422245</v>
+        <v>1616185</v>
       </c>
       <c r="V112" t="n">
-        <v>4681529</v>
+        <v>1825757</v>
       </c>
       <c r="W112" t="n">
-        <v>-497000</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>-1318146</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>-318576</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>162424</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>67518</v>
+        <v>11810</v>
       </c>
       <c r="AB112" t="n">
-        <v>59047</v>
+        <v>19013</v>
       </c>
       <c r="AC112" t="n">
-        <v>351770</v>
+        <v>1798</v>
       </c>
       <c r="AD112" t="n">
-        <v>464033</v>
+        <v>-94325</v>
       </c>
       <c r="AE112" t="n">
         <v>26</v>
@@ -19907,7 +19917,7 @@
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
@@ -19915,16 +19925,14 @@
         </is>
       </c>
       <c r="AL112" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AM112" t="n">
-        <v>-53.57</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="AM112" t="inlineStr"/>
       <c r="AN112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AO112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
@@ -19933,7 +19941,7 @@
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -19953,12 +19961,12 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -20835,12 +20843,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3062.TW</t>
+          <t>2328.TW</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>廣宇</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -20859,28 +20867,28 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>22.2</v>
+        <v>48.05</v>
       </c>
       <c r="G118" t="n">
-        <v>22.44</v>
+        <v>48.12</v>
       </c>
       <c r="H118" t="n">
-        <v>22.35</v>
+        <v>47.7</v>
       </c>
       <c r="I118" t="n">
-        <v>21.71</v>
+        <v>46.95</v>
       </c>
       <c r="J118" t="n">
-        <v>955361</v>
+        <v>878176</v>
       </c>
       <c r="K118" t="n">
-        <v>1373880</v>
+        <v>1618983</v>
       </c>
       <c r="L118" t="n">
-        <v>23.2</v>
+        <v>49.6</v>
       </c>
       <c r="M118" t="n">
-        <v>20.1</v>
+        <v>44.85</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -20888,28 +20896,28 @@
         </is>
       </c>
       <c r="O118" t="n">
-        <v>49512</v>
+        <v>308114</v>
       </c>
       <c r="P118" t="n">
-        <v>221687</v>
+        <v>456040</v>
       </c>
       <c r="Q118" t="n">
-        <v>735376</v>
+        <v>1569129</v>
       </c>
       <c r="R118" t="n">
-        <v>316160</v>
+        <v>2778526</v>
       </c>
       <c r="S118" t="n">
-        <v>125000</v>
+        <v>269066</v>
       </c>
       <c r="T118" t="n">
-        <v>357558</v>
+        <v>633992</v>
       </c>
       <c r="U118" t="n">
-        <v>778076</v>
+        <v>1480207</v>
       </c>
       <c r="V118" t="n">
-        <v>356730</v>
+        <v>2743529</v>
       </c>
       <c r="W118" t="n">
         <v>0</v>
@@ -20924,16 +20932,16 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>-75488</v>
+        <v>39048</v>
       </c>
       <c r="AB118" t="n">
-        <v>-135871</v>
+        <v>-177952</v>
       </c>
       <c r="AC118" t="n">
-        <v>-42700</v>
+        <v>88922</v>
       </c>
       <c r="AD118" t="n">
-        <v>-40570</v>
+        <v>34997</v>
       </c>
       <c r="AE118" t="n">
         <v>26</v>
@@ -20951,7 +20959,7 @@
         <v>0</v>
       </c>
       <c r="AJ118" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
@@ -20959,16 +20967,16 @@
         </is>
       </c>
       <c r="AL118" t="n">
-        <v>4</v>
+        <v>-16</v>
       </c>
       <c r="AM118" t="n">
-        <v>18.18</v>
+        <v>-38.1</v>
       </c>
       <c r="AN118" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AO118" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
@@ -20977,7 +20985,7 @@
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
@@ -21009,12 +21017,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2328.TW</t>
+          <t>2377.TW</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>廣宇</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -21033,28 +21041,28 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>48.05</v>
+        <v>154.5</v>
       </c>
       <c r="G119" t="n">
-        <v>48.12</v>
+        <v>155.1</v>
       </c>
       <c r="H119" t="n">
-        <v>47.7</v>
+        <v>153.25</v>
       </c>
       <c r="I119" t="n">
-        <v>46.95</v>
+        <v>152.68</v>
       </c>
       <c r="J119" t="n">
-        <v>878176</v>
+        <v>3266008</v>
       </c>
       <c r="K119" t="n">
-        <v>1618983</v>
+        <v>4750295</v>
       </c>
       <c r="L119" t="n">
-        <v>49.6</v>
+        <v>159</v>
       </c>
       <c r="M119" t="n">
-        <v>44.85</v>
+        <v>144.5</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -21062,52 +21070,52 @@
         </is>
       </c>
       <c r="O119" t="n">
-        <v>308114</v>
+        <v>245065</v>
       </c>
       <c r="P119" t="n">
-        <v>456040</v>
+        <v>1080788</v>
       </c>
       <c r="Q119" t="n">
-        <v>1569129</v>
+        <v>4455439</v>
       </c>
       <c r="R119" t="n">
-        <v>2778526</v>
+        <v>5307986</v>
       </c>
       <c r="S119" t="n">
-        <v>269066</v>
+        <v>674547</v>
       </c>
       <c r="T119" t="n">
-        <v>633992</v>
+        <v>2339887</v>
       </c>
       <c r="U119" t="n">
-        <v>1480207</v>
+        <v>4422245</v>
       </c>
       <c r="V119" t="n">
-        <v>2743529</v>
+        <v>4681529</v>
       </c>
       <c r="W119" t="n">
-        <v>0</v>
+        <v>-497000</v>
       </c>
       <c r="X119" t="n">
-        <v>0</v>
+        <v>-1318146</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>-318576</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>162424</v>
       </c>
       <c r="AA119" t="n">
-        <v>39048</v>
+        <v>67518</v>
       </c>
       <c r="AB119" t="n">
-        <v>-177952</v>
+        <v>59047</v>
       </c>
       <c r="AC119" t="n">
-        <v>88922</v>
+        <v>351770</v>
       </c>
       <c r="AD119" t="n">
-        <v>34997</v>
+        <v>464033</v>
       </c>
       <c r="AE119" t="n">
         <v>26</v>
@@ -21125,7 +21133,7 @@
         <v>0</v>
       </c>
       <c r="AJ119" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
@@ -21133,10 +21141,10 @@
         </is>
       </c>
       <c r="AL119" t="n">
-        <v>-16</v>
+        <v>-30</v>
       </c>
       <c r="AM119" t="n">
-        <v>-38.1</v>
+        <v>-53.57</v>
       </c>
       <c r="AN119" t="n">
         <v>10</v>
@@ -21171,24 +21179,24 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4960.TW</t>
+          <t>2347.TW</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>誠美材</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -21207,28 +21215,28 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>23.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>24.12</v>
+        <v>96.62</v>
       </c>
       <c r="H120" t="n">
-        <v>23.76</v>
+        <v>95.69</v>
       </c>
       <c r="I120" t="n">
-        <v>22.52</v>
+        <v>92.5</v>
       </c>
       <c r="J120" t="n">
-        <v>2386573</v>
+        <v>1894748</v>
       </c>
       <c r="K120" t="n">
-        <v>3427521</v>
+        <v>2647895</v>
       </c>
       <c r="L120" t="n">
-        <v>24.95</v>
+        <v>100</v>
       </c>
       <c r="M120" t="n">
-        <v>19.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -21236,52 +21244,52 @@
         </is>
       </c>
       <c r="O120" t="n">
-        <v>443097</v>
+        <v>476019</v>
       </c>
       <c r="P120" t="n">
-        <v>1556373</v>
+        <v>2136290</v>
       </c>
       <c r="Q120" t="n">
-        <v>1617983</v>
+        <v>5344563</v>
       </c>
       <c r="R120" t="n">
-        <v>1731432</v>
+        <v>13711783</v>
       </c>
       <c r="S120" t="n">
-        <v>431287</v>
+        <v>508992</v>
       </c>
       <c r="T120" t="n">
-        <v>1537360</v>
+        <v>2916152</v>
       </c>
       <c r="U120" t="n">
-        <v>1616185</v>
+        <v>6328142</v>
       </c>
       <c r="V120" t="n">
-        <v>1825757</v>
+        <v>13019958</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>-182000</v>
       </c>
       <c r="X120" t="n">
-        <v>0</v>
+        <v>-1049899</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>-1460760</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>-132781</v>
       </c>
       <c r="AA120" t="n">
-        <v>11810</v>
+        <v>149027</v>
       </c>
       <c r="AB120" t="n">
-        <v>19013</v>
+        <v>270037</v>
       </c>
       <c r="AC120" t="n">
-        <v>1798</v>
+        <v>477181</v>
       </c>
       <c r="AD120" t="n">
-        <v>-94325</v>
+        <v>824606</v>
       </c>
       <c r="AE120" t="n">
         <v>26</v>
@@ -21299,7 +21307,7 @@
         <v>0</v>
       </c>
       <c r="AJ120" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
@@ -21307,14 +21315,16 @@
         </is>
       </c>
       <c r="AL120" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM120" t="inlineStr"/>
+        <v>-16</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>-38.1</v>
+      </c>
       <c r="AN120" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AO120" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
@@ -21323,7 +21333,7 @@
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
@@ -21343,24 +21353,24 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2347.TW</t>
+          <t>2637.TW</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -21379,28 +21389,28 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>96.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="G121" t="n">
-        <v>96.62</v>
+        <v>98.34</v>
       </c>
       <c r="H121" t="n">
-        <v>95.69</v>
+        <v>97.94</v>
       </c>
       <c r="I121" t="n">
-        <v>92.5</v>
+        <v>99.44</v>
       </c>
       <c r="J121" t="n">
-        <v>1894748</v>
+        <v>1706603</v>
       </c>
       <c r="K121" t="n">
-        <v>2647895</v>
+        <v>2162301</v>
       </c>
       <c r="L121" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M121" t="n">
-        <v>87.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -21408,96 +21418,96 @@
         </is>
       </c>
       <c r="O121" t="n">
-        <v>476019</v>
+        <v>495472</v>
       </c>
       <c r="P121" t="n">
-        <v>2136290</v>
+        <v>-50659</v>
       </c>
       <c r="Q121" t="n">
-        <v>5344563</v>
+        <v>559188</v>
       </c>
       <c r="R121" t="n">
-        <v>13711783</v>
+        <v>-377210</v>
       </c>
       <c r="S121" t="n">
-        <v>508992</v>
+        <v>465620</v>
       </c>
       <c r="T121" t="n">
-        <v>2916152</v>
+        <v>-78807</v>
       </c>
       <c r="U121" t="n">
-        <v>6328142</v>
+        <v>466278</v>
       </c>
       <c r="V121" t="n">
-        <v>13019958</v>
+        <v>-717842</v>
       </c>
       <c r="W121" t="n">
-        <v>-182000</v>
+        <v>19000</v>
       </c>
       <c r="X121" t="n">
-        <v>-1049899</v>
+        <v>6719</v>
       </c>
       <c r="Y121" t="n">
-        <v>-1460760</v>
+        <v>84439</v>
       </c>
       <c r="Z121" t="n">
-        <v>-132781</v>
+        <v>335878</v>
       </c>
       <c r="AA121" t="n">
-        <v>149027</v>
+        <v>10852</v>
       </c>
       <c r="AB121" t="n">
-        <v>270037</v>
+        <v>21429</v>
       </c>
       <c r="AC121" t="n">
-        <v>477181</v>
+        <v>8471</v>
       </c>
       <c r="AD121" t="n">
-        <v>824606</v>
+        <v>4754</v>
       </c>
       <c r="AE121" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF121" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AH121" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AL121" t="n">
         <v>60</v>
       </c>
-      <c r="AI121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AL121" t="n">
-        <v>-16</v>
-      </c>
       <c r="AM121" t="n">
-        <v>-38.1</v>
+        <v>166.67</v>
       </c>
       <c r="AN121" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AO121" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
@@ -21512,17 +21522,17 @@
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -22399,12 +22409,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2637.TW</t>
+          <t>2535.TW</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -22423,28 +22433,28 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>98.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="G127" t="n">
-        <v>98.34</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="H127" t="n">
-        <v>97.94</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>99.44</v>
+        <v>89.44</v>
       </c>
       <c r="J127" t="n">
-        <v>1706603</v>
+        <v>379048</v>
       </c>
       <c r="K127" t="n">
-        <v>2162301</v>
+        <v>285835</v>
       </c>
       <c r="L127" t="n">
-        <v>105</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="M127" t="n">
-        <v>95</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -22452,52 +22462,52 @@
         </is>
       </c>
       <c r="O127" t="n">
-        <v>495472</v>
+        <v>269183</v>
       </c>
       <c r="P127" t="n">
-        <v>-50659</v>
+        <v>471875</v>
       </c>
       <c r="Q127" t="n">
-        <v>559188</v>
+        <v>305092</v>
       </c>
       <c r="R127" t="n">
-        <v>-377210</v>
+        <v>334647</v>
       </c>
       <c r="S127" t="n">
-        <v>465620</v>
+        <v>268411</v>
       </c>
       <c r="T127" t="n">
-        <v>-78807</v>
+        <v>467103</v>
       </c>
       <c r="U127" t="n">
-        <v>466278</v>
+        <v>299375</v>
       </c>
       <c r="V127" t="n">
-        <v>-717842</v>
+        <v>328813</v>
       </c>
       <c r="W127" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="X127" t="n">
-        <v>6719</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>84439</v>
+        <v>-1000</v>
       </c>
       <c r="Z127" t="n">
-        <v>335878</v>
+        <v>-1000</v>
       </c>
       <c r="AA127" t="n">
-        <v>10852</v>
+        <v>772</v>
       </c>
       <c r="AB127" t="n">
-        <v>21429</v>
+        <v>4772</v>
       </c>
       <c r="AC127" t="n">
-        <v>8471</v>
+        <v>6717</v>
       </c>
       <c r="AD127" t="n">
-        <v>4754</v>
+        <v>6834</v>
       </c>
       <c r="AE127" t="n">
         <v>24</v>
@@ -22515,7 +22525,7 @@
         <v>0</v>
       </c>
       <c r="AJ127" t="n">
-        <v>-36</v>
+        <v>-10</v>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
@@ -22523,25 +22533,25 @@
         </is>
       </c>
       <c r="AL127" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AM127" t="n">
-        <v>166.67</v>
+        <v>340</v>
       </c>
       <c r="AN127" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AO127" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
@@ -22556,29 +22566,29 @@
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2535.TW</t>
+          <t>2912.TW</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -22597,28 +22607,28 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>91.40000000000001</v>
+        <v>213</v>
       </c>
       <c r="G128" t="n">
-        <v>89.31999999999999</v>
+        <v>211.7</v>
       </c>
       <c r="H128" t="n">
-        <v>89.34999999999999</v>
+        <v>212.1</v>
       </c>
       <c r="I128" t="n">
-        <v>89.44</v>
+        <v>214.18</v>
       </c>
       <c r="J128" t="n">
-        <v>379048</v>
+        <v>1914231</v>
       </c>
       <c r="K128" t="n">
-        <v>285835</v>
+        <v>1906044</v>
       </c>
       <c r="L128" t="n">
-        <v>91.90000000000001</v>
+        <v>219</v>
       </c>
       <c r="M128" t="n">
-        <v>87.90000000000001</v>
+        <v>210</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -22626,70 +22636,70 @@
         </is>
       </c>
       <c r="O128" t="n">
-        <v>269183</v>
+        <v>750317</v>
       </c>
       <c r="P128" t="n">
-        <v>471875</v>
+        <v>2029597</v>
       </c>
       <c r="Q128" t="n">
-        <v>305092</v>
+        <v>879411</v>
       </c>
       <c r="R128" t="n">
-        <v>334647</v>
+        <v>275070</v>
       </c>
       <c r="S128" t="n">
-        <v>268411</v>
+        <v>726685</v>
       </c>
       <c r="T128" t="n">
-        <v>467103</v>
+        <v>1874750</v>
       </c>
       <c r="U128" t="n">
-        <v>299375</v>
+        <v>1555506</v>
       </c>
       <c r="V128" t="n">
-        <v>328813</v>
+        <v>710165</v>
       </c>
       <c r="W128" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="X128" t="n">
-        <v>0</v>
+        <v>146000</v>
       </c>
       <c r="Y128" t="n">
-        <v>-1000</v>
+        <v>-691000</v>
       </c>
       <c r="Z128" t="n">
-        <v>-1000</v>
+        <v>-557000</v>
       </c>
       <c r="AA128" t="n">
-        <v>772</v>
+        <v>2632</v>
       </c>
       <c r="AB128" t="n">
-        <v>4772</v>
+        <v>8847</v>
       </c>
       <c r="AC128" t="n">
-        <v>6717</v>
+        <v>14905</v>
       </c>
       <c r="AD128" t="n">
-        <v>6834</v>
+        <v>121905</v>
       </c>
       <c r="AE128" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF128" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG128" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="AH128" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
       </c>
       <c r="AJ128" t="n">
-        <v>-10</v>
+        <v>14</v>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
@@ -22697,25 +22707,25 @@
         </is>
       </c>
       <c r="AL128" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="AM128" t="n">
-        <v>340</v>
+        <v>57.14</v>
       </c>
       <c r="AN128" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AO128" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
@@ -22730,29 +22740,29 @@
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日高點、接近20日低點、法人連續偏買、5日法人買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2912.TW</t>
+          <t>2892.TW</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -22771,28 +22781,28 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>213</v>
+        <v>38.65</v>
       </c>
       <c r="G129" t="n">
-        <v>211.7</v>
+        <v>38.54</v>
       </c>
       <c r="H129" t="n">
-        <v>212.1</v>
+        <v>38.8</v>
       </c>
       <c r="I129" t="n">
-        <v>214.18</v>
+        <v>39.11</v>
       </c>
       <c r="J129" t="n">
-        <v>1914231</v>
+        <v>14704600</v>
       </c>
       <c r="K129" t="n">
-        <v>1906044</v>
+        <v>13952892</v>
       </c>
       <c r="L129" t="n">
-        <v>219</v>
+        <v>40.95</v>
       </c>
       <c r="M129" t="n">
-        <v>210</v>
+        <v>37.15</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -22800,52 +22810,52 @@
         </is>
       </c>
       <c r="O129" t="n">
-        <v>750317</v>
+        <v>213631</v>
       </c>
       <c r="P129" t="n">
-        <v>2029597</v>
+        <v>3348609</v>
       </c>
       <c r="Q129" t="n">
-        <v>879411</v>
+        <v>3346311</v>
       </c>
       <c r="R129" t="n">
-        <v>275070</v>
+        <v>13584604</v>
       </c>
       <c r="S129" t="n">
-        <v>726685</v>
+        <v>85897</v>
       </c>
       <c r="T129" t="n">
-        <v>1874750</v>
+        <v>5207101</v>
       </c>
       <c r="U129" t="n">
-        <v>1555506</v>
+        <v>-192087</v>
       </c>
       <c r="V129" t="n">
-        <v>710165</v>
+        <v>-2890074</v>
       </c>
       <c r="W129" t="n">
-        <v>21000</v>
+        <v>129893</v>
       </c>
       <c r="X129" t="n">
-        <v>146000</v>
+        <v>-1941243</v>
       </c>
       <c r="Y129" t="n">
-        <v>-691000</v>
+        <v>3503517</v>
       </c>
       <c r="Z129" t="n">
-        <v>-557000</v>
+        <v>16116517</v>
       </c>
       <c r="AA129" t="n">
-        <v>2632</v>
+        <v>-2159</v>
       </c>
       <c r="AB129" t="n">
-        <v>8847</v>
+        <v>82751</v>
       </c>
       <c r="AC129" t="n">
-        <v>14905</v>
+        <v>34881</v>
       </c>
       <c r="AD129" t="n">
-        <v>121905</v>
+        <v>358161</v>
       </c>
       <c r="AE129" t="n">
         <v>22</v>
@@ -22863,7 +22873,7 @@
         <v>0</v>
       </c>
       <c r="AJ129" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
@@ -22871,16 +22881,16 @@
         </is>
       </c>
       <c r="AL129" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AM129" t="n">
-        <v>57.14</v>
+        <v>120</v>
       </c>
       <c r="AN129" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO129" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
@@ -22889,7 +22899,7 @@
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
@@ -22909,24 +22919,24 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2323.TW</t>
+          <t>3653.TW</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>中環</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -22936,7 +22946,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -22945,28 +22955,28 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>11</v>
+        <v>7165</v>
       </c>
       <c r="G130" t="n">
-        <v>10.83</v>
+        <v>7011</v>
       </c>
       <c r="H130" t="n">
-        <v>10.74</v>
+        <v>6895.5</v>
       </c>
       <c r="I130" t="n">
-        <v>10.75</v>
+        <v>6257</v>
       </c>
       <c r="J130" t="n">
-        <v>14064496</v>
+        <v>1628778</v>
       </c>
       <c r="K130" t="n">
-        <v>6377380</v>
+        <v>1085614</v>
       </c>
       <c r="L130" t="n">
-        <v>11.15</v>
+        <v>7440</v>
       </c>
       <c r="M130" t="n">
-        <v>10.4</v>
+        <v>5210</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -22974,52 +22984,52 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>145617</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>106999</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>-129036</v>
       </c>
       <c r="R130" t="n">
-        <v>5058704</v>
+        <v>-488780</v>
       </c>
       <c r="S130" t="n">
-        <v>0</v>
+        <v>247986</v>
       </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>380920</v>
       </c>
       <c r="U130" t="n">
-        <v>0</v>
+        <v>62355</v>
       </c>
       <c r="V130" t="n">
-        <v>4973551</v>
+        <v>-780733</v>
       </c>
       <c r="W130" t="n">
-        <v>0</v>
+        <v>-52932</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>-226553</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>-144585</v>
       </c>
       <c r="Z130" t="n">
-        <v>100</v>
+        <v>294153</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>-49437</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>-47368</v>
       </c>
       <c r="AC130" t="n">
-        <v>0</v>
+        <v>-46806</v>
       </c>
       <c r="AD130" t="n">
-        <v>85053</v>
+        <v>-2200</v>
       </c>
       <c r="AE130" t="n">
         <v>22</v>
@@ -23028,42 +23038,42 @@
         <v>22</v>
       </c>
       <c r="AG130" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AH130" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="AI130" t="n">
         <v>0</v>
       </c>
       <c r="AJ130" t="n">
-        <v>-34</v>
+        <v>-20</v>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AL130" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="AM130" t="n">
-        <v>164.71</v>
+        <v>210</v>
       </c>
       <c r="AN130" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AO130" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
@@ -23078,29 +23088,29 @@
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>站上5日線、爆量、接近20日高點</t>
+          <t>站上5日線、多頭排列、成交量放大</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、爆量、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、成交量放大、短線籌碼止穩、5日法人賣超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2892.TW</t>
+          <t>6147.TWO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -23119,28 +23129,28 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>38.65</v>
+        <v>226</v>
       </c>
       <c r="G131" t="n">
-        <v>38.54</v>
+        <v>222.6</v>
       </c>
       <c r="H131" t="n">
-        <v>38.8</v>
+        <v>218.45</v>
       </c>
       <c r="I131" t="n">
-        <v>39.11</v>
+        <v>211.6</v>
       </c>
       <c r="J131" t="n">
-        <v>14704600</v>
+        <v>48534000</v>
       </c>
       <c r="K131" t="n">
-        <v>13952892</v>
+        <v>42631000</v>
       </c>
       <c r="L131" t="n">
-        <v>40.95</v>
+        <v>238</v>
       </c>
       <c r="M131" t="n">
-        <v>37.15</v>
+        <v>171</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -23148,52 +23158,52 @@
         </is>
       </c>
       <c r="O131" t="n">
-        <v>213631</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>3348609</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3346311</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>13584604</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>85897</v>
+        <v>0</v>
       </c>
       <c r="T131" t="n">
-        <v>5207101</v>
+        <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>-192087</v>
+        <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>-2890074</v>
+        <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>129893</v>
+        <v>0</v>
       </c>
       <c r="X131" t="n">
-        <v>-1941243</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>3503517</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>16116517</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>-2159</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>82751</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>34881</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>358161</v>
+        <v>0</v>
       </c>
       <c r="AE131" t="n">
         <v>22</v>
@@ -23202,16 +23212,16 @@
         <v>22</v>
       </c>
       <c r="AG131" t="n">
-        <v>-5</v>
+        <v>55</v>
       </c>
       <c r="AH131" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AI131" t="n">
         <v>0</v>
       </c>
       <c r="AJ131" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
@@ -23219,25 +23229,25 @@
         </is>
       </c>
       <c r="AL131" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="AM131" t="n">
-        <v>120</v>
+        <v>-8.33</v>
       </c>
       <c r="AN131" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AO131" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
@@ -23252,17 +23262,17 @@
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能溫和放大、接近20日低點、法人連續偏買、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -23791,12 +23801,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>3653.TW</t>
+          <t>2323.TW</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>中環</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -23806,7 +23816,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -23815,28 +23825,28 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>7165</v>
+        <v>11</v>
       </c>
       <c r="G135" t="n">
-        <v>7011</v>
+        <v>10.83</v>
       </c>
       <c r="H135" t="n">
-        <v>6895.5</v>
+        <v>10.74</v>
       </c>
       <c r="I135" t="n">
-        <v>6257</v>
+        <v>10.75</v>
       </c>
       <c r="J135" t="n">
-        <v>1628778</v>
+        <v>14064496</v>
       </c>
       <c r="K135" t="n">
-        <v>1085614</v>
+        <v>6377380</v>
       </c>
       <c r="L135" t="n">
-        <v>7440</v>
+        <v>11.15</v>
       </c>
       <c r="M135" t="n">
-        <v>5210</v>
+        <v>10.4</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -23844,52 +23854,52 @@
         </is>
       </c>
       <c r="O135" t="n">
-        <v>145617</v>
+        <v>0</v>
       </c>
       <c r="P135" t="n">
-        <v>106999</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>-129036</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>-488780</v>
+        <v>5058704</v>
       </c>
       <c r="S135" t="n">
-        <v>247986</v>
+        <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>380920</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
-        <v>62355</v>
+        <v>0</v>
       </c>
       <c r="V135" t="n">
-        <v>-780733</v>
+        <v>4973551</v>
       </c>
       <c r="W135" t="n">
-        <v>-52932</v>
+        <v>0</v>
       </c>
       <c r="X135" t="n">
-        <v>-226553</v>
+        <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>-144585</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>294153</v>
+        <v>100</v>
       </c>
       <c r="AA135" t="n">
-        <v>-49437</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>-47368</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
-        <v>-46806</v>
+        <v>0</v>
       </c>
       <c r="AD135" t="n">
-        <v>-2200</v>
+        <v>85053</v>
       </c>
       <c r="AE135" t="n">
         <v>22</v>
@@ -23898,42 +23908,42 @@
         <v>22</v>
       </c>
       <c r="AG135" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AH135" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
       </c>
       <c r="AJ135" t="n">
-        <v>-20</v>
+        <v>-34</v>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AL135" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="AM135" t="n">
-        <v>210</v>
+        <v>164.71</v>
       </c>
       <c r="AN135" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AO135" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR135" t="inlineStr">
@@ -23948,29 +23958,29 @@
       </c>
       <c r="AT135" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、成交量放大</t>
+          <t>站上5日線、爆量、接近20日高點</t>
         </is>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、成交量放大、短線籌碼止穩、5日法人賣超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、爆量、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>6147.TWO</t>
+          <t>1736.TW</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -23989,28 +23999,28 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="G136" t="n">
-        <v>222.6</v>
+        <v>122.6</v>
       </c>
       <c r="H136" t="n">
-        <v>218.45</v>
+        <v>125.05</v>
       </c>
       <c r="I136" t="n">
-        <v>211.6</v>
+        <v>125.33</v>
       </c>
       <c r="J136" t="n">
-        <v>48534000</v>
+        <v>460026</v>
       </c>
       <c r="K136" t="n">
-        <v>42631000</v>
+        <v>697276</v>
       </c>
       <c r="L136" t="n">
-        <v>238</v>
+        <v>133.5</v>
       </c>
       <c r="M136" t="n">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -24018,52 +24028,52 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>183265</v>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>182377</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>120259</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>593937</v>
       </c>
       <c r="S136" t="n">
-        <v>0</v>
+        <v>181858</v>
       </c>
       <c r="T136" t="n">
-        <v>0</v>
+        <v>183858</v>
       </c>
       <c r="U136" t="n">
-        <v>0</v>
+        <v>128988</v>
       </c>
       <c r="V136" t="n">
-        <v>0</v>
+        <v>598915</v>
       </c>
       <c r="W136" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X136" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>-2481</v>
       </c>
       <c r="AC136" t="n">
-        <v>0</v>
+        <v>-9729</v>
       </c>
       <c r="AD136" t="n">
-        <v>0</v>
+        <v>-5978</v>
       </c>
       <c r="AE136" t="n">
         <v>22</v>
@@ -24072,16 +24082,16 @@
         <v>22</v>
       </c>
       <c r="AG136" t="n">
-        <v>55</v>
+        <v>-15</v>
       </c>
       <c r="AH136" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AI136" t="n">
         <v>0</v>
       </c>
       <c r="AJ136" t="n">
-        <v>24</v>
+        <v>-20</v>
       </c>
       <c r="AK136" t="inlineStr">
         <is>
@@ -24089,25 +24099,25 @@
         </is>
       </c>
       <c r="AL136" t="n">
-        <v>-2</v>
+        <v>42</v>
       </c>
       <c r="AM136" t="n">
-        <v>-8.33</v>
+        <v>210</v>
       </c>
       <c r="AN136" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AO136" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
@@ -24122,29 +24132,29 @@
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能溫和放大、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1736.TW</t>
+          <t>4903.TWO</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>喬山</t>
+          <t>聯光通</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -24163,81 +24173,81 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>123</v>
+        <v>45.95</v>
       </c>
       <c r="G137" t="n">
-        <v>122.6</v>
+        <v>44.86</v>
       </c>
       <c r="H137" t="n">
-        <v>125.05</v>
+        <v>43.95</v>
       </c>
       <c r="I137" t="n">
-        <v>125.33</v>
+        <v>40.18</v>
       </c>
       <c r="J137" t="n">
-        <v>460026</v>
+        <v>19354000</v>
       </c>
       <c r="K137" t="n">
-        <v>697276</v>
+        <v>8237000</v>
       </c>
       <c r="L137" t="n">
-        <v>133.5</v>
+        <v>50.7</v>
       </c>
       <c r="M137" t="n">
-        <v>119</v>
+        <v>33.15</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="O137" t="n">
-        <v>183265</v>
+        <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>182377</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>120259</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>593937</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>181858</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>183858</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
-        <v>128988</v>
+        <v>0</v>
       </c>
       <c r="V137" t="n">
-        <v>598915</v>
+        <v>0</v>
       </c>
       <c r="W137" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X137" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>-2481</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
-        <v>-9729</v>
+        <v>0</v>
       </c>
       <c r="AD137" t="n">
-        <v>-5978</v>
+        <v>0</v>
       </c>
       <c r="AE137" t="n">
         <v>22</v>
@@ -24246,16 +24256,16 @@
         <v>22</v>
       </c>
       <c r="AG137" t="n">
-        <v>-15</v>
+        <v>65</v>
       </c>
       <c r="AH137" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AI137" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ137" t="n">
-        <v>-20</v>
+        <v>28</v>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
@@ -24263,25 +24273,25 @@
         </is>
       </c>
       <c r="AL137" t="n">
-        <v>42</v>
+        <v>-6</v>
       </c>
       <c r="AM137" t="n">
-        <v>210</v>
+        <v>-21.43</v>
       </c>
       <c r="AN137" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="AO137" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -24296,17 +24306,17 @@
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、爆量、爆量價未漲、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -24835,17 +24845,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>4903.TWO</t>
+          <t>00692.TW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>聯光通</t>
+          <t>富邦公司治理</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -24859,57 +24869,57 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>45.95</v>
+        <v>99</v>
       </c>
       <c r="G141" t="n">
-        <v>44.86</v>
+        <v>99.13</v>
       </c>
       <c r="H141" t="n">
-        <v>43.95</v>
+        <v>97.88</v>
       </c>
       <c r="I141" t="n">
-        <v>40.18</v>
+        <v>95.62</v>
       </c>
       <c r="J141" t="n">
-        <v>19354000</v>
+        <v>621175</v>
       </c>
       <c r="K141" t="n">
-        <v>8237000</v>
+        <v>782490</v>
       </c>
       <c r="L141" t="n">
-        <v>50.7</v>
+        <v>100.1</v>
       </c>
       <c r="M141" t="n">
-        <v>33.15</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>-90933</v>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>511477</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>777074</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>2112826</v>
       </c>
       <c r="S141" t="n">
-        <v>0</v>
+        <v>-15042</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>-225118</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>74909</v>
       </c>
       <c r="V141" t="n">
-        <v>0</v>
+        <v>-59064</v>
       </c>
       <c r="W141" t="n">
         <v>0</v>
@@ -24924,34 +24934,34 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>-75891</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>736595</v>
       </c>
       <c r="AC141" t="n">
-        <v>0</v>
+        <v>702165</v>
       </c>
       <c r="AD141" t="n">
-        <v>0</v>
+        <v>2171890</v>
       </c>
       <c r="AE141" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF141" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG141" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="AH141" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI141" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ141" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
@@ -24959,25 +24969,25 @@
         </is>
       </c>
       <c r="AL141" t="n">
-        <v>-6</v>
+        <v>-28</v>
       </c>
       <c r="AM141" t="n">
-        <v>-21.43</v>
+        <v>-58.33</v>
       </c>
       <c r="AN141" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="AO141" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
@@ -24992,17 +25002,17 @@
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、爆量價未漲</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、爆量、爆量價未漲、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -25183,12 +25193,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2207.TW</t>
+          <t>1789.TW</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>神隆</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -25207,28 +25217,28 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>518</v>
+        <v>19.1</v>
       </c>
       <c r="G143" t="n">
-        <v>516.4</v>
+        <v>18.76</v>
       </c>
       <c r="H143" t="n">
-        <v>514.2</v>
+        <v>18.76</v>
       </c>
       <c r="I143" t="n">
-        <v>521.55</v>
+        <v>18.73</v>
       </c>
       <c r="J143" t="n">
-        <v>229795</v>
+        <v>445648</v>
       </c>
       <c r="K143" t="n">
-        <v>267493</v>
+        <v>353517</v>
       </c>
       <c r="L143" t="n">
-        <v>541</v>
+        <v>19.85</v>
       </c>
       <c r="M143" t="n">
-        <v>506</v>
+        <v>17.9</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -25236,52 +25246,52 @@
         </is>
       </c>
       <c r="O143" t="n">
-        <v>-9970</v>
+        <v>90038</v>
       </c>
       <c r="P143" t="n">
-        <v>206456</v>
+        <v>179227</v>
       </c>
       <c r="Q143" t="n">
-        <v>302021</v>
+        <v>-234383</v>
       </c>
       <c r="R143" t="n">
-        <v>99038</v>
+        <v>-183593</v>
       </c>
       <c r="S143" t="n">
-        <v>-12443</v>
+        <v>90038</v>
       </c>
       <c r="T143" t="n">
-        <v>203875</v>
+        <v>180227</v>
       </c>
       <c r="U143" t="n">
-        <v>298065</v>
+        <v>-229106</v>
       </c>
       <c r="V143" t="n">
-        <v>38231</v>
+        <v>-189407</v>
       </c>
       <c r="W143" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>54000</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>-527</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>-1419</v>
+        <v>-1000</v>
       </c>
       <c r="AC143" t="n">
-        <v>-44</v>
+        <v>-5277</v>
       </c>
       <c r="AD143" t="n">
-        <v>6807</v>
+        <v>5814</v>
       </c>
       <c r="AE143" t="n">
         <v>20</v>
@@ -25290,16 +25300,16 @@
         <v>20</v>
       </c>
       <c r="AG143" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="AH143" t="n">
-        <v>40</v>
+        <v>-5</v>
       </c>
       <c r="AI143" t="n">
         <v>0</v>
       </c>
       <c r="AJ143" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
@@ -25307,25 +25317,25 @@
         </is>
       </c>
       <c r="AL143" t="n">
-        <v>-16</v>
+        <v>16</v>
       </c>
       <c r="AM143" t="n">
-        <v>-44.44</v>
+        <v>400</v>
       </c>
       <c r="AN143" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="AO143" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
@@ -25340,17 +25350,17 @@
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、黃金交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>5日法人買超、外資投信同步買超</t>
+          <t>短線籌碼止穩、5日法人賣超</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、短線籌碼止穩、5日法人賣超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -25531,17 +25541,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>00692.TW</t>
+          <t>2207.TW</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>富邦公司治理</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -25555,28 +25565,28 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>99</v>
+        <v>518</v>
       </c>
       <c r="G145" t="n">
-        <v>99.13</v>
+        <v>516.4</v>
       </c>
       <c r="H145" t="n">
-        <v>97.88</v>
+        <v>514.2</v>
       </c>
       <c r="I145" t="n">
-        <v>95.62</v>
+        <v>521.55</v>
       </c>
       <c r="J145" t="n">
-        <v>621175</v>
+        <v>229795</v>
       </c>
       <c r="K145" t="n">
-        <v>782490</v>
+        <v>267493</v>
       </c>
       <c r="L145" t="n">
-        <v>100.1</v>
+        <v>541</v>
       </c>
       <c r="M145" t="n">
-        <v>90.90000000000001</v>
+        <v>506</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -25584,52 +25594,52 @@
         </is>
       </c>
       <c r="O145" t="n">
-        <v>-90933</v>
+        <v>-9970</v>
       </c>
       <c r="P145" t="n">
-        <v>511477</v>
+        <v>206456</v>
       </c>
       <c r="Q145" t="n">
-        <v>777074</v>
+        <v>302021</v>
       </c>
       <c r="R145" t="n">
-        <v>2112826</v>
+        <v>99038</v>
       </c>
       <c r="S145" t="n">
-        <v>-15042</v>
+        <v>-12443</v>
       </c>
       <c r="T145" t="n">
-        <v>-225118</v>
+        <v>203875</v>
       </c>
       <c r="U145" t="n">
-        <v>74909</v>
+        <v>298065</v>
       </c>
       <c r="V145" t="n">
-        <v>-59064</v>
+        <v>38231</v>
       </c>
       <c r="W145" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="X145" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="Y145" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="AA145" t="n">
-        <v>-75891</v>
+        <v>-527</v>
       </c>
       <c r="AB145" t="n">
-        <v>736595</v>
+        <v>-1419</v>
       </c>
       <c r="AC145" t="n">
-        <v>702165</v>
+        <v>-44</v>
       </c>
       <c r="AD145" t="n">
-        <v>2171890</v>
+        <v>6807</v>
       </c>
       <c r="AE145" t="n">
         <v>20</v>
@@ -25638,33 +25648,33 @@
         <v>20</v>
       </c>
       <c r="AG145" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AL145" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>-44.44</v>
+      </c>
+      <c r="AN145" t="n">
         <v>20</v>
       </c>
-      <c r="AH145" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ145" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AL145" t="n">
-        <v>-28</v>
-      </c>
-      <c r="AM145" t="n">
-        <v>-58.33</v>
-      </c>
-      <c r="AN145" t="n">
-        <v>0</v>
-      </c>
       <c r="AO145" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
@@ -25673,7 +25683,7 @@
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
@@ -25688,29 +25698,29 @@
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日高點</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、接近20日高點、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日低點、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1789.TW</t>
+          <t>3680.TWO</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>神隆</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -25729,28 +25739,28 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>19.1</v>
+        <v>571</v>
       </c>
       <c r="G146" t="n">
-        <v>18.76</v>
+        <v>562.8</v>
       </c>
       <c r="H146" t="n">
-        <v>18.76</v>
+        <v>553.8</v>
       </c>
       <c r="I146" t="n">
-        <v>18.73</v>
+        <v>540.08</v>
       </c>
       <c r="J146" t="n">
-        <v>445648</v>
+        <v>1165000</v>
       </c>
       <c r="K146" t="n">
-        <v>353517</v>
+        <v>1561400</v>
       </c>
       <c r="L146" t="n">
-        <v>19.85</v>
+        <v>594</v>
       </c>
       <c r="M146" t="n">
-        <v>17.9</v>
+        <v>488.5</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
@@ -25758,28 +25768,28 @@
         </is>
       </c>
       <c r="O146" t="n">
-        <v>90038</v>
+        <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>179227</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>-234383</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>-183593</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>90038</v>
+        <v>0</v>
       </c>
       <c r="T146" t="n">
-        <v>180227</v>
+        <v>0</v>
       </c>
       <c r="U146" t="n">
-        <v>-229106</v>
+        <v>0</v>
       </c>
       <c r="V146" t="n">
-        <v>-189407</v>
+        <v>0</v>
       </c>
       <c r="W146" t="n">
         <v>0</v>
@@ -25797,82 +25807,82 @@
         <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
-        <v>-5277</v>
+        <v>0</v>
       </c>
       <c r="AD146" t="n">
-        <v>5814</v>
+        <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF146" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG146" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AL146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN146" t="n">
         <v>55</v>
       </c>
-      <c r="AH146" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ146" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AL146" t="n">
-        <v>16</v>
-      </c>
-      <c r="AM146" t="n">
-        <v>400</v>
-      </c>
-      <c r="AN146" t="n">
-        <v>70</v>
-      </c>
       <c r="AO146" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>⚠️整理</t>
+          <t>❌避開</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>整理觀察</t>
+          <t>觀望</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、短線籌碼止穩、5日法人賣超。多空訊號混合，建議降低追價衝動。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -26053,12 +26063,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3680.TWO</t>
+          <t>3293.TWO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -26077,28 +26087,28 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>571</v>
+        <v>788</v>
       </c>
       <c r="G148" t="n">
-        <v>562.8</v>
+        <v>786.6</v>
       </c>
       <c r="H148" t="n">
-        <v>553.8</v>
+        <v>780.4</v>
       </c>
       <c r="I148" t="n">
-        <v>540.08</v>
+        <v>745.85</v>
       </c>
       <c r="J148" t="n">
-        <v>1165000</v>
+        <v>1068000</v>
       </c>
       <c r="K148" t="n">
-        <v>1561400</v>
+        <v>1524600</v>
       </c>
       <c r="L148" t="n">
-        <v>594</v>
+        <v>819</v>
       </c>
       <c r="M148" t="n">
-        <v>488.5</v>
+        <v>687</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
@@ -26169,7 +26179,7 @@
         <v>0</v>
       </c>
       <c r="AJ148" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
@@ -26177,25 +26187,25 @@
         </is>
       </c>
       <c r="AL148" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AM148" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="AN148" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AO148" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
@@ -27445,12 +27455,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3293.TWO</t>
+          <t>1514.TW</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -27469,28 +27479,28 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>788</v>
+        <v>102.5</v>
       </c>
       <c r="G156" t="n">
-        <v>786.6</v>
+        <v>102.8</v>
       </c>
       <c r="H156" t="n">
-        <v>780.4</v>
+        <v>102.75</v>
       </c>
       <c r="I156" t="n">
-        <v>745.85</v>
+        <v>101.99</v>
       </c>
       <c r="J156" t="n">
-        <v>1068000</v>
+        <v>790867</v>
       </c>
       <c r="K156" t="n">
-        <v>1524600</v>
+        <v>1092443</v>
       </c>
       <c r="L156" t="n">
-        <v>819</v>
+        <v>105.5</v>
       </c>
       <c r="M156" t="n">
-        <v>687</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
@@ -27498,52 +27508,52 @@
         </is>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>-27667</v>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>412208</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>906576</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>1490858</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>-27550</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>403859</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>879850</v>
       </c>
       <c r="V156" t="n">
-        <v>0</v>
+        <v>1470510</v>
       </c>
       <c r="W156" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X156" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>-2117</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>-1651</v>
       </c>
       <c r="AC156" t="n">
-        <v>0</v>
+        <v>-3274</v>
       </c>
       <c r="AD156" t="n">
-        <v>0</v>
+        <v>-13652</v>
       </c>
       <c r="AE156" t="n">
         <v>18</v>
@@ -27552,16 +27562,16 @@
         <v>18</v>
       </c>
       <c r="AG156" t="n">
-        <v>45</v>
+        <v>-5</v>
       </c>
       <c r="AH156" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
       </c>
       <c r="AJ156" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="AK156" t="inlineStr">
         <is>
@@ -27569,25 +27579,25 @@
         </is>
       </c>
       <c r="AL156" t="n">
-        <v>16</v>
+        <v>-18</v>
       </c>
       <c r="AM156" t="n">
-        <v>800</v>
+        <v>-50</v>
       </c>
       <c r="AN156" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="AO156" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
@@ -27602,29 +27612,29 @@
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1514.TW</t>
+          <t>2880.TW</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -27643,28 +27653,28 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>102.5</v>
+        <v>45.8</v>
       </c>
       <c r="G157" t="n">
-        <v>102.8</v>
+        <v>45.52</v>
       </c>
       <c r="H157" t="n">
-        <v>102.75</v>
+        <v>45.46</v>
       </c>
       <c r="I157" t="n">
-        <v>101.99</v>
+        <v>45.95</v>
       </c>
       <c r="J157" t="n">
-        <v>790867</v>
+        <v>8913162</v>
       </c>
       <c r="K157" t="n">
-        <v>1092443</v>
+        <v>9425825</v>
       </c>
       <c r="L157" t="n">
-        <v>105.5</v>
+        <v>48.3</v>
       </c>
       <c r="M157" t="n">
-        <v>99.40000000000001</v>
+        <v>44</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
@@ -27672,70 +27682,70 @@
         </is>
       </c>
       <c r="O157" t="n">
-        <v>-27667</v>
+        <v>-1994441</v>
       </c>
       <c r="P157" t="n">
-        <v>412208</v>
+        <v>4045062</v>
       </c>
       <c r="Q157" t="n">
-        <v>906576</v>
+        <v>4910286</v>
       </c>
       <c r="R157" t="n">
-        <v>1490858</v>
+        <v>3992612</v>
       </c>
       <c r="S157" t="n">
-        <v>-27550</v>
+        <v>-3423755</v>
       </c>
       <c r="T157" t="n">
-        <v>403859</v>
+        <v>1401733</v>
       </c>
       <c r="U157" t="n">
-        <v>879850</v>
+        <v>-1833174</v>
       </c>
       <c r="V157" t="n">
-        <v>1470510</v>
+        <v>-10693226</v>
       </c>
       <c r="W157" t="n">
-        <v>2000</v>
+        <v>21595</v>
       </c>
       <c r="X157" t="n">
-        <v>10000</v>
+        <v>-61150</v>
       </c>
       <c r="Y157" t="n">
-        <v>30000</v>
+        <v>1781445</v>
       </c>
       <c r="Z157" t="n">
-        <v>34000</v>
+        <v>4707445</v>
       </c>
       <c r="AA157" t="n">
-        <v>-2117</v>
+        <v>1407719</v>
       </c>
       <c r="AB157" t="n">
-        <v>-1651</v>
+        <v>2704479</v>
       </c>
       <c r="AC157" t="n">
-        <v>-3274</v>
+        <v>4962015</v>
       </c>
       <c r="AD157" t="n">
-        <v>-13652</v>
+        <v>9978393</v>
       </c>
       <c r="AE157" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF157" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG157" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="AH157" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
       </c>
       <c r="AJ157" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
@@ -27743,16 +27753,16 @@
         </is>
       </c>
       <c r="AL157" t="n">
-        <v>-18</v>
+        <v>-10</v>
       </c>
       <c r="AM157" t="n">
-        <v>-50</v>
+        <v>-38.46</v>
       </c>
       <c r="AN157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AO157" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
@@ -27761,7 +27771,7 @@
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
@@ -27776,17 +27786,17 @@
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -27967,12 +27977,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2880.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -27991,28 +28001,28 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>45.8</v>
+        <v>202</v>
       </c>
       <c r="G159" t="n">
-        <v>45.52</v>
+        <v>210.6</v>
       </c>
       <c r="H159" t="n">
-        <v>45.46</v>
+        <v>209.7</v>
       </c>
       <c r="I159" t="n">
-        <v>45.95</v>
+        <v>195.07</v>
       </c>
       <c r="J159" t="n">
-        <v>8913162</v>
+        <v>3361860</v>
       </c>
       <c r="K159" t="n">
-        <v>9425825</v>
+        <v>4379258</v>
       </c>
       <c r="L159" t="n">
-        <v>48.3</v>
+        <v>223.5</v>
       </c>
       <c r="M159" t="n">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
@@ -28020,61 +28030,61 @@
         </is>
       </c>
       <c r="O159" t="n">
-        <v>-1994441</v>
+        <v>-353007</v>
       </c>
       <c r="P159" t="n">
-        <v>4045062</v>
+        <v>1142596</v>
       </c>
       <c r="Q159" t="n">
-        <v>4910286</v>
+        <v>4129551</v>
       </c>
       <c r="R159" t="n">
-        <v>3992612</v>
+        <v>8237526</v>
       </c>
       <c r="S159" t="n">
-        <v>-3423755</v>
+        <v>-225985</v>
       </c>
       <c r="T159" t="n">
-        <v>1401733</v>
+        <v>1261253</v>
       </c>
       <c r="U159" t="n">
-        <v>-1833174</v>
+        <v>4021309</v>
       </c>
       <c r="V159" t="n">
-        <v>-10693226</v>
+        <v>7950434</v>
       </c>
       <c r="W159" t="n">
-        <v>21595</v>
+        <v>0</v>
       </c>
       <c r="X159" t="n">
-        <v>-61150</v>
+        <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>1781445</v>
+        <v>0</v>
       </c>
       <c r="Z159" t="n">
-        <v>4707445</v>
+        <v>-8000</v>
       </c>
       <c r="AA159" t="n">
-        <v>1407719</v>
+        <v>-127022</v>
       </c>
       <c r="AB159" t="n">
-        <v>2704479</v>
+        <v>-118657</v>
       </c>
       <c r="AC159" t="n">
-        <v>4962015</v>
+        <v>108242</v>
       </c>
       <c r="AD159" t="n">
-        <v>9978393</v>
+        <v>295092</v>
       </c>
       <c r="AE159" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF159" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG159" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AH159" t="n">
         <v>30</v>
@@ -28091,16 +28101,16 @@
         </is>
       </c>
       <c r="AL159" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AM159" t="n">
-        <v>-38.46</v>
+        <v>-46.15</v>
       </c>
       <c r="AN159" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AO159" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
@@ -28109,7 +28119,7 @@
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
@@ -28124,17 +28134,17 @@
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、接近20日低點、5日法人明顯買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -28663,12 +28673,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>2534.TW</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>宏盛</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -28687,28 +28697,28 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>202</v>
+        <v>16.65</v>
       </c>
       <c r="G163" t="n">
-        <v>210.6</v>
+        <v>16.62</v>
       </c>
       <c r="H163" t="n">
-        <v>209.7</v>
+        <v>16.74</v>
       </c>
       <c r="I163" t="n">
-        <v>195.07</v>
+        <v>16.81</v>
       </c>
       <c r="J163" t="n">
-        <v>3361860</v>
+        <v>137378</v>
       </c>
       <c r="K163" t="n">
-        <v>4379258</v>
+        <v>222456</v>
       </c>
       <c r="L163" t="n">
-        <v>223.5</v>
+        <v>17.35</v>
       </c>
       <c r="M163" t="n">
-        <v>165</v>
+        <v>16.5</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
@@ -28716,28 +28726,28 @@
         </is>
       </c>
       <c r="O163" t="n">
-        <v>-353007</v>
+        <v>45000</v>
       </c>
       <c r="P163" t="n">
-        <v>1142596</v>
+        <v>17013</v>
       </c>
       <c r="Q163" t="n">
-        <v>4129551</v>
+        <v>148113</v>
       </c>
       <c r="R163" t="n">
-        <v>8237526</v>
+        <v>411693</v>
       </c>
       <c r="S163" t="n">
-        <v>-225985</v>
+        <v>45000</v>
       </c>
       <c r="T163" t="n">
-        <v>1261253</v>
+        <v>17013</v>
       </c>
       <c r="U163" t="n">
-        <v>4021309</v>
+        <v>148113</v>
       </c>
       <c r="V163" t="n">
-        <v>7950434</v>
+        <v>411051</v>
       </c>
       <c r="W163" t="n">
         <v>0</v>
@@ -28749,19 +28759,19 @@
         <v>0</v>
       </c>
       <c r="Z163" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>-127022</v>
+        <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>-118657</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
-        <v>108242</v>
+        <v>0</v>
       </c>
       <c r="AD163" t="n">
-        <v>295092</v>
+        <v>642</v>
       </c>
       <c r="AE163" t="n">
         <v>14</v>
@@ -28770,16 +28780,16 @@
         <v>14</v>
       </c>
       <c r="AG163" t="n">
-        <v>5</v>
+        <v>-15</v>
       </c>
       <c r="AH163" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI163" t="n">
         <v>0</v>
       </c>
       <c r="AJ163" t="n">
-        <v>26</v>
+        <v>-2</v>
       </c>
       <c r="AK163" t="inlineStr">
         <is>
@@ -28787,25 +28797,25 @@
         </is>
       </c>
       <c r="AL163" t="n">
-        <v>-12</v>
+        <v>16</v>
       </c>
       <c r="AM163" t="n">
-        <v>-46.15</v>
+        <v>800</v>
       </c>
       <c r="AN163" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AO163" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
@@ -28820,29 +28830,29 @@
       </c>
       <c r="AT163" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2534.TW</t>
+          <t>2329.TW</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>宏盛</t>
+          <t>華泰</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -28861,28 +28871,28 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>16.65</v>
+        <v>44.5</v>
       </c>
       <c r="G164" t="n">
-        <v>16.62</v>
+        <v>45.05</v>
       </c>
       <c r="H164" t="n">
-        <v>16.74</v>
+        <v>44.7</v>
       </c>
       <c r="I164" t="n">
-        <v>16.81</v>
+        <v>43.69</v>
       </c>
       <c r="J164" t="n">
-        <v>137378</v>
+        <v>4606023</v>
       </c>
       <c r="K164" t="n">
-        <v>222456</v>
+        <v>3258705</v>
       </c>
       <c r="L164" t="n">
-        <v>17.35</v>
+        <v>46.25</v>
       </c>
       <c r="M164" t="n">
-        <v>16.5</v>
+        <v>40.9</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
@@ -28890,28 +28900,28 @@
         </is>
       </c>
       <c r="O164" t="n">
-        <v>45000</v>
+        <v>-1417282</v>
       </c>
       <c r="P164" t="n">
-        <v>17013</v>
+        <v>220038</v>
       </c>
       <c r="Q164" t="n">
-        <v>148113</v>
+        <v>295456</v>
       </c>
       <c r="R164" t="n">
-        <v>411693</v>
+        <v>1198593</v>
       </c>
       <c r="S164" t="n">
-        <v>45000</v>
+        <v>-1376396</v>
       </c>
       <c r="T164" t="n">
-        <v>17013</v>
+        <v>276091</v>
       </c>
       <c r="U164" t="n">
-        <v>148113</v>
+        <v>365036</v>
       </c>
       <c r="V164" t="n">
-        <v>411051</v>
+        <v>1279950</v>
       </c>
       <c r="W164" t="n">
         <v>0</v>
@@ -28926,16 +28936,16 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>-40886</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>-56053</v>
       </c>
       <c r="AC164" t="n">
-        <v>0</v>
+        <v>-69580</v>
       </c>
       <c r="AD164" t="n">
-        <v>642</v>
+        <v>-81357</v>
       </c>
       <c r="AE164" t="n">
         <v>14</v>
@@ -28944,16 +28954,16 @@
         <v>14</v>
       </c>
       <c r="AG164" t="n">
-        <v>-15</v>
+        <v>15</v>
       </c>
       <c r="AH164" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AI164" t="n">
         <v>0</v>
       </c>
       <c r="AJ164" t="n">
-        <v>-2</v>
+        <v>48</v>
       </c>
       <c r="AK164" t="inlineStr">
         <is>
@@ -28961,25 +28971,25 @@
         </is>
       </c>
       <c r="AL164" t="n">
-        <v>16</v>
+        <v>-34</v>
       </c>
       <c r="AM164" t="n">
-        <v>800</v>
+        <v>-70.83</v>
       </c>
       <c r="AN164" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="AO164" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
@@ -28994,17 +29004,17 @@
       </c>
       <c r="AT164" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -29185,12 +29195,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4123.TWO</t>
+          <t>6202.TW</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -29209,28 +29219,28 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>31.35</v>
+        <v>58.9</v>
       </c>
       <c r="G166" t="n">
-        <v>31.06</v>
+        <v>60.88</v>
       </c>
       <c r="H166" t="n">
-        <v>31.13</v>
+        <v>59.87</v>
       </c>
       <c r="I166" t="n">
-        <v>30.87</v>
+        <v>57.8</v>
       </c>
       <c r="J166" t="n">
-        <v>1334000</v>
+        <v>1845781</v>
       </c>
       <c r="K166" t="n">
-        <v>1170800</v>
+        <v>2779674</v>
       </c>
       <c r="L166" t="n">
-        <v>31.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="M166" t="n">
-        <v>30</v>
+        <v>53.5</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
@@ -29238,28 +29248,28 @@
         </is>
       </c>
       <c r="O166" t="n">
-        <v>0</v>
+        <v>-542874</v>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>100494</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>715158</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>652773</v>
       </c>
       <c r="S166" t="n">
-        <v>0</v>
+        <v>-531428</v>
       </c>
       <c r="T166" t="n">
-        <v>0</v>
+        <v>141161</v>
       </c>
       <c r="U166" t="n">
-        <v>0</v>
+        <v>694345</v>
       </c>
       <c r="V166" t="n">
-        <v>0</v>
+        <v>567457</v>
       </c>
       <c r="W166" t="n">
         <v>0</v>
@@ -29271,19 +29281,19 @@
         <v>0</v>
       </c>
       <c r="Z166" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>-11446</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>-40667</v>
       </c>
       <c r="AC166" t="n">
-        <v>0</v>
+        <v>20813</v>
       </c>
       <c r="AD166" t="n">
-        <v>0</v>
+        <v>35316</v>
       </c>
       <c r="AE166" t="n">
         <v>14</v>
@@ -29292,16 +29302,16 @@
         <v>14</v>
       </c>
       <c r="AG166" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="AH166" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI166" t="n">
         <v>0</v>
       </c>
       <c r="AJ166" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AK166" t="inlineStr">
         <is>
@@ -29309,16 +29319,16 @@
         </is>
       </c>
       <c r="AL166" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="AM166" t="n">
-        <v>0</v>
+        <v>-46.15</v>
       </c>
       <c r="AN166" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AO166" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
@@ -29327,7 +29337,7 @@
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
@@ -29342,17 +29352,17 @@
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、接近20日高點、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -29533,12 +29543,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2329.TW</t>
+          <t>4123.TWO</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>華泰</t>
+          <t>晟德</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -29557,28 +29567,28 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>44.5</v>
+        <v>31.35</v>
       </c>
       <c r="G168" t="n">
-        <v>45.05</v>
+        <v>31.06</v>
       </c>
       <c r="H168" t="n">
-        <v>44.7</v>
+        <v>31.13</v>
       </c>
       <c r="I168" t="n">
-        <v>43.69</v>
+        <v>30.87</v>
       </c>
       <c r="J168" t="n">
-        <v>4606023</v>
+        <v>1334000</v>
       </c>
       <c r="K168" t="n">
-        <v>3258705</v>
+        <v>1170800</v>
       </c>
       <c r="L168" t="n">
-        <v>46.25</v>
+        <v>31.5</v>
       </c>
       <c r="M168" t="n">
-        <v>40.9</v>
+        <v>30</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -29586,28 +29596,28 @@
         </is>
       </c>
       <c r="O168" t="n">
-        <v>-1417282</v>
+        <v>0</v>
       </c>
       <c r="P168" t="n">
-        <v>220038</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>295456</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>1198593</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>-1376396</v>
+        <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>276091</v>
+        <v>0</v>
       </c>
       <c r="U168" t="n">
-        <v>365036</v>
+        <v>0</v>
       </c>
       <c r="V168" t="n">
-        <v>1279950</v>
+        <v>0</v>
       </c>
       <c r="W168" t="n">
         <v>0</v>
@@ -29622,16 +29632,16 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>-40886</v>
+        <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>-56053</v>
+        <v>0</v>
       </c>
       <c r="AC168" t="n">
-        <v>-69580</v>
+        <v>0</v>
       </c>
       <c r="AD168" t="n">
-        <v>-81357</v>
+        <v>0</v>
       </c>
       <c r="AE168" t="n">
         <v>14</v>
@@ -29640,16 +29650,16 @@
         <v>14</v>
       </c>
       <c r="AG168" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="AH168" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI168" t="n">
         <v>0</v>
       </c>
       <c r="AJ168" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="AK168" t="inlineStr">
         <is>
@@ -29657,10 +29667,10 @@
         </is>
       </c>
       <c r="AL168" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="AM168" t="n">
-        <v>-70.83</v>
+        <v>0</v>
       </c>
       <c r="AN168" t="n">
         <v>25</v>
@@ -29675,7 +29685,7 @@
       </c>
       <c r="AQ168" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AR168" t="inlineStr">
@@ -29690,17 +29700,17 @@
       </c>
       <c r="AT168" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、量能溫和放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、接近20日高點、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -30229,12 +30239,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>6202.TW</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -30253,28 +30263,28 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>58.9</v>
+        <v>177</v>
       </c>
       <c r="G172" t="n">
-        <v>60.88</v>
+        <v>178.8</v>
       </c>
       <c r="H172" t="n">
-        <v>59.87</v>
+        <v>177.15</v>
       </c>
       <c r="I172" t="n">
-        <v>57.8</v>
+        <v>174.43</v>
       </c>
       <c r="J172" t="n">
-        <v>1845781</v>
+        <v>70323153</v>
       </c>
       <c r="K172" t="n">
-        <v>2779674</v>
+        <v>71564064</v>
       </c>
       <c r="L172" t="n">
-        <v>64.09999999999999</v>
+        <v>190.5</v>
       </c>
       <c r="M172" t="n">
-        <v>53.5</v>
+        <v>158.5</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
@@ -30282,52 +30292,52 @@
         </is>
       </c>
       <c r="O172" t="n">
-        <v>-542874</v>
+        <v>-14590377</v>
       </c>
       <c r="P172" t="n">
-        <v>100494</v>
+        <v>-5500799</v>
       </c>
       <c r="Q172" t="n">
-        <v>715158</v>
+        <v>8208577</v>
       </c>
       <c r="R172" t="n">
-        <v>652773</v>
+        <v>59770154</v>
       </c>
       <c r="S172" t="n">
-        <v>-531428</v>
+        <v>-14220689</v>
       </c>
       <c r="T172" t="n">
-        <v>141161</v>
+        <v>13596778</v>
       </c>
       <c r="U172" t="n">
-        <v>694345</v>
+        <v>37785539</v>
       </c>
       <c r="V172" t="n">
-        <v>567457</v>
+        <v>91976442</v>
       </c>
       <c r="W172" t="n">
-        <v>0</v>
+        <v>-250134</v>
       </c>
       <c r="X172" t="n">
-        <v>0</v>
+        <v>-18344140</v>
       </c>
       <c r="Y172" t="n">
-        <v>0</v>
+        <v>-30416415</v>
       </c>
       <c r="Z172" t="n">
-        <v>50000</v>
+        <v>-36352416</v>
       </c>
       <c r="AA172" t="n">
-        <v>-11446</v>
+        <v>-119554</v>
       </c>
       <c r="AB172" t="n">
-        <v>-40667</v>
+        <v>-753437</v>
       </c>
       <c r="AC172" t="n">
-        <v>20813</v>
+        <v>839453</v>
       </c>
       <c r="AD172" t="n">
-        <v>35316</v>
+        <v>4146128</v>
       </c>
       <c r="AE172" t="n">
         <v>14</v>
@@ -30345,7 +30355,7 @@
         <v>0</v>
       </c>
       <c r="AJ172" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AK172" t="inlineStr">
         <is>
@@ -30353,10 +30363,10 @@
         </is>
       </c>
       <c r="AL172" t="n">
-        <v>-12</v>
+        <v>-28</v>
       </c>
       <c r="AM172" t="n">
-        <v>-46.15</v>
+        <v>-66.67</v>
       </c>
       <c r="AN172" t="n">
         <v>10</v>
@@ -30391,12 +30401,12 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -30577,12 +30587,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>3047.TW</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>訊舟</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -30601,28 +30611,28 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>177</v>
+        <v>14.35</v>
       </c>
       <c r="G174" t="n">
-        <v>178.8</v>
+        <v>14.45</v>
       </c>
       <c r="H174" t="n">
-        <v>177.15</v>
+        <v>14.53</v>
       </c>
       <c r="I174" t="n">
-        <v>174.43</v>
+        <v>14.22</v>
       </c>
       <c r="J174" t="n">
-        <v>70323153</v>
+        <v>323561</v>
       </c>
       <c r="K174" t="n">
-        <v>71564064</v>
+        <v>453484</v>
       </c>
       <c r="L174" t="n">
-        <v>190.5</v>
+        <v>15.3</v>
       </c>
       <c r="M174" t="n">
-        <v>158.5</v>
+        <v>13.3</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
@@ -30630,70 +30640,70 @@
         </is>
       </c>
       <c r="O174" t="n">
-        <v>-14590377</v>
+        <v>56314</v>
       </c>
       <c r="P174" t="n">
-        <v>-5500799</v>
+        <v>188880</v>
       </c>
       <c r="Q174" t="n">
-        <v>8208577</v>
+        <v>160403</v>
       </c>
       <c r="R174" t="n">
-        <v>59770154</v>
+        <v>478373</v>
       </c>
       <c r="S174" t="n">
-        <v>-14220689</v>
+        <v>56270</v>
       </c>
       <c r="T174" t="n">
-        <v>13596778</v>
+        <v>191836</v>
       </c>
       <c r="U174" t="n">
-        <v>37785539</v>
+        <v>163836</v>
       </c>
       <c r="V174" t="n">
-        <v>91976442</v>
+        <v>467288</v>
       </c>
       <c r="W174" t="n">
-        <v>-250134</v>
+        <v>0</v>
       </c>
       <c r="X174" t="n">
-        <v>-18344140</v>
+        <v>0</v>
       </c>
       <c r="Y174" t="n">
-        <v>-30416415</v>
+        <v>0</v>
       </c>
       <c r="Z174" t="n">
-        <v>-36352416</v>
+        <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>-119554</v>
+        <v>44</v>
       </c>
       <c r="AB174" t="n">
-        <v>-753437</v>
+        <v>-2956</v>
       </c>
       <c r="AC174" t="n">
-        <v>839453</v>
+        <v>-3433</v>
       </c>
       <c r="AD174" t="n">
-        <v>4146128</v>
+        <v>11085</v>
       </c>
       <c r="AE174" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AF174" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG174" t="n">
-        <v>5</v>
+        <v>-20</v>
       </c>
       <c r="AH174" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI174" t="n">
         <v>0</v>
       </c>
       <c r="AJ174" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
@@ -30701,16 +30711,16 @@
         </is>
       </c>
       <c r="AL174" t="n">
-        <v>-28</v>
+        <v>4</v>
       </c>
       <c r="AM174" t="n">
-        <v>-66.67</v>
+        <v>50</v>
       </c>
       <c r="AN174" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AO174" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
@@ -30719,7 +30729,7 @@
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
@@ -30734,17 +30744,17 @@
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -31447,17 +31457,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>3047.TW</t>
+          <t>00900.TW</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>訊舟</t>
+          <t>富邦特選高股息30</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -31471,28 +31481,28 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>14.35</v>
+        <v>19.52</v>
       </c>
       <c r="G179" t="n">
-        <v>14.45</v>
+        <v>19.54</v>
       </c>
       <c r="H179" t="n">
-        <v>14.53</v>
+        <v>19.5</v>
       </c>
       <c r="I179" t="n">
-        <v>14.22</v>
+        <v>19.58</v>
       </c>
       <c r="J179" t="n">
-        <v>323561</v>
+        <v>1903209</v>
       </c>
       <c r="K179" t="n">
-        <v>453484</v>
+        <v>5191611</v>
       </c>
       <c r="L179" t="n">
-        <v>15.3</v>
+        <v>19.93</v>
       </c>
       <c r="M179" t="n">
-        <v>13.3</v>
+        <v>19.19</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
@@ -31500,28 +31510,28 @@
         </is>
       </c>
       <c r="O179" t="n">
-        <v>56314</v>
+        <v>465457</v>
       </c>
       <c r="P179" t="n">
-        <v>188880</v>
+        <v>11553952</v>
       </c>
       <c r="Q179" t="n">
-        <v>160403</v>
+        <v>19730399</v>
       </c>
       <c r="R179" t="n">
-        <v>478373</v>
+        <v>28711947</v>
       </c>
       <c r="S179" t="n">
-        <v>56270</v>
+        <v>470000</v>
       </c>
       <c r="T179" t="n">
-        <v>191836</v>
+        <v>4461000</v>
       </c>
       <c r="U179" t="n">
-        <v>163836</v>
+        <v>9251215</v>
       </c>
       <c r="V179" t="n">
-        <v>467288</v>
+        <v>13887326</v>
       </c>
       <c r="W179" t="n">
         <v>0</v>
@@ -31536,16 +31546,16 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>44</v>
+        <v>-4543</v>
       </c>
       <c r="AB179" t="n">
-        <v>-2956</v>
+        <v>7092952</v>
       </c>
       <c r="AC179" t="n">
-        <v>-3433</v>
+        <v>10479184</v>
       </c>
       <c r="AD179" t="n">
-        <v>11085</v>
+        <v>14824621</v>
       </c>
       <c r="AE179" t="n">
         <v>12</v>
@@ -31554,16 +31564,16 @@
         <v>12</v>
       </c>
       <c r="AG179" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="AH179" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AI179" t="n">
         <v>0</v>
       </c>
       <c r="AJ179" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
@@ -31571,16 +31581,16 @@
         </is>
       </c>
       <c r="AL179" t="n">
-        <v>4</v>
+        <v>-16</v>
       </c>
       <c r="AM179" t="n">
-        <v>50</v>
+        <v>-57.14</v>
       </c>
       <c r="AN179" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AO179" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
@@ -31589,7 +31599,7 @@
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
@@ -31604,17 +31614,17 @@
       </c>
       <c r="AT179" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -32143,17 +32153,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>00900.TW</t>
+          <t>2379.TW</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>富邦特選高股息30</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -32167,28 +32177,28 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>19.52</v>
+        <v>749</v>
       </c>
       <c r="G183" t="n">
-        <v>19.54</v>
+        <v>750.8</v>
       </c>
       <c r="H183" t="n">
-        <v>19.5</v>
+        <v>754.6</v>
       </c>
       <c r="I183" t="n">
-        <v>19.58</v>
+        <v>736.2</v>
       </c>
       <c r="J183" t="n">
-        <v>1903209</v>
+        <v>1176621</v>
       </c>
       <c r="K183" t="n">
-        <v>5191611</v>
+        <v>1578286</v>
       </c>
       <c r="L183" t="n">
-        <v>19.93</v>
+        <v>794</v>
       </c>
       <c r="M183" t="n">
-        <v>19.19</v>
+        <v>686</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
@@ -32196,52 +32206,52 @@
         </is>
       </c>
       <c r="O183" t="n">
-        <v>465457</v>
+        <v>267564</v>
       </c>
       <c r="P183" t="n">
-        <v>11553952</v>
+        <v>327556</v>
       </c>
       <c r="Q183" t="n">
-        <v>19730399</v>
+        <v>366836</v>
       </c>
       <c r="R183" t="n">
-        <v>28711947</v>
+        <v>3533426</v>
       </c>
       <c r="S183" t="n">
-        <v>470000</v>
+        <v>95044</v>
       </c>
       <c r="T183" t="n">
-        <v>4461000</v>
+        <v>-90262</v>
       </c>
       <c r="U183" t="n">
-        <v>9251215</v>
+        <v>-357986</v>
       </c>
       <c r="V183" t="n">
-        <v>13887326</v>
+        <v>1508664</v>
       </c>
       <c r="W183" t="n">
-        <v>0</v>
+        <v>127000</v>
       </c>
       <c r="X183" t="n">
-        <v>0</v>
+        <v>338000</v>
       </c>
       <c r="Y183" t="n">
-        <v>0</v>
+        <v>547228</v>
       </c>
       <c r="Z183" t="n">
-        <v>0</v>
+        <v>1746228</v>
       </c>
       <c r="AA183" t="n">
-        <v>-4543</v>
+        <v>45520</v>
       </c>
       <c r="AB183" t="n">
-        <v>7092952</v>
+        <v>79818</v>
       </c>
       <c r="AC183" t="n">
-        <v>10479184</v>
+        <v>177594</v>
       </c>
       <c r="AD183" t="n">
-        <v>14824621</v>
+        <v>278534</v>
       </c>
       <c r="AE183" t="n">
         <v>12</v>
@@ -32250,16 +32260,16 @@
         <v>12</v>
       </c>
       <c r="AG183" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="AH183" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI183" t="n">
         <v>0</v>
       </c>
       <c r="AJ183" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AK183" t="inlineStr">
         <is>
@@ -32267,16 +32277,16 @@
         </is>
       </c>
       <c r="AL183" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AM183" t="n">
-        <v>-57.14</v>
+        <v>0</v>
       </c>
       <c r="AN183" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO183" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
@@ -32285,7 +32295,7 @@
       </c>
       <c r="AQ183" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR183" t="inlineStr">
@@ -32300,17 +32310,17 @@
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -32491,12 +32501,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2379.TW</t>
+          <t>3019.TW</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>亞光</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -32515,28 +32525,28 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>749</v>
+        <v>137</v>
       </c>
       <c r="G185" t="n">
-        <v>750.8</v>
+        <v>139.3</v>
       </c>
       <c r="H185" t="n">
-        <v>754.6</v>
+        <v>137.55</v>
       </c>
       <c r="I185" t="n">
-        <v>736.2</v>
+        <v>137.12</v>
       </c>
       <c r="J185" t="n">
-        <v>1176621</v>
+        <v>1612834</v>
       </c>
       <c r="K185" t="n">
-        <v>1578286</v>
+        <v>2779824</v>
       </c>
       <c r="L185" t="n">
-        <v>794</v>
+        <v>143.5</v>
       </c>
       <c r="M185" t="n">
-        <v>686</v>
+        <v>131</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
@@ -32544,87 +32554,87 @@
         </is>
       </c>
       <c r="O185" t="n">
-        <v>267564</v>
+        <v>-110141</v>
       </c>
       <c r="P185" t="n">
-        <v>327556</v>
+        <v>542047</v>
       </c>
       <c r="Q185" t="n">
-        <v>366836</v>
+        <v>2484485</v>
       </c>
       <c r="R185" t="n">
-        <v>3533426</v>
+        <v>-166408</v>
       </c>
       <c r="S185" t="n">
-        <v>95044</v>
+        <v>41453</v>
       </c>
       <c r="T185" t="n">
-        <v>-90262</v>
+        <v>702911</v>
       </c>
       <c r="U185" t="n">
-        <v>-357986</v>
+        <v>2349418</v>
       </c>
       <c r="V185" t="n">
-        <v>1508664</v>
+        <v>-289093</v>
       </c>
       <c r="W185" t="n">
-        <v>127000</v>
+        <v>0</v>
       </c>
       <c r="X185" t="n">
-        <v>338000</v>
+        <v>0</v>
       </c>
       <c r="Y185" t="n">
-        <v>547228</v>
+        <v>0</v>
       </c>
       <c r="Z185" t="n">
-        <v>1746228</v>
+        <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>45520</v>
+        <v>-151594</v>
       </c>
       <c r="AB185" t="n">
-        <v>79818</v>
+        <v>-160864</v>
       </c>
       <c r="AC185" t="n">
-        <v>177594</v>
+        <v>135067</v>
       </c>
       <c r="AD185" t="n">
-        <v>278534</v>
+        <v>122685</v>
       </c>
       <c r="AE185" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF185" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG185" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AL185" t="n">
         <v>-20</v>
       </c>
-      <c r="AH185" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI185" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ185" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AL185" t="n">
-        <v>0</v>
-      </c>
       <c r="AM185" t="n">
-        <v>0</v>
+        <v>-66.67</v>
       </c>
       <c r="AN185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AO185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
@@ -32633,7 +32643,7 @@
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
@@ -32648,17 +32658,17 @@
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、投信買外資賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、法人連續偏買、5日法人買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -33361,12 +33371,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3019.TW</t>
+          <t>2006.TW</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -33385,28 +33395,28 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>137</v>
+        <v>85.3</v>
       </c>
       <c r="G190" t="n">
-        <v>139.3</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="H190" t="n">
-        <v>137.55</v>
+        <v>85.92</v>
       </c>
       <c r="I190" t="n">
-        <v>137.12</v>
+        <v>84.53</v>
       </c>
       <c r="J190" t="n">
-        <v>1612834</v>
+        <v>761729</v>
       </c>
       <c r="K190" t="n">
-        <v>2779824</v>
+        <v>1016472</v>
       </c>
       <c r="L190" t="n">
-        <v>143.5</v>
+        <v>89</v>
       </c>
       <c r="M190" t="n">
-        <v>131</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
@@ -33414,52 +33424,52 @@
         </is>
       </c>
       <c r="O190" t="n">
-        <v>-110141</v>
+        <v>-152663</v>
       </c>
       <c r="P190" t="n">
-        <v>542047</v>
+        <v>-106587</v>
       </c>
       <c r="Q190" t="n">
-        <v>2484485</v>
+        <v>244906</v>
       </c>
       <c r="R190" t="n">
-        <v>-166408</v>
+        <v>107984</v>
       </c>
       <c r="S190" t="n">
-        <v>41453</v>
+        <v>-181652</v>
       </c>
       <c r="T190" t="n">
-        <v>702911</v>
+        <v>517016</v>
       </c>
       <c r="U190" t="n">
-        <v>2349418</v>
+        <v>838195</v>
       </c>
       <c r="V190" t="n">
-        <v>-289093</v>
+        <v>567823</v>
       </c>
       <c r="W190" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="X190" t="n">
-        <v>0</v>
+        <v>-698259</v>
       </c>
       <c r="Y190" t="n">
-        <v>0</v>
+        <v>-702517</v>
       </c>
       <c r="Z190" t="n">
-        <v>0</v>
+        <v>-581033</v>
       </c>
       <c r="AA190" t="n">
-        <v>-151594</v>
+        <v>24989</v>
       </c>
       <c r="AB190" t="n">
-        <v>-160864</v>
+        <v>74656</v>
       </c>
       <c r="AC190" t="n">
-        <v>135067</v>
+        <v>109228</v>
       </c>
       <c r="AD190" t="n">
-        <v>122685</v>
+        <v>121194</v>
       </c>
       <c r="AE190" t="n">
         <v>10</v>
@@ -33468,16 +33478,16 @@
         <v>10</v>
       </c>
       <c r="AG190" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AH190" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AI190" t="n">
         <v>0</v>
       </c>
       <c r="AJ190" t="n">
-        <v>30</v>
+        <v>-8</v>
       </c>
       <c r="AK190" t="inlineStr">
         <is>
@@ -33485,25 +33495,25 @@
         </is>
       </c>
       <c r="AL190" t="n">
-        <v>-20</v>
+        <v>18</v>
       </c>
       <c r="AM190" t="n">
-        <v>-66.67</v>
+        <v>225</v>
       </c>
       <c r="AN190" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AO190" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
@@ -33518,29 +33528,29 @@
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2006.TW</t>
+          <t>3048.TW</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>益登</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -33559,125 +33569,125 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>85.3</v>
+        <v>57</v>
       </c>
       <c r="G191" t="n">
-        <v>86.04000000000001</v>
+        <v>54.2</v>
       </c>
       <c r="H191" t="n">
-        <v>85.92</v>
+        <v>52.89</v>
       </c>
       <c r="I191" t="n">
-        <v>84.53</v>
+        <v>51.75</v>
       </c>
       <c r="J191" t="n">
-        <v>761729</v>
+        <v>12195758</v>
       </c>
       <c r="K191" t="n">
-        <v>1016472</v>
+        <v>4430341</v>
       </c>
       <c r="L191" t="n">
-        <v>89</v>
+        <v>58.3</v>
       </c>
       <c r="M191" t="n">
-        <v>80.59999999999999</v>
+        <v>49.3</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>帶量突破20日高點</t>
         </is>
       </c>
       <c r="O191" t="n">
-        <v>-152663</v>
+        <v>-1681590</v>
       </c>
       <c r="P191" t="n">
-        <v>-106587</v>
+        <v>-1667794</v>
       </c>
       <c r="Q191" t="n">
-        <v>244906</v>
+        <v>-3002370</v>
       </c>
       <c r="R191" t="n">
-        <v>107984</v>
+        <v>-3370707</v>
       </c>
       <c r="S191" t="n">
-        <v>-181652</v>
+        <v>-1845911</v>
       </c>
       <c r="T191" t="n">
-        <v>517016</v>
+        <v>-1921114</v>
       </c>
       <c r="U191" t="n">
-        <v>838195</v>
+        <v>-3413893</v>
       </c>
       <c r="V191" t="n">
-        <v>567823</v>
+        <v>-3775830</v>
       </c>
       <c r="W191" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="X191" t="n">
-        <v>-698259</v>
+        <v>0</v>
       </c>
       <c r="Y191" t="n">
-        <v>-702517</v>
+        <v>0</v>
       </c>
       <c r="Z191" t="n">
-        <v>-581033</v>
+        <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>24989</v>
+        <v>164321</v>
       </c>
       <c r="AB191" t="n">
-        <v>74656</v>
+        <v>253320</v>
       </c>
       <c r="AC191" t="n">
-        <v>109228</v>
+        <v>411523</v>
       </c>
       <c r="AD191" t="n">
-        <v>121194</v>
+        <v>405123</v>
       </c>
       <c r="AE191" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>65</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AL191" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AN191" t="n">
         <v>10</v>
       </c>
-      <c r="AF191" t="n">
+      <c r="AO191" t="n">
         <v>10</v>
       </c>
-      <c r="AG191" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH191" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI191" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ191" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="AL191" t="n">
-        <v>18</v>
-      </c>
-      <c r="AM191" t="n">
-        <v>225</v>
-      </c>
-      <c r="AN191" t="n">
-        <v>35</v>
-      </c>
-      <c r="AO191" t="n">
-        <v>35</v>
-      </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、爆量後不追價、分數轉弱</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
@@ -33692,29 +33702,29 @@
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3048.TW</t>
+          <t>1810.TW</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>益登</t>
+          <t>和成</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -33733,57 +33743,57 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>57</v>
+        <v>23.4</v>
       </c>
       <c r="G192" t="n">
-        <v>54.2</v>
+        <v>23.59</v>
       </c>
       <c r="H192" t="n">
-        <v>52.89</v>
+        <v>23.79</v>
       </c>
       <c r="I192" t="n">
-        <v>51.75</v>
+        <v>23.77</v>
       </c>
       <c r="J192" t="n">
-        <v>12195758</v>
+        <v>939503</v>
       </c>
       <c r="K192" t="n">
-        <v>4430341</v>
+        <v>1154906</v>
       </c>
       <c r="L192" t="n">
-        <v>58.3</v>
+        <v>24.6</v>
       </c>
       <c r="M192" t="n">
-        <v>49.3</v>
+        <v>23.2</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>帶量突破20日高點</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O192" t="n">
-        <v>-1681590</v>
+        <v>282188</v>
       </c>
       <c r="P192" t="n">
-        <v>-1667794</v>
+        <v>248412</v>
       </c>
       <c r="Q192" t="n">
-        <v>-3002370</v>
+        <v>306494</v>
       </c>
       <c r="R192" t="n">
-        <v>-3370707</v>
+        <v>1646608</v>
       </c>
       <c r="S192" t="n">
-        <v>-1845911</v>
+        <v>270187</v>
       </c>
       <c r="T192" t="n">
-        <v>-1921114</v>
+        <v>242579</v>
       </c>
       <c r="U192" t="n">
-        <v>-3413893</v>
+        <v>303726</v>
       </c>
       <c r="V192" t="n">
-        <v>-3775830</v>
+        <v>1636083</v>
       </c>
       <c r="W192" t="n">
         <v>0</v>
@@ -33798,34 +33808,34 @@
         <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>164321</v>
+        <v>12001</v>
       </c>
       <c r="AB192" t="n">
-        <v>253320</v>
+        <v>5833</v>
       </c>
       <c r="AC192" t="n">
-        <v>411523</v>
+        <v>2768</v>
       </c>
       <c r="AD192" t="n">
-        <v>405123</v>
+        <v>10525</v>
       </c>
       <c r="AE192" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF192" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG192" t="n">
-        <v>65</v>
+        <v>-30</v>
       </c>
       <c r="AH192" t="n">
-        <v>-55</v>
+        <v>50</v>
       </c>
       <c r="AI192" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AJ192" t="n">
-        <v>12</v>
+        <v>-20</v>
       </c>
       <c r="AK192" t="inlineStr">
         <is>
@@ -33833,16 +33843,16 @@
         </is>
       </c>
       <c r="AL192" t="n">
-        <v>-3</v>
+        <v>28</v>
       </c>
       <c r="AM192" t="n">
-        <v>-25</v>
+        <v>140</v>
       </c>
       <c r="AN192" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO192" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
@@ -33851,7 +33861,7 @@
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、爆量後不追價、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
@@ -33866,17 +33876,17 @@
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、帶量突破20日高點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、帶量突破20日高點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -34231,12 +34241,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1810.TW</t>
+          <t>2014.TW</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>和成</t>
+          <t>中鴻</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -34255,28 +34265,28 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>23.4</v>
+        <v>16.95</v>
       </c>
       <c r="G195" t="n">
-        <v>23.59</v>
+        <v>16.95</v>
       </c>
       <c r="H195" t="n">
-        <v>23.79</v>
+        <v>16.96</v>
       </c>
       <c r="I195" t="n">
-        <v>23.77</v>
+        <v>16.78</v>
       </c>
       <c r="J195" t="n">
-        <v>939503</v>
+        <v>1025766</v>
       </c>
       <c r="K195" t="n">
-        <v>1154906</v>
+        <v>1337417</v>
       </c>
       <c r="L195" t="n">
-        <v>24.6</v>
+        <v>17.45</v>
       </c>
       <c r="M195" t="n">
-        <v>23.2</v>
+        <v>16.2</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
@@ -34284,28 +34294,28 @@
         </is>
       </c>
       <c r="O195" t="n">
-        <v>282188</v>
+        <v>441429</v>
       </c>
       <c r="P195" t="n">
-        <v>248412</v>
+        <v>772378</v>
       </c>
       <c r="Q195" t="n">
-        <v>306494</v>
+        <v>244404</v>
       </c>
       <c r="R195" t="n">
-        <v>1646608</v>
+        <v>5464793</v>
       </c>
       <c r="S195" t="n">
-        <v>270187</v>
+        <v>378429</v>
       </c>
       <c r="T195" t="n">
-        <v>242579</v>
+        <v>709378</v>
       </c>
       <c r="U195" t="n">
-        <v>303726</v>
+        <v>194404</v>
       </c>
       <c r="V195" t="n">
-        <v>1636083</v>
+        <v>5401793</v>
       </c>
       <c r="W195" t="n">
         <v>0</v>
@@ -34320,16 +34330,16 @@
         <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>12001</v>
+        <v>63000</v>
       </c>
       <c r="AB195" t="n">
-        <v>5833</v>
+        <v>63000</v>
       </c>
       <c r="AC195" t="n">
-        <v>2768</v>
+        <v>50000</v>
       </c>
       <c r="AD195" t="n">
-        <v>10525</v>
+        <v>63000</v>
       </c>
       <c r="AE195" t="n">
         <v>8</v>
@@ -34347,7 +34357,7 @@
         <v>0</v>
       </c>
       <c r="AJ195" t="n">
-        <v>-20</v>
+        <v>-34</v>
       </c>
       <c r="AK195" t="inlineStr">
         <is>
@@ -34355,16 +34365,16 @@
         </is>
       </c>
       <c r="AL195" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AM195" t="n">
-        <v>140</v>
+        <v>123.53</v>
       </c>
       <c r="AN195" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO195" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
@@ -34373,7 +34383,7 @@
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AR195" t="inlineStr">
@@ -34927,12 +34937,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2014.TW</t>
+          <t>3406.TW</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>中鴻</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -34951,28 +34961,28 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>16.95</v>
+        <v>1060</v>
       </c>
       <c r="G199" t="n">
-        <v>16.95</v>
+        <v>1041.2</v>
       </c>
       <c r="H199" t="n">
-        <v>16.96</v>
+        <v>973.4</v>
       </c>
       <c r="I199" t="n">
-        <v>16.78</v>
+        <v>983</v>
       </c>
       <c r="J199" t="n">
-        <v>1025766</v>
+        <v>3077733</v>
       </c>
       <c r="K199" t="n">
-        <v>1337417</v>
+        <v>5460443</v>
       </c>
       <c r="L199" t="n">
-        <v>17.45</v>
+        <v>1140</v>
       </c>
       <c r="M199" t="n">
-        <v>16.2</v>
+        <v>869</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
@@ -34980,70 +34990,70 @@
         </is>
       </c>
       <c r="O199" t="n">
-        <v>441429</v>
+        <v>-122448</v>
       </c>
       <c r="P199" t="n">
-        <v>772378</v>
+        <v>128048</v>
       </c>
       <c r="Q199" t="n">
-        <v>244404</v>
+        <v>-112331</v>
       </c>
       <c r="R199" t="n">
-        <v>5464793</v>
+        <v>-728752</v>
       </c>
       <c r="S199" t="n">
-        <v>378429</v>
+        <v>-384724</v>
       </c>
       <c r="T199" t="n">
-        <v>709378</v>
+        <v>-927780</v>
       </c>
       <c r="U199" t="n">
-        <v>194404</v>
+        <v>-1635106</v>
       </c>
       <c r="V199" t="n">
-        <v>5401793</v>
+        <v>-2144094</v>
       </c>
       <c r="W199" t="n">
-        <v>0</v>
+        <v>276000</v>
       </c>
       <c r="X199" t="n">
-        <v>0</v>
+        <v>1072000</v>
       </c>
       <c r="Y199" t="n">
-        <v>0</v>
+        <v>1531500</v>
       </c>
       <c r="Z199" t="n">
-        <v>0</v>
+        <v>1472500</v>
       </c>
       <c r="AA199" t="n">
-        <v>63000</v>
+        <v>-13724</v>
       </c>
       <c r="AB199" t="n">
-        <v>63000</v>
+        <v>-16172</v>
       </c>
       <c r="AC199" t="n">
-        <v>50000</v>
+        <v>-8725</v>
       </c>
       <c r="AD199" t="n">
-        <v>63000</v>
+        <v>-57158</v>
       </c>
       <c r="AE199" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF199" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG199" t="n">
-        <v>-30</v>
+        <v>20</v>
       </c>
       <c r="AH199" t="n">
-        <v>50</v>
+        <v>-5</v>
       </c>
       <c r="AI199" t="n">
         <v>0</v>
       </c>
       <c r="AJ199" t="n">
-        <v>-34</v>
+        <v>6</v>
       </c>
       <c r="AK199" t="inlineStr">
         <is>
@@ -35051,25 +35061,25 @@
         </is>
       </c>
       <c r="AL199" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AM199" t="n">
-        <v>123.53</v>
+        <v>0</v>
       </c>
       <c r="AN199" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AO199" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
@@ -35084,17 +35094,17 @@
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、法人連續偏買、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -35275,12 +35285,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3406.TW</t>
+          <t>3013.TW</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>晟銘電</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -35299,28 +35309,28 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>1060</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="G201" t="n">
-        <v>1041.2</v>
+        <v>94.98</v>
       </c>
       <c r="H201" t="n">
-        <v>973.4</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>983</v>
+        <v>87.31</v>
       </c>
       <c r="J201" t="n">
-        <v>3077733</v>
+        <v>6377587</v>
       </c>
       <c r="K201" t="n">
-        <v>5460443</v>
+        <v>4857340</v>
       </c>
       <c r="L201" t="n">
-        <v>1140</v>
+        <v>98.8</v>
       </c>
       <c r="M201" t="n">
-        <v>869</v>
+        <v>81.5</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
@@ -35328,52 +35338,52 @@
         </is>
       </c>
       <c r="O201" t="n">
-        <v>-122448</v>
+        <v>-1014019</v>
       </c>
       <c r="P201" t="n">
-        <v>128048</v>
+        <v>-1257133</v>
       </c>
       <c r="Q201" t="n">
-        <v>-112331</v>
+        <v>-3270892</v>
       </c>
       <c r="R201" t="n">
-        <v>-728752</v>
+        <v>-3252078</v>
       </c>
       <c r="S201" t="n">
-        <v>-384724</v>
+        <v>-1036201</v>
       </c>
       <c r="T201" t="n">
-        <v>-927780</v>
+        <v>-1375601</v>
       </c>
       <c r="U201" t="n">
-        <v>-1635106</v>
+        <v>-3221506</v>
       </c>
       <c r="V201" t="n">
-        <v>-2144094</v>
+        <v>-3460184</v>
       </c>
       <c r="W201" t="n">
-        <v>276000</v>
+        <v>1000</v>
       </c>
       <c r="X201" t="n">
-        <v>1072000</v>
+        <v>1000</v>
       </c>
       <c r="Y201" t="n">
-        <v>1531500</v>
+        <v>1000</v>
       </c>
       <c r="Z201" t="n">
-        <v>1472500</v>
+        <v>2022</v>
       </c>
       <c r="AA201" t="n">
-        <v>-13724</v>
+        <v>21182</v>
       </c>
       <c r="AB201" t="n">
-        <v>-16172</v>
+        <v>117468</v>
       </c>
       <c r="AC201" t="n">
-        <v>-8725</v>
+        <v>-50386</v>
       </c>
       <c r="AD201" t="n">
-        <v>-57158</v>
+        <v>206084</v>
       </c>
       <c r="AE201" t="n">
         <v>6</v>
@@ -35382,16 +35392,16 @@
         <v>6</v>
       </c>
       <c r="AG201" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="AH201" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="AI201" t="n">
         <v>0</v>
       </c>
       <c r="AJ201" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AK201" t="inlineStr">
         <is>
@@ -35399,25 +35409,25 @@
         </is>
       </c>
       <c r="AL201" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM201" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN201" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="AO201" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣</t>
+          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
@@ -35432,17 +35442,17 @@
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超、投信買外資賣</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、短線籌碼止穩、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -36309,12 +36319,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3013.TW</t>
+          <t>3617.TW</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>晟銘電</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -36333,28 +36343,28 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>97.90000000000001</v>
+        <v>241.5</v>
       </c>
       <c r="G207" t="n">
-        <v>94.98</v>
+        <v>243.4</v>
       </c>
       <c r="H207" t="n">
-        <v>90.84999999999999</v>
+        <v>242.8</v>
       </c>
       <c r="I207" t="n">
-        <v>87.31</v>
+        <v>242.65</v>
       </c>
       <c r="J207" t="n">
-        <v>6377587</v>
+        <v>219126</v>
       </c>
       <c r="K207" t="n">
-        <v>4857340</v>
+        <v>254684</v>
       </c>
       <c r="L207" t="n">
-        <v>98.8</v>
+        <v>253.5</v>
       </c>
       <c r="M207" t="n">
-        <v>81.5</v>
+        <v>234</v>
       </c>
       <c r="N207" t="inlineStr">
         <is>
@@ -36362,52 +36372,52 @@
         </is>
       </c>
       <c r="O207" t="n">
-        <v>-1014019</v>
+        <v>-13733</v>
       </c>
       <c r="P207" t="n">
-        <v>-1257133</v>
+        <v>20335</v>
       </c>
       <c r="Q207" t="n">
-        <v>-3270892</v>
+        <v>33002</v>
       </c>
       <c r="R207" t="n">
-        <v>-3252078</v>
+        <v>238168</v>
       </c>
       <c r="S207" t="n">
-        <v>-1036201</v>
+        <v>-16976</v>
       </c>
       <c r="T207" t="n">
-        <v>-1375601</v>
+        <v>59149</v>
       </c>
       <c r="U207" t="n">
-        <v>-3221506</v>
+        <v>72818</v>
       </c>
       <c r="V207" t="n">
-        <v>-3460184</v>
+        <v>292891</v>
       </c>
       <c r="W207" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X207" t="n">
-        <v>1000</v>
+        <v>2115</v>
       </c>
       <c r="Y207" t="n">
-        <v>1000</v>
+        <v>2115</v>
       </c>
       <c r="Z207" t="n">
-        <v>2022</v>
+        <v>2115</v>
       </c>
       <c r="AA207" t="n">
-        <v>21182</v>
+        <v>3243</v>
       </c>
       <c r="AB207" t="n">
-        <v>117468</v>
+        <v>-40929</v>
       </c>
       <c r="AC207" t="n">
-        <v>-50386</v>
+        <v>-41931</v>
       </c>
       <c r="AD207" t="n">
-        <v>206084</v>
+        <v>-56838</v>
       </c>
       <c r="AE207" t="n">
         <v>6</v>
@@ -36416,16 +36426,16 @@
         <v>6</v>
       </c>
       <c r="AG207" t="n">
-        <v>70</v>
+        <v>-5</v>
       </c>
       <c r="AH207" t="n">
-        <v>-55</v>
+        <v>20</v>
       </c>
       <c r="AI207" t="n">
         <v>0</v>
       </c>
       <c r="AJ207" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
@@ -36433,25 +36443,25 @@
         </is>
       </c>
       <c r="AL207" t="n">
-        <v>4</v>
+        <v>-20</v>
       </c>
       <c r="AM207" t="n">
-        <v>200</v>
+        <v>-76.92</v>
       </c>
       <c r="AN207" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="AO207" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、均線多頭排列、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
@@ -36466,17 +36476,17 @@
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能溫和放大、接近20日高點</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、量能溫和放大、接近20日高點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、籌碼中性、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -36657,12 +36667,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3617.TW</t>
+          <t>6485.TWO</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -36681,28 +36691,28 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>241.5</v>
+        <v>81.2</v>
       </c>
       <c r="G209" t="n">
-        <v>243.4</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="H209" t="n">
-        <v>242.8</v>
+        <v>77.69</v>
       </c>
       <c r="I209" t="n">
-        <v>242.65</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>219126</v>
+        <v>2001000</v>
       </c>
       <c r="K209" t="n">
-        <v>254684</v>
+        <v>1879400</v>
       </c>
       <c r="L209" t="n">
-        <v>253.5</v>
+        <v>87.2</v>
       </c>
       <c r="M209" t="n">
-        <v>234</v>
+        <v>58.5</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
@@ -36710,52 +36720,52 @@
         </is>
       </c>
       <c r="O209" t="n">
-        <v>-13733</v>
+        <v>0</v>
       </c>
       <c r="P209" t="n">
-        <v>20335</v>
+        <v>0</v>
       </c>
       <c r="Q209" t="n">
-        <v>33002</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>238168</v>
+        <v>0</v>
       </c>
       <c r="S209" t="n">
-        <v>-16976</v>
+        <v>0</v>
       </c>
       <c r="T209" t="n">
-        <v>59149</v>
+        <v>0</v>
       </c>
       <c r="U209" t="n">
-        <v>72818</v>
+        <v>0</v>
       </c>
       <c r="V209" t="n">
-        <v>292891</v>
+        <v>0</v>
       </c>
       <c r="W209" t="n">
         <v>0</v>
       </c>
       <c r="X209" t="n">
-        <v>2115</v>
+        <v>0</v>
       </c>
       <c r="Y209" t="n">
-        <v>2115</v>
+        <v>0</v>
       </c>
       <c r="Z209" t="n">
-        <v>2115</v>
+        <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>3243</v>
+        <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>-40929</v>
+        <v>0</v>
       </c>
       <c r="AC209" t="n">
-        <v>-41931</v>
+        <v>0</v>
       </c>
       <c r="AD209" t="n">
-        <v>-56838</v>
+        <v>0</v>
       </c>
       <c r="AE209" t="n">
         <v>6</v>
@@ -36764,33 +36774,33 @@
         <v>6</v>
       </c>
       <c r="AG209" t="n">
-        <v>-5</v>
+        <v>15</v>
       </c>
       <c r="AH209" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI209" t="n">
         <v>0</v>
       </c>
       <c r="AJ209" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AL209" t="n">
-        <v>-20</v>
+        <v>-26</v>
       </c>
       <c r="AM209" t="n">
-        <v>-76.92</v>
+        <v>-81.25</v>
       </c>
       <c r="AN209" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO209" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
@@ -36799,7 +36809,7 @@
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
@@ -36814,17 +36824,17 @@
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>籌碼中性、外資投信同步買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、籌碼中性、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -714,16 +714,16 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1278216</v>
+        <v>1313216</v>
       </c>
       <c r="P2" t="n">
-        <v>1776282</v>
+        <v>1811282</v>
       </c>
       <c r="Q2" t="n">
-        <v>1880229</v>
+        <v>1915229</v>
       </c>
       <c r="R2" t="n">
-        <v>2441507</v>
+        <v>2476507</v>
       </c>
       <c r="S2" t="n">
         <v>1229305</v>
@@ -738,16 +738,16 @@
         <v>1812211</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="X2" t="n">
-        <v>9940</v>
+        <v>44940</v>
       </c>
       <c r="Y2" t="n">
-        <v>79940</v>
+        <v>114940</v>
       </c>
       <c r="Z2" t="n">
-        <v>114940</v>
+        <v>149940</v>
       </c>
       <c r="AA2" t="n">
         <v>48911</v>
@@ -5412,16 +5412,16 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>12986471</v>
+        <v>13084471</v>
       </c>
       <c r="P29" t="n">
-        <v>6009236</v>
+        <v>6107236</v>
       </c>
       <c r="Q29" t="n">
-        <v>32622433</v>
+        <v>32720433</v>
       </c>
       <c r="R29" t="n">
-        <v>74431376</v>
+        <v>74529376</v>
       </c>
       <c r="S29" t="n">
         <v>12382069</v>
@@ -5436,16 +5436,16 @@
         <v>37452092</v>
       </c>
       <c r="W29" t="n">
-        <v>-1119881</v>
+        <v>-1021881</v>
       </c>
       <c r="X29" t="n">
-        <v>-5703291</v>
+        <v>-5605291</v>
       </c>
       <c r="Y29" t="n">
-        <v>-7908113</v>
+        <v>-7810113</v>
       </c>
       <c r="Z29" t="n">
-        <v>13267338</v>
+        <v>13365338</v>
       </c>
       <c r="AA29" t="n">
         <v>1724283</v>
@@ -9064,16 +9064,16 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>14539025</v>
+        <v>14619025</v>
       </c>
       <c r="P50" t="n">
-        <v>30987280</v>
+        <v>31067280</v>
       </c>
       <c r="Q50" t="n">
-        <v>27323184</v>
+        <v>27403184</v>
       </c>
       <c r="R50" t="n">
-        <v>15339539</v>
+        <v>15419539</v>
       </c>
       <c r="S50" t="n">
         <v>15141742</v>
@@ -9088,16 +9088,16 @@
         <v>11358922</v>
       </c>
       <c r="W50" t="n">
-        <v>-1067995</v>
+        <v>-987995</v>
       </c>
       <c r="X50" t="n">
-        <v>-3140499</v>
+        <v>-3060499</v>
       </c>
       <c r="Y50" t="n">
-        <v>-2823505</v>
+        <v>-2743505</v>
       </c>
       <c r="Z50" t="n">
-        <v>-2761505</v>
+        <v>-2681505</v>
       </c>
       <c r="AA50" t="n">
         <v>465278</v>
@@ -9412,16 +9412,16 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>6974889</v>
+        <v>7133889</v>
       </c>
       <c r="P52" t="n">
-        <v>-862027</v>
+        <v>-703027</v>
       </c>
       <c r="Q52" t="n">
-        <v>23569394</v>
+        <v>23728394</v>
       </c>
       <c r="R52" t="n">
-        <v>7927628</v>
+        <v>8086628</v>
       </c>
       <c r="S52" t="n">
         <v>5076720</v>
@@ -9436,16 +9436,16 @@
         <v>-19330869</v>
       </c>
       <c r="W52" t="n">
-        <v>831954</v>
+        <v>990954</v>
       </c>
       <c r="X52" t="n">
-        <v>1279710</v>
+        <v>1438710</v>
       </c>
       <c r="Y52" t="n">
-        <v>1460771</v>
+        <v>1619771</v>
       </c>
       <c r="Z52" t="n">
-        <v>6035828</v>
+        <v>6194828</v>
       </c>
       <c r="AA52" t="n">
         <v>1066215</v>
@@ -17590,16 +17590,16 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>822499</v>
+        <v>890499</v>
       </c>
       <c r="P99" t="n">
-        <v>2779820</v>
+        <v>2847820</v>
       </c>
       <c r="Q99" t="n">
-        <v>7737149</v>
+        <v>7805149</v>
       </c>
       <c r="R99" t="n">
-        <v>42453000</v>
+        <v>42521000</v>
       </c>
       <c r="S99" t="n">
         <v>429577</v>
@@ -17614,16 +17614,16 @@
         <v>26193303</v>
       </c>
       <c r="W99" t="n">
-        <v>63990</v>
+        <v>131990</v>
       </c>
       <c r="X99" t="n">
-        <v>1520383</v>
+        <v>1588383</v>
       </c>
       <c r="Y99" t="n">
-        <v>6606263</v>
+        <v>6674263</v>
       </c>
       <c r="Z99" t="n">
-        <v>12639535</v>
+        <v>12707535</v>
       </c>
       <c r="AA99" t="n">
         <v>328932</v>
@@ -37357,12 +37357,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3481.TW</t>
+          <t>3035.TW</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -37381,28 +37381,28 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>48.5</v>
+        <v>198</v>
       </c>
       <c r="G213" t="n">
-        <v>47.76</v>
+        <v>196.2</v>
       </c>
       <c r="H213" t="n">
-        <v>49.45</v>
+        <v>199.25</v>
       </c>
       <c r="I213" t="n">
-        <v>50.38</v>
+        <v>203.62</v>
       </c>
       <c r="J213" t="n">
-        <v>83059939</v>
+        <v>3909585</v>
       </c>
       <c r="K213" t="n">
-        <v>106776965</v>
+        <v>5354700</v>
       </c>
       <c r="L213" t="n">
-        <v>56.2</v>
+        <v>223.5</v>
       </c>
       <c r="M213" t="n">
-        <v>45.65</v>
+        <v>186</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>
@@ -37410,52 +37410,52 @@
         </is>
       </c>
       <c r="O213" t="n">
-        <v>22234407</v>
+        <v>431635</v>
       </c>
       <c r="P213" t="n">
-        <v>17924980</v>
+        <v>140271</v>
       </c>
       <c r="Q213" t="n">
-        <v>-38389965</v>
+        <v>-1747623</v>
       </c>
       <c r="R213" t="n">
-        <v>-18143304</v>
+        <v>-603456</v>
       </c>
       <c r="S213" t="n">
-        <v>13782153</v>
+        <v>220792</v>
       </c>
       <c r="T213" t="n">
-        <v>7999931</v>
+        <v>109321</v>
       </c>
       <c r="U213" t="n">
-        <v>-42907624</v>
+        <v>-1563372</v>
       </c>
       <c r="V213" t="n">
-        <v>-20821637</v>
+        <v>-451988</v>
       </c>
       <c r="W213" t="n">
-        <v>286993</v>
+        <v>102000</v>
       </c>
       <c r="X213" t="n">
-        <v>794681</v>
+        <v>292944</v>
       </c>
       <c r="Y213" t="n">
-        <v>1427420</v>
+        <v>341944</v>
       </c>
       <c r="Z213" t="n">
-        <v>1744393</v>
+        <v>391944</v>
       </c>
       <c r="AA213" t="n">
-        <v>8165261</v>
+        <v>108843</v>
       </c>
       <c r="AB213" t="n">
-        <v>9130368</v>
+        <v>-261994</v>
       </c>
       <c r="AC213" t="n">
-        <v>3090239</v>
+        <v>-526195</v>
       </c>
       <c r="AD213" t="n">
-        <v>933940</v>
+        <v>-543412</v>
       </c>
       <c r="AE213" t="n">
         <v>-8</v>
@@ -37473,7 +37473,7 @@
         <v>0</v>
       </c>
       <c r="AJ213" t="n">
-        <v>-44</v>
+        <v>-40</v>
       </c>
       <c r="AK213" t="inlineStr">
         <is>
@@ -37481,10 +37481,10 @@
         </is>
       </c>
       <c r="AL213" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM213" t="n">
-        <v>81.81999999999999</v>
+        <v>80</v>
       </c>
       <c r="AN213" t="n">
         <v>35</v>
@@ -37695,12 +37695,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3450.TW</t>
+          <t>3293.TWO</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -37719,28 +37719,28 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>450</v>
+        <v>782</v>
       </c>
       <c r="G215" t="n">
-        <v>449.8</v>
+        <v>789</v>
       </c>
       <c r="H215" t="n">
-        <v>479.8</v>
+        <v>791.8</v>
       </c>
       <c r="I215" t="n">
-        <v>504.35</v>
+        <v>780.25</v>
       </c>
       <c r="J215" t="n">
-        <v>4067013</v>
+        <v>1168000</v>
       </c>
       <c r="K215" t="n">
-        <v>6198863</v>
+        <v>2232200</v>
       </c>
       <c r="L215" t="n">
-        <v>574</v>
+        <v>819</v>
       </c>
       <c r="M215" t="n">
-        <v>426.5</v>
+        <v>709</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
@@ -37748,52 +37748,52 @@
         </is>
       </c>
       <c r="O215" t="n">
-        <v>815579</v>
+        <v>0</v>
       </c>
       <c r="P215" t="n">
-        <v>726635</v>
+        <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>-1762804</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>-8038067</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
-        <v>806914</v>
+        <v>0</v>
       </c>
       <c r="T215" t="n">
-        <v>2679461</v>
+        <v>0</v>
       </c>
       <c r="U215" t="n">
-        <v>2576374</v>
+        <v>0</v>
       </c>
       <c r="V215" t="n">
-        <v>-933994</v>
+        <v>0</v>
       </c>
       <c r="W215" t="n">
         <v>0</v>
       </c>
       <c r="X215" t="n">
-        <v>-1894004</v>
+        <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>-3959004</v>
+        <v>0</v>
       </c>
       <c r="Z215" t="n">
-        <v>-6538004</v>
+        <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>8665</v>
+        <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>-58822</v>
+        <v>0</v>
       </c>
       <c r="AC215" t="n">
-        <v>-380174</v>
+        <v>0</v>
       </c>
       <c r="AD215" t="n">
-        <v>-566069</v>
+        <v>0</v>
       </c>
       <c r="AE215" t="n">
         <v>-8</v>
@@ -37802,16 +37802,16 @@
         <v>-8</v>
       </c>
       <c r="AG215" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="AH215" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AI215" t="n">
         <v>0</v>
       </c>
       <c r="AJ215" t="n">
-        <v>-44</v>
+        <v>2</v>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
@@ -37819,25 +37819,25 @@
         </is>
       </c>
       <c r="AL215" t="n">
-        <v>36</v>
+        <v>-10</v>
       </c>
       <c r="AM215" t="n">
-        <v>81.81999999999999</v>
+        <v>-500</v>
       </c>
       <c r="AN215" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AO215" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
@@ -37852,17 +37852,17 @@
       </c>
       <c r="AT215" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -38217,12 +38217,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3293.TWO</t>
+          <t>3481.TW</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -38241,28 +38241,28 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>782</v>
+        <v>48.5</v>
       </c>
       <c r="G218" t="n">
-        <v>789</v>
+        <v>47.76</v>
       </c>
       <c r="H218" t="n">
-        <v>791.8</v>
+        <v>49.45</v>
       </c>
       <c r="I218" t="n">
-        <v>780.25</v>
+        <v>50.38</v>
       </c>
       <c r="J218" t="n">
-        <v>1168000</v>
+        <v>83059939</v>
       </c>
       <c r="K218" t="n">
-        <v>2232200</v>
+        <v>106776965</v>
       </c>
       <c r="L218" t="n">
-        <v>819</v>
+        <v>56.2</v>
       </c>
       <c r="M218" t="n">
-        <v>709</v>
+        <v>45.65</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -38270,52 +38270,52 @@
         </is>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
+        <v>22234407</v>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>17924980</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>-38389965</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>-18143304</v>
       </c>
       <c r="S218" t="n">
-        <v>0</v>
+        <v>13782153</v>
       </c>
       <c r="T218" t="n">
-        <v>0</v>
+        <v>7999931</v>
       </c>
       <c r="U218" t="n">
-        <v>0</v>
+        <v>-42907624</v>
       </c>
       <c r="V218" t="n">
-        <v>0</v>
+        <v>-20821637</v>
       </c>
       <c r="W218" t="n">
-        <v>0</v>
+        <v>286993</v>
       </c>
       <c r="X218" t="n">
-        <v>0</v>
+        <v>794681</v>
       </c>
       <c r="Y218" t="n">
-        <v>0</v>
+        <v>1427420</v>
       </c>
       <c r="Z218" t="n">
-        <v>0</v>
+        <v>1744393</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>8165261</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>9130368</v>
       </c>
       <c r="AC218" t="n">
-        <v>0</v>
+        <v>3090239</v>
       </c>
       <c r="AD218" t="n">
-        <v>0</v>
+        <v>933940</v>
       </c>
       <c r="AE218" t="n">
         <v>-8</v>
@@ -38324,16 +38324,16 @@
         <v>-8</v>
       </c>
       <c r="AG218" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
       <c r="AH218" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AI218" t="n">
         <v>0</v>
       </c>
       <c r="AJ218" t="n">
-        <v>2</v>
+        <v>-44</v>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
@@ -38341,25 +38341,25 @@
         </is>
       </c>
       <c r="AL218" t="n">
-        <v>-10</v>
+        <v>36</v>
       </c>
       <c r="AM218" t="n">
-        <v>-500</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="AN218" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AO218" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR218" t="inlineStr">
@@ -38374,29 +38374,29 @@
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3035.TW</t>
+          <t>3504.TW</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -38415,28 +38415,28 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>198</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G219" t="n">
-        <v>196.2</v>
+        <v>77.28</v>
       </c>
       <c r="H219" t="n">
-        <v>199.25</v>
+        <v>80.19</v>
       </c>
       <c r="I219" t="n">
-        <v>203.62</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>3909585</v>
+        <v>2806164</v>
       </c>
       <c r="K219" t="n">
-        <v>5354700</v>
+        <v>2466135</v>
       </c>
       <c r="L219" t="n">
-        <v>223.5</v>
+        <v>87.2</v>
       </c>
       <c r="M219" t="n">
-        <v>186</v>
+        <v>73.5</v>
       </c>
       <c r="N219" t="inlineStr">
         <is>
@@ -38444,52 +38444,52 @@
         </is>
       </c>
       <c r="O219" t="n">
-        <v>431635</v>
+        <v>-243019</v>
       </c>
       <c r="P219" t="n">
-        <v>140271</v>
+        <v>-183359</v>
       </c>
       <c r="Q219" t="n">
-        <v>-1747623</v>
+        <v>23963</v>
       </c>
       <c r="R219" t="n">
-        <v>-603456</v>
+        <v>-379472</v>
       </c>
       <c r="S219" t="n">
-        <v>220792</v>
+        <v>-233560</v>
       </c>
       <c r="T219" t="n">
-        <v>109321</v>
+        <v>-160367</v>
       </c>
       <c r="U219" t="n">
-        <v>-1563372</v>
+        <v>45816</v>
       </c>
       <c r="V219" t="n">
-        <v>-451988</v>
+        <v>-349097</v>
       </c>
       <c r="W219" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="X219" t="n">
-        <v>292944</v>
+        <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>341944</v>
+        <v>0</v>
       </c>
       <c r="Z219" t="n">
-        <v>391944</v>
+        <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>108843</v>
+        <v>-9459</v>
       </c>
       <c r="AB219" t="n">
-        <v>-261994</v>
+        <v>-22992</v>
       </c>
       <c r="AC219" t="n">
-        <v>-526195</v>
+        <v>-21853</v>
       </c>
       <c r="AD219" t="n">
-        <v>-543412</v>
+        <v>-30375</v>
       </c>
       <c r="AE219" t="n">
         <v>-8</v>
@@ -38498,16 +38498,16 @@
         <v>-8</v>
       </c>
       <c r="AG219" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="AH219" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AI219" t="n">
         <v>0</v>
       </c>
       <c r="AJ219" t="n">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
@@ -38515,25 +38515,25 @@
         </is>
       </c>
       <c r="AL219" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="AM219" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AN219" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AO219" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
@@ -38548,29 +38548,29 @@
       </c>
       <c r="AT219" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3504.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -38589,28 +38589,28 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>73.90000000000001</v>
+        <v>578</v>
       </c>
       <c r="G220" t="n">
-        <v>77.28</v>
+        <v>549.6</v>
       </c>
       <c r="H220" t="n">
-        <v>80.19</v>
+        <v>563.5</v>
       </c>
       <c r="I220" t="n">
-        <v>80.04000000000001</v>
+        <v>538.45</v>
       </c>
       <c r="J220" t="n">
-        <v>2806164</v>
+        <v>34141516</v>
       </c>
       <c r="K220" t="n">
-        <v>2466135</v>
+        <v>27385791</v>
       </c>
       <c r="L220" t="n">
-        <v>87.2</v>
+        <v>613</v>
       </c>
       <c r="M220" t="n">
-        <v>73.5</v>
+        <v>463.5</v>
       </c>
       <c r="N220" t="inlineStr">
         <is>
@@ -38618,70 +38618,70 @@
         </is>
       </c>
       <c r="O220" t="n">
-        <v>-243019</v>
+        <v>2423014</v>
       </c>
       <c r="P220" t="n">
-        <v>-183359</v>
+        <v>-4204051</v>
       </c>
       <c r="Q220" t="n">
-        <v>23963</v>
+        <v>-4179414</v>
       </c>
       <c r="R220" t="n">
-        <v>-379472</v>
+        <v>2125257</v>
       </c>
       <c r="S220" t="n">
-        <v>-233560</v>
+        <v>1278760</v>
       </c>
       <c r="T220" t="n">
-        <v>-160367</v>
+        <v>-6844873</v>
       </c>
       <c r="U220" t="n">
-        <v>45816</v>
+        <v>-8477917</v>
       </c>
       <c r="V220" t="n">
-        <v>-349097</v>
+        <v>-4485381</v>
       </c>
       <c r="W220" t="n">
-        <v>0</v>
+        <v>719095</v>
       </c>
       <c r="X220" t="n">
-        <v>0</v>
+        <v>2410996</v>
       </c>
       <c r="Y220" t="n">
-        <v>0</v>
+        <v>4263320</v>
       </c>
       <c r="Z220" t="n">
-        <v>0</v>
+        <v>6785513</v>
       </c>
       <c r="AA220" t="n">
-        <v>-9459</v>
+        <v>425159</v>
       </c>
       <c r="AB220" t="n">
-        <v>-22992</v>
+        <v>229826</v>
       </c>
       <c r="AC220" t="n">
-        <v>-21853</v>
+        <v>35183</v>
       </c>
       <c r="AD220" t="n">
-        <v>-30375</v>
+        <v>-174875</v>
       </c>
       <c r="AE220" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AF220" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="AG220" t="n">
-        <v>-20</v>
+        <v>30</v>
       </c>
       <c r="AH220" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AI220" t="n">
         <v>0</v>
       </c>
       <c r="AJ220" t="n">
-        <v>-20</v>
+        <v>-36</v>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
@@ -38689,25 +38689,25 @@
         </is>
       </c>
       <c r="AL220" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AM220" t="n">
-        <v>60</v>
+        <v>72.22</v>
       </c>
       <c r="AN220" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AO220" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
@@ -38722,29 +38722,29 @@
       </c>
       <c r="AT220" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能溫和放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>3057.TW</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>喬鼎</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -38763,28 +38763,28 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>1010</v>
+        <v>14.3</v>
       </c>
       <c r="G221" t="n">
-        <v>983.2</v>
+        <v>14.38</v>
       </c>
       <c r="H221" t="n">
-        <v>1024.1</v>
+        <v>14.75</v>
       </c>
       <c r="I221" t="n">
-        <v>999.75</v>
+        <v>15.38</v>
       </c>
       <c r="J221" t="n">
-        <v>21361332</v>
+        <v>43368</v>
       </c>
       <c r="K221" t="n">
-        <v>14868266</v>
+        <v>127637</v>
       </c>
       <c r="L221" t="n">
-        <v>1150</v>
+        <v>16.7</v>
       </c>
       <c r="M221" t="n">
-        <v>824</v>
+        <v>13.9</v>
       </c>
       <c r="N221" t="inlineStr">
         <is>
@@ -38792,52 +38792,52 @@
         </is>
       </c>
       <c r="O221" t="n">
-        <v>174239</v>
+        <v>2000</v>
       </c>
       <c r="P221" t="n">
-        <v>-2748636</v>
+        <v>32000</v>
       </c>
       <c r="Q221" t="n">
-        <v>-4230584</v>
+        <v>44000</v>
       </c>
       <c r="R221" t="n">
-        <v>-1231739</v>
+        <v>42330</v>
       </c>
       <c r="S221" t="n">
-        <v>119663</v>
+        <v>2000</v>
       </c>
       <c r="T221" t="n">
-        <v>-4721109</v>
+        <v>34000</v>
       </c>
       <c r="U221" t="n">
-        <v>-7459295</v>
+        <v>44000</v>
       </c>
       <c r="V221" t="n">
-        <v>-5380638</v>
+        <v>44330</v>
       </c>
       <c r="W221" t="n">
-        <v>258000</v>
+        <v>0</v>
       </c>
       <c r="X221" t="n">
-        <v>2812241</v>
+        <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>4472241</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>5525518</v>
+        <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>-203424</v>
+        <v>0</v>
       </c>
       <c r="AB221" t="n">
-        <v>-839768</v>
+        <v>-2000</v>
       </c>
       <c r="AC221" t="n">
-        <v>-1243530</v>
+        <v>0</v>
       </c>
       <c r="AD221" t="n">
-        <v>-1376619</v>
+        <v>-2000</v>
       </c>
       <c r="AE221" t="n">
         <v>-10</v>
@@ -38846,16 +38846,16 @@
         <v>-10</v>
       </c>
       <c r="AG221" t="n">
-        <v>5</v>
+        <v>-55</v>
       </c>
       <c r="AH221" t="n">
-        <v>-30</v>
+        <v>30</v>
       </c>
       <c r="AI221" t="n">
         <v>0</v>
       </c>
       <c r="AJ221" t="n">
-        <v>-30</v>
+        <v>-22</v>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
@@ -38863,25 +38863,25 @@
         </is>
       </c>
       <c r="AL221" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AM221" t="n">
-        <v>66.67</v>
+        <v>54.55</v>
       </c>
       <c r="AN221" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="AO221" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
@@ -38896,17 +38896,17 @@
       </c>
       <c r="AT221" t="inlineStr">
         <is>
-          <t>站上5日線、死亡交叉、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏買</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、死亡交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -39261,12 +39261,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -39285,28 +39285,28 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>578</v>
+        <v>1010</v>
       </c>
       <c r="G224" t="n">
-        <v>549.6</v>
+        <v>983.2</v>
       </c>
       <c r="H224" t="n">
-        <v>563.5</v>
+        <v>1024.1</v>
       </c>
       <c r="I224" t="n">
-        <v>538.45</v>
+        <v>999.75</v>
       </c>
       <c r="J224" t="n">
-        <v>34141516</v>
+        <v>21361332</v>
       </c>
       <c r="K224" t="n">
-        <v>27385791</v>
+        <v>14868266</v>
       </c>
       <c r="L224" t="n">
-        <v>613</v>
+        <v>1150</v>
       </c>
       <c r="M224" t="n">
-        <v>463.5</v>
+        <v>824</v>
       </c>
       <c r="N224" t="inlineStr">
         <is>
@@ -39314,52 +39314,52 @@
         </is>
       </c>
       <c r="O224" t="n">
-        <v>2423014</v>
+        <v>174239</v>
       </c>
       <c r="P224" t="n">
-        <v>-4204051</v>
+        <v>-2748636</v>
       </c>
       <c r="Q224" t="n">
-        <v>-4179414</v>
+        <v>-4230584</v>
       </c>
       <c r="R224" t="n">
-        <v>2125257</v>
+        <v>-1231739</v>
       </c>
       <c r="S224" t="n">
-        <v>1278760</v>
+        <v>119663</v>
       </c>
       <c r="T224" t="n">
-        <v>-6844873</v>
+        <v>-4721109</v>
       </c>
       <c r="U224" t="n">
-        <v>-8477917</v>
+        <v>-7459295</v>
       </c>
       <c r="V224" t="n">
-        <v>-4485381</v>
+        <v>-5380638</v>
       </c>
       <c r="W224" t="n">
-        <v>719095</v>
+        <v>258000</v>
       </c>
       <c r="X224" t="n">
-        <v>2410996</v>
+        <v>2812241</v>
       </c>
       <c r="Y224" t="n">
-        <v>4263320</v>
+        <v>4472241</v>
       </c>
       <c r="Z224" t="n">
-        <v>6785513</v>
+        <v>5525518</v>
       </c>
       <c r="AA224" t="n">
-        <v>425159</v>
+        <v>-203424</v>
       </c>
       <c r="AB224" t="n">
-        <v>229826</v>
+        <v>-839768</v>
       </c>
       <c r="AC224" t="n">
-        <v>35183</v>
+        <v>-1243530</v>
       </c>
       <c r="AD224" t="n">
-        <v>-174875</v>
+        <v>-1376619</v>
       </c>
       <c r="AE224" t="n">
         <v>-10</v>
@@ -39368,16 +39368,16 @@
         <v>-10</v>
       </c>
       <c r="AG224" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AH224" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AI224" t="n">
         <v>0</v>
       </c>
       <c r="AJ224" t="n">
-        <v>-36</v>
+        <v>-30</v>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
@@ -39385,25 +39385,25 @@
         </is>
       </c>
       <c r="AL224" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AM224" t="n">
-        <v>72.22</v>
+        <v>66.67</v>
       </c>
       <c r="AN224" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AO224" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
@@ -39418,34 +39418,34 @@
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>站上5日線、死亡交叉、量能溫和放大</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能溫和放大、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、死亡交叉、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3057.TW</t>
+          <t>0056.TW</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>喬鼎</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -39459,28 +39459,28 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>14.3</v>
+        <v>58.75</v>
       </c>
       <c r="G225" t="n">
-        <v>14.38</v>
+        <v>58.24</v>
       </c>
       <c r="H225" t="n">
-        <v>14.75</v>
+        <v>58.47</v>
       </c>
       <c r="I225" t="n">
-        <v>15.38</v>
+        <v>57.77</v>
       </c>
       <c r="J225" t="n">
-        <v>43368</v>
+        <v>54408829</v>
       </c>
       <c r="K225" t="n">
-        <v>127637</v>
+        <v>98348638</v>
       </c>
       <c r="L225" t="n">
-        <v>16.7</v>
+        <v>59.7</v>
       </c>
       <c r="M225" t="n">
-        <v>13.9</v>
+        <v>56</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
@@ -39488,70 +39488,70 @@
         </is>
       </c>
       <c r="O225" t="n">
-        <v>2000</v>
+        <v>-17069488</v>
       </c>
       <c r="P225" t="n">
-        <v>32000</v>
+        <v>-203007096</v>
       </c>
       <c r="Q225" t="n">
-        <v>44000</v>
+        <v>-373753320</v>
       </c>
       <c r="R225" t="n">
-        <v>42330</v>
+        <v>-483221325</v>
       </c>
       <c r="S225" t="n">
-        <v>2000</v>
+        <v>154499</v>
       </c>
       <c r="T225" t="n">
-        <v>34000</v>
+        <v>-20376111</v>
       </c>
       <c r="U225" t="n">
-        <v>44000</v>
+        <v>-42631253</v>
       </c>
       <c r="V225" t="n">
-        <v>44330</v>
+        <v>-61069905</v>
       </c>
       <c r="W225" t="n">
-        <v>0</v>
+        <v>2670000</v>
       </c>
       <c r="X225" t="n">
-        <v>0</v>
+        <v>3343000</v>
       </c>
       <c r="Y225" t="n">
-        <v>0</v>
+        <v>10823000</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>11955000</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>-19893987</v>
       </c>
       <c r="AB225" t="n">
-        <v>-2000</v>
+        <v>-185973985</v>
       </c>
       <c r="AC225" t="n">
-        <v>0</v>
+        <v>-341945067</v>
       </c>
       <c r="AD225" t="n">
-        <v>-2000</v>
+        <v>-434106420</v>
       </c>
       <c r="AE225" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AF225" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AG225" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH225" t="n">
         <v>-55</v>
       </c>
-      <c r="AH225" t="n">
-        <v>30</v>
-      </c>
       <c r="AI225" t="n">
         <v>0</v>
       </c>
       <c r="AJ225" t="n">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
@@ -39559,25 +39559,25 @@
         </is>
       </c>
       <c r="AL225" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AM225" t="n">
-        <v>54.55</v>
+        <v>40</v>
       </c>
       <c r="AN225" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AO225" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
@@ -39592,34 +39592,34 @@
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>法人連續偏買</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>0056.TW</t>
+          <t>2516.TW</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>新建</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -39633,28 +39633,28 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>58.75</v>
+        <v>15.15</v>
       </c>
       <c r="G226" t="n">
-        <v>58.24</v>
+        <v>15.25</v>
       </c>
       <c r="H226" t="n">
-        <v>58.47</v>
+        <v>15.27</v>
       </c>
       <c r="I226" t="n">
-        <v>57.77</v>
+        <v>15.12</v>
       </c>
       <c r="J226" t="n">
-        <v>54408829</v>
+        <v>113582</v>
       </c>
       <c r="K226" t="n">
-        <v>98348638</v>
+        <v>229655</v>
       </c>
       <c r="L226" t="n">
-        <v>59.7</v>
+        <v>15.8</v>
       </c>
       <c r="M226" t="n">
-        <v>56</v>
+        <v>14.5</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
@@ -39662,52 +39662,52 @@
         </is>
       </c>
       <c r="O226" t="n">
-        <v>-17069488</v>
+        <v>-34947</v>
       </c>
       <c r="P226" t="n">
-        <v>-203007096</v>
+        <v>32511</v>
       </c>
       <c r="Q226" t="n">
-        <v>-373753320</v>
+        <v>16511</v>
       </c>
       <c r="R226" t="n">
-        <v>-483221325</v>
+        <v>121457</v>
       </c>
       <c r="S226" t="n">
-        <v>154499</v>
+        <v>-34947</v>
       </c>
       <c r="T226" t="n">
-        <v>-20376111</v>
+        <v>32511</v>
       </c>
       <c r="U226" t="n">
-        <v>-42631253</v>
+        <v>9511</v>
       </c>
       <c r="V226" t="n">
-        <v>-61069905</v>
+        <v>118461</v>
       </c>
       <c r="W226" t="n">
-        <v>2670000</v>
+        <v>0</v>
       </c>
       <c r="X226" t="n">
-        <v>3343000</v>
+        <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>10823000</v>
+        <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>11955000</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>-19893987</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
-        <v>-185973985</v>
+        <v>0</v>
       </c>
       <c r="AC226" t="n">
-        <v>-341945067</v>
+        <v>7000</v>
       </c>
       <c r="AD226" t="n">
-        <v>-434106420</v>
+        <v>2996</v>
       </c>
       <c r="AE226" t="n">
         <v>-12</v>
@@ -39716,16 +39716,16 @@
         <v>-12</v>
       </c>
       <c r="AG226" t="n">
-        <v>25</v>
+        <v>-30</v>
       </c>
       <c r="AH226" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="AI226" t="n">
         <v>0</v>
       </c>
       <c r="AJ226" t="n">
-        <v>-20</v>
+        <v>4</v>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
@@ -39733,25 +39733,25 @@
         </is>
       </c>
       <c r="AL226" t="n">
-        <v>8</v>
+        <v>-16</v>
       </c>
       <c r="AM226" t="n">
-        <v>40</v>
+        <v>-400</v>
       </c>
       <c r="AN226" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AO226" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
@@ -39766,29 +39766,29 @@
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>3227.TWO</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -39807,28 +39807,28 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>1500</v>
+        <v>185</v>
       </c>
       <c r="G227" t="n">
-        <v>1584</v>
+        <v>185.1</v>
       </c>
       <c r="H227" t="n">
-        <v>1650.5</v>
+        <v>186</v>
       </c>
       <c r="I227" t="n">
-        <v>1601.5</v>
+        <v>185.88</v>
       </c>
       <c r="J227" t="n">
-        <v>20818000</v>
+        <v>748000</v>
       </c>
       <c r="K227" t="n">
-        <v>13116000</v>
+        <v>1076200</v>
       </c>
       <c r="L227" t="n">
-        <v>1835</v>
+        <v>190.5</v>
       </c>
       <c r="M227" t="n">
-        <v>1355</v>
+        <v>181.5</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="AJ227" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
@@ -39907,10 +39907,10 @@
         </is>
       </c>
       <c r="AL227" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AM227" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="AN227" t="n">
         <v>0</v>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
@@ -39940,7 +39940,7 @@
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>跌破5日線、死亡交叉、成交量放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
@@ -39950,19 +39950,19 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、死亡交叉、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3227.TWO</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -39981,28 +39981,28 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>185</v>
+        <v>1500</v>
       </c>
       <c r="G228" t="n">
-        <v>185.1</v>
+        <v>1584</v>
       </c>
       <c r="H228" t="n">
-        <v>186</v>
+        <v>1650.5</v>
       </c>
       <c r="I228" t="n">
-        <v>185.88</v>
+        <v>1601.5</v>
       </c>
       <c r="J228" t="n">
-        <v>748000</v>
+        <v>20818000</v>
       </c>
       <c r="K228" t="n">
-        <v>1076200</v>
+        <v>13116000</v>
       </c>
       <c r="L228" t="n">
-        <v>190.5</v>
+        <v>1835</v>
       </c>
       <c r="M228" t="n">
-        <v>181.5</v>
+        <v>1355</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -40073,7 +40073,7 @@
         <v>0</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
@@ -40081,10 +40081,10 @@
         </is>
       </c>
       <c r="AL228" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM228" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="AN228" t="n">
         <v>0</v>
@@ -40099,7 +40099,7 @@
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
@@ -40114,7 +40114,7 @@
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>跌破5日線、死亡交叉、成交量放大</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
@@ -40124,19 +40124,19 @@
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、死亡交叉、成交量放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1234.TW</t>
+          <t>1611.TW</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>黑松</t>
+          <t>中電</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -40155,28 +40155,28 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>32.2</v>
+        <v>11.4</v>
       </c>
       <c r="G229" t="n">
-        <v>32.48</v>
+        <v>11.38</v>
       </c>
       <c r="H229" t="n">
-        <v>32.42</v>
+        <v>11.35</v>
       </c>
       <c r="I229" t="n">
-        <v>32.63</v>
+        <v>11.36</v>
       </c>
       <c r="J229" t="n">
-        <v>58897</v>
+        <v>237043</v>
       </c>
       <c r="K229" t="n">
-        <v>81715</v>
+        <v>579971</v>
       </c>
       <c r="L229" t="n">
-        <v>33.3</v>
+        <v>11.6</v>
       </c>
       <c r="M229" t="n">
-        <v>32</v>
+        <v>11.05</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
@@ -40184,28 +40184,28 @@
         </is>
       </c>
       <c r="O229" t="n">
-        <v>-8000</v>
+        <v>-110864</v>
       </c>
       <c r="P229" t="n">
-        <v>-11504</v>
+        <v>-573057</v>
       </c>
       <c r="Q229" t="n">
-        <v>39801</v>
+        <v>-1059379</v>
       </c>
       <c r="R229" t="n">
-        <v>33697</v>
+        <v>-1905929</v>
       </c>
       <c r="S229" t="n">
-        <v>-8000</v>
+        <v>-110864</v>
       </c>
       <c r="T229" t="n">
-        <v>-10995</v>
+        <v>-521043</v>
       </c>
       <c r="U229" t="n">
-        <v>40310</v>
+        <v>-838365</v>
       </c>
       <c r="V229" t="n">
-        <v>34150</v>
+        <v>-1167173</v>
       </c>
       <c r="W229" t="n">
         <v>0</v>
@@ -40223,13 +40223,13 @@
         <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>-509</v>
+        <v>-52014</v>
       </c>
       <c r="AC229" t="n">
-        <v>-509</v>
+        <v>-221014</v>
       </c>
       <c r="AD229" t="n">
-        <v>-453</v>
+        <v>-738756</v>
       </c>
       <c r="AE229" t="n">
         <v>-12</v>
@@ -40238,16 +40238,16 @@
         <v>-12</v>
       </c>
       <c r="AG229" t="n">
-        <v>-30</v>
+        <v>25</v>
       </c>
       <c r="AH229" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AI229" t="n">
         <v>0</v>
       </c>
       <c r="AJ229" t="n">
-        <v>-12</v>
+        <v>-24</v>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
@@ -40255,25 +40255,25 @@
         </is>
       </c>
       <c r="AL229" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AM229" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AN229" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO229" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
@@ -40288,29 +40288,29 @@
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2516.TW</t>
+          <t>1234.TW</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>新建</t>
+          <t>黑松</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -40329,28 +40329,28 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>15.15</v>
+        <v>32.2</v>
       </c>
       <c r="G230" t="n">
-        <v>15.25</v>
+        <v>32.48</v>
       </c>
       <c r="H230" t="n">
-        <v>15.27</v>
+        <v>32.42</v>
       </c>
       <c r="I230" t="n">
-        <v>15.12</v>
+        <v>32.63</v>
       </c>
       <c r="J230" t="n">
-        <v>113582</v>
+        <v>58897</v>
       </c>
       <c r="K230" t="n">
-        <v>229655</v>
+        <v>81715</v>
       </c>
       <c r="L230" t="n">
-        <v>15.8</v>
+        <v>33.3</v>
       </c>
       <c r="M230" t="n">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -40358,28 +40358,28 @@
         </is>
       </c>
       <c r="O230" t="n">
-        <v>-34947</v>
+        <v>-8000</v>
       </c>
       <c r="P230" t="n">
-        <v>32511</v>
+        <v>-11504</v>
       </c>
       <c r="Q230" t="n">
-        <v>16511</v>
+        <v>39801</v>
       </c>
       <c r="R230" t="n">
-        <v>121457</v>
+        <v>33697</v>
       </c>
       <c r="S230" t="n">
-        <v>-34947</v>
+        <v>-8000</v>
       </c>
       <c r="T230" t="n">
-        <v>32511</v>
+        <v>-10995</v>
       </c>
       <c r="U230" t="n">
-        <v>9511</v>
+        <v>40310</v>
       </c>
       <c r="V230" t="n">
-        <v>118461</v>
+        <v>34150</v>
       </c>
       <c r="W230" t="n">
         <v>0</v>
@@ -40397,13 +40397,13 @@
         <v>0</v>
       </c>
       <c r="AB230" t="n">
-        <v>0</v>
+        <v>-509</v>
       </c>
       <c r="AC230" t="n">
-        <v>7000</v>
+        <v>-509</v>
       </c>
       <c r="AD230" t="n">
-        <v>2996</v>
+        <v>-453</v>
       </c>
       <c r="AE230" t="n">
         <v>-12</v>
@@ -40421,7 +40421,7 @@
         <v>0</v>
       </c>
       <c r="AJ230" t="n">
-        <v>4</v>
+        <v>-12</v>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
@@ -40429,10 +40429,10 @@
         </is>
       </c>
       <c r="AL230" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AM230" t="n">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="AN230" t="n">
         <v>0</v>
@@ -40447,7 +40447,7 @@
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
@@ -40479,12 +40479,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1611.TW</t>
+          <t>3406.TW</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>中電</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -40503,28 +40503,28 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>11.4</v>
+        <v>1140</v>
       </c>
       <c r="G231" t="n">
-        <v>11.38</v>
+        <v>1085</v>
       </c>
       <c r="H231" t="n">
-        <v>11.35</v>
+        <v>1088</v>
       </c>
       <c r="I231" t="n">
-        <v>11.36</v>
+        <v>1017.2</v>
       </c>
       <c r="J231" t="n">
-        <v>237043</v>
+        <v>2682052</v>
       </c>
       <c r="K231" t="n">
-        <v>579971</v>
+        <v>8572271</v>
       </c>
       <c r="L231" t="n">
-        <v>11.6</v>
+        <v>1220</v>
       </c>
       <c r="M231" t="n">
-        <v>11.05</v>
+        <v>869</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -40532,61 +40532,61 @@
         </is>
       </c>
       <c r="O231" t="n">
-        <v>-110864</v>
+        <v>-452550</v>
       </c>
       <c r="P231" t="n">
-        <v>-573057</v>
+        <v>-949320</v>
       </c>
       <c r="Q231" t="n">
-        <v>-1059379</v>
+        <v>-2014775</v>
       </c>
       <c r="R231" t="n">
-        <v>-1905929</v>
+        <v>-3566262</v>
       </c>
       <c r="S231" t="n">
-        <v>-110864</v>
+        <v>-328519</v>
       </c>
       <c r="T231" t="n">
-        <v>-521043</v>
+        <v>-1042031</v>
       </c>
       <c r="U231" t="n">
-        <v>-838365</v>
+        <v>-2732390</v>
       </c>
       <c r="V231" t="n">
-        <v>-1167173</v>
+        <v>-5607070</v>
       </c>
       <c r="W231" t="n">
         <v>0</v>
       </c>
       <c r="X231" t="n">
-        <v>0</v>
+        <v>23973</v>
       </c>
       <c r="Y231" t="n">
-        <v>0</v>
+        <v>678973</v>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>2335473</v>
       </c>
       <c r="AA231" t="n">
-        <v>0</v>
+        <v>-124031</v>
       </c>
       <c r="AB231" t="n">
-        <v>-52014</v>
+        <v>68738</v>
       </c>
       <c r="AC231" t="n">
-        <v>-221014</v>
+        <v>38642</v>
       </c>
       <c r="AD231" t="n">
-        <v>-738756</v>
+        <v>-294665</v>
       </c>
       <c r="AE231" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="AF231" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="AG231" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AH231" t="n">
         <v>-55</v>
@@ -40595,7 +40595,7 @@
         <v>0</v>
       </c>
       <c r="AJ231" t="n">
-        <v>-24</v>
+        <v>-30</v>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
@@ -40603,16 +40603,16 @@
         </is>
       </c>
       <c r="AL231" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AM231" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="AN231" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AO231" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
@@ -40636,17 +40636,17 @@
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、接近20日高點、接近20日低點、法人連續偏賣、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -40827,12 +40827,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3406.TW</t>
+          <t>2449.TW</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -40851,28 +40851,28 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>1140</v>
+        <v>278</v>
       </c>
       <c r="G233" t="n">
-        <v>1085</v>
+        <v>269.6</v>
       </c>
       <c r="H233" t="n">
-        <v>1088</v>
+        <v>285.35</v>
       </c>
       <c r="I233" t="n">
-        <v>1017.2</v>
+        <v>292.98</v>
       </c>
       <c r="J233" t="n">
-        <v>2682052</v>
+        <v>23064413</v>
       </c>
       <c r="K233" t="n">
-        <v>8572271</v>
+        <v>25825216</v>
       </c>
       <c r="L233" t="n">
-        <v>1220</v>
+        <v>330</v>
       </c>
       <c r="M233" t="n">
-        <v>869</v>
+        <v>255</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -40880,52 +40880,52 @@
         </is>
       </c>
       <c r="O233" t="n">
-        <v>-452550</v>
+        <v>4668678</v>
       </c>
       <c r="P233" t="n">
-        <v>-949320</v>
+        <v>-1870049</v>
       </c>
       <c r="Q233" t="n">
-        <v>-2014775</v>
+        <v>-29331166</v>
       </c>
       <c r="R233" t="n">
-        <v>-3566262</v>
+        <v>-65172983</v>
       </c>
       <c r="S233" t="n">
-        <v>-328519</v>
+        <v>1550404</v>
       </c>
       <c r="T233" t="n">
-        <v>-1042031</v>
+        <v>-8013028</v>
       </c>
       <c r="U233" t="n">
-        <v>-2732390</v>
+        <v>-33394760</v>
       </c>
       <c r="V233" t="n">
-        <v>-5607070</v>
+        <v>-54203027</v>
       </c>
       <c r="W233" t="n">
-        <v>0</v>
+        <v>1162900</v>
       </c>
       <c r="X233" t="n">
-        <v>23973</v>
+        <v>4387451</v>
       </c>
       <c r="Y233" t="n">
-        <v>678973</v>
+        <v>4297201</v>
       </c>
       <c r="Z233" t="n">
-        <v>2335473</v>
+        <v>-9806348</v>
       </c>
       <c r="AA233" t="n">
-        <v>-124031</v>
+        <v>1955374</v>
       </c>
       <c r="AB233" t="n">
-        <v>68738</v>
+        <v>1755528</v>
       </c>
       <c r="AC233" t="n">
-        <v>38642</v>
+        <v>-233607</v>
       </c>
       <c r="AD233" t="n">
-        <v>-294665</v>
+        <v>-1163608</v>
       </c>
       <c r="AE233" t="n">
         <v>-14</v>
@@ -40934,16 +40934,16 @@
         <v>-14</v>
       </c>
       <c r="AG233" t="n">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="AH233" t="n">
-        <v>-55</v>
+        <v>-30</v>
       </c>
       <c r="AI233" t="n">
         <v>0</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-30</v>
+        <v>-44</v>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
@@ -40951,25 +40951,25 @@
         </is>
       </c>
       <c r="AL233" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AM233" t="n">
-        <v>53.33</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AN233" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="AO233" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
@@ -40984,17 +40984,17 @@
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -41523,12 +41523,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2449.TW</t>
+          <t>2472.TW</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -41547,28 +41547,28 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>278</v>
+        <v>219.5</v>
       </c>
       <c r="G237" t="n">
-        <v>269.6</v>
+        <v>219.8</v>
       </c>
       <c r="H237" t="n">
-        <v>285.35</v>
+        <v>230.9</v>
       </c>
       <c r="I237" t="n">
-        <v>292.98</v>
+        <v>225.55</v>
       </c>
       <c r="J237" t="n">
-        <v>23064413</v>
+        <v>2258876</v>
       </c>
       <c r="K237" t="n">
-        <v>25825216</v>
+        <v>3283177</v>
       </c>
       <c r="L237" t="n">
-        <v>330</v>
+        <v>252.5</v>
       </c>
       <c r="M237" t="n">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
@@ -41576,52 +41576,52 @@
         </is>
       </c>
       <c r="O237" t="n">
-        <v>4668678</v>
+        <v>274893</v>
       </c>
       <c r="P237" t="n">
-        <v>-1870049</v>
+        <v>788769</v>
       </c>
       <c r="Q237" t="n">
-        <v>-29331166</v>
+        <v>-762569</v>
       </c>
       <c r="R237" t="n">
-        <v>-65172983</v>
+        <v>-6899878</v>
       </c>
       <c r="S237" t="n">
-        <v>1550404</v>
+        <v>277109</v>
       </c>
       <c r="T237" t="n">
-        <v>-8013028</v>
+        <v>871072</v>
       </c>
       <c r="U237" t="n">
-        <v>-33394760</v>
+        <v>-620155</v>
       </c>
       <c r="V237" t="n">
-        <v>-54203027</v>
+        <v>-7169737</v>
       </c>
       <c r="W237" t="n">
-        <v>1162900</v>
+        <v>6000</v>
       </c>
       <c r="X237" t="n">
-        <v>4387451</v>
+        <v>10986</v>
       </c>
       <c r="Y237" t="n">
-        <v>4297201</v>
+        <v>93986</v>
       </c>
       <c r="Z237" t="n">
-        <v>-9806348</v>
+        <v>234986</v>
       </c>
       <c r="AA237" t="n">
-        <v>1955374</v>
+        <v>-8216</v>
       </c>
       <c r="AB237" t="n">
-        <v>1755528</v>
+        <v>-93289</v>
       </c>
       <c r="AC237" t="n">
-        <v>-233607</v>
+        <v>-236400</v>
       </c>
       <c r="AD237" t="n">
-        <v>-1163608</v>
+        <v>34873</v>
       </c>
       <c r="AE237" t="n">
         <v>-14</v>
@@ -41630,16 +41630,16 @@
         <v>-14</v>
       </c>
       <c r="AG237" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="AH237" t="n">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="AI237" t="n">
         <v>0</v>
       </c>
       <c r="AJ237" t="n">
-        <v>-44</v>
+        <v>-26</v>
       </c>
       <c r="AK237" t="inlineStr">
         <is>
@@ -41647,16 +41647,16 @@
         </is>
       </c>
       <c r="AL237" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AM237" t="n">
-        <v>68.18000000000001</v>
+        <v>46.15</v>
       </c>
       <c r="AN237" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AO237" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
@@ -41680,17 +41680,17 @@
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -41871,12 +41871,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2615.TW</t>
+          <t>3450.TW</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>萬海</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -41895,28 +41895,28 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>116.5</v>
+        <v>450</v>
       </c>
       <c r="G239" t="n">
-        <v>118.7</v>
+        <v>449.8</v>
       </c>
       <c r="H239" t="n">
-        <v>118.4</v>
+        <v>479.8</v>
       </c>
       <c r="I239" t="n">
-        <v>115.95</v>
+        <v>504.35</v>
       </c>
       <c r="J239" t="n">
-        <v>10192383</v>
+        <v>4067013</v>
       </c>
       <c r="K239" t="n">
-        <v>13655318</v>
+        <v>6198863</v>
       </c>
       <c r="L239" t="n">
-        <v>129.5</v>
+        <v>574</v>
       </c>
       <c r="M239" t="n">
-        <v>110</v>
+        <v>426.5</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -41924,52 +41924,52 @@
         </is>
       </c>
       <c r="O239" t="n">
-        <v>-83374</v>
+        <v>80579</v>
       </c>
       <c r="P239" t="n">
-        <v>-6847</v>
+        <v>-8365</v>
       </c>
       <c r="Q239" t="n">
-        <v>-89240</v>
+        <v>-2497804</v>
       </c>
       <c r="R239" t="n">
-        <v>3062882</v>
+        <v>-8773067</v>
       </c>
       <c r="S239" t="n">
-        <v>279020</v>
+        <v>806914</v>
       </c>
       <c r="T239" t="n">
-        <v>511490</v>
+        <v>2679461</v>
       </c>
       <c r="U239" t="n">
-        <v>244850</v>
+        <v>2576374</v>
       </c>
       <c r="V239" t="n">
-        <v>2599081</v>
+        <v>-933994</v>
       </c>
       <c r="W239" t="n">
-        <v>7872</v>
+        <v>-735000</v>
       </c>
       <c r="X239" t="n">
-        <v>538120</v>
+        <v>-2629004</v>
       </c>
       <c r="Y239" t="n">
-        <v>616516</v>
+        <v>-4694004</v>
       </c>
       <c r="Z239" t="n">
-        <v>1081516</v>
+        <v>-7273004</v>
       </c>
       <c r="AA239" t="n">
-        <v>-370266</v>
+        <v>8665</v>
       </c>
       <c r="AB239" t="n">
-        <v>-1056457</v>
+        <v>-58822</v>
       </c>
       <c r="AC239" t="n">
-        <v>-950606</v>
+        <v>-380174</v>
       </c>
       <c r="AD239" t="n">
-        <v>-617715</v>
+        <v>-566069</v>
       </c>
       <c r="AE239" t="n">
         <v>-14</v>
@@ -41978,16 +41978,16 @@
         <v>-14</v>
       </c>
       <c r="AG239" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AH239" t="n">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="AI239" t="n">
         <v>0</v>
       </c>
       <c r="AJ239" t="n">
-        <v>22</v>
+        <v>-44</v>
       </c>
       <c r="AK239" t="inlineStr">
         <is>
@@ -41995,25 +41995,25 @@
         </is>
       </c>
       <c r="AL239" t="n">
-        <v>-36</v>
+        <v>30</v>
       </c>
       <c r="AM239" t="n">
-        <v>-163.64</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AN239" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AO239" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
@@ -42028,29 +42028,29 @@
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人小幅賣超、外資投信同步買超</t>
+          <t>5日法人明顯賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人小幅賣超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2472.TW</t>
+          <t>2615.TW</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>萬海</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -42069,28 +42069,28 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>219.5</v>
+        <v>116.5</v>
       </c>
       <c r="G240" t="n">
-        <v>219.8</v>
+        <v>118.7</v>
       </c>
       <c r="H240" t="n">
-        <v>230.9</v>
+        <v>118.4</v>
       </c>
       <c r="I240" t="n">
-        <v>225.55</v>
+        <v>115.95</v>
       </c>
       <c r="J240" t="n">
-        <v>2258876</v>
+        <v>10192383</v>
       </c>
       <c r="K240" t="n">
-        <v>3283177</v>
+        <v>13655318</v>
       </c>
       <c r="L240" t="n">
-        <v>252.5</v>
+        <v>129.5</v>
       </c>
       <c r="M240" t="n">
-        <v>206</v>
+        <v>110</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -42098,52 +42098,52 @@
         </is>
       </c>
       <c r="O240" t="n">
-        <v>274893</v>
+        <v>-83374</v>
       </c>
       <c r="P240" t="n">
-        <v>788769</v>
+        <v>-6847</v>
       </c>
       <c r="Q240" t="n">
-        <v>-762569</v>
+        <v>-89240</v>
       </c>
       <c r="R240" t="n">
-        <v>-6899878</v>
+        <v>3062882</v>
       </c>
       <c r="S240" t="n">
-        <v>277109</v>
+        <v>279020</v>
       </c>
       <c r="T240" t="n">
-        <v>871072</v>
+        <v>511490</v>
       </c>
       <c r="U240" t="n">
-        <v>-620155</v>
+        <v>244850</v>
       </c>
       <c r="V240" t="n">
-        <v>-7169737</v>
+        <v>2599081</v>
       </c>
       <c r="W240" t="n">
-        <v>6000</v>
+        <v>7872</v>
       </c>
       <c r="X240" t="n">
-        <v>10986</v>
+        <v>538120</v>
       </c>
       <c r="Y240" t="n">
-        <v>93986</v>
+        <v>616516</v>
       </c>
       <c r="Z240" t="n">
-        <v>234986</v>
+        <v>1081516</v>
       </c>
       <c r="AA240" t="n">
-        <v>-8216</v>
+        <v>-370266</v>
       </c>
       <c r="AB240" t="n">
-        <v>-93289</v>
+        <v>-1056457</v>
       </c>
       <c r="AC240" t="n">
-        <v>-236400</v>
+        <v>-950606</v>
       </c>
       <c r="AD240" t="n">
-        <v>34873</v>
+        <v>-617715</v>
       </c>
       <c r="AE240" t="n">
         <v>-14</v>
@@ -42152,16 +42152,16 @@
         <v>-14</v>
       </c>
       <c r="AG240" t="n">
-        <v>-20</v>
+        <v>5</v>
       </c>
       <c r="AH240" t="n">
-        <v>-15</v>
+        <v>-40</v>
       </c>
       <c r="AI240" t="n">
         <v>0</v>
       </c>
       <c r="AJ240" t="n">
-        <v>-26</v>
+        <v>22</v>
       </c>
       <c r="AK240" t="inlineStr">
         <is>
@@ -42169,16 +42169,16 @@
         </is>
       </c>
       <c r="AL240" t="n">
-        <v>12</v>
+        <v>-36</v>
       </c>
       <c r="AM240" t="n">
-        <v>46.15</v>
+        <v>-163.64</v>
       </c>
       <c r="AN240" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO240" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR240" t="inlineStr">
@@ -42202,17 +42202,17 @@
       </c>
       <c r="AT240" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人小幅賣超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、法人連續偏賣、中期買超轉短線賣壓、5日法人小幅賣超、外資投信同步買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -42272,16 +42272,16 @@
         </is>
       </c>
       <c r="O241" t="n">
-        <v>11599233</v>
+        <v>11574233</v>
       </c>
       <c r="P241" t="n">
-        <v>1690941</v>
+        <v>1665941</v>
       </c>
       <c r="Q241" t="n">
-        <v>-5419724</v>
+        <v>-5444724</v>
       </c>
       <c r="R241" t="n">
-        <v>-45239215</v>
+        <v>-45264215</v>
       </c>
       <c r="S241" t="n">
         <v>11726206</v>
@@ -42296,16 +42296,16 @@
         <v>-28706613</v>
       </c>
       <c r="W241" t="n">
-        <v>-1987145</v>
+        <v>-2012145</v>
       </c>
       <c r="X241" t="n">
-        <v>-4268778</v>
+        <v>-4293778</v>
       </c>
       <c r="Y241" t="n">
-        <v>-4170975</v>
+        <v>-4195975</v>
       </c>
       <c r="Z241" t="n">
-        <v>-15779916</v>
+        <v>-15804916</v>
       </c>
       <c r="AA241" t="n">
         <v>1860172</v>
@@ -46448,16 +46448,16 @@
         </is>
       </c>
       <c r="O265" t="n">
-        <v>4065596</v>
+        <v>4040596</v>
       </c>
       <c r="P265" t="n">
-        <v>-5990432</v>
+        <v>-6015432</v>
       </c>
       <c r="Q265" t="n">
-        <v>-36845906</v>
+        <v>-36870906</v>
       </c>
       <c r="R265" t="n">
-        <v>-97756815</v>
+        <v>-97781815</v>
       </c>
       <c r="S265" t="n">
         <v>3814875</v>
@@ -46472,16 +46472,16 @@
         <v>-81533488</v>
       </c>
       <c r="W265" t="n">
-        <v>-940773</v>
+        <v>-965773</v>
       </c>
       <c r="X265" t="n">
-        <v>-1928347</v>
+        <v>-1953347</v>
       </c>
       <c r="Y265" t="n">
-        <v>-11428031</v>
+        <v>-11453031</v>
       </c>
       <c r="Z265" t="n">
-        <v>-15318477</v>
+        <v>-15343477</v>
       </c>
       <c r="AA265" t="n">
         <v>1191494</v>
@@ -52188,16 +52188,16 @@
         </is>
       </c>
       <c r="O298" t="n">
-        <v>-173973</v>
+        <v>-174463</v>
       </c>
       <c r="P298" t="n">
-        <v>154538</v>
+        <v>154048</v>
       </c>
       <c r="Q298" t="n">
-        <v>-136630</v>
+        <v>-137120</v>
       </c>
       <c r="R298" t="n">
-        <v>-2528521</v>
+        <v>-2529011</v>
       </c>
       <c r="S298" t="n">
         <v>-149469</v>
@@ -52212,16 +52212,16 @@
         <v>-2544465</v>
       </c>
       <c r="W298" t="n">
-        <v>1000</v>
+        <v>510</v>
       </c>
       <c r="X298" t="n">
-        <v>1662</v>
+        <v>1172</v>
       </c>
       <c r="Y298" t="n">
-        <v>-12185</v>
+        <v>-12675</v>
       </c>
       <c r="Z298" t="n">
-        <v>-10794</v>
+        <v>-11284</v>
       </c>
       <c r="AA298" t="n">
         <v>-25504</v>
@@ -52710,16 +52710,16 @@
         </is>
       </c>
       <c r="O301" t="n">
-        <v>-614272</v>
+        <v>-541272</v>
       </c>
       <c r="P301" t="n">
-        <v>-1184681</v>
+        <v>-1111681</v>
       </c>
       <c r="Q301" t="n">
-        <v>-2906860</v>
+        <v>-2833860</v>
       </c>
       <c r="R301" t="n">
-        <v>-3302939</v>
+        <v>-3229939</v>
       </c>
       <c r="S301" t="n">
         <v>-826476</v>
@@ -52734,16 +52734,16 @@
         <v>-3841905</v>
       </c>
       <c r="W301" t="n">
-        <v>241550</v>
+        <v>314550</v>
       </c>
       <c r="X301" t="n">
-        <v>412224</v>
+        <v>485224</v>
       </c>
       <c r="Y301" t="n">
-        <v>616832</v>
+        <v>689832</v>
       </c>
       <c r="Z301" t="n">
-        <v>488148</v>
+        <v>561148</v>
       </c>
       <c r="AA301" t="n">
         <v>-29346</v>
@@ -56016,16 +56016,16 @@
         </is>
       </c>
       <c r="O320" t="n">
-        <v>-15737845</v>
+        <v>-15727845</v>
       </c>
       <c r="P320" t="n">
-        <v>-13937354</v>
+        <v>-13927354</v>
       </c>
       <c r="Q320" t="n">
-        <v>-6589984</v>
+        <v>-6579984</v>
       </c>
       <c r="R320" t="n">
-        <v>136993</v>
+        <v>146993</v>
       </c>
       <c r="S320" t="n">
         <v>-15445427</v>
@@ -56040,16 +56040,16 @@
         <v>-6843213</v>
       </c>
       <c r="W320" t="n">
-        <v>113036</v>
+        <v>123036</v>
       </c>
       <c r="X320" t="n">
-        <v>2090693</v>
+        <v>2100693</v>
       </c>
       <c r="Y320" t="n">
-        <v>3586901</v>
+        <v>3596901</v>
       </c>
       <c r="Z320" t="n">
-        <v>8919901</v>
+        <v>8929901</v>
       </c>
       <c r="AA320" t="n">
         <v>-405454</v>
@@ -58452,16 +58452,16 @@
         </is>
       </c>
       <c r="O334" t="n">
-        <v>-143696</v>
+        <v>-223696</v>
       </c>
       <c r="P334" t="n">
-        <v>-143692</v>
+        <v>-223692</v>
       </c>
       <c r="Q334" t="n">
-        <v>-248313</v>
+        <v>-328313</v>
       </c>
       <c r="R334" t="n">
-        <v>-379753</v>
+        <v>-459753</v>
       </c>
       <c r="S334" t="n">
         <v>-179520</v>
@@ -58476,16 +58476,16 @@
         <v>-921105</v>
       </c>
       <c r="W334" t="n">
-        <v>77000</v>
+        <v>-3000</v>
       </c>
       <c r="X334" t="n">
-        <v>244976</v>
+        <v>164976</v>
       </c>
       <c r="Y334" t="n">
-        <v>573032</v>
+        <v>493032</v>
       </c>
       <c r="Z334" t="n">
-        <v>618963</v>
+        <v>538963</v>
       </c>
       <c r="AA334" t="n">
         <v>-41176</v>
@@ -62454,16 +62454,16 @@
         </is>
       </c>
       <c r="O357" t="n">
-        <v>-635357</v>
+        <v>-562357</v>
       </c>
       <c r="P357" t="n">
-        <v>-860312</v>
+        <v>-787312</v>
       </c>
       <c r="Q357" t="n">
-        <v>-3221787</v>
+        <v>-3148787</v>
       </c>
       <c r="R357" t="n">
-        <v>-5000661</v>
+        <v>-4927661</v>
       </c>
       <c r="S357" t="n">
         <v>-170456</v>
@@ -62478,16 +62478,16 @@
         <v>5379123</v>
       </c>
       <c r="W357" t="n">
-        <v>-194545</v>
+        <v>-121545</v>
       </c>
       <c r="X357" t="n">
-        <v>-1734792</v>
+        <v>-1661792</v>
       </c>
       <c r="Y357" t="n">
-        <v>-8355371</v>
+        <v>-8282371</v>
       </c>
       <c r="Z357" t="n">
-        <v>-10058650</v>
+        <v>-9985650</v>
       </c>
       <c r="AA357" t="n">
         <v>-270356</v>
@@ -62802,16 +62802,16 @@
         </is>
       </c>
       <c r="O359" t="n">
-        <v>-5814019</v>
+        <v>-5804019</v>
       </c>
       <c r="P359" t="n">
-        <v>-18781762</v>
+        <v>-18771762</v>
       </c>
       <c r="Q359" t="n">
-        <v>-64614076</v>
+        <v>-64604076</v>
       </c>
       <c r="R359" t="n">
-        <v>-109287560</v>
+        <v>-109277560</v>
       </c>
       <c r="S359" t="n">
         <v>-6153898</v>
@@ -62826,16 +62826,16 @@
         <v>-136793367</v>
       </c>
       <c r="W359" t="n">
-        <v>1387512</v>
+        <v>1397512</v>
       </c>
       <c r="X359" t="n">
-        <v>6301759</v>
+        <v>6311759</v>
       </c>
       <c r="Y359" t="n">
-        <v>10246999</v>
+        <v>10256999</v>
       </c>
       <c r="Z359" t="n">
-        <v>15500678</v>
+        <v>15510678</v>
       </c>
       <c r="AA359" t="n">
         <v>-1047633</v>
@@ -64728,16 +64728,16 @@
         <v>-978449815</v>
       </c>
       <c r="S370" t="n">
-        <v>-17720116</v>
+        <v>-16220116</v>
       </c>
       <c r="T370" t="n">
-        <v>-103643891</v>
+        <v>-102143891</v>
       </c>
       <c r="U370" t="n">
-        <v>-235742448</v>
+        <v>-234242448</v>
       </c>
       <c r="V370" t="n">
-        <v>-447494592</v>
+        <v>-445994592</v>
       </c>
       <c r="W370" t="n">
         <v>2350000</v>
@@ -64752,16 +64752,16 @@
         <v>20556150</v>
       </c>
       <c r="AA370" t="n">
-        <v>-11104549</v>
+        <v>-12604549</v>
       </c>
       <c r="AB370" t="n">
-        <v>-106481233</v>
+        <v>-107981233</v>
       </c>
       <c r="AC370" t="n">
-        <v>-394485582</v>
+        <v>-395985582</v>
       </c>
       <c r="AD370" t="n">
-        <v>-551511373</v>
+        <v>-553011373</v>
       </c>
       <c r="AE370" t="n">
         <v>-44</v>
@@ -65772,16 +65772,16 @@
         <v>-26040390</v>
       </c>
       <c r="S376" t="n">
-        <v>-1185605</v>
+        <v>-1161605</v>
       </c>
       <c r="T376" t="n">
-        <v>-3904427</v>
+        <v>-3880427</v>
       </c>
       <c r="U376" t="n">
-        <v>-12411175</v>
+        <v>-12387175</v>
       </c>
       <c r="V376" t="n">
-        <v>-26830874</v>
+        <v>-26806874</v>
       </c>
       <c r="W376" t="n">
         <v>167225</v>
@@ -65796,16 +65796,16 @@
         <v>1585720</v>
       </c>
       <c r="AA376" t="n">
-        <v>-627508</v>
+        <v>-651508</v>
       </c>
       <c r="AB376" t="n">
-        <v>-939383</v>
+        <v>-963383</v>
       </c>
       <c r="AC376" t="n">
-        <v>-858998</v>
+        <v>-882998</v>
       </c>
       <c r="AD376" t="n">
-        <v>-795236</v>
+        <v>-819236</v>
       </c>
       <c r="AE376" t="n">
         <v>-44</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -32487,12 +32487,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>6187.TWO</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -32511,28 +32511,28 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1420</v>
+        <v>1260</v>
       </c>
       <c r="G185" t="n">
-        <v>1543</v>
+        <v>1345</v>
       </c>
       <c r="H185" t="n">
-        <v>1620.5</v>
+        <v>1445.5</v>
       </c>
       <c r="I185" t="n">
-        <v>1600.75</v>
+        <v>1394</v>
       </c>
       <c r="J185" t="n">
-        <v>18732000</v>
+        <v>2023000</v>
       </c>
       <c r="K185" t="n">
-        <v>14012000</v>
+        <v>2374200</v>
       </c>
       <c r="L185" t="n">
-        <v>1835</v>
+        <v>1680</v>
       </c>
       <c r="M185" t="n">
-        <v>1395</v>
+        <v>1180</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
@@ -32603,24 +32603,24 @@
         <v>0</v>
       </c>
       <c r="AJ185" t="n">
-        <v>24</v>
+        <v>-18</v>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AL185" t="n">
-        <v>-32</v>
+        <v>10</v>
       </c>
       <c r="AM185" t="n">
-        <v>-133.33</v>
+        <v>55.56</v>
       </c>
       <c r="AN185" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO185" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
@@ -32644,7 +32644,7 @@
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
@@ -32654,19 +32654,19 @@
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>6187.TWO</t>
+          <t>3673.TW</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -32685,57 +32685,57 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1260</v>
+        <v>73</v>
       </c>
       <c r="G186" t="n">
-        <v>1345</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="H186" t="n">
-        <v>1445.5</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="I186" t="n">
-        <v>1394</v>
+        <v>72.61</v>
       </c>
       <c r="J186" t="n">
-        <v>2023000</v>
+        <v>36223049</v>
       </c>
       <c r="K186" t="n">
-        <v>2374200</v>
+        <v>17341534</v>
       </c>
       <c r="L186" t="n">
-        <v>1680</v>
+        <v>81</v>
       </c>
       <c r="M186" t="n">
-        <v>1180</v>
+        <v>64.2</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
+        <v>-2541256</v>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>-6327062</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>-5498046</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>-5543345</v>
       </c>
       <c r="S186" t="n">
-        <v>0</v>
+        <v>-2161322</v>
       </c>
       <c r="T186" t="n">
-        <v>0</v>
+        <v>-7056057</v>
       </c>
       <c r="U186" t="n">
-        <v>0</v>
+        <v>-5983326</v>
       </c>
       <c r="V186" t="n">
-        <v>0</v>
+        <v>-5138283</v>
       </c>
       <c r="W186" t="n">
         <v>0</v>
@@ -32744,22 +32744,22 @@
         <v>0</v>
       </c>
       <c r="Y186" t="n">
-        <v>0</v>
+        <v>-128000</v>
       </c>
       <c r="Z186" t="n">
-        <v>0</v>
+        <v>-128000</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>-379934</v>
       </c>
       <c r="AB186" t="n">
-        <v>0</v>
+        <v>728995</v>
       </c>
       <c r="AC186" t="n">
-        <v>0</v>
+        <v>613280</v>
       </c>
       <c r="AD186" t="n">
-        <v>0</v>
+        <v>-277062</v>
       </c>
       <c r="AE186" t="n">
         <v>-8</v>
@@ -32768,16 +32768,16 @@
         <v>-8</v>
       </c>
       <c r="AG186" t="n">
+        <v>65</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>-75</v>
+      </c>
+      <c r="AI186" t="n">
         <v>-20</v>
       </c>
-      <c r="AH186" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI186" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ186" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AK186" t="inlineStr">
         <is>
@@ -32785,25 +32785,25 @@
         </is>
       </c>
       <c r="AL186" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AM186" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="AN186" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="AO186" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
@@ -32818,29 +32818,29 @@
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>站上5日線、黃金交叉、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、黃金交叉、爆量、爆量價未漲、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>6121.TWO</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>新普</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -32859,28 +32859,28 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>364</v>
+        <v>1420</v>
       </c>
       <c r="G187" t="n">
-        <v>367.2</v>
+        <v>1543</v>
       </c>
       <c r="H187" t="n">
-        <v>365.75</v>
+        <v>1620.5</v>
       </c>
       <c r="I187" t="n">
-        <v>371.52</v>
+        <v>1600.75</v>
       </c>
       <c r="J187" t="n">
-        <v>515000</v>
+        <v>18732000</v>
       </c>
       <c r="K187" t="n">
-        <v>442600</v>
+        <v>14012000</v>
       </c>
       <c r="L187" t="n">
-        <v>386.5</v>
+        <v>1835</v>
       </c>
       <c r="M187" t="n">
-        <v>358</v>
+        <v>1395</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
@@ -32951,18 +32951,18 @@
         <v>0</v>
       </c>
       <c r="AJ187" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AL187" t="n">
-        <v>-12</v>
+        <v>-32</v>
       </c>
       <c r="AM187" t="n">
-        <v>-300</v>
+        <v>-133.33</v>
       </c>
       <c r="AN187" t="n">
         <v>0</v>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
@@ -33173,12 +33173,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1536.TW</t>
+          <t>6121.TWO</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>新普</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -33197,28 +33197,28 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>43.8</v>
+        <v>364</v>
       </c>
       <c r="G189" t="n">
-        <v>44.28</v>
+        <v>367.2</v>
       </c>
       <c r="H189" t="n">
-        <v>44.78</v>
+        <v>365.75</v>
       </c>
       <c r="I189" t="n">
-        <v>45.66</v>
+        <v>371.52</v>
       </c>
       <c r="J189" t="n">
-        <v>654630</v>
+        <v>515000</v>
       </c>
       <c r="K189" t="n">
-        <v>584708</v>
+        <v>442600</v>
       </c>
       <c r="L189" t="n">
-        <v>47.2</v>
+        <v>386.5</v>
       </c>
       <c r="M189" t="n">
-        <v>43.8</v>
+        <v>358</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
@@ -33226,28 +33226,28 @@
         </is>
       </c>
       <c r="O189" t="n">
-        <v>-221514</v>
+        <v>0</v>
       </c>
       <c r="P189" t="n">
-        <v>224045</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>312132</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>-1549284</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
-        <v>-207072</v>
+        <v>0</v>
       </c>
       <c r="T189" t="n">
-        <v>153659</v>
+        <v>0</v>
       </c>
       <c r="U189" t="n">
-        <v>246233</v>
+        <v>0</v>
       </c>
       <c r="V189" t="n">
-        <v>-1570482</v>
+        <v>0</v>
       </c>
       <c r="W189" t="n">
         <v>0</v>
@@ -33262,34 +33262,34 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>-14442</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>70386</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
-        <v>65899</v>
+        <v>0</v>
       </c>
       <c r="AD189" t="n">
-        <v>21198</v>
+        <v>0</v>
       </c>
       <c r="AE189" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AF189" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AG189" t="n">
-        <v>-45</v>
+        <v>-20</v>
       </c>
       <c r="AH189" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AI189" t="n">
         <v>0</v>
       </c>
       <c r="AJ189" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
@@ -33297,10 +33297,10 @@
         </is>
       </c>
       <c r="AL189" t="n">
-        <v>-20</v>
+        <v>-12</v>
       </c>
       <c r="AM189" t="n">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AN189" t="n">
         <v>0</v>
@@ -33330,17 +33330,17 @@
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -34565,12 +34565,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2355.TW</t>
+          <t>1536.TW</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>敬鵬</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -34589,28 +34589,28 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>50.7</v>
+        <v>43.8</v>
       </c>
       <c r="G197" t="n">
-        <v>51.94</v>
+        <v>44.28</v>
       </c>
       <c r="H197" t="n">
-        <v>51.08</v>
+        <v>44.78</v>
       </c>
       <c r="I197" t="n">
-        <v>46.83</v>
+        <v>45.66</v>
       </c>
       <c r="J197" t="n">
-        <v>5117634</v>
+        <v>654630</v>
       </c>
       <c r="K197" t="n">
-        <v>11984613</v>
+        <v>584708</v>
       </c>
       <c r="L197" t="n">
-        <v>56</v>
+        <v>47.2</v>
       </c>
       <c r="M197" t="n">
-        <v>41.25</v>
+        <v>43.8</v>
       </c>
       <c r="N197" t="inlineStr">
         <is>
@@ -34618,28 +34618,28 @@
         </is>
       </c>
       <c r="O197" t="n">
-        <v>518954</v>
+        <v>-221514</v>
       </c>
       <c r="P197" t="n">
-        <v>957553</v>
+        <v>224045</v>
       </c>
       <c r="Q197" t="n">
-        <v>-2193077</v>
+        <v>312132</v>
       </c>
       <c r="R197" t="n">
-        <v>189502</v>
+        <v>-1549284</v>
       </c>
       <c r="S197" t="n">
-        <v>687471</v>
+        <v>-207072</v>
       </c>
       <c r="T197" t="n">
-        <v>1228918</v>
+        <v>153659</v>
       </c>
       <c r="U197" t="n">
-        <v>-2146901</v>
+        <v>246233</v>
       </c>
       <c r="V197" t="n">
-        <v>-235020</v>
+        <v>-1570482</v>
       </c>
       <c r="W197" t="n">
         <v>0</v>
@@ -34654,16 +34654,16 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>-168517</v>
+        <v>-14442</v>
       </c>
       <c r="AB197" t="n">
-        <v>-271365</v>
+        <v>70386</v>
       </c>
       <c r="AC197" t="n">
-        <v>-46176</v>
+        <v>65899</v>
       </c>
       <c r="AD197" t="n">
-        <v>424522</v>
+        <v>21198</v>
       </c>
       <c r="AE197" t="n">
         <v>-10</v>
@@ -34672,16 +34672,16 @@
         <v>-10</v>
       </c>
       <c r="AG197" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="AH197" t="n">
-        <v>-30</v>
+        <v>20</v>
       </c>
       <c r="AI197" t="n">
         <v>0</v>
       </c>
       <c r="AJ197" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AK197" t="inlineStr">
         <is>
@@ -34689,16 +34689,16 @@
         </is>
       </c>
       <c r="AL197" t="n">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="AM197" t="n">
-        <v>-171.43</v>
+        <v>-200</v>
       </c>
       <c r="AN197" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO197" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
@@ -34722,29 +34722,29 @@
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人買超</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2201.TW</t>
+          <t>2355.TW</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>裕隆</t>
+          <t>敬鵬</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -34763,28 +34763,28 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>29.15</v>
+        <v>50.7</v>
       </c>
       <c r="G198" t="n">
-        <v>29.27</v>
+        <v>51.94</v>
       </c>
       <c r="H198" t="n">
-        <v>29.12</v>
+        <v>51.08</v>
       </c>
       <c r="I198" t="n">
-        <v>29.04</v>
+        <v>46.83</v>
       </c>
       <c r="J198" t="n">
-        <v>2212157</v>
+        <v>5117634</v>
       </c>
       <c r="K198" t="n">
-        <v>2843816</v>
+        <v>11984613</v>
       </c>
       <c r="L198" t="n">
-        <v>29.9</v>
+        <v>56</v>
       </c>
       <c r="M198" t="n">
-        <v>28.2</v>
+        <v>41.25</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
@@ -34792,52 +34792,52 @@
         </is>
       </c>
       <c r="O198" t="n">
-        <v>1627833</v>
+        <v>518954</v>
       </c>
       <c r="P198" t="n">
-        <v>1049601</v>
+        <v>957553</v>
       </c>
       <c r="Q198" t="n">
-        <v>-427106</v>
+        <v>-2193077</v>
       </c>
       <c r="R198" t="n">
-        <v>2915198</v>
+        <v>189502</v>
       </c>
       <c r="S198" t="n">
-        <v>1631150</v>
+        <v>687471</v>
       </c>
       <c r="T198" t="n">
-        <v>1030277</v>
+        <v>1228918</v>
       </c>
       <c r="U198" t="n">
-        <v>-373582</v>
+        <v>-2146901</v>
       </c>
       <c r="V198" t="n">
-        <v>2905509</v>
+        <v>-235020</v>
       </c>
       <c r="W198" t="n">
         <v>0</v>
       </c>
       <c r="X198" t="n">
-        <v>-1274</v>
+        <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>30726</v>
+        <v>0</v>
       </c>
       <c r="Z198" t="n">
-        <v>102726</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>-3317</v>
+        <v>-168517</v>
       </c>
       <c r="AB198" t="n">
-        <v>20598</v>
+        <v>-271365</v>
       </c>
       <c r="AC198" t="n">
-        <v>-84250</v>
+        <v>-46176</v>
       </c>
       <c r="AD198" t="n">
-        <v>-93037</v>
+        <v>424522</v>
       </c>
       <c r="AE198" t="n">
         <v>-10</v>
@@ -34846,16 +34846,16 @@
         <v>-10</v>
       </c>
       <c r="AG198" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="AH198" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="AI198" t="n">
         <v>0</v>
       </c>
       <c r="AJ198" t="n">
-        <v>-30</v>
+        <v>14</v>
       </c>
       <c r="AK198" t="inlineStr">
         <is>
@@ -34863,25 +34863,25 @@
         </is>
       </c>
       <c r="AL198" t="n">
-        <v>20</v>
+        <v>-24</v>
       </c>
       <c r="AM198" t="n">
-        <v>66.67</v>
+        <v>-171.43</v>
       </c>
       <c r="AN198" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AO198" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
@@ -34896,17 +34896,17 @@
       </c>
       <c r="AT198" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>5日法人賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -35087,12 +35087,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>6770.TW</t>
+          <t>2201.TW</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>裕隆</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -35111,28 +35111,28 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>66.40000000000001</v>
+        <v>29.15</v>
       </c>
       <c r="G200" t="n">
-        <v>65.86</v>
+        <v>29.27</v>
       </c>
       <c r="H200" t="n">
-        <v>67.76000000000001</v>
+        <v>29.12</v>
       </c>
       <c r="I200" t="n">
-        <v>70.79000000000001</v>
+        <v>29.04</v>
       </c>
       <c r="J200" t="n">
-        <v>113091204</v>
+        <v>2212157</v>
       </c>
       <c r="K200" t="n">
-        <v>83664500</v>
+        <v>2843816</v>
       </c>
       <c r="L200" t="n">
-        <v>78.09999999999999</v>
+        <v>29.9</v>
       </c>
       <c r="M200" t="n">
-        <v>63</v>
+        <v>28.2</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
@@ -35140,52 +35140,52 @@
         </is>
       </c>
       <c r="O200" t="n">
-        <v>1728244</v>
+        <v>1627833</v>
       </c>
       <c r="P200" t="n">
-        <v>-6906348</v>
+        <v>1049601</v>
       </c>
       <c r="Q200" t="n">
-        <v>-36788045</v>
+        <v>-427106</v>
       </c>
       <c r="R200" t="n">
-        <v>-266996795</v>
+        <v>2915198</v>
       </c>
       <c r="S200" t="n">
-        <v>529359</v>
+        <v>1631150</v>
       </c>
       <c r="T200" t="n">
-        <v>-15279698</v>
+        <v>1030277</v>
       </c>
       <c r="U200" t="n">
-        <v>-57585625</v>
+        <v>-373582</v>
       </c>
       <c r="V200" t="n">
-        <v>-274654113</v>
+        <v>2905509</v>
       </c>
       <c r="W200" t="n">
-        <v>1618000</v>
+        <v>0</v>
       </c>
       <c r="X200" t="n">
-        <v>8120573</v>
+        <v>-1274</v>
       </c>
       <c r="Y200" t="n">
-        <v>20853826</v>
+        <v>30726</v>
       </c>
       <c r="Z200" t="n">
-        <v>20783826</v>
+        <v>102726</v>
       </c>
       <c r="AA200" t="n">
-        <v>-419115</v>
+        <v>-3317</v>
       </c>
       <c r="AB200" t="n">
-        <v>252777</v>
+        <v>20598</v>
       </c>
       <c r="AC200" t="n">
-        <v>-56246</v>
+        <v>-84250</v>
       </c>
       <c r="AD200" t="n">
-        <v>-13126508</v>
+        <v>-93037</v>
       </c>
       <c r="AE200" t="n">
         <v>-10</v>
@@ -35194,42 +35194,42 @@
         <v>-10</v>
       </c>
       <c r="AG200" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AH200" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ200" t="n">
         <v>-30</v>
       </c>
-      <c r="AI200" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ200" t="n">
-        <v>-14</v>
-      </c>
       <c r="AK200" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
       <c r="AL200" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AM200" t="n">
-        <v>28.57</v>
+        <v>66.67</v>
       </c>
       <c r="AN200" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="AO200" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
@@ -35244,29 +35244,29 @@
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、接近20日低點、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4105.TWO</t>
+          <t>6770.TW</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>東洋</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -35285,28 +35285,28 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>80.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="G201" t="n">
-        <v>81.31999999999999</v>
+        <v>65.86</v>
       </c>
       <c r="H201" t="n">
-        <v>81.54000000000001</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="I201" t="n">
-        <v>80.17</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="J201" t="n">
-        <v>328000</v>
+        <v>113091204</v>
       </c>
       <c r="K201" t="n">
-        <v>775800</v>
+        <v>83664500</v>
       </c>
       <c r="L201" t="n">
-        <v>83.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="M201" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
@@ -35314,70 +35314,70 @@
         </is>
       </c>
       <c r="O201" t="n">
-        <v>0</v>
+        <v>1728244</v>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>-6906348</v>
       </c>
       <c r="Q201" t="n">
-        <v>0</v>
+        <v>-36788045</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>-266996795</v>
       </c>
       <c r="S201" t="n">
-        <v>0</v>
+        <v>529359</v>
       </c>
       <c r="T201" t="n">
-        <v>0</v>
+        <v>-15279698</v>
       </c>
       <c r="U201" t="n">
-        <v>0</v>
+        <v>-57585625</v>
       </c>
       <c r="V201" t="n">
-        <v>0</v>
+        <v>-274654113</v>
       </c>
       <c r="W201" t="n">
-        <v>0</v>
+        <v>1618000</v>
       </c>
       <c r="X201" t="n">
-        <v>0</v>
+        <v>8120573</v>
       </c>
       <c r="Y201" t="n">
-        <v>0</v>
+        <v>20853826</v>
       </c>
       <c r="Z201" t="n">
-        <v>0</v>
+        <v>20783826</v>
       </c>
       <c r="AA201" t="n">
-        <v>0</v>
+        <v>-419115</v>
       </c>
       <c r="AB201" t="n">
-        <v>0</v>
+        <v>252777</v>
       </c>
       <c r="AC201" t="n">
-        <v>0</v>
+        <v>-56246</v>
       </c>
       <c r="AD201" t="n">
-        <v>0</v>
+        <v>-13126508</v>
       </c>
       <c r="AE201" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AF201" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AG201" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH201" t="n">
         <v>-30</v>
       </c>
-      <c r="AH201" t="n">
-        <v>0</v>
-      </c>
       <c r="AI201" t="n">
         <v>0</v>
       </c>
       <c r="AJ201" t="n">
-        <v>-2</v>
+        <v>-14</v>
       </c>
       <c r="AK201" t="inlineStr">
         <is>
@@ -35385,25 +35385,25 @@
         </is>
       </c>
       <c r="AL201" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="AM201" t="n">
-        <v>-500</v>
+        <v>28.57</v>
       </c>
       <c r="AN201" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AO201" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
@@ -35418,29 +35418,29 @@
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>5314.TWO</t>
+          <t>4105.TWO</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>世紀</t>
+          <t>東洋</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -35459,28 +35459,28 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>25.1</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G202" t="n">
-        <v>26.46</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="H202" t="n">
-        <v>26.37</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="I202" t="n">
-        <v>27.2</v>
+        <v>80.17</v>
       </c>
       <c r="J202" t="n">
-        <v>22149000</v>
+        <v>328000</v>
       </c>
       <c r="K202" t="n">
-        <v>27269200</v>
+        <v>775800</v>
       </c>
       <c r="L202" t="n">
-        <v>31.65</v>
+        <v>83.8</v>
       </c>
       <c r="M202" t="n">
-        <v>24.65</v>
+        <v>78</v>
       </c>
       <c r="N202" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>0</v>
       </c>
       <c r="AJ202" t="n">
-        <v>-18</v>
+        <v>-2</v>
       </c>
       <c r="AK202" t="inlineStr">
         <is>
@@ -35559,16 +35559,16 @@
         </is>
       </c>
       <c r="AL202" t="n">
-        <v>6</v>
+        <v>-10</v>
       </c>
       <c r="AM202" t="n">
-        <v>33.33</v>
+        <v>-500</v>
       </c>
       <c r="AN202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO202" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
@@ -36131,12 +36131,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2539.TW</t>
+          <t>5314.TWO</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>櫻花建</t>
+          <t>世紀</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -36155,28 +36155,28 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>32.5</v>
+        <v>25.1</v>
       </c>
       <c r="G206" t="n">
-        <v>33.27</v>
+        <v>26.46</v>
       </c>
       <c r="H206" t="n">
-        <v>33.46</v>
+        <v>26.37</v>
       </c>
       <c r="I206" t="n">
-        <v>33.83</v>
+        <v>27.2</v>
       </c>
       <c r="J206" t="n">
-        <v>1860794</v>
+        <v>22149000</v>
       </c>
       <c r="K206" t="n">
-        <v>968661</v>
+        <v>27269200</v>
       </c>
       <c r="L206" t="n">
-        <v>35.3</v>
+        <v>31.65</v>
       </c>
       <c r="M206" t="n">
-        <v>32.4</v>
+        <v>24.65</v>
       </c>
       <c r="N206" t="inlineStr">
         <is>
@@ -36184,52 +36184,52 @@
         </is>
       </c>
       <c r="O206" t="n">
-        <v>-206340</v>
+        <v>0</v>
       </c>
       <c r="P206" t="n">
-        <v>-533373</v>
+        <v>0</v>
       </c>
       <c r="Q206" t="n">
-        <v>85269</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>1649104</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
-        <v>-206340</v>
+        <v>0</v>
       </c>
       <c r="T206" t="n">
-        <v>-494227</v>
+        <v>0</v>
       </c>
       <c r="U206" t="n">
-        <v>-276165</v>
+        <v>0</v>
       </c>
       <c r="V206" t="n">
-        <v>1322799</v>
+        <v>0</v>
       </c>
       <c r="W206" t="n">
         <v>0</v>
       </c>
       <c r="X206" t="n">
-        <v>8471</v>
+        <v>0</v>
       </c>
       <c r="Y206" t="n">
-        <v>441471</v>
+        <v>0</v>
       </c>
       <c r="Z206" t="n">
-        <v>442471</v>
+        <v>0</v>
       </c>
       <c r="AA206" t="n">
         <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>-47617</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
-        <v>-80037</v>
+        <v>0</v>
       </c>
       <c r="AD206" t="n">
-        <v>-116166</v>
+        <v>0</v>
       </c>
       <c r="AE206" t="n">
         <v>-12</v>
@@ -36238,16 +36238,16 @@
         <v>-12</v>
       </c>
       <c r="AG206" t="n">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="AH206" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI206" t="n">
         <v>0</v>
       </c>
       <c r="AJ206" t="n">
-        <v>-2</v>
+        <v>-18</v>
       </c>
       <c r="AK206" t="inlineStr">
         <is>
@@ -36255,16 +36255,16 @@
         </is>
       </c>
       <c r="AL206" t="n">
-        <v>-10</v>
+        <v>6</v>
       </c>
       <c r="AM206" t="n">
-        <v>-500</v>
+        <v>33.33</v>
       </c>
       <c r="AN206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
@@ -36288,29 +36288,29 @@
       </c>
       <c r="AT206" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>5日法人小幅買超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、5日法人小幅買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>2539.TW</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>櫻花建</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -36329,28 +36329,28 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>1840</v>
+        <v>32.5</v>
       </c>
       <c r="G207" t="n">
-        <v>1875</v>
+        <v>33.27</v>
       </c>
       <c r="H207" t="n">
-        <v>2010.5</v>
+        <v>33.46</v>
       </c>
       <c r="I207" t="n">
-        <v>2075.25</v>
+        <v>33.83</v>
       </c>
       <c r="J207" t="n">
-        <v>4732956</v>
+        <v>1860794</v>
       </c>
       <c r="K207" t="n">
-        <v>7294982</v>
+        <v>968661</v>
       </c>
       <c r="L207" t="n">
-        <v>2335</v>
+        <v>35.3</v>
       </c>
       <c r="M207" t="n">
-        <v>1795</v>
+        <v>32.4</v>
       </c>
       <c r="N207" t="inlineStr">
         <is>
@@ -36358,70 +36358,70 @@
         </is>
       </c>
       <c r="O207" t="n">
-        <v>321786</v>
+        <v>-206340</v>
       </c>
       <c r="P207" t="n">
-        <v>-26158</v>
+        <v>-533373</v>
       </c>
       <c r="Q207" t="n">
-        <v>382009</v>
+        <v>85269</v>
       </c>
       <c r="R207" t="n">
-        <v>-4075004</v>
+        <v>1649104</v>
       </c>
       <c r="S207" t="n">
-        <v>1277659</v>
+        <v>-206340</v>
       </c>
       <c r="T207" t="n">
-        <v>1416235</v>
+        <v>-494227</v>
       </c>
       <c r="U207" t="n">
-        <v>6985973</v>
+        <v>-276165</v>
       </c>
       <c r="V207" t="n">
-        <v>7140903</v>
+        <v>1322799</v>
       </c>
       <c r="W207" t="n">
-        <v>-944315</v>
+        <v>0</v>
       </c>
       <c r="X207" t="n">
-        <v>-1192479</v>
+        <v>8471</v>
       </c>
       <c r="Y207" t="n">
-        <v>-6708294</v>
+        <v>441471</v>
       </c>
       <c r="Z207" t="n">
-        <v>-10912562</v>
+        <v>442471</v>
       </c>
       <c r="AA207" t="n">
-        <v>-11558</v>
+        <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>-249914</v>
+        <v>-47617</v>
       </c>
       <c r="AC207" t="n">
-        <v>104330</v>
+        <v>-80037</v>
       </c>
       <c r="AD207" t="n">
-        <v>-303345</v>
+        <v>-116166</v>
       </c>
       <c r="AE207" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AF207" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AG207" t="n">
-        <v>-55</v>
+        <v>-40</v>
       </c>
       <c r="AH207" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AI207" t="n">
         <v>0</v>
       </c>
       <c r="AJ207" t="n">
-        <v>-44</v>
+        <v>-2</v>
       </c>
       <c r="AK207" t="inlineStr">
         <is>
@@ -36429,10 +36429,10 @@
         </is>
       </c>
       <c r="AL207" t="n">
-        <v>30</v>
+        <v>-10</v>
       </c>
       <c r="AM207" t="n">
-        <v>68.18000000000001</v>
+        <v>-500</v>
       </c>
       <c r="AN207" t="n">
         <v>0</v>
@@ -36447,7 +36447,7 @@
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
@@ -36462,29 +36462,29 @@
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人小幅買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、成交量放大、接近20日低點、5日法人小幅買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1303.TW</t>
+          <t>3105.TWO</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -36503,28 +36503,28 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>301</v>
+        <v>486</v>
       </c>
       <c r="G208" t="n">
-        <v>305.6</v>
+        <v>491.2</v>
       </c>
       <c r="H208" t="n">
-        <v>312.35</v>
+        <v>523.2</v>
       </c>
       <c r="I208" t="n">
-        <v>286.5</v>
+        <v>534.55</v>
       </c>
       <c r="J208" t="n">
-        <v>101068589</v>
+        <v>24584000</v>
       </c>
       <c r="K208" t="n">
-        <v>109993779</v>
+        <v>21512000</v>
       </c>
       <c r="L208" t="n">
-        <v>350.5</v>
+        <v>630</v>
       </c>
       <c r="M208" t="n">
-        <v>223</v>
+        <v>454</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
@@ -36532,52 +36532,52 @@
         </is>
       </c>
       <c r="O208" t="n">
-        <v>-20712762</v>
+        <v>0</v>
       </c>
       <c r="P208" t="n">
-        <v>1581819</v>
+        <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>-21414183</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>-45835178</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
-        <v>-20416205</v>
+        <v>0</v>
       </c>
       <c r="T208" t="n">
-        <v>-1375375</v>
+        <v>0</v>
       </c>
       <c r="U208" t="n">
-        <v>-29179722</v>
+        <v>0</v>
       </c>
       <c r="V208" t="n">
-        <v>-67652934</v>
+        <v>0</v>
       </c>
       <c r="W208" t="n">
-        <v>-475000</v>
+        <v>0</v>
       </c>
       <c r="X208" t="n">
-        <v>-1951004</v>
+        <v>0</v>
       </c>
       <c r="Y208" t="n">
-        <v>1020783</v>
+        <v>0</v>
       </c>
       <c r="Z208" t="n">
-        <v>12490683</v>
+        <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>178443</v>
+        <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>4908198</v>
+        <v>0</v>
       </c>
       <c r="AC208" t="n">
-        <v>6744756</v>
+        <v>0</v>
       </c>
       <c r="AD208" t="n">
-        <v>9327073</v>
+        <v>0</v>
       </c>
       <c r="AE208" t="n">
         <v>-14</v>
@@ -36586,16 +36586,16 @@
         <v>-14</v>
       </c>
       <c r="AG208" t="n">
-        <v>-20</v>
+        <v>-35</v>
       </c>
       <c r="AH208" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AI208" t="n">
         <v>0</v>
       </c>
       <c r="AJ208" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AK208" t="inlineStr">
         <is>
@@ -36603,10 +36603,10 @@
         </is>
       </c>
       <c r="AL208" t="n">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="AM208" t="n">
-        <v>-333.33</v>
+        <v>-800</v>
       </c>
       <c r="AN208" t="n">
         <v>0</v>
@@ -36621,7 +36621,7 @@
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
@@ -36636,29 +36636,29 @@
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3105.TWO</t>
+          <t>1303.TW</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -36677,28 +36677,28 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>486</v>
+        <v>301</v>
       </c>
       <c r="G209" t="n">
-        <v>491.2</v>
+        <v>305.6</v>
       </c>
       <c r="H209" t="n">
-        <v>523.2</v>
+        <v>312.35</v>
       </c>
       <c r="I209" t="n">
-        <v>534.55</v>
+        <v>286.5</v>
       </c>
       <c r="J209" t="n">
-        <v>24584000</v>
+        <v>101068589</v>
       </c>
       <c r="K209" t="n">
-        <v>21512000</v>
+        <v>109993779</v>
       </c>
       <c r="L209" t="n">
-        <v>630</v>
+        <v>350.5</v>
       </c>
       <c r="M209" t="n">
-        <v>454</v>
+        <v>223</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
@@ -36706,52 +36706,52 @@
         </is>
       </c>
       <c r="O209" t="n">
-        <v>0</v>
+        <v>-20712762</v>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>1581819</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>-21414183</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>-45835178</v>
       </c>
       <c r="S209" t="n">
-        <v>0</v>
+        <v>-20416205</v>
       </c>
       <c r="T209" t="n">
-        <v>0</v>
+        <v>-1375375</v>
       </c>
       <c r="U209" t="n">
-        <v>0</v>
+        <v>-29179722</v>
       </c>
       <c r="V209" t="n">
-        <v>0</v>
+        <v>-67652934</v>
       </c>
       <c r="W209" t="n">
-        <v>0</v>
+        <v>-475000</v>
       </c>
       <c r="X209" t="n">
-        <v>0</v>
+        <v>-1951004</v>
       </c>
       <c r="Y209" t="n">
-        <v>0</v>
+        <v>1020783</v>
       </c>
       <c r="Z209" t="n">
-        <v>0</v>
+        <v>12490683</v>
       </c>
       <c r="AA209" t="n">
-        <v>0</v>
+        <v>178443</v>
       </c>
       <c r="AB209" t="n">
-        <v>0</v>
+        <v>4908198</v>
       </c>
       <c r="AC209" t="n">
-        <v>0</v>
+        <v>6744756</v>
       </c>
       <c r="AD209" t="n">
-        <v>0</v>
+        <v>9327073</v>
       </c>
       <c r="AE209" t="n">
         <v>-14</v>
@@ -36760,16 +36760,16 @@
         <v>-14</v>
       </c>
       <c r="AG209" t="n">
-        <v>-35</v>
+        <v>-20</v>
       </c>
       <c r="AH209" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AI209" t="n">
         <v>0</v>
       </c>
       <c r="AJ209" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK209" t="inlineStr">
         <is>
@@ -36777,10 +36777,10 @@
         </is>
       </c>
       <c r="AL209" t="n">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="AM209" t="n">
-        <v>-800</v>
+        <v>-333.33</v>
       </c>
       <c r="AN209" t="n">
         <v>0</v>
@@ -36795,7 +36795,7 @@
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
@@ -36810,29 +36810,29 @@
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>短線籌碼止穩、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、短線籌碼止穩、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2476.TW</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -36851,81 +36851,81 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>114</v>
+        <v>1840</v>
       </c>
       <c r="G210" t="n">
-        <v>120.8</v>
+        <v>1875</v>
       </c>
       <c r="H210" t="n">
-        <v>123.85</v>
+        <v>2010.5</v>
       </c>
       <c r="I210" t="n">
-        <v>124.75</v>
+        <v>2075.25</v>
       </c>
       <c r="J210" t="n">
-        <v>2286228</v>
+        <v>4732956</v>
       </c>
       <c r="K210" t="n">
-        <v>1046808</v>
+        <v>7294982</v>
       </c>
       <c r="L210" t="n">
-        <v>134.5</v>
+        <v>2335</v>
       </c>
       <c r="M210" t="n">
-        <v>112.5</v>
+        <v>1795</v>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O210" t="n">
-        <v>-154934</v>
+        <v>321786</v>
       </c>
       <c r="P210" t="n">
-        <v>-349153</v>
+        <v>-26158</v>
       </c>
       <c r="Q210" t="n">
-        <v>86247</v>
+        <v>382009</v>
       </c>
       <c r="R210" t="n">
-        <v>958020</v>
+        <v>-4075004</v>
       </c>
       <c r="S210" t="n">
-        <v>-244748</v>
+        <v>1277659</v>
       </c>
       <c r="T210" t="n">
-        <v>-790095</v>
+        <v>1416235</v>
       </c>
       <c r="U210" t="n">
-        <v>-488858</v>
+        <v>6985973</v>
       </c>
       <c r="V210" t="n">
-        <v>397027</v>
+        <v>7140903</v>
       </c>
       <c r="W210" t="n">
-        <v>0</v>
+        <v>-944315</v>
       </c>
       <c r="X210" t="n">
-        <v>0</v>
+        <v>-1192479</v>
       </c>
       <c r="Y210" t="n">
-        <v>75000</v>
+        <v>-6708294</v>
       </c>
       <c r="Z210" t="n">
-        <v>75000</v>
+        <v>-10912562</v>
       </c>
       <c r="AA210" t="n">
-        <v>89814</v>
+        <v>-11558</v>
       </c>
       <c r="AB210" t="n">
-        <v>440942</v>
+        <v>-249914</v>
       </c>
       <c r="AC210" t="n">
-        <v>500105</v>
+        <v>104330</v>
       </c>
       <c r="AD210" t="n">
-        <v>485993</v>
+        <v>-303345</v>
       </c>
       <c r="AE210" t="n">
         <v>-14</v>
@@ -36934,16 +36934,16 @@
         <v>-14</v>
       </c>
       <c r="AG210" t="n">
-        <v>-35</v>
+        <v>-55</v>
       </c>
       <c r="AH210" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AI210" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ210" t="n">
-        <v>-8</v>
+        <v>-44</v>
       </c>
       <c r="AK210" t="inlineStr">
         <is>
@@ -36951,10 +36951,10 @@
         </is>
       </c>
       <c r="AL210" t="n">
-        <v>-6</v>
+        <v>30</v>
       </c>
       <c r="AM210" t="n">
-        <v>-75</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AN210" t="n">
         <v>0</v>
@@ -36969,7 +36969,7 @@
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR210" t="inlineStr">
@@ -36984,29 +36984,29 @@
       </c>
       <c r="AT210" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>5日法人小幅買超、投信買外資賣</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲、5日法人小幅買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2908.TW</t>
+          <t>2476.TW</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>特力</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -37025,57 +37025,57 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>22.05</v>
+        <v>114</v>
       </c>
       <c r="G211" t="n">
-        <v>21.92</v>
+        <v>120.8</v>
       </c>
       <c r="H211" t="n">
-        <v>21.95</v>
+        <v>123.85</v>
       </c>
       <c r="I211" t="n">
-        <v>22</v>
+        <v>124.75</v>
       </c>
       <c r="J211" t="n">
-        <v>277345</v>
+        <v>2286228</v>
       </c>
       <c r="K211" t="n">
-        <v>296028</v>
+        <v>1046808</v>
       </c>
       <c r="L211" t="n">
-        <v>22.25</v>
+        <v>134.5</v>
       </c>
       <c r="M211" t="n">
-        <v>21.55</v>
+        <v>112.5</v>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="O211" t="n">
-        <v>4000</v>
+        <v>-154934</v>
       </c>
       <c r="P211" t="n">
-        <v>-167462</v>
+        <v>-349153</v>
       </c>
       <c r="Q211" t="n">
-        <v>-94461</v>
+        <v>86247</v>
       </c>
       <c r="R211" t="n">
-        <v>76149</v>
+        <v>958020</v>
       </c>
       <c r="S211" t="n">
-        <v>4000</v>
+        <v>-244748</v>
       </c>
       <c r="T211" t="n">
-        <v>-161462</v>
+        <v>-790095</v>
       </c>
       <c r="U211" t="n">
-        <v>-88461</v>
+        <v>-488858</v>
       </c>
       <c r="V211" t="n">
-        <v>77149</v>
+        <v>397027</v>
       </c>
       <c r="W211" t="n">
         <v>0</v>
@@ -37084,22 +37084,22 @@
         <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="Z211" t="n">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>89814</v>
       </c>
       <c r="AB211" t="n">
-        <v>-6000</v>
+        <v>440942</v>
       </c>
       <c r="AC211" t="n">
-        <v>-6000</v>
+        <v>500105</v>
       </c>
       <c r="AD211" t="n">
-        <v>-1000</v>
+        <v>485993</v>
       </c>
       <c r="AE211" t="n">
         <v>-14</v>
@@ -37108,16 +37108,16 @@
         <v>-14</v>
       </c>
       <c r="AG211" t="n">
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="AH211" t="n">
-        <v>-35</v>
+        <v>10</v>
       </c>
       <c r="AI211" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ211" t="n">
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="AK211" t="inlineStr">
         <is>
@@ -37125,25 +37125,25 @@
         </is>
       </c>
       <c r="AL211" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="AM211" t="n">
-        <v>22.22</v>
+        <v>-75</v>
       </c>
       <c r="AN211" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AO211" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR211" t="inlineStr">
@@ -37158,17 +37158,17 @@
       </c>
       <c r="AT211" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲</t>
         </is>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人小幅賣超</t>
+          <t>5日法人小幅買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日高點、接近20日低點、中期買超轉短線賣壓、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、爆量、接近20日低點、爆量價未漲、5日法人小幅買超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -37523,12 +37523,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2357.TW</t>
+          <t>2908.TW</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>特力</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -37547,28 +37547,28 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>946</v>
+        <v>22.05</v>
       </c>
       <c r="G214" t="n">
-        <v>974.6</v>
+        <v>21.92</v>
       </c>
       <c r="H214" t="n">
-        <v>977.7</v>
+        <v>21.95</v>
       </c>
       <c r="I214" t="n">
-        <v>973.8</v>
+        <v>22</v>
       </c>
       <c r="J214" t="n">
-        <v>2657092</v>
+        <v>277345</v>
       </c>
       <c r="K214" t="n">
-        <v>2626363</v>
+        <v>296028</v>
       </c>
       <c r="L214" t="n">
-        <v>1010</v>
+        <v>22.25</v>
       </c>
       <c r="M214" t="n">
-        <v>942</v>
+        <v>21.55</v>
       </c>
       <c r="N214" t="inlineStr">
         <is>
@@ -37576,70 +37576,70 @@
         </is>
       </c>
       <c r="O214" t="n">
-        <v>-638818</v>
+        <v>4000</v>
       </c>
       <c r="P214" t="n">
-        <v>-102787</v>
+        <v>-167462</v>
       </c>
       <c r="Q214" t="n">
-        <v>46310</v>
+        <v>-94461</v>
       </c>
       <c r="R214" t="n">
-        <v>1527033</v>
+        <v>76149</v>
       </c>
       <c r="S214" t="n">
-        <v>-821452</v>
+        <v>4000</v>
       </c>
       <c r="T214" t="n">
-        <v>-277892</v>
+        <v>-161462</v>
       </c>
       <c r="U214" t="n">
-        <v>-204338</v>
+        <v>-88461</v>
       </c>
       <c r="V214" t="n">
-        <v>493178</v>
+        <v>77149</v>
       </c>
       <c r="W214" t="n">
-        <v>-62400</v>
+        <v>0</v>
       </c>
       <c r="X214" t="n">
-        <v>-538648</v>
+        <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>-770589</v>
+        <v>0</v>
       </c>
       <c r="Z214" t="n">
-        <v>-641408</v>
+        <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>245034</v>
+        <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>713753</v>
+        <v>-6000</v>
       </c>
       <c r="AC214" t="n">
-        <v>1021237</v>
+        <v>-6000</v>
       </c>
       <c r="AD214" t="n">
-        <v>1675263</v>
+        <v>-1000</v>
       </c>
       <c r="AE214" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AF214" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AG214" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AH214" t="n">
-        <v>-20</v>
+        <v>-35</v>
       </c>
       <c r="AI214" t="n">
         <v>0</v>
       </c>
       <c r="AJ214" t="n">
-        <v>16</v>
+        <v>-18</v>
       </c>
       <c r="AK214" t="inlineStr">
         <is>
@@ -37647,25 +37647,25 @@
         </is>
       </c>
       <c r="AL214" t="n">
-        <v>-32</v>
+        <v>4</v>
       </c>
       <c r="AM214" t="n">
-        <v>-200</v>
+        <v>22.22</v>
       </c>
       <c r="AN214" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AO214" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ214" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR214" t="inlineStr">
@@ -37680,29 +37680,29 @@
       </c>
       <c r="AT214" t="inlineStr">
         <is>
-          <t>跌破5日線、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>籌碼中性、外資投信同步賣超</t>
+          <t>中期買超轉短線賣壓、5日法人小幅賣超</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日高點、接近20日低點、中期買超轉短線賣壓、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>6415.TW</t>
+          <t>2357.TW</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -37721,28 +37721,28 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>472</v>
+        <v>946</v>
       </c>
       <c r="G215" t="n">
-        <v>477.8</v>
+        <v>974.6</v>
       </c>
       <c r="H215" t="n">
-        <v>465.75</v>
+        <v>977.7</v>
       </c>
       <c r="I215" t="n">
-        <v>447.15</v>
+        <v>973.8</v>
       </c>
       <c r="J215" t="n">
-        <v>7980243</v>
+        <v>2657092</v>
       </c>
       <c r="K215" t="n">
-        <v>7585614</v>
+        <v>2626363</v>
       </c>
       <c r="L215" t="n">
-        <v>513</v>
+        <v>1010</v>
       </c>
       <c r="M215" t="n">
-        <v>406.5</v>
+        <v>942</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
@@ -37750,52 +37750,52 @@
         </is>
       </c>
       <c r="O215" t="n">
-        <v>-539696</v>
+        <v>-638818</v>
       </c>
       <c r="P215" t="n">
-        <v>-392917</v>
+        <v>-102787</v>
       </c>
       <c r="Q215" t="n">
-        <v>-1015922</v>
+        <v>46310</v>
       </c>
       <c r="R215" t="n">
-        <v>-2884890</v>
+        <v>1527033</v>
       </c>
       <c r="S215" t="n">
-        <v>-389712</v>
+        <v>-821452</v>
       </c>
       <c r="T215" t="n">
-        <v>-538668</v>
+        <v>-277892</v>
       </c>
       <c r="U215" t="n">
-        <v>-1331477</v>
+        <v>-204338</v>
       </c>
       <c r="V215" t="n">
-        <v>-3553243</v>
+        <v>493178</v>
       </c>
       <c r="W215" t="n">
-        <v>-51000</v>
+        <v>-62400</v>
       </c>
       <c r="X215" t="n">
-        <v>-22051</v>
+        <v>-538648</v>
       </c>
       <c r="Y215" t="n">
-        <v>109949</v>
+        <v>-770589</v>
       </c>
       <c r="Z215" t="n">
-        <v>462949</v>
+        <v>-641408</v>
       </c>
       <c r="AA215" t="n">
-        <v>-98984</v>
+        <v>245034</v>
       </c>
       <c r="AB215" t="n">
-        <v>167802</v>
+        <v>713753</v>
       </c>
       <c r="AC215" t="n">
-        <v>205606</v>
+        <v>1021237</v>
       </c>
       <c r="AD215" t="n">
-        <v>205404</v>
+        <v>1675263</v>
       </c>
       <c r="AE215" t="n">
         <v>-16</v>
@@ -37804,16 +37804,16 @@
         <v>-16</v>
       </c>
       <c r="AG215" t="n">
-        <v>15</v>
+        <v>-20</v>
       </c>
       <c r="AH215" t="n">
-        <v>-55</v>
+        <v>-20</v>
       </c>
       <c r="AI215" t="n">
         <v>0</v>
       </c>
       <c r="AJ215" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
@@ -37821,16 +37821,16 @@
         </is>
       </c>
       <c r="AL215" t="n">
-        <v>-22</v>
+        <v>-32</v>
       </c>
       <c r="AM215" t="n">
-        <v>-366.67</v>
+        <v>-200</v>
       </c>
       <c r="AN215" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO215" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
@@ -37839,7 +37839,7 @@
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
@@ -37854,17 +37854,17 @@
       </c>
       <c r="AT215" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>跌破5日線、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>籌碼中性、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能溫和放大、接近20日低點、籌碼中性、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -38219,12 +38219,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>4966.TWO</t>
+          <t>6415.TW</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -38243,28 +38243,28 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>512</v>
+        <v>472</v>
       </c>
       <c r="G218" t="n">
-        <v>526</v>
+        <v>477.8</v>
       </c>
       <c r="H218" t="n">
-        <v>538.7</v>
+        <v>465.75</v>
       </c>
       <c r="I218" t="n">
-        <v>554.8</v>
+        <v>447.15</v>
       </c>
       <c r="J218" t="n">
-        <v>400000</v>
+        <v>7980243</v>
       </c>
       <c r="K218" t="n">
-        <v>352000</v>
+        <v>7585614</v>
       </c>
       <c r="L218" t="n">
-        <v>586</v>
+        <v>513</v>
       </c>
       <c r="M218" t="n">
-        <v>512</v>
+        <v>406.5</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -38272,87 +38272,87 @@
         </is>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
+        <v>-539696</v>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>-392917</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>-1015922</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>-2884890</v>
       </c>
       <c r="S218" t="n">
-        <v>0</v>
+        <v>-389712</v>
       </c>
       <c r="T218" t="n">
-        <v>0</v>
+        <v>-538668</v>
       </c>
       <c r="U218" t="n">
-        <v>0</v>
+        <v>-1331477</v>
       </c>
       <c r="V218" t="n">
-        <v>0</v>
+        <v>-3553243</v>
       </c>
       <c r="W218" t="n">
-        <v>0</v>
+        <v>-51000</v>
       </c>
       <c r="X218" t="n">
-        <v>0</v>
+        <v>-22051</v>
       </c>
       <c r="Y218" t="n">
-        <v>0</v>
+        <v>109949</v>
       </c>
       <c r="Z218" t="n">
-        <v>0</v>
+        <v>462949</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>-98984</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>167802</v>
       </c>
       <c r="AC218" t="n">
-        <v>0</v>
+        <v>205606</v>
       </c>
       <c r="AD218" t="n">
-        <v>0</v>
+        <v>205404</v>
       </c>
       <c r="AE218" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AF218" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AG218" t="n">
-        <v>-45</v>
+        <v>15</v>
       </c>
       <c r="AH218" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="AI218" t="n">
         <v>0</v>
       </c>
       <c r="AJ218" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AL218" t="n">
         <v>-22</v>
       </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AL218" t="n">
-        <v>4</v>
-      </c>
       <c r="AM218" t="n">
-        <v>18.18</v>
+        <v>-366.67</v>
       </c>
       <c r="AN218" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AO218" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR218" t="inlineStr">
@@ -38376,17 +38376,17 @@
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -38567,12 +38567,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3680.TWO</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -38591,28 +38591,28 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="G220" t="n">
-        <v>510.2</v>
+        <v>526</v>
       </c>
       <c r="H220" t="n">
-        <v>530.6</v>
+        <v>538.7</v>
       </c>
       <c r="I220" t="n">
-        <v>540.55</v>
+        <v>554.8</v>
       </c>
       <c r="J220" t="n">
-        <v>861000</v>
+        <v>400000</v>
       </c>
       <c r="K220" t="n">
-        <v>803400</v>
+        <v>352000</v>
       </c>
       <c r="L220" t="n">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="M220" t="n">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="N220" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>0</v>
       </c>
       <c r="AJ220" t="n">
-        <v>-2</v>
+        <v>-22</v>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
@@ -38691,16 +38691,16 @@
         </is>
       </c>
       <c r="AL220" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="AM220" t="n">
-        <v>-800</v>
+        <v>18.18</v>
       </c>
       <c r="AN220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO220" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
@@ -39959,12 +39959,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>3680.TWO</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -39983,28 +39983,28 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>320</v>
+        <v>503</v>
       </c>
       <c r="G228" t="n">
-        <v>337.9</v>
+        <v>510.2</v>
       </c>
       <c r="H228" t="n">
-        <v>353.1</v>
+        <v>530.6</v>
       </c>
       <c r="I228" t="n">
-        <v>371.68</v>
+        <v>540.55</v>
       </c>
       <c r="J228" t="n">
-        <v>2118000</v>
+        <v>861000</v>
       </c>
       <c r="K228" t="n">
-        <v>1725400</v>
+        <v>803400</v>
       </c>
       <c r="L228" t="n">
-        <v>406.5</v>
+        <v>594</v>
       </c>
       <c r="M228" t="n">
-        <v>320</v>
+        <v>491</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>0</v>
       </c>
       <c r="AJ228" t="n">
-        <v>-22</v>
+        <v>-2</v>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
@@ -40083,16 +40083,16 @@
         </is>
       </c>
       <c r="AL228" t="n">
-        <v>4</v>
+        <v>-16</v>
       </c>
       <c r="AM228" t="n">
-        <v>18.18</v>
+        <v>-800</v>
       </c>
       <c r="AN228" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AO228" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
@@ -40655,12 +40655,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -40679,28 +40679,28 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>2375</v>
+        <v>320</v>
       </c>
       <c r="G232" t="n">
-        <v>2521</v>
+        <v>337.9</v>
       </c>
       <c r="H232" t="n">
-        <v>2683.5</v>
+        <v>353.1</v>
       </c>
       <c r="I232" t="n">
-        <v>2751.5</v>
+        <v>371.68</v>
       </c>
       <c r="J232" t="n">
-        <v>3614000</v>
+        <v>2118000</v>
       </c>
       <c r="K232" t="n">
-        <v>3020400</v>
+        <v>1725400</v>
       </c>
       <c r="L232" t="n">
-        <v>3210</v>
+        <v>406.5</v>
       </c>
       <c r="M232" t="n">
-        <v>2365</v>
+        <v>320</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         <v>0</v>
       </c>
       <c r="AJ232" t="n">
-        <v>-2</v>
+        <v>-22</v>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
@@ -40779,16 +40779,16 @@
         </is>
       </c>
       <c r="AL232" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="AM232" t="n">
-        <v>-800</v>
+        <v>18.18</v>
       </c>
       <c r="AN232" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO232" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
@@ -40797,7 +40797,7 @@
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
@@ -40829,12 +40829,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>4931.TWO</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>新盛力</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -40853,28 +40853,28 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>200</v>
+        <v>2375</v>
       </c>
       <c r="G233" t="n">
-        <v>209.7</v>
+        <v>2521</v>
       </c>
       <c r="H233" t="n">
-        <v>220.8</v>
+        <v>2683.5</v>
       </c>
       <c r="I233" t="n">
-        <v>234.4</v>
+        <v>2751.5</v>
       </c>
       <c r="J233" t="n">
-        <v>1660000</v>
+        <v>3614000</v>
       </c>
       <c r="K233" t="n">
-        <v>1419000</v>
+        <v>3020400</v>
       </c>
       <c r="L233" t="n">
-        <v>264</v>
+        <v>3210</v>
       </c>
       <c r="M233" t="n">
-        <v>200</v>
+        <v>2365</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>0</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
@@ -40953,10 +40953,10 @@
         </is>
       </c>
       <c r="AL233" t="n">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="AM233" t="n">
-        <v>-200</v>
+        <v>-800</v>
       </c>
       <c r="AN233" t="n">
         <v>0</v>
@@ -41177,12 +41177,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3673.TW</t>
+          <t>4931.TWO</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>新盛力</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -41201,57 +41201,57 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="G235" t="n">
-        <v>72.73999999999999</v>
+        <v>209.7</v>
       </c>
       <c r="H235" t="n">
-        <v>72.81999999999999</v>
+        <v>220.8</v>
       </c>
       <c r="I235" t="n">
-        <v>72.47</v>
+        <v>234.4</v>
       </c>
       <c r="J235" t="n">
-        <v>36223049</v>
+        <v>1660000</v>
       </c>
       <c r="K235" t="n">
-        <v>17341534</v>
+        <v>1419000</v>
       </c>
       <c r="L235" t="n">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="M235" t="n">
-        <v>61.6</v>
+        <v>200</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O235" t="n">
-        <v>-2541256</v>
+        <v>0</v>
       </c>
       <c r="P235" t="n">
-        <v>-6327062</v>
+        <v>0</v>
       </c>
       <c r="Q235" t="n">
-        <v>-5498046</v>
+        <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>-5543345</v>
+        <v>0</v>
       </c>
       <c r="S235" t="n">
-        <v>-2161322</v>
+        <v>0</v>
       </c>
       <c r="T235" t="n">
-        <v>-7056057</v>
+        <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>-5983326</v>
+        <v>0</v>
       </c>
       <c r="V235" t="n">
-        <v>-5138283</v>
+        <v>0</v>
       </c>
       <c r="W235" t="n">
         <v>0</v>
@@ -41260,22 +41260,22 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>-128000</v>
+        <v>0</v>
       </c>
       <c r="Z235" t="n">
-        <v>-128000</v>
+        <v>0</v>
       </c>
       <c r="AA235" t="n">
-        <v>-379934</v>
+        <v>0</v>
       </c>
       <c r="AB235" t="n">
-        <v>728995</v>
+        <v>0</v>
       </c>
       <c r="AC235" t="n">
-        <v>613280</v>
+        <v>0</v>
       </c>
       <c r="AD235" t="n">
-        <v>-277062</v>
+        <v>0</v>
       </c>
       <c r="AE235" t="n">
         <v>-18</v>
@@ -41284,16 +41284,16 @@
         <v>-18</v>
       </c>
       <c r="AG235" t="n">
-        <v>40</v>
+        <v>-45</v>
       </c>
       <c r="AH235" t="n">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="AI235" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ235" t="n">
-        <v>-16</v>
+        <v>-6</v>
       </c>
       <c r="AK235" t="inlineStr">
         <is>
@@ -41301,25 +41301,25 @@
         </is>
       </c>
       <c r="AL235" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="AM235" t="n">
-        <v>-12.5</v>
+        <v>-200</v>
       </c>
       <c r="AN235" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AO235" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
@@ -41334,17 +41334,17 @@
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>站上5日線、爆量、爆量價未漲</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、外資投信同步賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、爆量、爆量價未漲、法人連續偏賣、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -9762,16 +9762,16 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>1386539</v>
+        <v>1413539</v>
       </c>
       <c r="P54" t="n">
-        <v>5203900</v>
+        <v>5230900</v>
       </c>
       <c r="Q54" t="n">
-        <v>7161221</v>
+        <v>7188221</v>
       </c>
       <c r="R54" t="n">
-        <v>48978054</v>
+        <v>49005054</v>
       </c>
       <c r="S54" t="n">
         <v>1230622</v>
@@ -9786,16 +9786,16 @@
         <v>32877140</v>
       </c>
       <c r="W54" t="n">
-        <v>53489</v>
+        <v>80489</v>
       </c>
       <c r="X54" t="n">
-        <v>-353521</v>
+        <v>-326521</v>
       </c>
       <c r="Y54" t="n">
-        <v>1102872</v>
+        <v>1129872</v>
       </c>
       <c r="Z54" t="n">
-        <v>11797835</v>
+        <v>11824835</v>
       </c>
       <c r="AA54" t="n">
         <v>102428</v>
@@ -17588,16 +17588,16 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>12948417</v>
+        <v>12923417</v>
       </c>
       <c r="P99" t="n">
-        <v>13309614</v>
+        <v>13284614</v>
       </c>
       <c r="Q99" t="n">
-        <v>3253586</v>
+        <v>3228586</v>
       </c>
       <c r="R99" t="n">
-        <v>-101086624</v>
+        <v>-101111624</v>
       </c>
       <c r="S99" t="n">
         <v>11566360</v>
@@ -17612,16 +17612,16 @@
         <v>-85798390</v>
       </c>
       <c r="W99" t="n">
-        <v>515683</v>
+        <v>490683</v>
       </c>
       <c r="X99" t="n">
-        <v>-2635210</v>
+        <v>-2660210</v>
       </c>
       <c r="Y99" t="n">
-        <v>-3622784</v>
+        <v>-3647784</v>
       </c>
       <c r="Z99" t="n">
-        <v>-15708702</v>
+        <v>-15733702</v>
       </c>
       <c r="AA99" t="n">
         <v>866374</v>
@@ -22982,16 +22982,16 @@
         </is>
       </c>
       <c r="O130" t="n">
-        <v>858367</v>
+        <v>857567</v>
       </c>
       <c r="P130" t="n">
-        <v>760548</v>
+        <v>759748</v>
       </c>
       <c r="Q130" t="n">
-        <v>760552</v>
+        <v>759752</v>
       </c>
       <c r="R130" t="n">
-        <v>472443</v>
+        <v>471643</v>
       </c>
       <c r="S130" t="n">
         <v>780229</v>
@@ -23006,16 +23006,16 @@
         <v>-139766</v>
       </c>
       <c r="W130" t="n">
-        <v>59100</v>
+        <v>58300</v>
       </c>
       <c r="X130" t="n">
-        <v>-134400</v>
+        <v>-135200</v>
       </c>
       <c r="Y130" t="n">
-        <v>33576</v>
+        <v>32776</v>
       </c>
       <c r="Z130" t="n">
-        <v>619616</v>
+        <v>618816</v>
       </c>
       <c r="AA130" t="n">
         <v>19038</v>
@@ -30102,16 +30102,16 @@
         </is>
       </c>
       <c r="O171" t="n">
-        <v>54051</v>
+        <v>49161</v>
       </c>
       <c r="P171" t="n">
-        <v>179295</v>
+        <v>174405</v>
       </c>
       <c r="Q171" t="n">
-        <v>267428</v>
+        <v>262538</v>
       </c>
       <c r="R171" t="n">
-        <v>119313</v>
+        <v>114423</v>
       </c>
       <c r="S171" t="n">
         <v>-238001</v>
@@ -30126,16 +30126,16 @@
         <v>-687592</v>
       </c>
       <c r="W171" t="n">
-        <v>292000</v>
+        <v>287110</v>
       </c>
       <c r="X171" t="n">
-        <v>392500</v>
+        <v>387610</v>
       </c>
       <c r="Y171" t="n">
-        <v>548450</v>
+        <v>543560</v>
       </c>
       <c r="Z171" t="n">
-        <v>764540</v>
+        <v>759650</v>
       </c>
       <c r="AA171" t="n">
         <v>52</v>
@@ -30276,16 +30276,16 @@
         </is>
       </c>
       <c r="O172" t="n">
-        <v>-1026300</v>
+        <v>-932300</v>
       </c>
       <c r="P172" t="n">
-        <v>-943746</v>
+        <v>-849746</v>
       </c>
       <c r="Q172" t="n">
-        <v>-1440516</v>
+        <v>-1346516</v>
       </c>
       <c r="R172" t="n">
-        <v>-4063088</v>
+        <v>-3969088</v>
       </c>
       <c r="S172" t="n">
         <v>-1538829</v>
@@ -30300,16 +30300,16 @@
         <v>-6196114</v>
       </c>
       <c r="W172" t="n">
-        <v>554000</v>
+        <v>648000</v>
       </c>
       <c r="X172" t="n">
-        <v>1101000</v>
+        <v>1195000</v>
       </c>
       <c r="Y172" t="n">
-        <v>1124973</v>
+        <v>1218973</v>
       </c>
       <c r="Z172" t="n">
-        <v>2436473</v>
+        <v>2530473</v>
       </c>
       <c r="AA172" t="n">
         <v>-41471</v>
@@ -37050,16 +37050,16 @@
         </is>
       </c>
       <c r="O211" t="n">
-        <v>113398</v>
+        <v>118948</v>
       </c>
       <c r="P211" t="n">
-        <v>215786</v>
+        <v>221336</v>
       </c>
       <c r="Q211" t="n">
-        <v>-259357</v>
+        <v>-253807</v>
       </c>
       <c r="R211" t="n">
-        <v>-837975</v>
+        <v>-832425</v>
       </c>
       <c r="S211" t="n">
         <v>-65827</v>
@@ -37074,16 +37074,16 @@
         <v>-2083975</v>
       </c>
       <c r="W211" t="n">
-        <v>179000</v>
+        <v>184550</v>
       </c>
       <c r="X211" t="n">
-        <v>285510</v>
+        <v>291060</v>
       </c>
       <c r="Y211" t="n">
-        <v>328596</v>
+        <v>334146</v>
       </c>
       <c r="Z211" t="n">
-        <v>1847057</v>
+        <v>1852607</v>
       </c>
       <c r="AA211" t="n">
         <v>225</v>
@@ -43488,16 +43488,16 @@
         </is>
       </c>
       <c r="O248" t="n">
-        <v>576880</v>
+        <v>552592</v>
       </c>
       <c r="P248" t="n">
-        <v>-1399146</v>
+        <v>-1423434</v>
       </c>
       <c r="Q248" t="n">
-        <v>-223922</v>
+        <v>-248210</v>
       </c>
       <c r="R248" t="n">
-        <v>-1399365</v>
+        <v>-1423653</v>
       </c>
       <c r="S248" t="n">
         <v>475662</v>
@@ -43512,16 +43512,16 @@
         <v>-3982072</v>
       </c>
       <c r="W248" t="n">
-        <v>46025</v>
+        <v>21737</v>
       </c>
       <c r="X248" t="n">
-        <v>11964</v>
+        <v>-12324</v>
       </c>
       <c r="Y248" t="n">
-        <v>876927</v>
+        <v>852639</v>
       </c>
       <c r="Z248" t="n">
-        <v>2781817</v>
+        <v>2757529</v>
       </c>
       <c r="AA248" t="n">
         <v>55193</v>
@@ -47490,16 +47490,16 @@
         </is>
       </c>
       <c r="O271" t="n">
-        <v>-466644</v>
+        <v>-485644</v>
       </c>
       <c r="P271" t="n">
-        <v>331556</v>
+        <v>312556</v>
       </c>
       <c r="Q271" t="n">
-        <v>-2677829</v>
+        <v>-2696829</v>
       </c>
       <c r="R271" t="n">
-        <v>-11993949</v>
+        <v>-12012949</v>
       </c>
       <c r="S271" t="n">
         <v>-2867456</v>
@@ -47514,16 +47514,16 @@
         <v>-20064609</v>
       </c>
       <c r="W271" t="n">
-        <v>2111020</v>
+        <v>2092020</v>
       </c>
       <c r="X271" t="n">
-        <v>4496329</v>
+        <v>4477329</v>
       </c>
       <c r="Y271" t="n">
-        <v>5907199</v>
+        <v>5888199</v>
       </c>
       <c r="Z271" t="n">
-        <v>7268812</v>
+        <v>7249812</v>
       </c>
       <c r="AA271" t="n">
         <v>289792</v>
@@ -51490,16 +51490,16 @@
         </is>
       </c>
       <c r="O294" t="n">
-        <v>319639</v>
+        <v>289532</v>
       </c>
       <c r="P294" t="n">
-        <v>507382</v>
+        <v>477275</v>
       </c>
       <c r="Q294" t="n">
-        <v>-455257</v>
+        <v>-485364</v>
       </c>
       <c r="R294" t="n">
-        <v>1333749</v>
+        <v>1303642</v>
       </c>
       <c r="S294" t="n">
         <v>-264972</v>
@@ -51514,16 +51514,16 @@
         <v>-11908639</v>
       </c>
       <c r="W294" t="n">
-        <v>572009</v>
+        <v>541902</v>
       </c>
       <c r="X294" t="n">
-        <v>1472779</v>
+        <v>1442672</v>
       </c>
       <c r="Y294" t="n">
-        <v>3420875</v>
+        <v>3390768</v>
       </c>
       <c r="Z294" t="n">
-        <v>13231434</v>
+        <v>13201327</v>
       </c>
       <c r="AA294" t="n">
         <v>12602</v>
@@ -53926,16 +53926,16 @@
         </is>
       </c>
       <c r="O308" t="n">
-        <v>2709398</v>
+        <v>2709033</v>
       </c>
       <c r="P308" t="n">
-        <v>-13243796</v>
+        <v>-13244161</v>
       </c>
       <c r="Q308" t="n">
-        <v>-26211539</v>
+        <v>-26211904</v>
       </c>
       <c r="R308" t="n">
-        <v>-105067703</v>
+        <v>-105068068</v>
       </c>
       <c r="S308" t="n">
         <v>-1618431</v>
@@ -53950,16 +53950,16 @@
         <v>-137640086</v>
       </c>
       <c r="W308" t="n">
-        <v>2420780</v>
+        <v>2420415</v>
       </c>
       <c r="X308" t="n">
-        <v>5168243</v>
+        <v>5167878</v>
       </c>
       <c r="Y308" t="n">
-        <v>10082490</v>
+        <v>10082125</v>
       </c>
       <c r="Z308" t="n">
-        <v>18421620</v>
+        <v>18421255</v>
       </c>
       <c r="AA308" t="n">
         <v>1907049</v>
@@ -57058,16 +57058,16 @@
         </is>
       </c>
       <c r="O326" t="n">
-        <v>-2660245</v>
+        <v>-2661551</v>
       </c>
       <c r="P326" t="n">
-        <v>-8205945</v>
+        <v>-8207251</v>
       </c>
       <c r="Q326" t="n">
-        <v>-12261681</v>
+        <v>-12262987</v>
       </c>
       <c r="R326" t="n">
-        <v>-36415252</v>
+        <v>-36416558</v>
       </c>
       <c r="S326" t="n">
         <v>-3333809</v>
@@ -57082,16 +57082,16 @@
         <v>-35306002</v>
       </c>
       <c r="W326" t="n">
-        <v>8648</v>
+        <v>7342</v>
       </c>
       <c r="X326" t="n">
-        <v>439204</v>
+        <v>437898</v>
       </c>
       <c r="Y326" t="n">
-        <v>1675459</v>
+        <v>1674153</v>
       </c>
       <c r="Z326" t="n">
-        <v>-129194</v>
+        <v>-130500</v>
       </c>
       <c r="AA326" t="n">
         <v>664916</v>
@@ -57406,16 +57406,16 @@
         </is>
       </c>
       <c r="O328" t="n">
-        <v>-758782</v>
+        <v>-759782</v>
       </c>
       <c r="P328" t="n">
-        <v>-679874</v>
+        <v>-680874</v>
       </c>
       <c r="Q328" t="n">
-        <v>-951527</v>
+        <v>-952527</v>
       </c>
       <c r="R328" t="n">
-        <v>-2417922</v>
+        <v>-2418922</v>
       </c>
       <c r="S328" t="n">
         <v>-1054978</v>
@@ -57430,16 +57430,16 @@
         <v>-3027005</v>
       </c>
       <c r="W328" t="n">
-        <v>147954</v>
+        <v>146954</v>
       </c>
       <c r="X328" t="n">
-        <v>331455</v>
+        <v>330455</v>
       </c>
       <c r="Y328" t="n">
-        <v>407060</v>
+        <v>406060</v>
       </c>
       <c r="Z328" t="n">
-        <v>628713</v>
+        <v>627713</v>
       </c>
       <c r="AA328" t="n">
         <v>148242</v>
@@ -57580,16 +57580,16 @@
         </is>
       </c>
       <c r="O329" t="n">
-        <v>-1488884</v>
+        <v>-1491508</v>
       </c>
       <c r="P329" t="n">
-        <v>-3765771</v>
+        <v>-3768395</v>
       </c>
       <c r="Q329" t="n">
-        <v>-6335165</v>
+        <v>-6337789</v>
       </c>
       <c r="R329" t="n">
-        <v>-21708155</v>
+        <v>-21710779</v>
       </c>
       <c r="S329" t="n">
         <v>-2339361</v>
@@ -57604,16 +57604,16 @@
         <v>-24439230</v>
       </c>
       <c r="W329" t="n">
-        <v>677160</v>
+        <v>674536</v>
       </c>
       <c r="X329" t="n">
-        <v>1201385</v>
+        <v>1198761</v>
       </c>
       <c r="Y329" t="n">
-        <v>1662688</v>
+        <v>1660064</v>
       </c>
       <c r="Z329" t="n">
-        <v>3061908</v>
+        <v>3059284</v>
       </c>
       <c r="AA329" t="n">
         <v>173317</v>
@@ -58972,16 +58972,16 @@
         </is>
       </c>
       <c r="O337" t="n">
-        <v>-935246</v>
+        <v>-849246</v>
       </c>
       <c r="P337" t="n">
-        <v>-3628080</v>
+        <v>-3542080</v>
       </c>
       <c r="Q337" t="n">
-        <v>-5474733</v>
+        <v>-5388733</v>
       </c>
       <c r="R337" t="n">
-        <v>-25684609</v>
+        <v>-25598609</v>
       </c>
       <c r="S337" t="n">
         <v>-5280946</v>
@@ -58996,16 +58996,16 @@
         <v>-38683452</v>
       </c>
       <c r="W337" t="n">
-        <v>3700227</v>
+        <v>3786227</v>
       </c>
       <c r="X337" t="n">
-        <v>6219174</v>
+        <v>6305174</v>
       </c>
       <c r="Y337" t="n">
-        <v>8414261</v>
+        <v>8500261</v>
       </c>
       <c r="Z337" t="n">
-        <v>12394849</v>
+        <v>12480849</v>
       </c>
       <c r="AA337" t="n">
         <v>645473</v>
@@ -60886,16 +60886,16 @@
         </is>
       </c>
       <c r="O348" t="n">
-        <v>-63419</v>
+        <v>-41465</v>
       </c>
       <c r="P348" t="n">
-        <v>-870613</v>
+        <v>-848659</v>
       </c>
       <c r="Q348" t="n">
-        <v>-1441022</v>
+        <v>-1419068</v>
       </c>
       <c r="R348" t="n">
-        <v>-4144888</v>
+        <v>-4122934</v>
       </c>
       <c r="S348" t="n">
         <v>-169275</v>
@@ -60910,16 +60910,16 @@
         <v>-5118179</v>
       </c>
       <c r="W348" t="n">
-        <v>56261</v>
+        <v>78215</v>
       </c>
       <c r="X348" t="n">
-        <v>499811</v>
+        <v>521765</v>
       </c>
       <c r="Y348" t="n">
-        <v>670485</v>
+        <v>692439</v>
       </c>
       <c r="Z348" t="n">
-        <v>703322</v>
+        <v>725276</v>
       </c>
       <c r="AA348" t="n">
         <v>49595</v>
@@ -65062,16 +65062,16 @@
         </is>
       </c>
       <c r="O372" t="n">
-        <v>-5398961</v>
+        <v>-5248961</v>
       </c>
       <c r="P372" t="n">
-        <v>-26701806</v>
+        <v>-26551806</v>
       </c>
       <c r="Q372" t="n">
-        <v>-24901315</v>
+        <v>-24751315</v>
       </c>
       <c r="R372" t="n">
-        <v>-8414321</v>
+        <v>-8264321</v>
       </c>
       <c r="S372" t="n">
         <v>-5362056</v>
@@ -65086,16 +65086,16 @@
         <v>-14292647</v>
       </c>
       <c r="W372" t="n">
-        <v>121081</v>
+        <v>271081</v>
       </c>
       <c r="X372" t="n">
-        <v>385117</v>
+        <v>535117</v>
       </c>
       <c r="Y372" t="n">
-        <v>2362774</v>
+        <v>2512774</v>
       </c>
       <c r="Z372" t="n">
-        <v>8372982</v>
+        <v>8522982</v>
       </c>
       <c r="AA372" t="n">
         <v>-157986</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -42043,12 +42043,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>3491.TWO</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -42067,28 +42067,28 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>538</v>
+        <v>1275</v>
       </c>
       <c r="G240" t="n">
-        <v>560.4</v>
+        <v>1348</v>
       </c>
       <c r="H240" t="n">
-        <v>598.2</v>
+        <v>1390.5</v>
       </c>
       <c r="I240" t="n">
-        <v>637</v>
+        <v>1487.25</v>
       </c>
       <c r="J240" t="n">
-        <v>2093000</v>
+        <v>1771000</v>
       </c>
       <c r="K240" t="n">
-        <v>1715800</v>
+        <v>1339200</v>
       </c>
       <c r="L240" t="n">
-        <v>725</v>
+        <v>1760</v>
       </c>
       <c r="M240" t="n">
-        <v>533</v>
+        <v>1225</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>0</v>
       </c>
       <c r="AJ240" t="n">
-        <v>-18</v>
+        <v>-22</v>
       </c>
       <c r="AK240" t="inlineStr">
         <is>
@@ -42167,16 +42167,16 @@
         </is>
       </c>
       <c r="AL240" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM240" t="n">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="AN240" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AO240" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
         </is>
       </c>
       <c r="AR240" t="inlineStr">
@@ -42217,12 +42217,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3491.TWO</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -42241,28 +42241,28 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>1275</v>
+        <v>214.5</v>
       </c>
       <c r="G241" t="n">
-        <v>1348</v>
+        <v>221.2</v>
       </c>
       <c r="H241" t="n">
-        <v>1390.5</v>
+        <v>230.8</v>
       </c>
       <c r="I241" t="n">
-        <v>1487.25</v>
+        <v>243.65</v>
       </c>
       <c r="J241" t="n">
-        <v>1771000</v>
+        <v>1354000</v>
       </c>
       <c r="K241" t="n">
-        <v>1339200</v>
+        <v>1132800</v>
       </c>
       <c r="L241" t="n">
-        <v>1760</v>
+        <v>270</v>
       </c>
       <c r="M241" t="n">
-        <v>1225</v>
+        <v>212</v>
       </c>
       <c r="N241" t="inlineStr">
         <is>
@@ -42347,10 +42347,10 @@
         <v>18.18</v>
       </c>
       <c r="AN241" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AO241" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
       </c>
       <c r="AQ241" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR241" t="inlineStr">
@@ -42391,12 +42391,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>6275.TWO</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -42415,28 +42415,28 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>214.5</v>
+        <v>43.7</v>
       </c>
       <c r="G242" t="n">
-        <v>221.2</v>
+        <v>44.5</v>
       </c>
       <c r="H242" t="n">
-        <v>230.8</v>
+        <v>45.1</v>
       </c>
       <c r="I242" t="n">
-        <v>243.65</v>
+        <v>46.03</v>
       </c>
       <c r="J242" t="n">
-        <v>1354000</v>
+        <v>126000</v>
       </c>
       <c r="K242" t="n">
-        <v>1132800</v>
+        <v>119000</v>
       </c>
       <c r="L242" t="n">
-        <v>270</v>
+        <v>48.05</v>
       </c>
       <c r="M242" t="n">
-        <v>212</v>
+        <v>43.6</v>
       </c>
       <c r="N242" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>0</v>
       </c>
       <c r="AJ242" t="n">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="AK242" t="inlineStr">
         <is>
@@ -42515,16 +42515,16 @@
         </is>
       </c>
       <c r="AL242" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="AM242" t="n">
-        <v>18.18</v>
+        <v>-12.5</v>
       </c>
       <c r="AN242" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO242" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
@@ -42533,7 +42533,7 @@
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
@@ -42739,12 +42739,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>6275.TWO</t>
+          <t>4966.TWO</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -42763,28 +42763,28 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>43.7</v>
+        <v>522</v>
       </c>
       <c r="G244" t="n">
-        <v>44.5</v>
+        <v>522.4</v>
       </c>
       <c r="H244" t="n">
-        <v>45.1</v>
+        <v>535.1</v>
       </c>
       <c r="I244" t="n">
-        <v>46.03</v>
+        <v>551.8</v>
       </c>
       <c r="J244" t="n">
-        <v>126000</v>
+        <v>363000</v>
       </c>
       <c r="K244" t="n">
-        <v>119000</v>
+        <v>319400</v>
       </c>
       <c r="L244" t="n">
-        <v>48.05</v>
+        <v>583</v>
       </c>
       <c r="M244" t="n">
-        <v>43.6</v>
+        <v>512</v>
       </c>
       <c r="N244" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>0</v>
       </c>
       <c r="AJ244" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="AK244" t="inlineStr">
         <is>
@@ -42863,10 +42863,10 @@
         </is>
       </c>
       <c r="AL244" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AM244" t="n">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="AN244" t="n">
         <v>0</v>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
@@ -42913,12 +42913,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>4966.TWO</t>
+          <t>2492.TW</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -42937,28 +42937,28 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>522</v>
+        <v>372.5</v>
       </c>
       <c r="G245" t="n">
-        <v>522.4</v>
+        <v>375.8</v>
       </c>
       <c r="H245" t="n">
-        <v>535.1</v>
+        <v>391.55</v>
       </c>
       <c r="I245" t="n">
-        <v>551.8</v>
+        <v>371.55</v>
       </c>
       <c r="J245" t="n">
-        <v>363000</v>
+        <v>26559330</v>
       </c>
       <c r="K245" t="n">
-        <v>319400</v>
+        <v>31043647</v>
       </c>
       <c r="L245" t="n">
-        <v>583</v>
+        <v>431.5</v>
       </c>
       <c r="M245" t="n">
-        <v>512</v>
+        <v>298.5</v>
       </c>
       <c r="N245" t="inlineStr">
         <is>
@@ -42966,70 +42966,70 @@
         </is>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>1417709</v>
       </c>
       <c r="P245" t="n">
-        <v>0</v>
+        <v>-3178539</v>
       </c>
       <c r="Q245" t="n">
-        <v>0</v>
+        <v>-6265105</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>-2005892</v>
       </c>
       <c r="S245" t="n">
-        <v>0</v>
+        <v>-665182</v>
       </c>
       <c r="T245" t="n">
-        <v>0</v>
+        <v>-6743176</v>
       </c>
       <c r="U245" t="n">
-        <v>0</v>
+        <v>-12208715</v>
       </c>
       <c r="V245" t="n">
-        <v>0</v>
+        <v>-7029555</v>
       </c>
       <c r="W245" t="n">
-        <v>0</v>
+        <v>2103000</v>
       </c>
       <c r="X245" t="n">
-        <v>0</v>
+        <v>4426000</v>
       </c>
       <c r="Y245" t="n">
-        <v>0</v>
+        <v>7481038</v>
       </c>
       <c r="Z245" t="n">
-        <v>0</v>
+        <v>7387038</v>
       </c>
       <c r="AA245" t="n">
-        <v>0</v>
+        <v>-20109</v>
       </c>
       <c r="AB245" t="n">
-        <v>0</v>
+        <v>-861363</v>
       </c>
       <c r="AC245" t="n">
-        <v>0</v>
+        <v>-1537428</v>
       </c>
       <c r="AD245" t="n">
-        <v>0</v>
+        <v>-2363375</v>
       </c>
       <c r="AE245" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="AF245" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="AG245" t="n">
-        <v>-45</v>
+        <v>-20</v>
       </c>
       <c r="AH245" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="AI245" t="n">
         <v>0</v>
       </c>
       <c r="AJ245" t="n">
-        <v>-18</v>
+        <v>-26</v>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
@@ -43037,16 +43037,16 @@
         </is>
       </c>
       <c r="AL245" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM245" t="n">
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="AN245" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO245" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
@@ -43070,29 +43070,29 @@
       </c>
       <c r="AT245" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2492.TW</t>
+          <t>2345.TW</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -43111,28 +43111,28 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>372.5</v>
+        <v>1760</v>
       </c>
       <c r="G246" t="n">
-        <v>375.8</v>
+        <v>1865</v>
       </c>
       <c r="H246" t="n">
-        <v>391.55</v>
+        <v>1947.5</v>
       </c>
       <c r="I246" t="n">
-        <v>371.55</v>
+        <v>1946</v>
       </c>
       <c r="J246" t="n">
-        <v>26559330</v>
+        <v>4386205</v>
       </c>
       <c r="K246" t="n">
-        <v>31043647</v>
+        <v>4860919</v>
       </c>
       <c r="L246" t="n">
-        <v>431.5</v>
+        <v>2145</v>
       </c>
       <c r="M246" t="n">
-        <v>298.5</v>
+        <v>1740</v>
       </c>
       <c r="N246" t="inlineStr">
         <is>
@@ -43140,52 +43140,52 @@
         </is>
       </c>
       <c r="O246" t="n">
-        <v>1417709</v>
+        <v>552592</v>
       </c>
       <c r="P246" t="n">
-        <v>-3178539</v>
+        <v>-1423434</v>
       </c>
       <c r="Q246" t="n">
-        <v>-6265105</v>
+        <v>-248210</v>
       </c>
       <c r="R246" t="n">
-        <v>-2005892</v>
+        <v>-1423653</v>
       </c>
       <c r="S246" t="n">
-        <v>-665182</v>
+        <v>475662</v>
       </c>
       <c r="T246" t="n">
-        <v>-6743176</v>
+        <v>-1308920</v>
       </c>
       <c r="U246" t="n">
-        <v>-12208715</v>
+        <v>-853415</v>
       </c>
       <c r="V246" t="n">
-        <v>-7029555</v>
+        <v>-3982072</v>
       </c>
       <c r="W246" t="n">
-        <v>2103000</v>
+        <v>21737</v>
       </c>
       <c r="X246" t="n">
-        <v>4426000</v>
+        <v>-12324</v>
       </c>
       <c r="Y246" t="n">
-        <v>7481038</v>
+        <v>852639</v>
       </c>
       <c r="Z246" t="n">
-        <v>7387038</v>
+        <v>2757529</v>
       </c>
       <c r="AA246" t="n">
-        <v>-20109</v>
+        <v>55193</v>
       </c>
       <c r="AB246" t="n">
-        <v>-861363</v>
+        <v>-102190</v>
       </c>
       <c r="AC246" t="n">
-        <v>-1537428</v>
+        <v>-247434</v>
       </c>
       <c r="AD246" t="n">
-        <v>-2363375</v>
+        <v>-199110</v>
       </c>
       <c r="AE246" t="n">
         <v>-20</v>
@@ -43194,33 +43194,33 @@
         <v>-20</v>
       </c>
       <c r="AG246" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AH246" t="n">
         <v>-20</v>
       </c>
-      <c r="AH246" t="n">
+      <c r="AI246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ246" t="n">
         <v>-30</v>
       </c>
-      <c r="AI246" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ246" t="n">
-        <v>-26</v>
-      </c>
       <c r="AK246" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
       <c r="AL246" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AM246" t="n">
-        <v>23.08</v>
+        <v>33.33</v>
       </c>
       <c r="AN246" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AO246" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
@@ -43244,17 +43244,17 @@
       </c>
       <c r="AT246" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -43435,12 +43435,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2345.TW</t>
+          <t>2607.TW</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>榮運</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -43459,28 +43459,28 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>1760</v>
+        <v>56.5</v>
       </c>
       <c r="G248" t="n">
-        <v>1865</v>
+        <v>56.16</v>
       </c>
       <c r="H248" t="n">
-        <v>1947.5</v>
+        <v>57.21</v>
       </c>
       <c r="I248" t="n">
-        <v>1946</v>
+        <v>55.63</v>
       </c>
       <c r="J248" t="n">
-        <v>4386205</v>
+        <v>3289050</v>
       </c>
       <c r="K248" t="n">
-        <v>4860919</v>
+        <v>1309451</v>
       </c>
       <c r="L248" t="n">
-        <v>2145</v>
+        <v>59.8</v>
       </c>
       <c r="M248" t="n">
-        <v>1740</v>
+        <v>53</v>
       </c>
       <c r="N248" t="inlineStr">
         <is>
@@ -43488,52 +43488,52 @@
         </is>
       </c>
       <c r="O248" t="n">
-        <v>552592</v>
+        <v>-120668</v>
       </c>
       <c r="P248" t="n">
-        <v>-1423434</v>
+        <v>-136597</v>
       </c>
       <c r="Q248" t="n">
-        <v>-248210</v>
+        <v>-201288</v>
       </c>
       <c r="R248" t="n">
-        <v>-1423653</v>
+        <v>2295028</v>
       </c>
       <c r="S248" t="n">
-        <v>475662</v>
+        <v>-95794</v>
       </c>
       <c r="T248" t="n">
-        <v>-1308920</v>
+        <v>-112723</v>
       </c>
       <c r="U248" t="n">
-        <v>-853415</v>
+        <v>-152214</v>
       </c>
       <c r="V248" t="n">
-        <v>-3982072</v>
+        <v>2226452</v>
       </c>
       <c r="W248" t="n">
-        <v>21737</v>
+        <v>0</v>
       </c>
       <c r="X248" t="n">
-        <v>-12324</v>
+        <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>852639</v>
+        <v>-122</v>
       </c>
       <c r="Z248" t="n">
-        <v>2757529</v>
+        <v>-122</v>
       </c>
       <c r="AA248" t="n">
-        <v>55193</v>
+        <v>-24874</v>
       </c>
       <c r="AB248" t="n">
-        <v>-102190</v>
+        <v>-23874</v>
       </c>
       <c r="AC248" t="n">
-        <v>-247434</v>
+        <v>-48952</v>
       </c>
       <c r="AD248" t="n">
-        <v>-199110</v>
+        <v>68698</v>
       </c>
       <c r="AE248" t="n">
         <v>-20</v>
@@ -43542,16 +43542,16 @@
         <v>-20</v>
       </c>
       <c r="AG248" t="n">
-        <v>-30</v>
+        <v>40</v>
       </c>
       <c r="AH248" t="n">
-        <v>-20</v>
+        <v>-90</v>
       </c>
       <c r="AI248" t="n">
         <v>0</v>
       </c>
       <c r="AJ248" t="n">
-        <v>-30</v>
+        <v>4</v>
       </c>
       <c r="AK248" t="inlineStr">
         <is>
@@ -43559,16 +43559,16 @@
         </is>
       </c>
       <c r="AL248" t="n">
-        <v>10</v>
+        <v>-24</v>
       </c>
       <c r="AM248" t="n">
-        <v>33.33</v>
+        <v>-600</v>
       </c>
       <c r="AN248" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AO248" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、爆量後不追價、分數轉弱</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
@@ -43592,17 +43592,17 @@
       </c>
       <c r="AT248" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、爆量</t>
         </is>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>5日法人賣超、投信買外資賣</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、爆量、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -44131,12 +44131,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2607.TW</t>
+          <t>2385.TW</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>榮運</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -44155,28 +44155,28 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>56.5</v>
+        <v>103.5</v>
       </c>
       <c r="G252" t="n">
-        <v>56.16</v>
+        <v>102.3</v>
       </c>
       <c r="H252" t="n">
-        <v>57.21</v>
+        <v>103.5</v>
       </c>
       <c r="I252" t="n">
-        <v>55.63</v>
+        <v>104.1</v>
       </c>
       <c r="J252" t="n">
-        <v>3289050</v>
+        <v>7953348</v>
       </c>
       <c r="K252" t="n">
-        <v>1309451</v>
+        <v>4062945</v>
       </c>
       <c r="L252" t="n">
-        <v>59.8</v>
+        <v>107</v>
       </c>
       <c r="M252" t="n">
-        <v>53</v>
+        <v>100.5</v>
       </c>
       <c r="N252" t="inlineStr">
         <is>
@@ -44184,52 +44184,52 @@
         </is>
       </c>
       <c r="O252" t="n">
-        <v>-120668</v>
+        <v>869547</v>
       </c>
       <c r="P252" t="n">
-        <v>-136597</v>
+        <v>577220</v>
       </c>
       <c r="Q252" t="n">
-        <v>-201288</v>
+        <v>-2290735</v>
       </c>
       <c r="R252" t="n">
-        <v>2295028</v>
+        <v>1691983</v>
       </c>
       <c r="S252" t="n">
-        <v>-95794</v>
+        <v>862366</v>
       </c>
       <c r="T252" t="n">
-        <v>-112723</v>
+        <v>876176</v>
       </c>
       <c r="U252" t="n">
-        <v>-152214</v>
+        <v>-1909615</v>
       </c>
       <c r="V252" t="n">
-        <v>2226452</v>
+        <v>1843390</v>
       </c>
       <c r="W252" t="n">
-        <v>0</v>
+        <v>-8432</v>
       </c>
       <c r="X252" t="n">
-        <v>0</v>
+        <v>-584870</v>
       </c>
       <c r="Y252" t="n">
-        <v>-122</v>
+        <v>-1043387</v>
       </c>
       <c r="Z252" t="n">
-        <v>-122</v>
+        <v>-1274700</v>
       </c>
       <c r="AA252" t="n">
-        <v>-24874</v>
+        <v>15613</v>
       </c>
       <c r="AB252" t="n">
-        <v>-23874</v>
+        <v>285914</v>
       </c>
       <c r="AC252" t="n">
-        <v>-48952</v>
+        <v>662267</v>
       </c>
       <c r="AD252" t="n">
-        <v>68698</v>
+        <v>1123293</v>
       </c>
       <c r="AE252" t="n">
         <v>-20</v>
@@ -44238,16 +44238,16 @@
         <v>-20</v>
       </c>
       <c r="AG252" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AH252" t="n">
-        <v>-90</v>
+        <v>-50</v>
       </c>
       <c r="AI252" t="n">
         <v>0</v>
       </c>
       <c r="AJ252" t="n">
-        <v>4</v>
+        <v>-48</v>
       </c>
       <c r="AK252" t="inlineStr">
         <is>
@@ -44255,25 +44255,25 @@
         </is>
       </c>
       <c r="AL252" t="n">
-        <v>-24</v>
+        <v>28</v>
       </c>
       <c r="AM252" t="n">
-        <v>-600</v>
+        <v>58.33</v>
       </c>
       <c r="AN252" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="AO252" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、爆量後不追價、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
@@ -44288,29 +44288,29 @@
       </c>
       <c r="AT252" t="inlineStr">
         <is>
-          <t>站上5日線、爆量</t>
+          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、爆量、法人連續偏賣、中期買超轉短線賣壓、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、成交量放大、接近20日低點、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2385.TW</t>
+          <t>1513.TW</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -44329,28 +44329,28 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>103.5</v>
+        <v>159</v>
       </c>
       <c r="G253" t="n">
-        <v>102.3</v>
+        <v>160.8</v>
       </c>
       <c r="H253" t="n">
-        <v>103.5</v>
+        <v>163.7</v>
       </c>
       <c r="I253" t="n">
-        <v>104.1</v>
+        <v>165.3</v>
       </c>
       <c r="J253" t="n">
-        <v>7953348</v>
+        <v>1812767</v>
       </c>
       <c r="K253" t="n">
-        <v>4062945</v>
+        <v>1633736</v>
       </c>
       <c r="L253" t="n">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="M253" t="n">
-        <v>100.5</v>
+        <v>158</v>
       </c>
       <c r="N253" t="inlineStr">
         <is>
@@ -44358,96 +44358,96 @@
         </is>
       </c>
       <c r="O253" t="n">
-        <v>869547</v>
+        <v>-69223</v>
       </c>
       <c r="P253" t="n">
-        <v>577220</v>
+        <v>141082</v>
       </c>
       <c r="Q253" t="n">
-        <v>-2290735</v>
+        <v>-69611</v>
       </c>
       <c r="R253" t="n">
-        <v>1691983</v>
+        <v>2099728</v>
       </c>
       <c r="S253" t="n">
-        <v>862366</v>
+        <v>-62403</v>
       </c>
       <c r="T253" t="n">
-        <v>876176</v>
+        <v>303637</v>
       </c>
       <c r="U253" t="n">
-        <v>-1909615</v>
+        <v>284377</v>
       </c>
       <c r="V253" t="n">
-        <v>1843390</v>
+        <v>2252859</v>
       </c>
       <c r="W253" t="n">
-        <v>-8432</v>
+        <v>-2506</v>
       </c>
       <c r="X253" t="n">
-        <v>-584870</v>
+        <v>-356506</v>
       </c>
       <c r="Y253" t="n">
-        <v>-1043387</v>
+        <v>-664633</v>
       </c>
       <c r="Z253" t="n">
-        <v>-1274700</v>
+        <v>-552633</v>
       </c>
       <c r="AA253" t="n">
-        <v>15613</v>
+        <v>-4314</v>
       </c>
       <c r="AB253" t="n">
-        <v>285914</v>
+        <v>193951</v>
       </c>
       <c r="AC253" t="n">
-        <v>662267</v>
+        <v>310645</v>
       </c>
       <c r="AD253" t="n">
-        <v>1123293</v>
+        <v>399502</v>
       </c>
       <c r="AE253" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>-45</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AL253" t="n">
         <v>-20</v>
       </c>
-      <c r="AF253" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AG253" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH253" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AI253" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ253" t="n">
-        <v>-48</v>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="AL253" t="n">
-        <v>28</v>
-      </c>
       <c r="AM253" t="n">
-        <v>58.33</v>
+        <v>-1000</v>
       </c>
       <c r="AN253" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="AO253" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
@@ -44462,17 +44462,17 @@
       </c>
       <c r="AT253" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、成交量放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>5日法人小幅賣超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、成交量放大、接近20日低點、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人小幅賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -44827,12 +44827,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1513.TW</t>
+          <t>5484.TW</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>慧友</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -44851,28 +44851,28 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>159</v>
+        <v>35.5</v>
       </c>
       <c r="G256" t="n">
-        <v>160.8</v>
+        <v>35.87</v>
       </c>
       <c r="H256" t="n">
-        <v>163.7</v>
+        <v>36.59</v>
       </c>
       <c r="I256" t="n">
-        <v>165.3</v>
+        <v>37.84</v>
       </c>
       <c r="J256" t="n">
-        <v>1812767</v>
+        <v>104581</v>
       </c>
       <c r="K256" t="n">
-        <v>1633736</v>
+        <v>119361</v>
       </c>
       <c r="L256" t="n">
-        <v>171</v>
+        <v>40</v>
       </c>
       <c r="M256" t="n">
-        <v>158</v>
+        <v>34.9</v>
       </c>
       <c r="N256" t="inlineStr">
         <is>
@@ -44880,52 +44880,52 @@
         </is>
       </c>
       <c r="O256" t="n">
-        <v>-69223</v>
+        <v>29436</v>
       </c>
       <c r="P256" t="n">
-        <v>141082</v>
+        <v>10415</v>
       </c>
       <c r="Q256" t="n">
-        <v>-69611</v>
+        <v>-4707</v>
       </c>
       <c r="R256" t="n">
-        <v>2099728</v>
+        <v>15144</v>
       </c>
       <c r="S256" t="n">
-        <v>-62403</v>
+        <v>29436</v>
       </c>
       <c r="T256" t="n">
-        <v>303637</v>
+        <v>10436</v>
       </c>
       <c r="U256" t="n">
-        <v>284377</v>
+        <v>-5632</v>
       </c>
       <c r="V256" t="n">
-        <v>2252859</v>
+        <v>19110</v>
       </c>
       <c r="W256" t="n">
-        <v>-2506</v>
+        <v>0</v>
       </c>
       <c r="X256" t="n">
-        <v>-356506</v>
+        <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>-664633</v>
+        <v>0</v>
       </c>
       <c r="Z256" t="n">
-        <v>-552633</v>
+        <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>-4314</v>
+        <v>0</v>
       </c>
       <c r="AB256" t="n">
-        <v>193951</v>
+        <v>-21</v>
       </c>
       <c r="AC256" t="n">
-        <v>310645</v>
+        <v>925</v>
       </c>
       <c r="AD256" t="n">
-        <v>399502</v>
+        <v>-3966</v>
       </c>
       <c r="AE256" t="n">
         <v>-22</v>
@@ -44934,16 +44934,16 @@
         <v>-22</v>
       </c>
       <c r="AG256" t="n">
-        <v>-45</v>
+        <v>-55</v>
       </c>
       <c r="AH256" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AI256" t="n">
         <v>0</v>
       </c>
       <c r="AJ256" t="n">
-        <v>-2</v>
+        <v>-22</v>
       </c>
       <c r="AK256" t="inlineStr">
         <is>
@@ -44951,10 +44951,10 @@
         </is>
       </c>
       <c r="AL256" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AM256" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AN256" t="n">
         <v>0</v>
@@ -44969,7 +44969,7 @@
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR256" t="inlineStr">
@@ -44984,17 +44984,17 @@
       </c>
       <c r="AT256" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>5日法人小幅賣超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人小幅賣超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -45208,7 +45208,7 @@
         <v>536.55</v>
       </c>
       <c r="I258" t="n">
-        <v>596.67</v>
+        <v>606.98</v>
       </c>
       <c r="J258" t="n">
         <v>1204000</v>
@@ -45217,7 +45217,7 @@
         <v>1631800</v>
       </c>
       <c r="L258" t="n">
-        <v>693</v>
+        <v>747</v>
       </c>
       <c r="M258" t="n">
         <v>499.5</v>
@@ -46219,12 +46219,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5484.TW</t>
+          <t>3680.TWO</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>慧友</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -46243,28 +46243,28 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>35.5</v>
+        <v>505</v>
       </c>
       <c r="G264" t="n">
-        <v>35.87</v>
+        <v>508.6</v>
       </c>
       <c r="H264" t="n">
-        <v>36.59</v>
+        <v>524</v>
       </c>
       <c r="I264" t="n">
-        <v>37.84</v>
+        <v>538.9</v>
       </c>
       <c r="J264" t="n">
-        <v>104581</v>
+        <v>557000</v>
       </c>
       <c r="K264" t="n">
-        <v>119361</v>
+        <v>766600</v>
       </c>
       <c r="L264" t="n">
-        <v>40</v>
+        <v>594</v>
       </c>
       <c r="M264" t="n">
-        <v>34.9</v>
+        <v>491</v>
       </c>
       <c r="N264" t="inlineStr">
         <is>
@@ -46272,28 +46272,28 @@
         </is>
       </c>
       <c r="O264" t="n">
-        <v>29436</v>
+        <v>0</v>
       </c>
       <c r="P264" t="n">
-        <v>10415</v>
+        <v>0</v>
       </c>
       <c r="Q264" t="n">
-        <v>-4707</v>
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>15144</v>
+        <v>0</v>
       </c>
       <c r="S264" t="n">
-        <v>29436</v>
+        <v>0</v>
       </c>
       <c r="T264" t="n">
-        <v>10436</v>
+        <v>0</v>
       </c>
       <c r="U264" t="n">
-        <v>-5632</v>
+        <v>0</v>
       </c>
       <c r="V264" t="n">
-        <v>19110</v>
+        <v>0</v>
       </c>
       <c r="W264" t="n">
         <v>0</v>
@@ -46311,13 +46311,13 @@
         <v>0</v>
       </c>
       <c r="AB264" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="AC264" t="n">
-        <v>925</v>
+        <v>0</v>
       </c>
       <c r="AD264" t="n">
-        <v>-3966</v>
+        <v>0</v>
       </c>
       <c r="AE264" t="n">
         <v>-22</v>
@@ -46335,7 +46335,7 @@
         <v>0</v>
       </c>
       <c r="AJ264" t="n">
-        <v>-22</v>
+        <v>-18</v>
       </c>
       <c r="AK264" t="inlineStr">
         <is>
@@ -46343,10 +46343,10 @@
         </is>
       </c>
       <c r="AL264" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AM264" t="n">
-        <v>0</v>
+        <v>-22.22</v>
       </c>
       <c r="AN264" t="n">
         <v>0</v>
@@ -46361,7 +46361,7 @@
       </c>
       <c r="AQ264" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR264" t="inlineStr">
@@ -46393,12 +46393,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>3680.TWO</t>
+          <t>3211.TWO</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -46417,28 +46417,28 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>505</v>
+        <v>327</v>
       </c>
       <c r="G265" t="n">
-        <v>508.6</v>
+        <v>334.1</v>
       </c>
       <c r="H265" t="n">
-        <v>524</v>
+        <v>347</v>
       </c>
       <c r="I265" t="n">
-        <v>538.9</v>
+        <v>368.77</v>
       </c>
       <c r="J265" t="n">
-        <v>557000</v>
+        <v>1252000</v>
       </c>
       <c r="K265" t="n">
-        <v>766600</v>
+        <v>1696000</v>
       </c>
       <c r="L265" t="n">
-        <v>594</v>
+        <v>406.5</v>
       </c>
       <c r="M265" t="n">
-        <v>491</v>
+        <v>320</v>
       </c>
       <c r="N265" t="inlineStr">
         <is>
@@ -46567,12 +46567,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>3211.TWO</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -46582,7 +46582,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -46591,28 +46591,28 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>327</v>
+        <v>643</v>
       </c>
       <c r="G266" t="n">
-        <v>334.1</v>
+        <v>654.4</v>
       </c>
       <c r="H266" t="n">
-        <v>347</v>
+        <v>655.4</v>
       </c>
       <c r="I266" t="n">
-        <v>368.77</v>
+        <v>690.55</v>
       </c>
       <c r="J266" t="n">
-        <v>1252000</v>
+        <v>1071000</v>
       </c>
       <c r="K266" t="n">
-        <v>1696000</v>
+        <v>1163200</v>
       </c>
       <c r="L266" t="n">
-        <v>406.5</v>
+        <v>790</v>
       </c>
       <c r="M266" t="n">
-        <v>320</v>
+        <v>631</v>
       </c>
       <c r="N266" t="inlineStr">
         <is>
@@ -46682,20 +46682,10 @@
       <c r="AI266" t="n">
         <v>0</v>
       </c>
-      <c r="AJ266" t="n">
-        <v>-18</v>
-      </c>
-      <c r="AK266" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="AL266" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AM266" t="n">
-        <v>-22.22</v>
-      </c>
+      <c r="AJ266" t="inlineStr"/>
+      <c r="AK266" t="inlineStr"/>
+      <c r="AL266" t="inlineStr"/>
+      <c r="AM266" t="inlineStr"/>
       <c r="AN266" t="n">
         <v>0</v>
       </c>
@@ -46709,7 +46699,7 @@
       </c>
       <c r="AQ266" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR266" t="inlineStr">

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -5041,10 +5041,10 @@
         <v>48.19</v>
       </c>
       <c r="H27" t="n">
-        <v>48.19</v>
+        <v>48.18</v>
       </c>
       <c r="I27" t="n">
-        <v>47.48</v>
+        <v>47.62</v>
       </c>
       <c r="J27" t="n">
         <v>472115</v>
@@ -37701,12 +37701,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3491.TWO</t>
+          <t>6510.TWO</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -37725,28 +37725,28 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1340</v>
+        <v>3200</v>
       </c>
       <c r="G215" t="n">
-        <v>1339</v>
+        <v>3100</v>
       </c>
       <c r="H215" t="n">
-        <v>1372</v>
+        <v>3120</v>
       </c>
       <c r="I215" t="n">
-        <v>1476</v>
+        <v>3135.25</v>
       </c>
       <c r="J215" t="n">
-        <v>647000</v>
+        <v>481000</v>
       </c>
       <c r="K215" t="n">
-        <v>1210600</v>
+        <v>715400</v>
       </c>
       <c r="L215" t="n">
-        <v>1760</v>
+        <v>3580</v>
       </c>
       <c r="M215" t="n">
-        <v>1225</v>
+        <v>2825</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
@@ -37817,18 +37817,18 @@
         <v>0</v>
       </c>
       <c r="AJ215" t="n">
-        <v>-18</v>
+        <v>-22</v>
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AL215" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AM215" t="n">
-        <v>88.89</v>
+        <v>90.91</v>
       </c>
       <c r="AN215" t="n">
         <v>45</v>
@@ -37843,7 +37843,7 @@
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
@@ -37875,12 +37875,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>4147.TWO</t>
+          <t>3491.TWO</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>中裕</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -37899,28 +37899,28 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>60.3</v>
+        <v>1340</v>
       </c>
       <c r="G216" t="n">
-        <v>61.26</v>
+        <v>1339</v>
       </c>
       <c r="H216" t="n">
-        <v>60.62</v>
+        <v>1372</v>
       </c>
       <c r="I216" t="n">
-        <v>61.16</v>
+        <v>1476</v>
       </c>
       <c r="J216" t="n">
-        <v>446000</v>
+        <v>647000</v>
       </c>
       <c r="K216" t="n">
-        <v>650200</v>
+        <v>1210600</v>
       </c>
       <c r="L216" t="n">
-        <v>65.5</v>
+        <v>1760</v>
       </c>
       <c r="M216" t="n">
-        <v>58</v>
+        <v>1225</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>0</v>
       </c>
       <c r="AJ216" t="n">
-        <v>-8</v>
+        <v>-18</v>
       </c>
       <c r="AK216" t="inlineStr">
         <is>
@@ -37999,25 +37999,25 @@
         </is>
       </c>
       <c r="AL216" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AM216" t="n">
-        <v>75</v>
+        <v>88.89</v>
       </c>
       <c r="AN216" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="AO216" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR216" t="inlineStr">
@@ -38032,7 +38032,7 @@
       </c>
       <c r="AT216" t="inlineStr">
         <is>
-          <t>跌破5日線、黃金交叉、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU216" t="inlineStr">
@@ -38042,19 +38042,19 @@
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、黃金交叉、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>6485.TWO</t>
+          <t>4147.TWO</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>中裕</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -38073,28 +38073,28 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>74.40000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="G217" t="n">
-        <v>73.58</v>
+        <v>61.26</v>
       </c>
       <c r="H217" t="n">
-        <v>75.45999999999999</v>
+        <v>60.62</v>
       </c>
       <c r="I217" t="n">
-        <v>77.11</v>
+        <v>61.16</v>
       </c>
       <c r="J217" t="n">
-        <v>210000</v>
+        <v>446000</v>
       </c>
       <c r="K217" t="n">
-        <v>283600</v>
+        <v>650200</v>
       </c>
       <c r="L217" t="n">
-        <v>87.2</v>
+        <v>65.5</v>
       </c>
       <c r="M217" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="N217" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>0</v>
       </c>
       <c r="AJ217" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="AK217" t="inlineStr">
         <is>
@@ -38173,25 +38173,25 @@
         </is>
       </c>
       <c r="AL217" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AM217" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="AN217" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="AO217" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
@@ -38206,7 +38206,7 @@
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>跌破5日線、黃金交叉、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
@@ -38216,7 +38216,7 @@
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、黃金交叉、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -38745,12 +38745,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3363.TWO</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>波若威</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -38769,28 +38769,28 @@
         </is>
       </c>
       <c r="F221" t="n">
+        <v>569</v>
+      </c>
+      <c r="G221" t="n">
+        <v>559.6</v>
+      </c>
+      <c r="H221" t="n">
+        <v>586.2</v>
+      </c>
+      <c r="I221" t="n">
+        <v>632.3</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1417000</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1571200</v>
+      </c>
+      <c r="L221" t="n">
+        <v>725</v>
+      </c>
+      <c r="M221" t="n">
         <v>533</v>
-      </c>
-      <c r="G221" t="n">
-        <v>520.9</v>
-      </c>
-      <c r="H221" t="n">
-        <v>529.65</v>
-      </c>
-      <c r="I221" t="n">
-        <v>591.17</v>
-      </c>
-      <c r="J221" t="n">
-        <v>1588000</v>
-      </c>
-      <c r="K221" t="n">
-        <v>1638400</v>
-      </c>
-      <c r="L221" t="n">
-        <v>693</v>
-      </c>
-      <c r="M221" t="n">
-        <v>499.5</v>
       </c>
       <c r="N221" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AL221" t="n">
@@ -38919,12 +38919,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>3363.TWO</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -38943,28 +38943,28 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>569</v>
+        <v>533</v>
       </c>
       <c r="G222" t="n">
-        <v>559.6</v>
+        <v>520.9</v>
       </c>
       <c r="H222" t="n">
-        <v>586.2</v>
+        <v>529.65</v>
       </c>
       <c r="I222" t="n">
-        <v>632.3</v>
+        <v>591.17</v>
       </c>
       <c r="J222" t="n">
-        <v>1417000</v>
+        <v>1588000</v>
       </c>
       <c r="K222" t="n">
-        <v>1571200</v>
+        <v>1638400</v>
       </c>
       <c r="L222" t="n">
-        <v>725</v>
+        <v>693</v>
       </c>
       <c r="M222" t="n">
-        <v>533</v>
+        <v>499.5</v>
       </c>
       <c r="N222" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AL222" t="n">
@@ -40833,12 +40833,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2605.TW</t>
+          <t>6485.TWO</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>新興</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -40857,28 +40857,28 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>35.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G233" t="n">
-        <v>35.06</v>
+        <v>73.58</v>
       </c>
       <c r="H233" t="n">
-        <v>35.75</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="I233" t="n">
-        <v>35.94</v>
+        <v>77.11</v>
       </c>
       <c r="J233" t="n">
-        <v>6599525</v>
+        <v>210000</v>
       </c>
       <c r="K233" t="n">
-        <v>5245835</v>
+        <v>283600</v>
       </c>
       <c r="L233" t="n">
-        <v>38.15</v>
+        <v>87.2</v>
       </c>
       <c r="M233" t="n">
-        <v>33.85</v>
+        <v>67</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -40886,28 +40886,28 @@
         </is>
       </c>
       <c r="O233" t="n">
-        <v>3523887</v>
+        <v>0</v>
       </c>
       <c r="P233" t="n">
-        <v>824425</v>
+        <v>0</v>
       </c>
       <c r="Q233" t="n">
-        <v>-493363</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
-        <v>-605926</v>
+        <v>0</v>
       </c>
       <c r="S233" t="n">
-        <v>3363402</v>
+        <v>0</v>
       </c>
       <c r="T233" t="n">
-        <v>61758</v>
+        <v>0</v>
       </c>
       <c r="U233" t="n">
-        <v>42286</v>
+        <v>0</v>
       </c>
       <c r="V233" t="n">
-        <v>723526</v>
+        <v>0</v>
       </c>
       <c r="W233" t="n">
         <v>0</v>
@@ -40919,37 +40919,37 @@
         <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="AA233" t="n">
-        <v>160485</v>
+        <v>0</v>
       </c>
       <c r="AB233" t="n">
-        <v>762667</v>
+        <v>0</v>
       </c>
       <c r="AC233" t="n">
-        <v>-535649</v>
+        <v>0</v>
       </c>
       <c r="AD233" t="n">
-        <v>-1319452</v>
+        <v>0</v>
       </c>
       <c r="AE233" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AF233" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="AG233" t="n">
         <v>-5</v>
       </c>
       <c r="AH233" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="AI233" t="n">
         <v>0</v>
       </c>
       <c r="AJ233" t="n">
-        <v>-46</v>
+        <v>-14</v>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
@@ -40957,25 +40957,25 @@
         </is>
       </c>
       <c r="AL233" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="AM233" t="n">
-        <v>91.3</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="AN233" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AO233" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
@@ -40990,34 +40990,34 @@
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、短線籌碼止穩、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>00713.TW</t>
+          <t>2605.TW</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>新興</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -41031,81 +41031,81 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>65.90000000000001</v>
+        <v>35.2</v>
       </c>
       <c r="G234" t="n">
-        <v>65.66</v>
+        <v>35.06</v>
       </c>
       <c r="H234" t="n">
-        <v>65.41</v>
+        <v>35.75</v>
       </c>
       <c r="I234" t="n">
-        <v>64.23</v>
+        <v>35.94</v>
       </c>
       <c r="J234" t="n">
-        <v>8927272</v>
+        <v>6599525</v>
       </c>
       <c r="K234" t="n">
-        <v>4426453</v>
+        <v>5245835</v>
       </c>
       <c r="L234" t="n">
-        <v>66.65000000000001</v>
+        <v>38.15</v>
       </c>
       <c r="M234" t="n">
-        <v>62.55</v>
+        <v>33.85</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O234" t="n">
-        <v>-4078313</v>
+        <v>3523887</v>
       </c>
       <c r="P234" t="n">
-        <v>-3103896</v>
+        <v>824425</v>
       </c>
       <c r="Q234" t="n">
-        <v>-2873786</v>
+        <v>-493363</v>
       </c>
       <c r="R234" t="n">
-        <v>27314117</v>
+        <v>-605926</v>
       </c>
       <c r="S234" t="n">
-        <v>-27642</v>
+        <v>3363402</v>
       </c>
       <c r="T234" t="n">
-        <v>-226106</v>
+        <v>61758</v>
       </c>
       <c r="U234" t="n">
-        <v>-458622</v>
+        <v>42286</v>
       </c>
       <c r="V234" t="n">
-        <v>3049542</v>
+        <v>723526</v>
       </c>
       <c r="W234" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="X234" t="n">
-        <v>130000</v>
+        <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>3447000</v>
+        <v>-10000</v>
       </c>
       <c r="AA234" t="n">
-        <v>-4180671</v>
+        <v>160485</v>
       </c>
       <c r="AB234" t="n">
-        <v>-3007790</v>
+        <v>762667</v>
       </c>
       <c r="AC234" t="n">
-        <v>-2645164</v>
+        <v>-535649</v>
       </c>
       <c r="AD234" t="n">
-        <v>20817575</v>
+        <v>-1319452</v>
       </c>
       <c r="AE234" t="n">
         <v>-4</v>
@@ -41114,16 +41114,16 @@
         <v>-4</v>
       </c>
       <c r="AG234" t="n">
-        <v>80</v>
+        <v>-5</v>
       </c>
       <c r="AH234" t="n">
-        <v>-80</v>
+        <v>-5</v>
       </c>
       <c r="AI234" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ234" t="n">
-        <v>52</v>
+        <v>-46</v>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
@@ -41131,16 +41131,16 @@
         </is>
       </c>
       <c r="AL234" t="n">
-        <v>-56</v>
+        <v>42</v>
       </c>
       <c r="AM234" t="n">
-        <v>-107.69</v>
+        <v>91.3</v>
       </c>
       <c r="AN234" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AO234" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
@@ -41164,17 +41164,17 @@
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、爆量、接近20日高點、爆量價未漲</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人賣超</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、多頭排列、爆量、接近20日高點、爆量價未漲、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、短線籌碼止穩、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -41703,17 +41703,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2231.TW</t>
+          <t>00713.TW</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>為升</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -41727,81 +41727,81 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>87.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G238" t="n">
-        <v>87.36</v>
+        <v>65.66</v>
       </c>
       <c r="H238" t="n">
-        <v>88.70999999999999</v>
+        <v>65.41</v>
       </c>
       <c r="I238" t="n">
-        <v>90.27</v>
+        <v>64.23</v>
       </c>
       <c r="J238" t="n">
-        <v>104380</v>
+        <v>8927272</v>
       </c>
       <c r="K238" t="n">
-        <v>151930</v>
+        <v>4426453</v>
       </c>
       <c r="L238" t="n">
-        <v>97.5</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="M238" t="n">
-        <v>86</v>
+        <v>62.55</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="O238" t="n">
-        <v>54840</v>
+        <v>-4078313</v>
       </c>
       <c r="P238" t="n">
-        <v>12964</v>
+        <v>-3103896</v>
       </c>
       <c r="Q238" t="n">
-        <v>-59036</v>
+        <v>-2873786</v>
       </c>
       <c r="R238" t="n">
-        <v>-36247</v>
+        <v>27314117</v>
       </c>
       <c r="S238" t="n">
-        <v>55000</v>
+        <v>-27642</v>
       </c>
       <c r="T238" t="n">
-        <v>12785</v>
+        <v>-226106</v>
       </c>
       <c r="U238" t="n">
-        <v>-56215</v>
+        <v>-458622</v>
       </c>
       <c r="V238" t="n">
-        <v>-6901</v>
+        <v>3049542</v>
       </c>
       <c r="W238" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="X238" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="Y238" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="Z238" t="n">
-        <v>0</v>
+        <v>3447000</v>
       </c>
       <c r="AA238" t="n">
-        <v>-160</v>
+        <v>-4180671</v>
       </c>
       <c r="AB238" t="n">
-        <v>179</v>
+        <v>-3007790</v>
       </c>
       <c r="AC238" t="n">
-        <v>-2821</v>
+        <v>-2645164</v>
       </c>
       <c r="AD238" t="n">
-        <v>-29346</v>
+        <v>20817575</v>
       </c>
       <c r="AE238" t="n">
         <v>-4</v>
@@ -41810,16 +41810,16 @@
         <v>-4</v>
       </c>
       <c r="AG238" t="n">
-        <v>-15</v>
+        <v>80</v>
       </c>
       <c r="AH238" t="n">
-        <v>5</v>
+        <v>-80</v>
       </c>
       <c r="AI238" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ238" t="n">
-        <v>-36</v>
+        <v>52</v>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
@@ -41827,25 +41827,25 @@
         </is>
       </c>
       <c r="AL238" t="n">
-        <v>32</v>
+        <v>-56</v>
       </c>
       <c r="AM238" t="n">
-        <v>88.89</v>
+        <v>-107.69</v>
       </c>
       <c r="AN238" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="AO238" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
@@ -41860,17 +41860,17 @@
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、爆量、接近20日高點、爆量價未漲</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人小幅賣超</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、多頭排列、爆量、接近20日高點、爆量價未漲、法人連續偏賣、中期買超轉短線賣壓、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -42051,12 +42051,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3030.TW</t>
+          <t>2231.TW</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>為升</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -42075,28 +42075,28 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>276.5</v>
+        <v>87.8</v>
       </c>
       <c r="G240" t="n">
-        <v>271.1</v>
+        <v>87.36</v>
       </c>
       <c r="H240" t="n">
-        <v>283.1</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="I240" t="n">
-        <v>290.07</v>
+        <v>90.27</v>
       </c>
       <c r="J240" t="n">
-        <v>1742887</v>
+        <v>104380</v>
       </c>
       <c r="K240" t="n">
-        <v>1555109</v>
+        <v>151930</v>
       </c>
       <c r="L240" t="n">
-        <v>322</v>
+        <v>97.5</v>
       </c>
       <c r="M240" t="n">
-        <v>259</v>
+        <v>86</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -42104,70 +42104,70 @@
         </is>
       </c>
       <c r="O240" t="n">
-        <v>385528</v>
+        <v>54840</v>
       </c>
       <c r="P240" t="n">
-        <v>-113963</v>
+        <v>12964</v>
       </c>
       <c r="Q240" t="n">
-        <v>-451841</v>
+        <v>-59036</v>
       </c>
       <c r="R240" t="n">
-        <v>-764432</v>
+        <v>-36247</v>
       </c>
       <c r="S240" t="n">
-        <v>299672</v>
+        <v>55000</v>
       </c>
       <c r="T240" t="n">
-        <v>-78421</v>
+        <v>12785</v>
       </c>
       <c r="U240" t="n">
-        <v>-381004</v>
+        <v>-56215</v>
       </c>
       <c r="V240" t="n">
-        <v>-597362</v>
+        <v>-6901</v>
       </c>
       <c r="W240" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X240" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>3940</v>
+        <v>0</v>
       </c>
       <c r="Z240" t="n">
-        <v>11940</v>
+        <v>0</v>
       </c>
       <c r="AA240" t="n">
-        <v>84856</v>
+        <v>-160</v>
       </c>
       <c r="AB240" t="n">
-        <v>-38542</v>
+        <v>179</v>
       </c>
       <c r="AC240" t="n">
-        <v>-74777</v>
+        <v>-2821</v>
       </c>
       <c r="AD240" t="n">
-        <v>-179010</v>
+        <v>-29346</v>
       </c>
       <c r="AE240" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AF240" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="AG240" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AH240" t="n">
         <v>5</v>
       </c>
-      <c r="AH240" t="n">
-        <v>-20</v>
-      </c>
       <c r="AI240" t="n">
         <v>0</v>
       </c>
       <c r="AJ240" t="n">
-        <v>-44</v>
+        <v>-36</v>
       </c>
       <c r="AK240" t="inlineStr">
         <is>
@@ -42175,10 +42175,10 @@
         </is>
       </c>
       <c r="AL240" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM240" t="n">
-        <v>86.36</v>
+        <v>88.89</v>
       </c>
       <c r="AN240" t="n">
         <v>35</v>
@@ -42208,17 +42208,17 @@
       </c>
       <c r="AT240" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>5日法人賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人小幅賣超</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -42399,12 +42399,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1810.TW</t>
+          <t>3030.TW</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>和成</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -42423,28 +42423,28 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>22.25</v>
+        <v>276.5</v>
       </c>
       <c r="G242" t="n">
-        <v>22.56</v>
+        <v>271.1</v>
       </c>
       <c r="H242" t="n">
-        <v>22.9</v>
+        <v>283.1</v>
       </c>
       <c r="I242" t="n">
-        <v>23.32</v>
+        <v>290.07</v>
       </c>
       <c r="J242" t="n">
-        <v>1140170</v>
+        <v>1742887</v>
       </c>
       <c r="K242" t="n">
-        <v>1096596</v>
+        <v>1555109</v>
       </c>
       <c r="L242" t="n">
-        <v>24.6</v>
+        <v>322</v>
       </c>
       <c r="M242" t="n">
-        <v>22</v>
+        <v>259</v>
       </c>
       <c r="N242" t="inlineStr">
         <is>
@@ -42452,52 +42452,52 @@
         </is>
       </c>
       <c r="O242" t="n">
-        <v>-151310</v>
+        <v>385528</v>
       </c>
       <c r="P242" t="n">
-        <v>747714</v>
+        <v>-113963</v>
       </c>
       <c r="Q242" t="n">
-        <v>1046662</v>
+        <v>-451841</v>
       </c>
       <c r="R242" t="n">
-        <v>1933958</v>
+        <v>-764432</v>
       </c>
       <c r="S242" t="n">
-        <v>-154310</v>
+        <v>299672</v>
       </c>
       <c r="T242" t="n">
-        <v>742716</v>
+        <v>-78421</v>
       </c>
       <c r="U242" t="n">
-        <v>1047662</v>
+        <v>-381004</v>
       </c>
       <c r="V242" t="n">
-        <v>1969661</v>
+        <v>-597362</v>
       </c>
       <c r="W242" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X242" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="Y242" t="n">
-        <v>0</v>
+        <v>3940</v>
       </c>
       <c r="Z242" t="n">
-        <v>0</v>
+        <v>11940</v>
       </c>
       <c r="AA242" t="n">
-        <v>3000</v>
+        <v>84856</v>
       </c>
       <c r="AB242" t="n">
-        <v>4998</v>
+        <v>-38542</v>
       </c>
       <c r="AC242" t="n">
-        <v>-1000</v>
+        <v>-74777</v>
       </c>
       <c r="AD242" t="n">
-        <v>-35703</v>
+        <v>-179010</v>
       </c>
       <c r="AE242" t="n">
         <v>-6</v>
@@ -42506,16 +42506,16 @@
         <v>-6</v>
       </c>
       <c r="AG242" t="n">
-        <v>-45</v>
+        <v>5</v>
       </c>
       <c r="AH242" t="n">
-        <v>30</v>
+        <v>-20</v>
       </c>
       <c r="AI242" t="n">
         <v>0</v>
       </c>
       <c r="AJ242" t="n">
-        <v>2</v>
+        <v>-44</v>
       </c>
       <c r="AK242" t="inlineStr">
         <is>
@@ -42523,25 +42523,25 @@
         </is>
       </c>
       <c r="AL242" t="n">
-        <v>-8</v>
+        <v>38</v>
       </c>
       <c r="AM242" t="n">
-        <v>-400</v>
+        <v>86.36</v>
       </c>
       <c r="AN242" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AO242" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
@@ -42556,17 +42556,17 @@
       </c>
       <c r="AT242" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>5日法人明顯買超</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -42747,12 +42747,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>5439.TWO</t>
+          <t>2634.TW</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>漢翔</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -42771,28 +42771,28 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>220.5</v>
+        <v>60.9</v>
       </c>
       <c r="G244" t="n">
-        <v>219.8</v>
+        <v>61.06</v>
       </c>
       <c r="H244" t="n">
-        <v>227.4</v>
+        <v>61.28</v>
       </c>
       <c r="I244" t="n">
-        <v>242.03</v>
+        <v>62.57</v>
       </c>
       <c r="J244" t="n">
-        <v>569000</v>
+        <v>4948586</v>
       </c>
       <c r="K244" t="n">
-        <v>1001600</v>
+        <v>3994478</v>
       </c>
       <c r="L244" t="n">
-        <v>270</v>
+        <v>67</v>
       </c>
       <c r="M244" t="n">
-        <v>212</v>
+        <v>60.1</v>
       </c>
       <c r="N244" t="inlineStr">
         <is>
@@ -42800,52 +42800,52 @@
         </is>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
+        <v>-1273743</v>
       </c>
       <c r="P244" t="n">
-        <v>0</v>
+        <v>905177</v>
       </c>
       <c r="Q244" t="n">
-        <v>0</v>
+        <v>3187532</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>4982183</v>
       </c>
       <c r="S244" t="n">
-        <v>0</v>
+        <v>-1229445</v>
       </c>
       <c r="T244" t="n">
-        <v>0</v>
+        <v>1623983</v>
       </c>
       <c r="U244" t="n">
-        <v>0</v>
+        <v>4314024</v>
       </c>
       <c r="V244" t="n">
-        <v>0</v>
+        <v>6977412</v>
       </c>
       <c r="W244" t="n">
         <v>0</v>
       </c>
       <c r="X244" t="n">
-        <v>0</v>
+        <v>-642000</v>
       </c>
       <c r="Y244" t="n">
-        <v>0</v>
+        <v>-1261305</v>
       </c>
       <c r="Z244" t="n">
-        <v>0</v>
+        <v>-1603305</v>
       </c>
       <c r="AA244" t="n">
-        <v>0</v>
+        <v>-44298</v>
       </c>
       <c r="AB244" t="n">
-        <v>0</v>
+        <v>-76806</v>
       </c>
       <c r="AC244" t="n">
-        <v>0</v>
+        <v>134813</v>
       </c>
       <c r="AD244" t="n">
-        <v>0</v>
+        <v>-391924</v>
       </c>
       <c r="AE244" t="n">
         <v>-6</v>
@@ -42854,16 +42854,16 @@
         <v>-6</v>
       </c>
       <c r="AG244" t="n">
-        <v>-15</v>
+        <v>-45</v>
       </c>
       <c r="AH244" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI244" t="n">
         <v>0</v>
       </c>
       <c r="AJ244" t="n">
-        <v>-18</v>
+        <v>18</v>
       </c>
       <c r="AK244" t="inlineStr">
         <is>
@@ -42871,25 +42871,25 @@
         </is>
       </c>
       <c r="AL244" t="n">
-        <v>12</v>
+        <v>-24</v>
       </c>
       <c r="AM244" t="n">
-        <v>66.67</v>
+        <v>-133.33</v>
       </c>
       <c r="AN244" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AO244" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
@@ -42904,29 +42904,29 @@
       </c>
       <c r="AT244" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3026.TW</t>
+          <t>5439.TWO</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -42945,28 +42945,28 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>751</v>
+        <v>220.5</v>
       </c>
       <c r="G245" t="n">
-        <v>764.4</v>
+        <v>219.8</v>
       </c>
       <c r="H245" t="n">
-        <v>783.4</v>
+        <v>227.4</v>
       </c>
       <c r="I245" t="n">
-        <v>804.35</v>
+        <v>242.03</v>
       </c>
       <c r="J245" t="n">
-        <v>5848294</v>
+        <v>569000</v>
       </c>
       <c r="K245" t="n">
-        <v>11771960</v>
+        <v>1001600</v>
       </c>
       <c r="L245" t="n">
-        <v>888</v>
+        <v>270</v>
       </c>
       <c r="M245" t="n">
-        <v>704</v>
+        <v>212</v>
       </c>
       <c r="N245" t="inlineStr">
         <is>
@@ -42974,52 +42974,52 @@
         </is>
       </c>
       <c r="O245" t="n">
-        <v>964256</v>
+        <v>0</v>
       </c>
       <c r="P245" t="n">
-        <v>-302675</v>
+        <v>0</v>
       </c>
       <c r="Q245" t="n">
-        <v>1492128</v>
+        <v>0</v>
       </c>
       <c r="R245" t="n">
-        <v>-67303</v>
+        <v>0</v>
       </c>
       <c r="S245" t="n">
-        <v>968131</v>
+        <v>0</v>
       </c>
       <c r="T245" t="n">
-        <v>402508</v>
+        <v>0</v>
       </c>
       <c r="U245" t="n">
-        <v>1918205</v>
+        <v>0</v>
       </c>
       <c r="V245" t="n">
-        <v>-217330</v>
+        <v>0</v>
       </c>
       <c r="W245" t="n">
         <v>0</v>
       </c>
       <c r="X245" t="n">
-        <v>-568000</v>
+        <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>-399991</v>
+        <v>0</v>
       </c>
       <c r="Z245" t="n">
-        <v>694009</v>
+        <v>0</v>
       </c>
       <c r="AA245" t="n">
-        <v>-3875</v>
+        <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>-137183</v>
+        <v>0</v>
       </c>
       <c r="AC245" t="n">
-        <v>-26086</v>
+        <v>0</v>
       </c>
       <c r="AD245" t="n">
-        <v>-543982</v>
+        <v>0</v>
       </c>
       <c r="AE245" t="n">
         <v>-6</v>
@@ -43028,16 +43028,16 @@
         <v>-6</v>
       </c>
       <c r="AG245" t="n">
-        <v>-45</v>
+        <v>-15</v>
       </c>
       <c r="AH245" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI245" t="n">
         <v>0</v>
       </c>
       <c r="AJ245" t="n">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
@@ -43045,25 +43045,25 @@
         </is>
       </c>
       <c r="AL245" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AM245" t="n">
-        <v>40</v>
+        <v>66.67</v>
       </c>
       <c r="AN245" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="AO245" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
@@ -43078,29 +43078,29 @@
       </c>
       <c r="AT245" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2439.TW</t>
+          <t>1810.TW</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>和成</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -43119,28 +43119,28 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>80.40000000000001</v>
+        <v>22.25</v>
       </c>
       <c r="G246" t="n">
-        <v>80</v>
+        <v>22.56</v>
       </c>
       <c r="H246" t="n">
-        <v>80.48</v>
+        <v>22.9</v>
       </c>
       <c r="I246" t="n">
-        <v>79.06999999999999</v>
+        <v>23.32</v>
       </c>
       <c r="J246" t="n">
-        <v>1018175</v>
+        <v>1140170</v>
       </c>
       <c r="K246" t="n">
-        <v>1722348</v>
+        <v>1096596</v>
       </c>
       <c r="L246" t="n">
-        <v>82.40000000000001</v>
+        <v>24.6</v>
       </c>
       <c r="M246" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="N246" t="inlineStr">
         <is>
@@ -43148,52 +43148,52 @@
         </is>
       </c>
       <c r="O246" t="n">
-        <v>366032</v>
+        <v>-151310</v>
       </c>
       <c r="P246" t="n">
-        <v>-824947</v>
+        <v>747714</v>
       </c>
       <c r="Q246" t="n">
-        <v>-55677</v>
+        <v>1046662</v>
       </c>
       <c r="R246" t="n">
-        <v>1051825</v>
+        <v>1933958</v>
       </c>
       <c r="S246" t="n">
-        <v>328165</v>
+        <v>-154310</v>
       </c>
       <c r="T246" t="n">
-        <v>-854857</v>
+        <v>742716</v>
       </c>
       <c r="U246" t="n">
-        <v>-203751</v>
+        <v>1047662</v>
       </c>
       <c r="V246" t="n">
-        <v>1059762</v>
+        <v>1969661</v>
       </c>
       <c r="W246" t="n">
-        <v>11444</v>
+        <v>0</v>
       </c>
       <c r="X246" t="n">
-        <v>20444</v>
+        <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>276444</v>
+        <v>0</v>
       </c>
       <c r="Z246" t="n">
-        <v>339299</v>
+        <v>0</v>
       </c>
       <c r="AA246" t="n">
-        <v>26423</v>
+        <v>3000</v>
       </c>
       <c r="AB246" t="n">
-        <v>9466</v>
+        <v>4998</v>
       </c>
       <c r="AC246" t="n">
-        <v>-128370</v>
+        <v>-1000</v>
       </c>
       <c r="AD246" t="n">
-        <v>-347236</v>
+        <v>-35703</v>
       </c>
       <c r="AE246" t="n">
         <v>-6</v>
@@ -43202,16 +43202,16 @@
         <v>-6</v>
       </c>
       <c r="AG246" t="n">
-        <v>20</v>
+        <v>-45</v>
       </c>
       <c r="AH246" t="n">
-        <v>-35</v>
+        <v>30</v>
       </c>
       <c r="AI246" t="n">
         <v>0</v>
       </c>
       <c r="AJ246" t="n">
-        <v>-34</v>
+        <v>2</v>
       </c>
       <c r="AK246" t="inlineStr">
         <is>
@@ -43219,25 +43219,25 @@
         </is>
       </c>
       <c r="AL246" t="n">
-        <v>28</v>
+        <v>-8</v>
       </c>
       <c r="AM246" t="n">
-        <v>82.34999999999999</v>
+        <v>-400</v>
       </c>
       <c r="AN246" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AO246" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
@@ -43252,17 +43252,17 @@
       </c>
       <c r="AT246" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人小幅賣超、投信買外資賣</t>
+          <t>5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、中期買超轉短線賣壓、5日法人小幅賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -43443,12 +43443,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2606.TW</t>
+          <t>2439.TW</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -43467,28 +43467,28 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>73.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G248" t="n">
-        <v>72.94</v>
+        <v>80</v>
       </c>
       <c r="H248" t="n">
-        <v>74.48</v>
+        <v>80.48</v>
       </c>
       <c r="I248" t="n">
-        <v>74.70999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="J248" t="n">
-        <v>1046551</v>
+        <v>1018175</v>
       </c>
       <c r="K248" t="n">
-        <v>2242890</v>
+        <v>1722348</v>
       </c>
       <c r="L248" t="n">
-        <v>79.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="M248" t="n">
-        <v>71.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="N248" t="inlineStr">
         <is>
@@ -43496,52 +43496,52 @@
         </is>
       </c>
       <c r="O248" t="n">
-        <v>385535</v>
+        <v>366032</v>
       </c>
       <c r="P248" t="n">
-        <v>500523</v>
+        <v>-824947</v>
       </c>
       <c r="Q248" t="n">
-        <v>-39867</v>
+        <v>-55677</v>
       </c>
       <c r="R248" t="n">
-        <v>1164314</v>
+        <v>1051825</v>
       </c>
       <c r="S248" t="n">
-        <v>367176</v>
+        <v>328165</v>
       </c>
       <c r="T248" t="n">
-        <v>788625</v>
+        <v>-854857</v>
       </c>
       <c r="U248" t="n">
-        <v>966170</v>
+        <v>-203751</v>
       </c>
       <c r="V248" t="n">
-        <v>2128277</v>
+        <v>1059762</v>
       </c>
       <c r="W248" t="n">
-        <v>5000</v>
+        <v>11444</v>
       </c>
       <c r="X248" t="n">
-        <v>-283000</v>
+        <v>20444</v>
       </c>
       <c r="Y248" t="n">
-        <v>-438243</v>
+        <v>276444</v>
       </c>
       <c r="Z248" t="n">
-        <v>-29243</v>
+        <v>339299</v>
       </c>
       <c r="AA248" t="n">
-        <v>13359</v>
+        <v>26423</v>
       </c>
       <c r="AB248" t="n">
-        <v>-5102</v>
+        <v>9466</v>
       </c>
       <c r="AC248" t="n">
-        <v>-567794</v>
+        <v>-128370</v>
       </c>
       <c r="AD248" t="n">
-        <v>-934720</v>
+        <v>-347236</v>
       </c>
       <c r="AE248" t="n">
         <v>-6</v>
@@ -43550,16 +43550,16 @@
         <v>-6</v>
       </c>
       <c r="AG248" t="n">
-        <v>-15</v>
+        <v>20</v>
       </c>
       <c r="AH248" t="n">
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="AI248" t="n">
         <v>0</v>
       </c>
       <c r="AJ248" t="n">
-        <v>-40</v>
+        <v>-34</v>
       </c>
       <c r="AK248" t="inlineStr">
         <is>
@@ -43567,25 +43567,25 @@
         </is>
       </c>
       <c r="AL248" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AM248" t="n">
-        <v>85</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="AN248" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AO248" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
@@ -43600,29 +43600,29 @@
       </c>
       <c r="AT248" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>籌碼中性、外資買投信賣</t>
+          <t>中期買超轉短線賣壓、5日法人小幅賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、中期買超轉短線賣壓、5日法人小幅賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2634.TW</t>
+          <t>2606.TW</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>漢翔</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -43641,28 +43641,28 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>60.9</v>
+        <v>73.5</v>
       </c>
       <c r="G249" t="n">
-        <v>61.06</v>
+        <v>72.94</v>
       </c>
       <c r="H249" t="n">
-        <v>61.28</v>
+        <v>74.48</v>
       </c>
       <c r="I249" t="n">
-        <v>62.57</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="J249" t="n">
-        <v>4948586</v>
+        <v>1046551</v>
       </c>
       <c r="K249" t="n">
-        <v>3994478</v>
+        <v>2242890</v>
       </c>
       <c r="L249" t="n">
-        <v>67</v>
+        <v>79.3</v>
       </c>
       <c r="M249" t="n">
-        <v>60.1</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="N249" t="inlineStr">
         <is>
@@ -43670,52 +43670,52 @@
         </is>
       </c>
       <c r="O249" t="n">
-        <v>-1273743</v>
+        <v>385535</v>
       </c>
       <c r="P249" t="n">
-        <v>905177</v>
+        <v>500523</v>
       </c>
       <c r="Q249" t="n">
-        <v>3187532</v>
+        <v>-39867</v>
       </c>
       <c r="R249" t="n">
-        <v>4982183</v>
+        <v>1164314</v>
       </c>
       <c r="S249" t="n">
-        <v>-1229445</v>
+        <v>367176</v>
       </c>
       <c r="T249" t="n">
-        <v>1623983</v>
+        <v>788625</v>
       </c>
       <c r="U249" t="n">
-        <v>4314024</v>
+        <v>966170</v>
       </c>
       <c r="V249" t="n">
-        <v>6977412</v>
+        <v>2128277</v>
       </c>
       <c r="W249" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="X249" t="n">
-        <v>-642000</v>
+        <v>-283000</v>
       </c>
       <c r="Y249" t="n">
-        <v>-1261305</v>
+        <v>-438243</v>
       </c>
       <c r="Z249" t="n">
-        <v>-1603305</v>
+        <v>-29243</v>
       </c>
       <c r="AA249" t="n">
-        <v>-44298</v>
+        <v>13359</v>
       </c>
       <c r="AB249" t="n">
-        <v>-76806</v>
+        <v>-5102</v>
       </c>
       <c r="AC249" t="n">
-        <v>134813</v>
+        <v>-567794</v>
       </c>
       <c r="AD249" t="n">
-        <v>-391924</v>
+        <v>-934720</v>
       </c>
       <c r="AE249" t="n">
         <v>-6</v>
@@ -43724,16 +43724,16 @@
         <v>-6</v>
       </c>
       <c r="AG249" t="n">
-        <v>-45</v>
+        <v>-15</v>
       </c>
       <c r="AH249" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI249" t="n">
         <v>0</v>
       </c>
       <c r="AJ249" t="n">
-        <v>18</v>
+        <v>-40</v>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
@@ -43741,25 +43741,25 @@
         </is>
       </c>
       <c r="AL249" t="n">
-        <v>-24</v>
+        <v>34</v>
       </c>
       <c r="AM249" t="n">
-        <v>-133.33</v>
+        <v>85</v>
       </c>
       <c r="AN249" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AO249" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
@@ -43774,17 +43774,17 @@
       </c>
       <c r="AT249" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>籌碼中性、外資買投信賣</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、籌碼中性、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -44139,17 +44139,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>00692.TW</t>
+          <t>3026.TW</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>富邦公司治理</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -44163,28 +44163,28 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>94.09999999999999</v>
+        <v>751</v>
       </c>
       <c r="G252" t="n">
-        <v>93.05</v>
+        <v>764.4</v>
       </c>
       <c r="H252" t="n">
-        <v>94.19</v>
+        <v>783.4</v>
       </c>
       <c r="I252" t="n">
-        <v>96.16</v>
+        <v>804.35</v>
       </c>
       <c r="J252" t="n">
-        <v>414591</v>
+        <v>5848294</v>
       </c>
       <c r="K252" t="n">
-        <v>758596</v>
+        <v>11771960</v>
       </c>
       <c r="L252" t="n">
-        <v>100.1</v>
+        <v>888</v>
       </c>
       <c r="M252" t="n">
-        <v>91.95</v>
+        <v>704</v>
       </c>
       <c r="N252" t="inlineStr">
         <is>
@@ -44192,70 +44192,70 @@
         </is>
       </c>
       <c r="O252" t="n">
-        <v>228927</v>
+        <v>964256</v>
       </c>
       <c r="P252" t="n">
-        <v>85227</v>
+        <v>-302675</v>
       </c>
       <c r="Q252" t="n">
-        <v>-142376</v>
+        <v>1492128</v>
       </c>
       <c r="R252" t="n">
-        <v>-1566136</v>
+        <v>-67303</v>
       </c>
       <c r="S252" t="n">
-        <v>20000</v>
+        <v>968131</v>
       </c>
       <c r="T252" t="n">
-        <v>-91000</v>
+        <v>402508</v>
       </c>
       <c r="U252" t="n">
-        <v>-230776</v>
+        <v>1918205</v>
       </c>
       <c r="V252" t="n">
-        <v>-998060</v>
+        <v>-217330</v>
       </c>
       <c r="W252" t="n">
         <v>0</v>
       </c>
       <c r="X252" t="n">
-        <v>0</v>
+        <v>-568000</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>-399991</v>
       </c>
       <c r="Z252" t="n">
-        <v>0</v>
+        <v>694009</v>
       </c>
       <c r="AA252" t="n">
-        <v>208927</v>
+        <v>-3875</v>
       </c>
       <c r="AB252" t="n">
-        <v>176227</v>
+        <v>-137183</v>
       </c>
       <c r="AC252" t="n">
-        <v>88400</v>
+        <v>-26086</v>
       </c>
       <c r="AD252" t="n">
-        <v>-568076</v>
+        <v>-543982</v>
       </c>
       <c r="AE252" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AF252" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="AG252" t="n">
-        <v>-15</v>
+        <v>-45</v>
       </c>
       <c r="AH252" t="n">
-        <v>-5</v>
+        <v>30</v>
       </c>
       <c r="AI252" t="n">
         <v>0</v>
       </c>
       <c r="AJ252" t="n">
-        <v>-34</v>
+        <v>-10</v>
       </c>
       <c r="AK252" t="inlineStr">
         <is>
@@ -44263,25 +44263,25 @@
         </is>
       </c>
       <c r="AL252" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AM252" t="n">
-        <v>76.47</v>
+        <v>40</v>
       </c>
       <c r="AN252" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="AO252" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
@@ -44296,17 +44296,17 @@
       </c>
       <c r="AT252" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、5日法人明顯買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -44825,17 +44825,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2607.TW</t>
+          <t>00692.TW</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>榮運</t>
+          <t>富邦公司治理</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -44849,28 +44849,28 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>56.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G256" t="n">
-        <v>56.12</v>
+        <v>93.05</v>
       </c>
       <c r="H256" t="n">
-        <v>57.16</v>
+        <v>94.19</v>
       </c>
       <c r="I256" t="n">
-        <v>55.79</v>
+        <v>96.16</v>
       </c>
       <c r="J256" t="n">
-        <v>461332</v>
+        <v>414591</v>
       </c>
       <c r="K256" t="n">
-        <v>1154408</v>
+        <v>758596</v>
       </c>
       <c r="L256" t="n">
-        <v>59.8</v>
+        <v>100.1</v>
       </c>
       <c r="M256" t="n">
-        <v>53</v>
+        <v>91.95</v>
       </c>
       <c r="N256" t="inlineStr">
         <is>
@@ -44878,28 +44878,28 @@
         </is>
       </c>
       <c r="O256" t="n">
-        <v>89168</v>
+        <v>228927</v>
       </c>
       <c r="P256" t="n">
-        <v>129485</v>
+        <v>85227</v>
       </c>
       <c r="Q256" t="n">
-        <v>-144266</v>
+        <v>-142376</v>
       </c>
       <c r="R256" t="n">
-        <v>2292022</v>
+        <v>-1566136</v>
       </c>
       <c r="S256" t="n">
-        <v>66168</v>
+        <v>20000</v>
       </c>
       <c r="T256" t="n">
-        <v>128359</v>
+        <v>-91000</v>
       </c>
       <c r="U256" t="n">
-        <v>-133517</v>
+        <v>-230776</v>
       </c>
       <c r="V256" t="n">
-        <v>2204446</v>
+        <v>-998060</v>
       </c>
       <c r="W256" t="n">
         <v>0</v>
@@ -44908,22 +44908,22 @@
         <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>-122</v>
+        <v>0</v>
       </c>
       <c r="Z256" t="n">
-        <v>-122</v>
+        <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>23000</v>
+        <v>208927</v>
       </c>
       <c r="AB256" t="n">
-        <v>1126</v>
+        <v>176227</v>
       </c>
       <c r="AC256" t="n">
-        <v>-10627</v>
+        <v>88400</v>
       </c>
       <c r="AD256" t="n">
-        <v>87698</v>
+        <v>-568076</v>
       </c>
       <c r="AE256" t="n">
         <v>-8</v>
@@ -44932,16 +44932,16 @@
         <v>-8</v>
       </c>
       <c r="AG256" t="n">
-        <v>20</v>
+        <v>-15</v>
       </c>
       <c r="AH256" t="n">
-        <v>-40</v>
+        <v>-5</v>
       </c>
       <c r="AI256" t="n">
         <v>0</v>
       </c>
       <c r="AJ256" t="n">
-        <v>-20</v>
+        <v>-34</v>
       </c>
       <c r="AK256" t="inlineStr">
         <is>
@@ -44949,25 +44949,25 @@
         </is>
       </c>
       <c r="AL256" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AM256" t="n">
-        <v>60</v>
+        <v>76.47</v>
       </c>
       <c r="AN256" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AO256" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR256" t="inlineStr">
@@ -44982,29 +44982,29 @@
       </c>
       <c r="AT256" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>5日法人賣超、外資投信同步賣超</t>
+          <t>短線籌碼止穩、5日法人賣超</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、短線籌碼止穩、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2449.TW</t>
+          <t>2607.TW</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>榮運</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -45023,28 +45023,28 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>277.5</v>
+        <v>56.8</v>
       </c>
       <c r="G257" t="n">
-        <v>269.3</v>
+        <v>56.12</v>
       </c>
       <c r="H257" t="n">
-        <v>275.85</v>
+        <v>57.16</v>
       </c>
       <c r="I257" t="n">
-        <v>287.3</v>
+        <v>55.79</v>
       </c>
       <c r="J257" t="n">
-        <v>12721709</v>
+        <v>461332</v>
       </c>
       <c r="K257" t="n">
-        <v>22055634</v>
+        <v>1154408</v>
       </c>
       <c r="L257" t="n">
-        <v>315.5</v>
+        <v>59.8</v>
       </c>
       <c r="M257" t="n">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="N257" t="inlineStr">
         <is>
@@ -45052,96 +45052,96 @@
         </is>
       </c>
       <c r="O257" t="n">
-        <v>1489420</v>
+        <v>89168</v>
       </c>
       <c r="P257" t="n">
-        <v>-4360014</v>
+        <v>129485</v>
       </c>
       <c r="Q257" t="n">
-        <v>-323942</v>
+        <v>-144266</v>
       </c>
       <c r="R257" t="n">
-        <v>-50783106</v>
+        <v>2292022</v>
       </c>
       <c r="S257" t="n">
-        <v>1562498</v>
+        <v>66168</v>
       </c>
       <c r="T257" t="n">
-        <v>-4487057</v>
+        <v>128359</v>
       </c>
       <c r="U257" t="n">
-        <v>-5750104</v>
+        <v>-133517</v>
       </c>
       <c r="V257" t="n">
-        <v>-53749679</v>
+        <v>2204446</v>
       </c>
       <c r="W257" t="n">
-        <v>272401</v>
+        <v>0</v>
       </c>
       <c r="X257" t="n">
-        <v>1146901</v>
+        <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>4799596</v>
+        <v>-122</v>
       </c>
       <c r="Z257" t="n">
-        <v>5703230</v>
+        <v>-122</v>
       </c>
       <c r="AA257" t="n">
-        <v>-345479</v>
+        <v>23000</v>
       </c>
       <c r="AB257" t="n">
-        <v>-1019858</v>
+        <v>1126</v>
       </c>
       <c r="AC257" t="n">
-        <v>626566</v>
+        <v>-10627</v>
       </c>
       <c r="AD257" t="n">
-        <v>-2736657</v>
+        <v>87698</v>
       </c>
       <c r="AE257" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AF257" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="AG257" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="AH257" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ257" t="n">
         <v>-20</v>
       </c>
-      <c r="AI257" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ257" t="n">
-        <v>-10</v>
-      </c>
       <c r="AK257" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
       <c r="AL257" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AM257" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN257" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AO257" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR257" t="inlineStr">
@@ -45156,29 +45156,29 @@
       </c>
       <c r="AT257" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>5日法人賣超、投信買外資賣</t>
+          <t>5日法人賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2516.TW</t>
+          <t>2645.TW</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>新建</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -45197,28 +45197,28 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>15.55</v>
+        <v>167.5</v>
       </c>
       <c r="G258" t="n">
-        <v>15.4</v>
+        <v>169.1</v>
       </c>
       <c r="H258" t="n">
-        <v>15.4</v>
+        <v>170.05</v>
       </c>
       <c r="I258" t="n">
-        <v>15.23</v>
+        <v>171.28</v>
       </c>
       <c r="J258" t="n">
-        <v>411517</v>
+        <v>933094</v>
       </c>
       <c r="K258" t="n">
-        <v>850036</v>
+        <v>680904</v>
       </c>
       <c r="L258" t="n">
-        <v>15.8</v>
+        <v>176.5</v>
       </c>
       <c r="M258" t="n">
-        <v>14.5</v>
+        <v>166.5</v>
       </c>
       <c r="N258" t="inlineStr">
         <is>
@@ -45226,52 +45226,52 @@
         </is>
       </c>
       <c r="O258" t="n">
-        <v>-1031</v>
+        <v>-506768</v>
       </c>
       <c r="P258" t="n">
-        <v>-5005</v>
+        <v>-90507</v>
       </c>
       <c r="Q258" t="n">
-        <v>-51911</v>
+        <v>275804</v>
       </c>
       <c r="R258" t="n">
-        <v>20506</v>
+        <v>488208</v>
       </c>
       <c r="S258" t="n">
-        <v>-1031</v>
+        <v>-491070</v>
       </c>
       <c r="T258" t="n">
-        <v>-2005</v>
+        <v>-26176</v>
       </c>
       <c r="U258" t="n">
-        <v>-48911</v>
+        <v>366519</v>
       </c>
       <c r="V258" t="n">
-        <v>18506</v>
+        <v>307390</v>
       </c>
       <c r="W258" t="n">
         <v>0</v>
       </c>
       <c r="X258" t="n">
-        <v>0</v>
+        <v>-63000</v>
       </c>
       <c r="Y258" t="n">
-        <v>0</v>
+        <v>-166136</v>
       </c>
       <c r="Z258" t="n">
-        <v>0</v>
+        <v>-215136</v>
       </c>
       <c r="AA258" t="n">
-        <v>0</v>
+        <v>-15698</v>
       </c>
       <c r="AB258" t="n">
-        <v>-3000</v>
+        <v>-1331</v>
       </c>
       <c r="AC258" t="n">
-        <v>-3000</v>
+        <v>75421</v>
       </c>
       <c r="AD258" t="n">
-        <v>2000</v>
+        <v>395954</v>
       </c>
       <c r="AE258" t="n">
         <v>-10</v>
@@ -45280,16 +45280,16 @@
         <v>-10</v>
       </c>
       <c r="AG258" t="n">
-        <v>35</v>
+        <v>-45</v>
       </c>
       <c r="AH258" t="n">
-        <v>-60</v>
+        <v>20</v>
       </c>
       <c r="AI258" t="n">
         <v>0</v>
       </c>
       <c r="AJ258" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AK258" t="inlineStr">
         <is>
@@ -45297,25 +45297,25 @@
         </is>
       </c>
       <c r="AL258" t="n">
-        <v>-28</v>
+        <v>-12</v>
       </c>
       <c r="AM258" t="n">
-        <v>-155.56</v>
+        <v>-600</v>
       </c>
       <c r="AN258" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AO258" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR258" t="inlineStr">
@@ -45330,29 +45330,29 @@
       </c>
       <c r="AT258" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日高點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人小幅賣超</t>
+          <t>5日法人買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、接近20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2645.TW</t>
+          <t>4958.TW</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -45371,28 +45371,28 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>167.5</v>
+        <v>550</v>
       </c>
       <c r="G259" t="n">
-        <v>169.1</v>
+        <v>552.4</v>
       </c>
       <c r="H259" t="n">
-        <v>170.05</v>
+        <v>550.4</v>
       </c>
       <c r="I259" t="n">
-        <v>171.28</v>
+        <v>548.7</v>
       </c>
       <c r="J259" t="n">
-        <v>933094</v>
+        <v>19865905</v>
       </c>
       <c r="K259" t="n">
-        <v>680904</v>
+        <v>35072026</v>
       </c>
       <c r="L259" t="n">
-        <v>176.5</v>
+        <v>614</v>
       </c>
       <c r="M259" t="n">
-        <v>166.5</v>
+        <v>472</v>
       </c>
       <c r="N259" t="inlineStr">
         <is>
@@ -45400,52 +45400,52 @@
         </is>
       </c>
       <c r="O259" t="n">
-        <v>-506768</v>
+        <v>681666</v>
       </c>
       <c r="P259" t="n">
-        <v>-90507</v>
+        <v>-10459808</v>
       </c>
       <c r="Q259" t="n">
-        <v>275804</v>
+        <v>-10706616</v>
       </c>
       <c r="R259" t="n">
-        <v>488208</v>
+        <v>-13950843</v>
       </c>
       <c r="S259" t="n">
-        <v>-491070</v>
+        <v>-55345</v>
       </c>
       <c r="T259" t="n">
-        <v>-26176</v>
+        <v>-11932213</v>
       </c>
       <c r="U259" t="n">
-        <v>366519</v>
+        <v>-14114478</v>
       </c>
       <c r="V259" t="n">
-        <v>307390</v>
+        <v>-21533905</v>
       </c>
       <c r="W259" t="n">
-        <v>0</v>
+        <v>296574</v>
       </c>
       <c r="X259" t="n">
-        <v>-63000</v>
+        <v>1336651</v>
       </c>
       <c r="Y259" t="n">
-        <v>-166136</v>
+        <v>2953941</v>
       </c>
       <c r="Z259" t="n">
-        <v>-215136</v>
+        <v>7527928</v>
       </c>
       <c r="AA259" t="n">
-        <v>-15698</v>
+        <v>440437</v>
       </c>
       <c r="AB259" t="n">
-        <v>-1331</v>
+        <v>135754</v>
       </c>
       <c r="AC259" t="n">
-        <v>75421</v>
+        <v>453921</v>
       </c>
       <c r="AD259" t="n">
-        <v>395954</v>
+        <v>55134</v>
       </c>
       <c r="AE259" t="n">
         <v>-10</v>
@@ -45454,16 +45454,16 @@
         <v>-10</v>
       </c>
       <c r="AG259" t="n">
-        <v>-45</v>
+        <v>5</v>
       </c>
       <c r="AH259" t="n">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="AI259" t="n">
         <v>0</v>
       </c>
       <c r="AJ259" t="n">
-        <v>2</v>
+        <v>-26</v>
       </c>
       <c r="AK259" t="inlineStr">
         <is>
@@ -45471,25 +45471,25 @@
         </is>
       </c>
       <c r="AL259" t="n">
-        <v>-12</v>
+        <v>16</v>
       </c>
       <c r="AM259" t="n">
-        <v>-600</v>
+        <v>61.54</v>
       </c>
       <c r="AN259" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AO259" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR259" t="inlineStr">
@@ -45504,17 +45504,17 @@
       </c>
       <c r="AT259" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>5日法人買超、外資買投信賣</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、5日法人買超、外資買投信賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -45695,12 +45695,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>4958.TW</t>
+          <t>2449.TW</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -45719,28 +45719,28 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>550</v>
+        <v>277.5</v>
       </c>
       <c r="G261" t="n">
-        <v>552.4</v>
+        <v>269.3</v>
       </c>
       <c r="H261" t="n">
-        <v>550.4</v>
+        <v>275.85</v>
       </c>
       <c r="I261" t="n">
-        <v>548.7</v>
+        <v>287.3</v>
       </c>
       <c r="J261" t="n">
-        <v>19865905</v>
+        <v>12721709</v>
       </c>
       <c r="K261" t="n">
-        <v>35072026</v>
+        <v>22055634</v>
       </c>
       <c r="L261" t="n">
-        <v>614</v>
+        <v>315.5</v>
       </c>
       <c r="M261" t="n">
-        <v>472</v>
+        <v>255</v>
       </c>
       <c r="N261" t="inlineStr">
         <is>
@@ -45748,52 +45748,52 @@
         </is>
       </c>
       <c r="O261" t="n">
-        <v>681666</v>
+        <v>1489420</v>
       </c>
       <c r="P261" t="n">
-        <v>-10459808</v>
+        <v>-4360014</v>
       </c>
       <c r="Q261" t="n">
-        <v>-10706616</v>
+        <v>-323942</v>
       </c>
       <c r="R261" t="n">
-        <v>-13950843</v>
+        <v>-50783106</v>
       </c>
       <c r="S261" t="n">
-        <v>-55345</v>
+        <v>1562498</v>
       </c>
       <c r="T261" t="n">
-        <v>-11932213</v>
+        <v>-4487057</v>
       </c>
       <c r="U261" t="n">
-        <v>-14114478</v>
+        <v>-5750104</v>
       </c>
       <c r="V261" t="n">
-        <v>-21533905</v>
+        <v>-53749679</v>
       </c>
       <c r="W261" t="n">
-        <v>296574</v>
+        <v>272401</v>
       </c>
       <c r="X261" t="n">
-        <v>1336651</v>
+        <v>1146901</v>
       </c>
       <c r="Y261" t="n">
-        <v>2953941</v>
+        <v>4799596</v>
       </c>
       <c r="Z261" t="n">
-        <v>7527928</v>
+        <v>5703230</v>
       </c>
       <c r="AA261" t="n">
-        <v>440437</v>
+        <v>-345479</v>
       </c>
       <c r="AB261" t="n">
-        <v>135754</v>
+        <v>-1019858</v>
       </c>
       <c r="AC261" t="n">
-        <v>453921</v>
+        <v>626566</v>
       </c>
       <c r="AD261" t="n">
-        <v>55134</v>
+        <v>-2736657</v>
       </c>
       <c r="AE261" t="n">
         <v>-10</v>
@@ -45802,16 +45802,16 @@
         <v>-10</v>
       </c>
       <c r="AG261" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="AH261" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="AI261" t="n">
         <v>0</v>
       </c>
       <c r="AJ261" t="n">
-        <v>-26</v>
+        <v>-10</v>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
@@ -45819,25 +45819,25 @@
         </is>
       </c>
       <c r="AL261" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AM261" t="n">
-        <v>61.54</v>
+        <v>0</v>
       </c>
       <c r="AN261" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AO261" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可</t>
         </is>
       </c>
       <c r="AR261" t="inlineStr">
@@ -45852,29 +45852,29 @@
       </c>
       <c r="AT261" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、多頭排列、量能未放大、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>5009.TWO</t>
+          <t>2516.TW</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>榮剛</t>
+          <t>新建</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -45893,28 +45893,28 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>33.35</v>
+        <v>15.55</v>
       </c>
       <c r="G262" t="n">
-        <v>33.61</v>
+        <v>15.4</v>
       </c>
       <c r="H262" t="n">
-        <v>33.77</v>
+        <v>15.4</v>
       </c>
       <c r="I262" t="n">
-        <v>33.34</v>
+        <v>15.23</v>
       </c>
       <c r="J262" t="n">
-        <v>728000</v>
+        <v>411517</v>
       </c>
       <c r="K262" t="n">
-        <v>1636000</v>
+        <v>850036</v>
       </c>
       <c r="L262" t="n">
-        <v>34.8</v>
+        <v>15.8</v>
       </c>
       <c r="M262" t="n">
-        <v>31.8</v>
+        <v>14.5</v>
       </c>
       <c r="N262" t="inlineStr">
         <is>
@@ -45922,28 +45922,28 @@
         </is>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
+        <v>-1031</v>
       </c>
       <c r="P262" t="n">
-        <v>0</v>
+        <v>-5005</v>
       </c>
       <c r="Q262" t="n">
-        <v>0</v>
+        <v>-51911</v>
       </c>
       <c r="R262" t="n">
-        <v>0</v>
+        <v>20506</v>
       </c>
       <c r="S262" t="n">
-        <v>0</v>
+        <v>-1031</v>
       </c>
       <c r="T262" t="n">
-        <v>0</v>
+        <v>-2005</v>
       </c>
       <c r="U262" t="n">
-        <v>0</v>
+        <v>-48911</v>
       </c>
       <c r="V262" t="n">
-        <v>0</v>
+        <v>18506</v>
       </c>
       <c r="W262" t="n">
         <v>0</v>
@@ -45961,31 +45961,31 @@
         <v>0</v>
       </c>
       <c r="AB262" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="AC262" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="AD262" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AE262" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AF262" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AG262" t="n">
-        <v>-30</v>
+        <v>35</v>
       </c>
       <c r="AH262" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="AI262" t="n">
         <v>0</v>
       </c>
       <c r="AJ262" t="n">
-        <v>-8</v>
+        <v>18</v>
       </c>
       <c r="AK262" t="inlineStr">
         <is>
@@ -45993,25 +45993,25 @@
         </is>
       </c>
       <c r="AL262" t="n">
-        <v>-4</v>
+        <v>-28</v>
       </c>
       <c r="AM262" t="n">
-        <v>-50</v>
+        <v>-155.56</v>
       </c>
       <c r="AN262" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO262" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ262" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR262" t="inlineStr">
@@ -46026,29 +46026,29 @@
       </c>
       <c r="AT262" t="inlineStr">
         <is>
-          <t>跌破5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>法人連續偏賣、中期買超轉短線賣壓、5日法人小幅賣超</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、接近20日高點、法人連續偏賣、中期買超轉短線賣壓、5日法人小幅賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2707.TW</t>
+          <t>5009.TWO</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>晶華</t>
+          <t>榮剛</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -46067,28 +46067,28 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>175</v>
+        <v>33.35</v>
       </c>
       <c r="G263" t="n">
-        <v>175.8</v>
+        <v>33.61</v>
       </c>
       <c r="H263" t="n">
-        <v>176.6</v>
+        <v>33.77</v>
       </c>
       <c r="I263" t="n">
-        <v>176.03</v>
+        <v>33.34</v>
       </c>
       <c r="J263" t="n">
-        <v>106079</v>
+        <v>728000</v>
       </c>
       <c r="K263" t="n">
-        <v>207939</v>
+        <v>1636000</v>
       </c>
       <c r="L263" t="n">
-        <v>179</v>
+        <v>34.8</v>
       </c>
       <c r="M263" t="n">
-        <v>174.5</v>
+        <v>31.8</v>
       </c>
       <c r="N263" t="inlineStr">
         <is>
@@ -46096,28 +46096,28 @@
         </is>
       </c>
       <c r="O263" t="n">
-        <v>-17675</v>
+        <v>0</v>
       </c>
       <c r="P263" t="n">
-        <v>37952</v>
+        <v>0</v>
       </c>
       <c r="Q263" t="n">
-        <v>-28037</v>
+        <v>0</v>
       </c>
       <c r="R263" t="n">
-        <v>352801</v>
+        <v>0</v>
       </c>
       <c r="S263" t="n">
-        <v>-17675</v>
+        <v>0</v>
       </c>
       <c r="T263" t="n">
-        <v>36952</v>
+        <v>0</v>
       </c>
       <c r="U263" t="n">
-        <v>-25021</v>
+        <v>0</v>
       </c>
       <c r="V263" t="n">
-        <v>357103</v>
+        <v>0</v>
       </c>
       <c r="W263" t="n">
         <v>0</v>
@@ -46129,19 +46129,19 @@
         <v>0</v>
       </c>
       <c r="Z263" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="AA263" t="n">
         <v>0</v>
       </c>
       <c r="AB263" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC263" t="n">
-        <v>-3016</v>
+        <v>0</v>
       </c>
       <c r="AD263" t="n">
-        <v>-2302</v>
+        <v>0</v>
       </c>
       <c r="AE263" t="n">
         <v>-12</v>
@@ -46159,7 +46159,7 @@
         <v>0</v>
       </c>
       <c r="AJ263" t="n">
-        <v>-16</v>
+        <v>-8</v>
       </c>
       <c r="AK263" t="inlineStr">
         <is>
@@ -46167,16 +46167,16 @@
         </is>
       </c>
       <c r="AL263" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="AM263" t="n">
-        <v>25</v>
+        <v>-50</v>
       </c>
       <c r="AN263" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO263" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
       </c>
       <c r="AQ263" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR263" t="inlineStr">
@@ -46217,12 +46217,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2820.TW</t>
+          <t>2707.TW</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>華票</t>
+          <t>晶華</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -46241,28 +46241,28 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>16.7</v>
+        <v>175</v>
       </c>
       <c r="G264" t="n">
-        <v>16.65</v>
+        <v>175.8</v>
       </c>
       <c r="H264" t="n">
-        <v>16.71</v>
+        <v>176.6</v>
       </c>
       <c r="I264" t="n">
-        <v>16.74</v>
+        <v>176.03</v>
       </c>
       <c r="J264" t="n">
-        <v>1703982</v>
+        <v>106079</v>
       </c>
       <c r="K264" t="n">
-        <v>2697020</v>
+        <v>207939</v>
       </c>
       <c r="L264" t="n">
-        <v>17.25</v>
+        <v>179</v>
       </c>
       <c r="M264" t="n">
-        <v>16.45</v>
+        <v>174.5</v>
       </c>
       <c r="N264" t="inlineStr">
         <is>
@@ -46270,28 +46270,28 @@
         </is>
       </c>
       <c r="O264" t="n">
-        <v>54050</v>
+        <v>-17675</v>
       </c>
       <c r="P264" t="n">
-        <v>1470460</v>
+        <v>37952</v>
       </c>
       <c r="Q264" t="n">
-        <v>-285540</v>
+        <v>-28037</v>
       </c>
       <c r="R264" t="n">
-        <v>715814</v>
+        <v>352801</v>
       </c>
       <c r="S264" t="n">
-        <v>54050</v>
+        <v>-17675</v>
       </c>
       <c r="T264" t="n">
-        <v>1470460</v>
+        <v>36952</v>
       </c>
       <c r="U264" t="n">
-        <v>-251540</v>
+        <v>-25021</v>
       </c>
       <c r="V264" t="n">
-        <v>959443</v>
+        <v>357103</v>
       </c>
       <c r="W264" t="n">
         <v>0</v>
@@ -46303,37 +46303,37 @@
         <v>0</v>
       </c>
       <c r="Z264" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="AA264" t="n">
         <v>0</v>
       </c>
       <c r="AB264" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC264" t="n">
-        <v>-34000</v>
+        <v>-3016</v>
       </c>
       <c r="AD264" t="n">
-        <v>-243629</v>
+        <v>-2302</v>
       </c>
       <c r="AE264" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AF264" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="AG264" t="n">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="AH264" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AI264" t="n">
         <v>0</v>
       </c>
       <c r="AJ264" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="AK264" t="inlineStr">
         <is>
@@ -46341,16 +46341,16 @@
         </is>
       </c>
       <c r="AL264" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="AM264" t="n">
-        <v>-75</v>
+        <v>25</v>
       </c>
       <c r="AN264" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="AO264" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
       </c>
       <c r="AQ264" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR264" t="inlineStr">
@@ -46374,29 +46374,29 @@
       </c>
       <c r="AT264" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>5日法人賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>6213.TW</t>
+          <t>2441.TW</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>超豐</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -46415,28 +46415,28 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>778</v>
+        <v>115.5</v>
       </c>
       <c r="G265" t="n">
-        <v>774.6</v>
+        <v>113.7</v>
       </c>
       <c r="H265" t="n">
-        <v>786.4</v>
+        <v>117.95</v>
       </c>
       <c r="I265" t="n">
-        <v>748.95</v>
+        <v>121.83</v>
       </c>
       <c r="J265" t="n">
-        <v>19553506</v>
+        <v>1621941</v>
       </c>
       <c r="K265" t="n">
-        <v>23238530</v>
+        <v>2837423</v>
       </c>
       <c r="L265" t="n">
-        <v>885</v>
+        <v>132.5</v>
       </c>
       <c r="M265" t="n">
-        <v>588</v>
+        <v>110.5</v>
       </c>
       <c r="N265" t="inlineStr">
         <is>
@@ -46444,52 +46444,52 @@
         </is>
       </c>
       <c r="O265" t="n">
-        <v>-1562540</v>
+        <v>587214</v>
       </c>
       <c r="P265" t="n">
-        <v>-7785258</v>
+        <v>-457446</v>
       </c>
       <c r="Q265" t="n">
-        <v>-7878209</v>
+        <v>-325043</v>
       </c>
       <c r="R265" t="n">
-        <v>-9025891</v>
+        <v>-5694330</v>
       </c>
       <c r="S265" t="n">
-        <v>-1402720</v>
+        <v>551877</v>
       </c>
       <c r="T265" t="n">
-        <v>-9451407</v>
+        <v>-361490</v>
       </c>
       <c r="U265" t="n">
-        <v>-9444105</v>
+        <v>-421676</v>
       </c>
       <c r="V265" t="n">
-        <v>-11012273</v>
+        <v>-7474668</v>
       </c>
       <c r="W265" t="n">
-        <v>-6000</v>
+        <v>2000</v>
       </c>
       <c r="X265" t="n">
-        <v>1312000</v>
+        <v>-8000</v>
       </c>
       <c r="Y265" t="n">
-        <v>1395973</v>
+        <v>27007</v>
       </c>
       <c r="Z265" t="n">
-        <v>2513973</v>
+        <v>2297007</v>
       </c>
       <c r="AA265" t="n">
-        <v>-153820</v>
+        <v>33337</v>
       </c>
       <c r="AB265" t="n">
-        <v>354149</v>
+        <v>-87956</v>
       </c>
       <c r="AC265" t="n">
-        <v>169923</v>
+        <v>69626</v>
       </c>
       <c r="AD265" t="n">
-        <v>-527591</v>
+        <v>-516669</v>
       </c>
       <c r="AE265" t="n">
         <v>-14</v>
@@ -46498,10 +46498,10 @@
         <v>-14</v>
       </c>
       <c r="AG265" t="n">
-        <v>20</v>
+        <v>-15</v>
       </c>
       <c r="AH265" t="n">
-        <v>-55</v>
+        <v>-20</v>
       </c>
       <c r="AI265" t="n">
         <v>0</v>
@@ -46521,10 +46521,10 @@
         <v>41.67</v>
       </c>
       <c r="AN265" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AO265" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
@@ -46533,7 +46533,7 @@
       </c>
       <c r="AQ265" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR265" t="inlineStr">
@@ -46548,29 +46548,29 @@
       </c>
       <c r="AT265" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2420.TW</t>
+          <t>6213.TW</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>新巨</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -46589,28 +46589,28 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>53.6</v>
+        <v>778</v>
       </c>
       <c r="G266" t="n">
-        <v>53.38</v>
+        <v>774.6</v>
       </c>
       <c r="H266" t="n">
-        <v>54.08</v>
+        <v>786.4</v>
       </c>
       <c r="I266" t="n">
-        <v>55.18</v>
+        <v>748.95</v>
       </c>
       <c r="J266" t="n">
-        <v>185525</v>
+        <v>19553506</v>
       </c>
       <c r="K266" t="n">
-        <v>376279</v>
+        <v>23238530</v>
       </c>
       <c r="L266" t="n">
-        <v>59.5</v>
+        <v>885</v>
       </c>
       <c r="M266" t="n">
-        <v>52.2</v>
+        <v>588</v>
       </c>
       <c r="N266" t="inlineStr">
         <is>
@@ -46618,52 +46618,52 @@
         </is>
       </c>
       <c r="O266" t="n">
-        <v>88374</v>
+        <v>-1562540</v>
       </c>
       <c r="P266" t="n">
-        <v>-168323</v>
+        <v>-7785258</v>
       </c>
       <c r="Q266" t="n">
-        <v>-351079</v>
+        <v>-7878209</v>
       </c>
       <c r="R266" t="n">
-        <v>-651051</v>
+        <v>-9025891</v>
       </c>
       <c r="S266" t="n">
-        <v>89000</v>
+        <v>-1402720</v>
       </c>
       <c r="T266" t="n">
-        <v>-205280</v>
+        <v>-9451407</v>
       </c>
       <c r="U266" t="n">
-        <v>-382269</v>
+        <v>-9444105</v>
       </c>
       <c r="V266" t="n">
-        <v>-678976</v>
+        <v>-11012273</v>
       </c>
       <c r="W266" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="X266" t="n">
-        <v>0</v>
+        <v>1312000</v>
       </c>
       <c r="Y266" t="n">
-        <v>0</v>
+        <v>1395973</v>
       </c>
       <c r="Z266" t="n">
-        <v>0</v>
+        <v>2513973</v>
       </c>
       <c r="AA266" t="n">
-        <v>-626</v>
+        <v>-153820</v>
       </c>
       <c r="AB266" t="n">
-        <v>36957</v>
+        <v>354149</v>
       </c>
       <c r="AC266" t="n">
-        <v>31190</v>
+        <v>169923</v>
       </c>
       <c r="AD266" t="n">
-        <v>27925</v>
+        <v>-527591</v>
       </c>
       <c r="AE266" t="n">
         <v>-14</v>
@@ -46672,16 +46672,16 @@
         <v>-14</v>
       </c>
       <c r="AG266" t="n">
-        <v>-15</v>
+        <v>20</v>
       </c>
       <c r="AH266" t="n">
-        <v>-20</v>
+        <v>-55</v>
       </c>
       <c r="AI266" t="n">
         <v>0</v>
       </c>
       <c r="AJ266" t="n">
-        <v>-40</v>
+        <v>-24</v>
       </c>
       <c r="AK266" t="inlineStr">
         <is>
@@ -46689,25 +46689,25 @@
         </is>
       </c>
       <c r="AL266" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AM266" t="n">
-        <v>65</v>
+        <v>41.67</v>
       </c>
       <c r="AN266" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AO266" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ266" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR266" t="inlineStr">
@@ -46722,29 +46722,29 @@
       </c>
       <c r="AT266" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>5日法人賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、量能未放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2441.TW</t>
+          <t>2420.TW</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>新巨</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -46763,28 +46763,28 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>115.5</v>
+        <v>53.6</v>
       </c>
       <c r="G267" t="n">
-        <v>113.7</v>
+        <v>53.38</v>
       </c>
       <c r="H267" t="n">
-        <v>117.95</v>
+        <v>54.08</v>
       </c>
       <c r="I267" t="n">
-        <v>121.83</v>
+        <v>55.18</v>
       </c>
       <c r="J267" t="n">
-        <v>1621941</v>
+        <v>185525</v>
       </c>
       <c r="K267" t="n">
-        <v>2837423</v>
+        <v>376279</v>
       </c>
       <c r="L267" t="n">
-        <v>132.5</v>
+        <v>59.5</v>
       </c>
       <c r="M267" t="n">
-        <v>110.5</v>
+        <v>52.2</v>
       </c>
       <c r="N267" t="inlineStr">
         <is>
@@ -46792,52 +46792,52 @@
         </is>
       </c>
       <c r="O267" t="n">
-        <v>587214</v>
+        <v>88374</v>
       </c>
       <c r="P267" t="n">
-        <v>-457446</v>
+        <v>-168323</v>
       </c>
       <c r="Q267" t="n">
-        <v>-325043</v>
+        <v>-351079</v>
       </c>
       <c r="R267" t="n">
-        <v>-5694330</v>
+        <v>-651051</v>
       </c>
       <c r="S267" t="n">
-        <v>551877</v>
+        <v>89000</v>
       </c>
       <c r="T267" t="n">
-        <v>-361490</v>
+        <v>-205280</v>
       </c>
       <c r="U267" t="n">
-        <v>-421676</v>
+        <v>-382269</v>
       </c>
       <c r="V267" t="n">
-        <v>-7474668</v>
+        <v>-678976</v>
       </c>
       <c r="W267" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X267" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="Y267" t="n">
-        <v>27007</v>
+        <v>0</v>
       </c>
       <c r="Z267" t="n">
-        <v>2297007</v>
+        <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>33337</v>
+        <v>-626</v>
       </c>
       <c r="AB267" t="n">
-        <v>-87956</v>
+        <v>36957</v>
       </c>
       <c r="AC267" t="n">
-        <v>69626</v>
+        <v>31190</v>
       </c>
       <c r="AD267" t="n">
-        <v>-516669</v>
+        <v>27925</v>
       </c>
       <c r="AE267" t="n">
         <v>-14</v>
@@ -46855,7 +46855,7 @@
         <v>0</v>
       </c>
       <c r="AJ267" t="n">
-        <v>-24</v>
+        <v>-40</v>
       </c>
       <c r="AK267" t="inlineStr">
         <is>
@@ -46863,25 +46863,25 @@
         </is>
       </c>
       <c r="AL267" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AM267" t="n">
-        <v>41.67</v>
+        <v>65</v>
       </c>
       <c r="AN267" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AO267" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ267" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR267" t="inlineStr">
@@ -46901,12 +46901,12 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>5日法人賣超、投信買外資賣</t>
+          <t>5日法人賣超</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -47609,12 +47609,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2545.TW</t>
+          <t>2820.TW</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>皇翔</t>
+          <t>華票</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -47633,28 +47633,28 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>33.9</v>
+        <v>16.7</v>
       </c>
       <c r="G272" t="n">
-        <v>33.33</v>
+        <v>16.65</v>
       </c>
       <c r="H272" t="n">
-        <v>33.86</v>
+        <v>16.71</v>
       </c>
       <c r="I272" t="n">
-        <v>33.97</v>
+        <v>16.74</v>
       </c>
       <c r="J272" t="n">
-        <v>475529</v>
+        <v>1703982</v>
       </c>
       <c r="K272" t="n">
-        <v>784865</v>
+        <v>2697020</v>
       </c>
       <c r="L272" t="n">
-        <v>34.95</v>
+        <v>17.25</v>
       </c>
       <c r="M272" t="n">
-        <v>32.75</v>
+        <v>16.45</v>
       </c>
       <c r="N272" t="inlineStr">
         <is>
@@ -47662,28 +47662,28 @@
         </is>
       </c>
       <c r="O272" t="n">
-        <v>317110</v>
+        <v>54050</v>
       </c>
       <c r="P272" t="n">
-        <v>144577</v>
+        <v>1470460</v>
       </c>
       <c r="Q272" t="n">
-        <v>-100409</v>
+        <v>-285540</v>
       </c>
       <c r="R272" t="n">
-        <v>63773</v>
+        <v>715814</v>
       </c>
       <c r="S272" t="n">
-        <v>295110</v>
+        <v>54050</v>
       </c>
       <c r="T272" t="n">
-        <v>85391</v>
+        <v>1470460</v>
       </c>
       <c r="U272" t="n">
-        <v>-139529</v>
+        <v>-251540</v>
       </c>
       <c r="V272" t="n">
-        <v>74653</v>
+        <v>959443</v>
       </c>
       <c r="W272" t="n">
         <v>0</v>
@@ -47698,16 +47698,16 @@
         <v>0</v>
       </c>
       <c r="AA272" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="AB272" t="n">
-        <v>59186</v>
+        <v>0</v>
       </c>
       <c r="AC272" t="n">
-        <v>39120</v>
+        <v>-34000</v>
       </c>
       <c r="AD272" t="n">
-        <v>-10880</v>
+        <v>-243629</v>
       </c>
       <c r="AE272" t="n">
         <v>-14</v>
@@ -47725,7 +47725,7 @@
         <v>0</v>
       </c>
       <c r="AJ272" t="n">
-        <v>-40</v>
+        <v>-8</v>
       </c>
       <c r="AK272" t="inlineStr">
         <is>
@@ -47733,25 +47733,25 @@
         </is>
       </c>
       <c r="AL272" t="n">
-        <v>26</v>
+        <v>-6</v>
       </c>
       <c r="AM272" t="n">
-        <v>65</v>
+        <v>-75</v>
       </c>
       <c r="AN272" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AO272" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ272" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR272" t="inlineStr">
@@ -47957,12 +47957,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2342.TW</t>
+          <t>2545.TW</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>茂矽</t>
+          <t>皇翔</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -47981,28 +47981,28 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>42.65</v>
+        <v>33.9</v>
       </c>
       <c r="G274" t="n">
-        <v>41.26</v>
+        <v>33.33</v>
       </c>
       <c r="H274" t="n">
-        <v>42.1</v>
+        <v>33.86</v>
       </c>
       <c r="I274" t="n">
-        <v>45.77</v>
+        <v>33.97</v>
       </c>
       <c r="J274" t="n">
-        <v>1697401</v>
+        <v>475529</v>
       </c>
       <c r="K274" t="n">
-        <v>1345605</v>
+        <v>784865</v>
       </c>
       <c r="L274" t="n">
-        <v>53</v>
+        <v>34.95</v>
       </c>
       <c r="M274" t="n">
-        <v>39.6</v>
+        <v>32.75</v>
       </c>
       <c r="N274" t="inlineStr">
         <is>
@@ -48010,28 +48010,28 @@
         </is>
       </c>
       <c r="O274" t="n">
-        <v>385045</v>
+        <v>317110</v>
       </c>
       <c r="P274" t="n">
-        <v>-236749</v>
+        <v>144577</v>
       </c>
       <c r="Q274" t="n">
-        <v>-114322</v>
+        <v>-100409</v>
       </c>
       <c r="R274" t="n">
-        <v>39996</v>
+        <v>63773</v>
       </c>
       <c r="S274" t="n">
-        <v>384117</v>
+        <v>295110</v>
       </c>
       <c r="T274" t="n">
-        <v>-223997</v>
+        <v>85391</v>
       </c>
       <c r="U274" t="n">
-        <v>-101766</v>
+        <v>-139529</v>
       </c>
       <c r="V274" t="n">
-        <v>94941</v>
+        <v>74653</v>
       </c>
       <c r="W274" t="n">
         <v>0</v>
@@ -48046,34 +48046,34 @@
         <v>0</v>
       </c>
       <c r="AA274" t="n">
-        <v>928</v>
+        <v>22000</v>
       </c>
       <c r="AB274" t="n">
-        <v>-12752</v>
+        <v>59186</v>
       </c>
       <c r="AC274" t="n">
-        <v>-12556</v>
+        <v>39120</v>
       </c>
       <c r="AD274" t="n">
-        <v>-54945</v>
+        <v>-10880</v>
       </c>
       <c r="AE274" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AF274" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="AG274" t="n">
-        <v>5</v>
+        <v>-15</v>
       </c>
       <c r="AH274" t="n">
-        <v>-45</v>
+        <v>-20</v>
       </c>
       <c r="AI274" t="n">
         <v>0</v>
       </c>
       <c r="AJ274" t="n">
-        <v>-44</v>
+        <v>-40</v>
       </c>
       <c r="AK274" t="inlineStr">
         <is>
@@ -48081,25 +48081,25 @@
         </is>
       </c>
       <c r="AL274" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM274" t="n">
-        <v>63.64</v>
+        <v>65</v>
       </c>
       <c r="AN274" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AO274" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ274" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AR274" t="inlineStr">
@@ -48114,17 +48114,17 @@
       </c>
       <c r="AT274" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>中期買超轉短線賣壓、5日法人賣超</t>
+          <t>5日法人賣超</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -48479,12 +48479,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2457.TW</t>
+          <t>2342.TW</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>飛宏</t>
+          <t>茂矽</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -48503,28 +48503,28 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>20.75</v>
+        <v>42.65</v>
       </c>
       <c r="G277" t="n">
-        <v>21.11</v>
+        <v>41.26</v>
       </c>
       <c r="H277" t="n">
-        <v>21.53</v>
+        <v>42.1</v>
       </c>
       <c r="I277" t="n">
-        <v>21.83</v>
+        <v>45.77</v>
       </c>
       <c r="J277" t="n">
-        <v>1137446</v>
+        <v>1697401</v>
       </c>
       <c r="K277" t="n">
-        <v>946253</v>
+        <v>1345605</v>
       </c>
       <c r="L277" t="n">
-        <v>22.75</v>
+        <v>53</v>
       </c>
       <c r="M277" t="n">
-        <v>20.45</v>
+        <v>39.6</v>
       </c>
       <c r="N277" t="inlineStr">
         <is>
@@ -48532,28 +48532,28 @@
         </is>
       </c>
       <c r="O277" t="n">
-        <v>391065</v>
+        <v>385045</v>
       </c>
       <c r="P277" t="n">
-        <v>-115889</v>
+        <v>-236749</v>
       </c>
       <c r="Q277" t="n">
-        <v>3642</v>
+        <v>-114322</v>
       </c>
       <c r="R277" t="n">
-        <v>95141</v>
+        <v>39996</v>
       </c>
       <c r="S277" t="n">
-        <v>397401</v>
+        <v>384117</v>
       </c>
       <c r="T277" t="n">
-        <v>-136370</v>
+        <v>-223997</v>
       </c>
       <c r="U277" t="n">
-        <v>17961</v>
+        <v>-101766</v>
       </c>
       <c r="V277" t="n">
-        <v>144905</v>
+        <v>94941</v>
       </c>
       <c r="W277" t="n">
         <v>0</v>
@@ -48568,34 +48568,34 @@
         <v>0</v>
       </c>
       <c r="AA277" t="n">
-        <v>-6336</v>
+        <v>928</v>
       </c>
       <c r="AB277" t="n">
-        <v>20481</v>
+        <v>-12752</v>
       </c>
       <c r="AC277" t="n">
-        <v>-14319</v>
+        <v>-12556</v>
       </c>
       <c r="AD277" t="n">
-        <v>-49764</v>
+        <v>-54945</v>
       </c>
       <c r="AE277" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AF277" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AG277" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH277" t="n">
         <v>-45</v>
       </c>
-      <c r="AH277" t="n">
-        <v>0</v>
-      </c>
       <c r="AI277" t="n">
         <v>0</v>
       </c>
       <c r="AJ277" t="n">
-        <v>-50</v>
+        <v>-44</v>
       </c>
       <c r="AK277" t="inlineStr">
         <is>
@@ -48603,25 +48603,25 @@
         </is>
       </c>
       <c r="AL277" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AM277" t="n">
-        <v>64</v>
+        <v>63.64</v>
       </c>
       <c r="AN277" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AO277" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ277" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
+          <t>DT尚未轉強、5MA乖離尚可、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR277" t="inlineStr">
@@ -48636,29 +48636,29 @@
       </c>
       <c r="AT277" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>中期買超轉短線賣壓、5日法人賣超</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、中期買超轉短線賣壓、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>00927.TW</t>
+          <t>00881.TW</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>群益半導體收益</t>
+          <t>國泰台灣5G+</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -48677,28 +48677,28 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>35.87</v>
+        <v>49.41</v>
       </c>
       <c r="G278" t="n">
-        <v>35.22</v>
+        <v>49.02</v>
       </c>
       <c r="H278" t="n">
-        <v>36.74</v>
+        <v>49.88</v>
       </c>
       <c r="I278" t="n">
-        <v>38.5</v>
+        <v>51.52</v>
       </c>
       <c r="J278" t="n">
-        <v>20984948</v>
+        <v>10004086</v>
       </c>
       <c r="K278" t="n">
-        <v>27199914</v>
+        <v>15744547</v>
       </c>
       <c r="L278" t="n">
-        <v>41.36</v>
+        <v>54.75</v>
       </c>
       <c r="M278" t="n">
-        <v>34.42</v>
+        <v>47.97</v>
       </c>
       <c r="N278" t="inlineStr">
         <is>
@@ -48706,28 +48706,28 @@
         </is>
       </c>
       <c r="O278" t="n">
-        <v>3755466</v>
+        <v>144179</v>
       </c>
       <c r="P278" t="n">
-        <v>-27869121</v>
+        <v>-20519691</v>
       </c>
       <c r="Q278" t="n">
-        <v>-54277288</v>
+        <v>-32102401</v>
       </c>
       <c r="R278" t="n">
-        <v>-513018633</v>
+        <v>-106269423</v>
       </c>
       <c r="S278" t="n">
-        <v>9773000</v>
+        <v>-1040580</v>
       </c>
       <c r="T278" t="n">
-        <v>3662065</v>
+        <v>-9424843</v>
       </c>
       <c r="U278" t="n">
-        <v>-2918250</v>
+        <v>-12487096</v>
       </c>
       <c r="V278" t="n">
-        <v>-35530433</v>
+        <v>-38171531</v>
       </c>
       <c r="W278" t="n">
         <v>0</v>
@@ -48742,16 +48742,16 @@
         <v>0</v>
       </c>
       <c r="AA278" t="n">
-        <v>-6017534</v>
+        <v>1184759</v>
       </c>
       <c r="AB278" t="n">
-        <v>-31531186</v>
+        <v>-11094848</v>
       </c>
       <c r="AC278" t="n">
-        <v>-51359038</v>
+        <v>-19615305</v>
       </c>
       <c r="AD278" t="n">
-        <v>-477488200</v>
+        <v>-68097892</v>
       </c>
       <c r="AE278" t="n">
         <v>-18</v>
@@ -48769,7 +48769,7 @@
         <v>0</v>
       </c>
       <c r="AJ278" t="n">
-        <v>-44</v>
+        <v>-40</v>
       </c>
       <c r="AK278" t="inlineStr">
         <is>
@@ -48777,25 +48777,25 @@
         </is>
       </c>
       <c r="AL278" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AM278" t="n">
-        <v>59.09</v>
+        <v>55</v>
       </c>
       <c r="AN278" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AO278" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ278" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR278" t="inlineStr">
@@ -48827,17 +48827,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3413.TW</t>
+          <t>00927.TW</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>京鼎</t>
+          <t>群益半導體收益</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -48851,28 +48851,28 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>279.5</v>
+        <v>35.87</v>
       </c>
       <c r="G279" t="n">
-        <v>278.5</v>
+        <v>35.22</v>
       </c>
       <c r="H279" t="n">
-        <v>279.7</v>
+        <v>36.74</v>
       </c>
       <c r="I279" t="n">
-        <v>285.32</v>
+        <v>38.5</v>
       </c>
       <c r="J279" t="n">
-        <v>685132</v>
+        <v>20984948</v>
       </c>
       <c r="K279" t="n">
-        <v>537251</v>
+        <v>27199914</v>
       </c>
       <c r="L279" t="n">
-        <v>298</v>
+        <v>41.36</v>
       </c>
       <c r="M279" t="n">
-        <v>273.5</v>
+        <v>34.42</v>
       </c>
       <c r="N279" t="inlineStr">
         <is>
@@ -48880,52 +48880,52 @@
         </is>
       </c>
       <c r="O279" t="n">
-        <v>12975</v>
+        <v>3755466</v>
       </c>
       <c r="P279" t="n">
-        <v>-75449</v>
+        <v>-27869121</v>
       </c>
       <c r="Q279" t="n">
-        <v>-120136</v>
+        <v>-54277288</v>
       </c>
       <c r="R279" t="n">
-        <v>-293741</v>
+        <v>-513018633</v>
       </c>
       <c r="S279" t="n">
-        <v>95224</v>
+        <v>9773000</v>
       </c>
       <c r="T279" t="n">
-        <v>8790</v>
+        <v>3662065</v>
       </c>
       <c r="U279" t="n">
-        <v>-35882</v>
+        <v>-2918250</v>
       </c>
       <c r="V279" t="n">
-        <v>-59616</v>
+        <v>-35530433</v>
       </c>
       <c r="W279" t="n">
-        <v>-82000</v>
+        <v>0</v>
       </c>
       <c r="X279" t="n">
-        <v>-82000</v>
+        <v>0</v>
       </c>
       <c r="Y279" t="n">
-        <v>-82032</v>
+        <v>0</v>
       </c>
       <c r="Z279" t="n">
-        <v>-204032</v>
+        <v>0</v>
       </c>
       <c r="AA279" t="n">
-        <v>-249</v>
+        <v>-6017534</v>
       </c>
       <c r="AB279" t="n">
-        <v>-2239</v>
+        <v>-31531186</v>
       </c>
       <c r="AC279" t="n">
-        <v>-2222</v>
+        <v>-51359038</v>
       </c>
       <c r="AD279" t="n">
-        <v>-30093</v>
+        <v>-477488200</v>
       </c>
       <c r="AE279" t="n">
         <v>-18</v>
@@ -48934,16 +48934,16 @@
         <v>-18</v>
       </c>
       <c r="AG279" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="AH279" t="n">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="AI279" t="n">
         <v>0</v>
       </c>
       <c r="AJ279" t="n">
-        <v>-16</v>
+        <v>-44</v>
       </c>
       <c r="AK279" t="inlineStr">
         <is>
@@ -48951,10 +48951,10 @@
         </is>
       </c>
       <c r="AL279" t="n">
-        <v>-2</v>
+        <v>26</v>
       </c>
       <c r="AM279" t="n">
-        <v>-12.5</v>
+        <v>59.09</v>
       </c>
       <c r="AN279" t="n">
         <v>35</v>
@@ -48969,7 +48969,7 @@
       </c>
       <c r="AQ279" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR279" t="inlineStr">
@@ -48984,17 +48984,17 @@
       </c>
       <c r="AT279" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>5日法人賣超、外資投信同步賣超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -49349,17 +49349,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>00403A.TW</t>
+          <t>2457.TW</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>主動統一升級50</t>
+          <t>飛宏</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -49373,28 +49373,28 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>10.25</v>
+        <v>20.75</v>
       </c>
       <c r="G282" t="n">
-        <v>10.13</v>
+        <v>21.11</v>
       </c>
       <c r="H282" t="n">
-        <v>10.37</v>
+        <v>21.53</v>
       </c>
       <c r="I282" t="n">
-        <v>10.74</v>
+        <v>21.83</v>
       </c>
       <c r="J282" t="n">
-        <v>120342669</v>
+        <v>1137446</v>
       </c>
       <c r="K282" t="n">
-        <v>164784330</v>
+        <v>946253</v>
       </c>
       <c r="L282" t="n">
-        <v>11.53</v>
+        <v>22.75</v>
       </c>
       <c r="M282" t="n">
-        <v>9.779999999999999</v>
+        <v>20.45</v>
       </c>
       <c r="N282" t="inlineStr">
         <is>
@@ -49402,28 +49402,28 @@
         </is>
       </c>
       <c r="O282" t="n">
-        <v>40472199</v>
+        <v>391065</v>
       </c>
       <c r="P282" t="n">
-        <v>-226140697</v>
+        <v>-115889</v>
       </c>
       <c r="Q282" t="n">
-        <v>-245279436</v>
+        <v>3642</v>
       </c>
       <c r="R282" t="n">
-        <v>-487182537</v>
+        <v>95141</v>
       </c>
       <c r="S282" t="n">
-        <v>37395055</v>
+        <v>397401</v>
       </c>
       <c r="T282" t="n">
-        <v>-53236939</v>
+        <v>-136370</v>
       </c>
       <c r="U282" t="n">
-        <v>-68498421</v>
+        <v>17961</v>
       </c>
       <c r="V282" t="n">
-        <v>-299382277</v>
+        <v>144905</v>
       </c>
       <c r="W282" t="n">
         <v>0</v>
@@ -49438,16 +49438,16 @@
         <v>0</v>
       </c>
       <c r="AA282" t="n">
-        <v>3077144</v>
+        <v>-6336</v>
       </c>
       <c r="AB282" t="n">
-        <v>-172903758</v>
+        <v>20481</v>
       </c>
       <c r="AC282" t="n">
-        <v>-176781015</v>
+        <v>-14319</v>
       </c>
       <c r="AD282" t="n">
-        <v>-187800260</v>
+        <v>-49764</v>
       </c>
       <c r="AE282" t="n">
         <v>-18</v>
@@ -49456,16 +49456,16 @@
         <v>-18</v>
       </c>
       <c r="AG282" t="n">
-        <v>-15</v>
+        <v>-45</v>
       </c>
       <c r="AH282" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AI282" t="n">
         <v>0</v>
       </c>
       <c r="AJ282" t="n">
-        <v>-38</v>
+        <v>-50</v>
       </c>
       <c r="AK282" t="inlineStr">
         <is>
@@ -49473,25 +49473,25 @@
         </is>
       </c>
       <c r="AL282" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AM282" t="n">
-        <v>52.63</v>
+        <v>64</v>
       </c>
       <c r="AN282" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AO282" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ282" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、量能溫和放大、分數升溫過快</t>
         </is>
       </c>
       <c r="AR282" t="inlineStr">
@@ -49506,17 +49506,17 @@
       </c>
       <c r="AT282" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能溫和放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -50045,17 +50045,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2812.TW</t>
+          <t>00923.TW</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t>群益台ESG低碳50</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -50069,28 +50069,28 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>18.6</v>
+        <v>39.81</v>
       </c>
       <c r="G286" t="n">
-        <v>18.58</v>
+        <v>39.32</v>
       </c>
       <c r="H286" t="n">
-        <v>18.64</v>
+        <v>39.9</v>
       </c>
       <c r="I286" t="n">
-        <v>18.71</v>
+        <v>41.03</v>
       </c>
       <c r="J286" t="n">
-        <v>5859899</v>
+        <v>2159316</v>
       </c>
       <c r="K286" t="n">
-        <v>7750993</v>
+        <v>3410278</v>
       </c>
       <c r="L286" t="n">
-        <v>19.2</v>
+        <v>43.22</v>
       </c>
       <c r="M286" t="n">
-        <v>18.45</v>
+        <v>38.66</v>
       </c>
       <c r="N286" t="inlineStr">
         <is>
@@ -50098,52 +50098,52 @@
         </is>
       </c>
       <c r="O286" t="n">
-        <v>-1319265</v>
+        <v>262771</v>
       </c>
       <c r="P286" t="n">
-        <v>5287728</v>
+        <v>-2915822</v>
       </c>
       <c r="Q286" t="n">
-        <v>-1474960</v>
+        <v>-5858531</v>
       </c>
       <c r="R286" t="n">
-        <v>8894765</v>
+        <v>-17153352</v>
       </c>
       <c r="S286" t="n">
-        <v>-1344265</v>
+        <v>-79880</v>
       </c>
       <c r="T286" t="n">
-        <v>5259490</v>
+        <v>-200230</v>
       </c>
       <c r="U286" t="n">
-        <v>-1416760</v>
+        <v>-77381</v>
       </c>
       <c r="V286" t="n">
-        <v>5457583</v>
+        <v>-2682417</v>
       </c>
       <c r="W286" t="n">
         <v>0</v>
       </c>
       <c r="X286" t="n">
-        <v>-15746</v>
+        <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>5156</v>
+        <v>0</v>
       </c>
       <c r="Z286" t="n">
-        <v>3565156</v>
+        <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>25000</v>
+        <v>342651</v>
       </c>
       <c r="AB286" t="n">
-        <v>43984</v>
+        <v>-2715592</v>
       </c>
       <c r="AC286" t="n">
-        <v>-63356</v>
+        <v>-5781150</v>
       </c>
       <c r="AD286" t="n">
-        <v>-127974</v>
+        <v>-14470935</v>
       </c>
       <c r="AE286" t="n">
         <v>-18</v>
@@ -50161,7 +50161,7 @@
         <v>0</v>
       </c>
       <c r="AJ286" t="n">
-        <v>-12</v>
+        <v>-40</v>
       </c>
       <c r="AK286" t="inlineStr">
         <is>
@@ -50169,25 +50169,25 @@
         </is>
       </c>
       <c r="AL286" t="n">
-        <v>-6</v>
+        <v>22</v>
       </c>
       <c r="AM286" t="n">
-        <v>-50</v>
+        <v>55</v>
       </c>
       <c r="AN286" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AO286" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ286" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR286" t="inlineStr">
@@ -50207,24 +50207,24 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、投信買外資賣</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>6274.TWO</t>
+          <t>3413.TW</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>京鼎</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -50243,28 +50243,28 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>1375</v>
+        <v>279.5</v>
       </c>
       <c r="G287" t="n">
-        <v>1425</v>
+        <v>278.5</v>
       </c>
       <c r="H287" t="n">
-        <v>1538.5</v>
+        <v>279.7</v>
       </c>
       <c r="I287" t="n">
-        <v>1588.5</v>
+        <v>285.32</v>
       </c>
       <c r="J287" t="n">
-        <v>8595000</v>
+        <v>685132</v>
       </c>
       <c r="K287" t="n">
-        <v>14763600</v>
+        <v>537251</v>
       </c>
       <c r="L287" t="n">
-        <v>1835</v>
+        <v>298</v>
       </c>
       <c r="M287" t="n">
-        <v>1280</v>
+        <v>273.5</v>
       </c>
       <c r="N287" t="inlineStr">
         <is>
@@ -50272,52 +50272,52 @@
         </is>
       </c>
       <c r="O287" t="n">
-        <v>0</v>
+        <v>12975</v>
       </c>
       <c r="P287" t="n">
-        <v>0</v>
+        <v>-75449</v>
       </c>
       <c r="Q287" t="n">
-        <v>0</v>
+        <v>-120136</v>
       </c>
       <c r="R287" t="n">
-        <v>0</v>
+        <v>-293741</v>
       </c>
       <c r="S287" t="n">
-        <v>0</v>
+        <v>95224</v>
       </c>
       <c r="T287" t="n">
-        <v>0</v>
+        <v>8790</v>
       </c>
       <c r="U287" t="n">
-        <v>0</v>
+        <v>-35882</v>
       </c>
       <c r="V287" t="n">
-        <v>0</v>
+        <v>-59616</v>
       </c>
       <c r="W287" t="n">
-        <v>0</v>
+        <v>-82000</v>
       </c>
       <c r="X287" t="n">
-        <v>0</v>
+        <v>-82000</v>
       </c>
       <c r="Y287" t="n">
-        <v>0</v>
+        <v>-82032</v>
       </c>
       <c r="Z287" t="n">
-        <v>0</v>
+        <v>-204032</v>
       </c>
       <c r="AA287" t="n">
-        <v>0</v>
+        <v>-249</v>
       </c>
       <c r="AB287" t="n">
-        <v>0</v>
+        <v>-2239</v>
       </c>
       <c r="AC287" t="n">
-        <v>0</v>
+        <v>-2222</v>
       </c>
       <c r="AD287" t="n">
-        <v>0</v>
+        <v>-30093</v>
       </c>
       <c r="AE287" t="n">
         <v>-18</v>
@@ -50326,16 +50326,16 @@
         <v>-18</v>
       </c>
       <c r="AG287" t="n">
-        <v>-45</v>
+        <v>-5</v>
       </c>
       <c r="AH287" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="AI287" t="n">
         <v>0</v>
       </c>
       <c r="AJ287" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="AK287" t="inlineStr">
         <is>
@@ -50343,25 +50343,25 @@
         </is>
       </c>
       <c r="AL287" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AM287" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="AN287" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AO287" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ287" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、量能溫和放大、分數轉弱</t>
         </is>
       </c>
       <c r="AR287" t="inlineStr">
@@ -50376,34 +50376,34 @@
       </c>
       <c r="AT287" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、接近20日低點、5日法人賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>00881.TW</t>
+          <t>6274.TWO</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>國泰台灣5G+</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -50417,28 +50417,28 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>49.41</v>
+        <v>1375</v>
       </c>
       <c r="G288" t="n">
-        <v>49.02</v>
+        <v>1425</v>
       </c>
       <c r="H288" t="n">
-        <v>49.88</v>
+        <v>1538.5</v>
       </c>
       <c r="I288" t="n">
-        <v>51.52</v>
+        <v>1588.5</v>
       </c>
       <c r="J288" t="n">
-        <v>10004086</v>
+        <v>8595000</v>
       </c>
       <c r="K288" t="n">
-        <v>15744547</v>
+        <v>14763600</v>
       </c>
       <c r="L288" t="n">
-        <v>54.75</v>
+        <v>1835</v>
       </c>
       <c r="M288" t="n">
-        <v>47.97</v>
+        <v>1280</v>
       </c>
       <c r="N288" t="inlineStr">
         <is>
@@ -50446,28 +50446,28 @@
         </is>
       </c>
       <c r="O288" t="n">
-        <v>144179</v>
+        <v>0</v>
       </c>
       <c r="P288" t="n">
-        <v>-20519691</v>
+        <v>0</v>
       </c>
       <c r="Q288" t="n">
-        <v>-32102401</v>
+        <v>0</v>
       </c>
       <c r="R288" t="n">
-        <v>-106269423</v>
+        <v>0</v>
       </c>
       <c r="S288" t="n">
-        <v>-1040580</v>
+        <v>0</v>
       </c>
       <c r="T288" t="n">
-        <v>-9424843</v>
+        <v>0</v>
       </c>
       <c r="U288" t="n">
-        <v>-12487096</v>
+        <v>0</v>
       </c>
       <c r="V288" t="n">
-        <v>-38171531</v>
+        <v>0</v>
       </c>
       <c r="W288" t="n">
         <v>0</v>
@@ -50482,16 +50482,16 @@
         <v>0</v>
       </c>
       <c r="AA288" t="n">
-        <v>1184759</v>
+        <v>0</v>
       </c>
       <c r="AB288" t="n">
-        <v>-11094848</v>
+        <v>0</v>
       </c>
       <c r="AC288" t="n">
-        <v>-19615305</v>
+        <v>0</v>
       </c>
       <c r="AD288" t="n">
-        <v>-68097892</v>
+        <v>0</v>
       </c>
       <c r="AE288" t="n">
         <v>-18</v>
@@ -50500,16 +50500,16 @@
         <v>-18</v>
       </c>
       <c r="AG288" t="n">
-        <v>-15</v>
+        <v>-45</v>
       </c>
       <c r="AH288" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="AI288" t="n">
         <v>0</v>
       </c>
       <c r="AJ288" t="n">
-        <v>-40</v>
+        <v>-18</v>
       </c>
       <c r="AK288" t="inlineStr">
         <is>
@@ -50517,25 +50517,25 @@
         </is>
       </c>
       <c r="AL288" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AM288" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AN288" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AO288" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ288" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
         </is>
       </c>
       <c r="AR288" t="inlineStr">
@@ -50550,17 +50550,17 @@
       </c>
       <c r="AT288" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -50741,12 +50741,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>00923.TW</t>
+          <t>00403A.TW</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>群益台ESG低碳50</t>
+          <t>主動統一升級50</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -50765,28 +50765,28 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>39.81</v>
+        <v>10.25</v>
       </c>
       <c r="G290" t="n">
-        <v>39.32</v>
+        <v>10.13</v>
       </c>
       <c r="H290" t="n">
-        <v>39.9</v>
+        <v>10.37</v>
       </c>
       <c r="I290" t="n">
-        <v>41.03</v>
+        <v>10.74</v>
       </c>
       <c r="J290" t="n">
-        <v>2159316</v>
+        <v>120342669</v>
       </c>
       <c r="K290" t="n">
-        <v>3410278</v>
+        <v>164784330</v>
       </c>
       <c r="L290" t="n">
-        <v>43.22</v>
+        <v>11.53</v>
       </c>
       <c r="M290" t="n">
-        <v>38.66</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="N290" t="inlineStr">
         <is>
@@ -50794,28 +50794,28 @@
         </is>
       </c>
       <c r="O290" t="n">
-        <v>262771</v>
+        <v>40472199</v>
       </c>
       <c r="P290" t="n">
-        <v>-2915822</v>
+        <v>-226140697</v>
       </c>
       <c r="Q290" t="n">
-        <v>-5858531</v>
+        <v>-245279436</v>
       </c>
       <c r="R290" t="n">
-        <v>-17153352</v>
+        <v>-487182537</v>
       </c>
       <c r="S290" t="n">
-        <v>-79880</v>
+        <v>37395055</v>
       </c>
       <c r="T290" t="n">
-        <v>-200230</v>
+        <v>-53236939</v>
       </c>
       <c r="U290" t="n">
-        <v>-77381</v>
+        <v>-68498421</v>
       </c>
       <c r="V290" t="n">
-        <v>-2682417</v>
+        <v>-299382277</v>
       </c>
       <c r="W290" t="n">
         <v>0</v>
@@ -50830,16 +50830,16 @@
         <v>0</v>
       </c>
       <c r="AA290" t="n">
-        <v>342651</v>
+        <v>3077144</v>
       </c>
       <c r="AB290" t="n">
-        <v>-2715592</v>
+        <v>-172903758</v>
       </c>
       <c r="AC290" t="n">
-        <v>-5781150</v>
+        <v>-176781015</v>
       </c>
       <c r="AD290" t="n">
-        <v>-14470935</v>
+        <v>-187800260</v>
       </c>
       <c r="AE290" t="n">
         <v>-18</v>
@@ -50857,7 +50857,7 @@
         <v>0</v>
       </c>
       <c r="AJ290" t="n">
-        <v>-40</v>
+        <v>-38</v>
       </c>
       <c r="AK290" t="inlineStr">
         <is>
@@ -50865,10 +50865,10 @@
         </is>
       </c>
       <c r="AL290" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AM290" t="n">
-        <v>55</v>
+        <v>52.63</v>
       </c>
       <c r="AN290" t="n">
         <v>45</v>
@@ -50915,17 +50915,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>00922.TW</t>
+          <t>2812.TW</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>國泰台灣領袖50</t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>個股</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -50939,28 +50939,28 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>40.13</v>
+        <v>18.6</v>
       </c>
       <c r="G291" t="n">
-        <v>39.67</v>
+        <v>18.58</v>
       </c>
       <c r="H291" t="n">
-        <v>41.11</v>
+        <v>18.64</v>
       </c>
       <c r="I291" t="n">
-        <v>42.73</v>
+        <v>18.71</v>
       </c>
       <c r="J291" t="n">
-        <v>3932798</v>
+        <v>5859899</v>
       </c>
       <c r="K291" t="n">
-        <v>10187115</v>
+        <v>7750993</v>
       </c>
       <c r="L291" t="n">
-        <v>45.36</v>
+        <v>19.2</v>
       </c>
       <c r="M291" t="n">
-        <v>38.98</v>
+        <v>18.45</v>
       </c>
       <c r="N291" t="inlineStr">
         <is>
@@ -50968,52 +50968,52 @@
         </is>
       </c>
       <c r="O291" t="n">
-        <v>333451</v>
+        <v>-1319265</v>
       </c>
       <c r="P291" t="n">
-        <v>-12912086</v>
+        <v>5287728</v>
       </c>
       <c r="Q291" t="n">
-        <v>-22815463</v>
+        <v>-1474960</v>
       </c>
       <c r="R291" t="n">
-        <v>-108081553</v>
+        <v>8894765</v>
       </c>
       <c r="S291" t="n">
-        <v>-530955</v>
+        <v>-1344265</v>
       </c>
       <c r="T291" t="n">
-        <v>-2506984</v>
+        <v>5259490</v>
       </c>
       <c r="U291" t="n">
-        <v>-2669854</v>
+        <v>-1416760</v>
       </c>
       <c r="V291" t="n">
-        <v>-1762198</v>
+        <v>5457583</v>
       </c>
       <c r="W291" t="n">
         <v>0</v>
       </c>
       <c r="X291" t="n">
-        <v>0</v>
+        <v>-15746</v>
       </c>
       <c r="Y291" t="n">
-        <v>0</v>
+        <v>5156</v>
       </c>
       <c r="Z291" t="n">
-        <v>0</v>
+        <v>3565156</v>
       </c>
       <c r="AA291" t="n">
-        <v>864406</v>
+        <v>25000</v>
       </c>
       <c r="AB291" t="n">
-        <v>-10405102</v>
+        <v>43984</v>
       </c>
       <c r="AC291" t="n">
-        <v>-20145609</v>
+        <v>-63356</v>
       </c>
       <c r="AD291" t="n">
-        <v>-106319355</v>
+        <v>-127974</v>
       </c>
       <c r="AE291" t="n">
         <v>-18</v>
@@ -51031,7 +51031,7 @@
         <v>0</v>
       </c>
       <c r="AJ291" t="n">
-        <v>-44</v>
+        <v>-12</v>
       </c>
       <c r="AK291" t="inlineStr">
         <is>
@@ -51039,25 +51039,25 @@
         </is>
       </c>
       <c r="AL291" t="n">
-        <v>26</v>
+        <v>-6</v>
       </c>
       <c r="AM291" t="n">
-        <v>59.09</v>
+        <v>-50</v>
       </c>
       <c r="AN291" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AO291" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ291" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數轉弱</t>
         </is>
       </c>
       <c r="AR291" t="inlineStr">
@@ -51077,29 +51077,29 @@
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超</t>
+          <t>5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV291" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3504.TW</t>
+          <t>00922.TW</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>揚明光</t>
+          <t>國泰台灣領袖50</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>個股</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -51113,28 +51113,28 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>70.90000000000001</v>
+        <v>40.13</v>
       </c>
       <c r="G292" t="n">
-        <v>71.26000000000001</v>
+        <v>39.67</v>
       </c>
       <c r="H292" t="n">
-        <v>75.83</v>
+        <v>41.11</v>
       </c>
       <c r="I292" t="n">
-        <v>78.64</v>
+        <v>42.73</v>
       </c>
       <c r="J292" t="n">
-        <v>1444301</v>
+        <v>3932798</v>
       </c>
       <c r="K292" t="n">
-        <v>2009216</v>
+        <v>10187115</v>
       </c>
       <c r="L292" t="n">
-        <v>87.2</v>
+        <v>45.36</v>
       </c>
       <c r="M292" t="n">
-        <v>65.8</v>
+        <v>38.98</v>
       </c>
       <c r="N292" t="inlineStr">
         <is>
@@ -51142,28 +51142,28 @@
         </is>
       </c>
       <c r="O292" t="n">
-        <v>219920</v>
+        <v>333451</v>
       </c>
       <c r="P292" t="n">
-        <v>11147</v>
+        <v>-12912086</v>
       </c>
       <c r="Q292" t="n">
-        <v>-193538</v>
+        <v>-22815463</v>
       </c>
       <c r="R292" t="n">
-        <v>-654250</v>
+        <v>-108081553</v>
       </c>
       <c r="S292" t="n">
-        <v>219080</v>
+        <v>-530955</v>
       </c>
       <c r="T292" t="n">
-        <v>21574</v>
+        <v>-2506984</v>
       </c>
       <c r="U292" t="n">
-        <v>-167793</v>
+        <v>-2669854</v>
       </c>
       <c r="V292" t="n">
-        <v>-611005</v>
+        <v>-1762198</v>
       </c>
       <c r="W292" t="n">
         <v>0</v>
@@ -51178,34 +51178,34 @@
         <v>0</v>
       </c>
       <c r="AA292" t="n">
-        <v>840</v>
+        <v>864406</v>
       </c>
       <c r="AB292" t="n">
-        <v>-10427</v>
+        <v>-10405102</v>
       </c>
       <c r="AC292" t="n">
-        <v>-25745</v>
+        <v>-20145609</v>
       </c>
       <c r="AD292" t="n">
-        <v>-43245</v>
+        <v>-106319355</v>
       </c>
       <c r="AE292" t="n">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="AF292" t="n">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="AG292" t="n">
-        <v>-45</v>
+        <v>-15</v>
       </c>
       <c r="AH292" t="n">
-        <v>-5</v>
+        <v>-30</v>
       </c>
       <c r="AI292" t="n">
         <v>0</v>
       </c>
       <c r="AJ292" t="n">
-        <v>-40</v>
+        <v>-44</v>
       </c>
       <c r="AK292" t="inlineStr">
         <is>
@@ -51213,25 +51213,25 @@
         </is>
       </c>
       <c r="AL292" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AM292" t="n">
-        <v>50</v>
+        <v>59.09</v>
       </c>
       <c r="AN292" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AO292" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AP292" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ292" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR292" t="inlineStr">
@@ -51246,29 +51246,29 @@
       </c>
       <c r="AT292" t="inlineStr">
         <is>
-          <t>跌破5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>短線籌碼止穩、5日法人賣超</t>
+          <t>5日法人明顯賣超</t>
         </is>
       </c>
       <c r="AV292" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、接近20日低點、5日法人明顯賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>3504.TW</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>揚明光</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -51287,28 +51287,28 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>1100</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G293" t="n">
-        <v>1080</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="H293" t="n">
-        <v>1105</v>
+        <v>75.83</v>
       </c>
       <c r="I293" t="n">
-        <v>1178</v>
+        <v>78.64</v>
       </c>
       <c r="J293" t="n">
-        <v>24498433</v>
+        <v>1444301</v>
       </c>
       <c r="K293" t="n">
-        <v>21726921</v>
+        <v>2009216</v>
       </c>
       <c r="L293" t="n">
-        <v>1420</v>
+        <v>87.2</v>
       </c>
       <c r="M293" t="n">
-        <v>1035</v>
+        <v>65.8</v>
       </c>
       <c r="N293" t="inlineStr">
         <is>
@@ -51316,52 +51316,52 @@
         </is>
       </c>
       <c r="O293" t="n">
-        <v>-1370164</v>
+        <v>219920</v>
       </c>
       <c r="P293" t="n">
-        <v>-391613</v>
+        <v>11147</v>
       </c>
       <c r="Q293" t="n">
-        <v>-3037134</v>
+        <v>-193538</v>
       </c>
       <c r="R293" t="n">
-        <v>-13859886</v>
+        <v>-654250</v>
       </c>
       <c r="S293" t="n">
-        <v>-1913667</v>
+        <v>219080</v>
       </c>
       <c r="T293" t="n">
-        <v>-4752973</v>
+        <v>21574</v>
       </c>
       <c r="U293" t="n">
-        <v>-8970813</v>
+        <v>-167793</v>
       </c>
       <c r="V293" t="n">
-        <v>-23200649</v>
+        <v>-611005</v>
       </c>
       <c r="W293" t="n">
-        <v>514522</v>
+        <v>0</v>
       </c>
       <c r="X293" t="n">
-        <v>4021542</v>
+        <v>0</v>
       </c>
       <c r="Y293" t="n">
-        <v>5699284</v>
+        <v>0</v>
       </c>
       <c r="Z293" t="n">
-        <v>8544334</v>
+        <v>0</v>
       </c>
       <c r="AA293" t="n">
-        <v>28981</v>
+        <v>840</v>
       </c>
       <c r="AB293" t="n">
-        <v>339818</v>
+        <v>-10427</v>
       </c>
       <c r="AC293" t="n">
-        <v>234395</v>
+        <v>-25745</v>
       </c>
       <c r="AD293" t="n">
-        <v>796429</v>
+        <v>-43245</v>
       </c>
       <c r="AE293" t="n">
         <v>-20</v>
@@ -51370,16 +51370,16 @@
         <v>-20</v>
       </c>
       <c r="AG293" t="n">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="AH293" t="n">
-        <v>-55</v>
+        <v>-5</v>
       </c>
       <c r="AI293" t="n">
         <v>0</v>
       </c>
       <c r="AJ293" t="n">
-        <v>-22</v>
+        <v>-40</v>
       </c>
       <c r="AK293" t="inlineStr">
         <is>
@@ -51387,25 +51387,25 @@
         </is>
       </c>
       <c r="AL293" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AM293" t="n">
-        <v>9.09</v>
+        <v>50</v>
       </c>
       <c r="AN293" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AO293" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="AP293" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ293" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數剛升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR293" t="inlineStr">
@@ -51420,17 +51420,17 @@
       </c>
       <c r="AT293" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能溫和放大</t>
+          <t>跌破5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
+          <t>短線籌碼止穩、5日法人賣超</t>
         </is>
       </c>
       <c r="AV293" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：跌破5日線、空頭排列、量能未放大、短線籌碼止穩、5日法人賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -52133,12 +52133,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2467.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -52157,28 +52157,28 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>479</v>
+        <v>1100</v>
       </c>
       <c r="G298" t="n">
-        <v>469.6</v>
+        <v>1080</v>
       </c>
       <c r="H298" t="n">
-        <v>495.6</v>
+        <v>1105</v>
       </c>
       <c r="I298" t="n">
-        <v>526.35</v>
+        <v>1178</v>
       </c>
       <c r="J298" t="n">
-        <v>498166</v>
+        <v>24498433</v>
       </c>
       <c r="K298" t="n">
-        <v>733673</v>
+        <v>21726921</v>
       </c>
       <c r="L298" t="n">
-        <v>597</v>
+        <v>1420</v>
       </c>
       <c r="M298" t="n">
-        <v>448.5</v>
+        <v>1035</v>
       </c>
       <c r="N298" t="inlineStr">
         <is>
@@ -52186,87 +52186,87 @@
         </is>
       </c>
       <c r="O298" t="n">
-        <v>59319</v>
+        <v>-1370164</v>
       </c>
       <c r="P298" t="n">
-        <v>-260811</v>
+        <v>-391613</v>
       </c>
       <c r="Q298" t="n">
-        <v>-774062</v>
+        <v>-3037134</v>
       </c>
       <c r="R298" t="n">
-        <v>-2666636</v>
+        <v>-13859886</v>
       </c>
       <c r="S298" t="n">
-        <v>49395</v>
+        <v>-1913667</v>
       </c>
       <c r="T298" t="n">
-        <v>-246511</v>
+        <v>-4752973</v>
       </c>
       <c r="U298" t="n">
-        <v>-648302</v>
+        <v>-8970813</v>
       </c>
       <c r="V298" t="n">
-        <v>-2369024</v>
+        <v>-23200649</v>
       </c>
       <c r="W298" t="n">
-        <v>1000</v>
+        <v>514522</v>
       </c>
       <c r="X298" t="n">
-        <v>-17000</v>
+        <v>4021542</v>
       </c>
       <c r="Y298" t="n">
-        <v>-114002</v>
+        <v>5699284</v>
       </c>
       <c r="Z298" t="n">
-        <v>-155648</v>
+        <v>8544334</v>
       </c>
       <c r="AA298" t="n">
-        <v>8924</v>
+        <v>28981</v>
       </c>
       <c r="AB298" t="n">
-        <v>2700</v>
+        <v>339818</v>
       </c>
       <c r="AC298" t="n">
-        <v>-11758</v>
+        <v>234395</v>
       </c>
       <c r="AD298" t="n">
-        <v>-141964</v>
+        <v>796429</v>
       </c>
       <c r="AE298" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AF298" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AG298" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH298" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AI298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ298" t="n">
         <v>-22</v>
       </c>
-      <c r="AF298" t="n">
-        <v>-22</v>
-      </c>
-      <c r="AG298" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH298" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AI298" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ298" t="n">
-        <v>-52</v>
-      </c>
       <c r="AK298" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
       </c>
       <c r="AL298" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="AM298" t="n">
-        <v>57.69</v>
+        <v>9.09</v>
       </c>
       <c r="AN298" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AO298" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AP298" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
       </c>
       <c r="AQ298" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數剛升溫</t>
         </is>
       </c>
       <c r="AR298" t="inlineStr">
@@ -52290,17 +52290,17 @@
       </c>
       <c r="AT298" t="inlineStr">
         <is>
-          <t>站上5日線、空頭排列、量能未放大</t>
+          <t>站上5日線、空頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>5日法人明顯賣超、外資投信同步賣超</t>
+          <t>法人連續偏賣、5日法人明顯賣超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能溫和放大、法人連續偏賣、5日法人明顯賣超、投信買外資賣。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>
@@ -52481,12 +52481,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3042.TW</t>
+          <t>2467.TW</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>晶技</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -52505,28 +52505,28 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>178.5</v>
+        <v>479</v>
       </c>
       <c r="G300" t="n">
-        <v>176.2</v>
+        <v>469.6</v>
       </c>
       <c r="H300" t="n">
-        <v>184.15</v>
+        <v>495.6</v>
       </c>
       <c r="I300" t="n">
-        <v>198.22</v>
+        <v>526.35</v>
       </c>
       <c r="J300" t="n">
-        <v>3546061</v>
+        <v>498166</v>
       </c>
       <c r="K300" t="n">
-        <v>6909062</v>
+        <v>733673</v>
       </c>
       <c r="L300" t="n">
-        <v>235.5</v>
+        <v>597</v>
       </c>
       <c r="M300" t="n">
-        <v>168.5</v>
+        <v>448.5</v>
       </c>
       <c r="N300" t="inlineStr">
         <is>
@@ -52534,52 +52534,52 @@
         </is>
       </c>
       <c r="O300" t="n">
-        <v>550251</v>
+        <v>59319</v>
       </c>
       <c r="P300" t="n">
-        <v>-2477031</v>
+        <v>-260811</v>
       </c>
       <c r="Q300" t="n">
-        <v>-3787425</v>
+        <v>-774062</v>
       </c>
       <c r="R300" t="n">
-        <v>-5274082</v>
+        <v>-2666636</v>
       </c>
       <c r="S300" t="n">
-        <v>605810</v>
+        <v>49395</v>
       </c>
       <c r="T300" t="n">
-        <v>-443735</v>
+        <v>-246511</v>
       </c>
       <c r="U300" t="n">
-        <v>-1197894</v>
+        <v>-648302</v>
       </c>
       <c r="V300" t="n">
-        <v>-1204194</v>
+        <v>-2369024</v>
       </c>
       <c r="W300" t="n">
-        <v>-188000</v>
+        <v>1000</v>
       </c>
       <c r="X300" t="n">
-        <v>-1969000</v>
+        <v>-17000</v>
       </c>
       <c r="Y300" t="n">
-        <v>-1897026</v>
+        <v>-114002</v>
       </c>
       <c r="Z300" t="n">
-        <v>-1758026</v>
+        <v>-155648</v>
       </c>
       <c r="AA300" t="n">
-        <v>132441</v>
+        <v>8924</v>
       </c>
       <c r="AB300" t="n">
-        <v>-64296</v>
+        <v>2700</v>
       </c>
       <c r="AC300" t="n">
-        <v>-692505</v>
+        <v>-11758</v>
       </c>
       <c r="AD300" t="n">
-        <v>-2311862</v>
+        <v>-141964</v>
       </c>
       <c r="AE300" t="n">
         <v>-22</v>
@@ -52597,7 +52597,7 @@
         <v>0</v>
       </c>
       <c r="AJ300" t="n">
-        <v>-42</v>
+        <v>-52</v>
       </c>
       <c r="AK300" t="inlineStr">
         <is>
@@ -52605,25 +52605,25 @@
         </is>
       </c>
       <c r="AL300" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AM300" t="n">
-        <v>47.62</v>
+        <v>57.69</v>
       </c>
       <c r="AN300" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AO300" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ300" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數升溫過快</t>
         </is>
       </c>
       <c r="AR300" t="inlineStr">
@@ -53177,12 +53177,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>6510.TWO</t>
+          <t>3042.TW</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>晶技</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -53192,7 +53192,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -53201,28 +53201,28 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>3065</v>
+        <v>178.5</v>
       </c>
       <c r="G304" t="n">
-        <v>3338</v>
+        <v>176.2</v>
       </c>
       <c r="H304" t="n">
-        <v>3338</v>
+        <v>184.15</v>
       </c>
       <c r="I304" t="n">
-        <v>3393.25</v>
+        <v>198.22</v>
       </c>
       <c r="J304" t="n">
-        <v>1036000</v>
+        <v>3546061</v>
       </c>
       <c r="K304" t="n">
-        <v>1204200</v>
+        <v>6909062</v>
       </c>
       <c r="L304" t="n">
-        <v>3935</v>
+        <v>235.5</v>
       </c>
       <c r="M304" t="n">
-        <v>2925</v>
+        <v>168.5</v>
       </c>
       <c r="N304" t="inlineStr">
         <is>
@@ -53230,52 +53230,52 @@
         </is>
       </c>
       <c r="O304" t="n">
-        <v>0</v>
+        <v>550251</v>
       </c>
       <c r="P304" t="n">
-        <v>0</v>
+        <v>-2477031</v>
       </c>
       <c r="Q304" t="n">
-        <v>0</v>
+        <v>-3787425</v>
       </c>
       <c r="R304" t="n">
-        <v>0</v>
+        <v>-5274082</v>
       </c>
       <c r="S304" t="n">
-        <v>0</v>
+        <v>605810</v>
       </c>
       <c r="T304" t="n">
-        <v>0</v>
+        <v>-443735</v>
       </c>
       <c r="U304" t="n">
-        <v>0</v>
+        <v>-1197894</v>
       </c>
       <c r="V304" t="n">
-        <v>0</v>
+        <v>-1204194</v>
       </c>
       <c r="W304" t="n">
-        <v>0</v>
+        <v>-188000</v>
       </c>
       <c r="X304" t="n">
-        <v>0</v>
+        <v>-1969000</v>
       </c>
       <c r="Y304" t="n">
-        <v>0</v>
+        <v>-1897026</v>
       </c>
       <c r="Z304" t="n">
-        <v>0</v>
+        <v>-1758026</v>
       </c>
       <c r="AA304" t="n">
-        <v>0</v>
+        <v>132441</v>
       </c>
       <c r="AB304" t="n">
-        <v>0</v>
+        <v>-64296</v>
       </c>
       <c r="AC304" t="n">
-        <v>0</v>
+        <v>-692505</v>
       </c>
       <c r="AD304" t="n">
-        <v>0</v>
+        <v>-2311862</v>
       </c>
       <c r="AE304" t="n">
         <v>-22</v>
@@ -53284,32 +53284,42 @@
         <v>-22</v>
       </c>
       <c r="AG304" t="n">
-        <v>-55</v>
+        <v>-5</v>
       </c>
       <c r="AH304" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="AI304" t="n">
         <v>0</v>
       </c>
-      <c r="AJ304" t="inlineStr"/>
-      <c r="AK304" t="inlineStr"/>
-      <c r="AL304" t="inlineStr"/>
-      <c r="AM304" t="inlineStr"/>
+      <c r="AJ304" t="n">
+        <v>-42</v>
+      </c>
+      <c r="AK304" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AL304" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>47.62</v>
+      </c>
       <c r="AN304" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AO304" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ304" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、位置偏低但需等轉強</t>
+          <t>DT尚未轉強、貼近5MA、位置偏低但需等轉強、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR304" t="inlineStr">
@@ -53324,17 +53334,17 @@
       </c>
       <c r="AT304" t="inlineStr">
         <is>
-          <t>跌破5日線、死亡交叉、量能未放大、接近20日低點</t>
+          <t>站上5日線、空頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯賣超、外資投信同步賣超</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>風險偏高：跌破5日線、死亡交叉、量能未放大、接近20日低點、籌碼中性。目前不適合積極追蹤，等待結構改善。</t>
+          <t>風險偏高：站上5日線、空頭排列、量能未放大、5日法人明顯賣超、外資投信同步賣超。目前不適合積極追蹤，等待結構改善。</t>
         </is>
       </c>
     </row>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -5041,10 +5041,10 @@
         <v>48.19</v>
       </c>
       <c r="H27" t="n">
-        <v>48.18</v>
+        <v>48.19</v>
       </c>
       <c r="I27" t="n">
-        <v>47.62</v>
+        <v>47.48</v>
       </c>
       <c r="J27" t="n">
         <v>472115</v>

--- a/output/universe_analysis_result.xlsx
+++ b/output/universe_analysis_result.xlsx
@@ -6577,12 +6577,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2855.TW</t>
+          <t>2049.TW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>統一證</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6601,28 +6601,28 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>56</v>
+        <v>337</v>
       </c>
       <c r="G36" t="n">
-        <v>55.42</v>
+        <v>323.2</v>
       </c>
       <c r="H36" t="n">
-        <v>56.48</v>
+        <v>317.65</v>
       </c>
       <c r="I36" t="n">
-        <v>56.4</v>
+        <v>326.98</v>
       </c>
       <c r="J36" t="n">
-        <v>1770749</v>
+        <v>2339178</v>
       </c>
       <c r="K36" t="n">
-        <v>3030181</v>
+        <v>3808826</v>
       </c>
       <c r="L36" t="n">
-        <v>60.2</v>
+        <v>357</v>
       </c>
       <c r="M36" t="n">
-        <v>47.75</v>
+        <v>298</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -6630,52 +6630,52 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>908211</v>
+        <v>317997</v>
       </c>
       <c r="P36" t="n">
-        <v>3770108</v>
+        <v>3836972</v>
       </c>
       <c r="Q36" t="n">
-        <v>6497395</v>
+        <v>4342988</v>
       </c>
       <c r="R36" t="n">
-        <v>6457441</v>
+        <v>1453408</v>
       </c>
       <c r="S36" t="n">
-        <v>906211</v>
+        <v>270928</v>
       </c>
       <c r="T36" t="n">
-        <v>3684608</v>
+        <v>3670518</v>
       </c>
       <c r="U36" t="n">
-        <v>6339895</v>
+        <v>4239352</v>
       </c>
       <c r="V36" t="n">
-        <v>6056090</v>
+        <v>3271346</v>
       </c>
       <c r="W36" t="n">
-        <v>2000</v>
+        <v>43000</v>
       </c>
       <c r="X36" t="n">
-        <v>85500</v>
+        <v>42603</v>
       </c>
       <c r="Y36" t="n">
-        <v>157500</v>
+        <v>41603</v>
       </c>
       <c r="Z36" t="n">
-        <v>401351</v>
+        <v>-1715497</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>4069</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>123851</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>62033</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>-102441</v>
       </c>
       <c r="AE36" t="n">
         <v>40</v>
@@ -6693,7 +6693,7 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
@@ -6701,25 +6701,25 @@
         </is>
       </c>
       <c r="AL36" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AM36" t="n">
-        <v>53.85</v>
+        <v>33.33</v>
       </c>
       <c r="AN36" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="AO36" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>DT進入觀察區、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT進入觀察區、5MA乖離尚可、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
@@ -6925,12 +6925,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2049.TW</t>
+          <t>4904.TW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6949,28 +6949,28 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>337</v>
+        <v>113</v>
       </c>
       <c r="G38" t="n">
-        <v>323.2</v>
+        <v>113.2</v>
       </c>
       <c r="H38" t="n">
-        <v>317.65</v>
+        <v>112.5</v>
       </c>
       <c r="I38" t="n">
-        <v>326.98</v>
+        <v>108.95</v>
       </c>
       <c r="J38" t="n">
-        <v>2339178</v>
+        <v>8400943</v>
       </c>
       <c r="K38" t="n">
-        <v>3808826</v>
+        <v>6707014</v>
       </c>
       <c r="L38" t="n">
-        <v>357</v>
+        <v>116</v>
       </c>
       <c r="M38" t="n">
-        <v>298</v>
+        <v>103</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -6978,61 +6978,61 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>317997</v>
+        <v>1547123</v>
       </c>
       <c r="P38" t="n">
-        <v>3836972</v>
+        <v>2798025</v>
       </c>
       <c r="Q38" t="n">
-        <v>4342988</v>
+        <v>6490844</v>
       </c>
       <c r="R38" t="n">
-        <v>1453408</v>
+        <v>18354453</v>
       </c>
       <c r="S38" t="n">
-        <v>270928</v>
+        <v>2876281</v>
       </c>
       <c r="T38" t="n">
-        <v>3670518</v>
+        <v>3416261</v>
       </c>
       <c r="U38" t="n">
-        <v>4239352</v>
+        <v>5907978</v>
       </c>
       <c r="V38" t="n">
-        <v>3271346</v>
+        <v>9561619</v>
       </c>
       <c r="W38" t="n">
-        <v>43000</v>
+        <v>-880691</v>
       </c>
       <c r="X38" t="n">
-        <v>42603</v>
+        <v>-133741</v>
       </c>
       <c r="Y38" t="n">
-        <v>41603</v>
+        <v>395259</v>
       </c>
       <c r="Z38" t="n">
-        <v>-1715497</v>
+        <v>4780374</v>
       </c>
       <c r="AA38" t="n">
-        <v>4069</v>
+        <v>-448467</v>
       </c>
       <c r="AB38" t="n">
-        <v>123851</v>
+        <v>-484495</v>
       </c>
       <c r="AC38" t="n">
-        <v>62033</v>
+        <v>187607</v>
       </c>
       <c r="AD38" t="n">
-        <v>-102441</v>
+        <v>4012460</v>
       </c>
       <c r="AE38" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF38" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AH38" t="n">
         <v>80</v>
@@ -7041,7 +7041,7 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
@@ -7049,25 +7049,25 @@
         </is>
       </c>
       <c r="AL38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AO38" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>DT進入觀察區、5MA乖離尚可、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>跌破5日線、多頭排列、量能溫和放大</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
@@ -7092,19 +7092,19 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4904.TW</t>
+          <t>2883.TW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>開發金</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7123,28 +7123,28 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>113</v>
+        <v>38.5</v>
       </c>
       <c r="G39" t="n">
-        <v>113.2</v>
+        <v>38.3</v>
       </c>
       <c r="H39" t="n">
-        <v>112.5</v>
+        <v>38.31</v>
       </c>
       <c r="I39" t="n">
-        <v>108.95</v>
+        <v>38.18</v>
       </c>
       <c r="J39" t="n">
-        <v>8400943</v>
+        <v>24345468</v>
       </c>
       <c r="K39" t="n">
-        <v>6707014</v>
+        <v>40431198</v>
       </c>
       <c r="L39" t="n">
-        <v>116</v>
+        <v>39.75</v>
       </c>
       <c r="M39" t="n">
-        <v>103</v>
+        <v>36.4</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -7152,52 +7152,52 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>1547123</v>
+        <v>-1848543</v>
       </c>
       <c r="P39" t="n">
-        <v>2798025</v>
+        <v>14264197</v>
       </c>
       <c r="Q39" t="n">
-        <v>6490844</v>
+        <v>15828357</v>
       </c>
       <c r="R39" t="n">
-        <v>18354453</v>
+        <v>27776225</v>
       </c>
       <c r="S39" t="n">
-        <v>2876281</v>
+        <v>-2410211</v>
       </c>
       <c r="T39" t="n">
-        <v>3416261</v>
+        <v>7241921</v>
       </c>
       <c r="U39" t="n">
-        <v>5907978</v>
+        <v>85612</v>
       </c>
       <c r="V39" t="n">
-        <v>9561619</v>
+        <v>-3265129</v>
       </c>
       <c r="W39" t="n">
-        <v>-880691</v>
+        <v>713743</v>
       </c>
       <c r="X39" t="n">
-        <v>-133741</v>
+        <v>5599979</v>
       </c>
       <c r="Y39" t="n">
-        <v>395259</v>
+        <v>9599254</v>
       </c>
       <c r="Z39" t="n">
-        <v>4780374</v>
+        <v>5674613</v>
       </c>
       <c r="AA39" t="n">
-        <v>-448467</v>
+        <v>-152075</v>
       </c>
       <c r="AB39" t="n">
-        <v>-484495</v>
+        <v>1422297</v>
       </c>
       <c r="AC39" t="n">
-        <v>187607</v>
+        <v>6143491</v>
       </c>
       <c r="AD39" t="n">
-        <v>4012460</v>
+        <v>25366741</v>
       </c>
       <c r="AE39" t="n">
         <v>38</v>
@@ -7206,16 +7206,16 @@
         <v>38</v>
       </c>
       <c r="AG39" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="AH39" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
@@ -7223,25 +7223,25 @@
         </is>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="AN39" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="AO39" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、量能溫和放大</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
@@ -7256,17 +7256,17 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能溫和放大</t>
+          <t>站上5日線、黃金交叉、量能未放大</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能溫和放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、黃金交叉、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -7447,12 +7447,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2883.TW</t>
+          <t>1522.TW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>開發金</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7471,28 +7471,28 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>38.5</v>
+        <v>26.75</v>
       </c>
       <c r="G41" t="n">
-        <v>38.3</v>
+        <v>26.56</v>
       </c>
       <c r="H41" t="n">
-        <v>38.31</v>
+        <v>26.74</v>
       </c>
       <c r="I41" t="n">
-        <v>38.18</v>
+        <v>26.49</v>
       </c>
       <c r="J41" t="n">
-        <v>24345468</v>
+        <v>378425</v>
       </c>
       <c r="K41" t="n">
-        <v>40431198</v>
+        <v>265260</v>
       </c>
       <c r="L41" t="n">
-        <v>39.75</v>
+        <v>27.6</v>
       </c>
       <c r="M41" t="n">
-        <v>36.4</v>
+        <v>25.4</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -7500,70 +7500,70 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>-1848543</v>
+        <v>195544</v>
       </c>
       <c r="P41" t="n">
-        <v>14264197</v>
+        <v>362265</v>
       </c>
       <c r="Q41" t="n">
-        <v>15828357</v>
+        <v>526714</v>
       </c>
       <c r="R41" t="n">
-        <v>27776225</v>
+        <v>1182178</v>
       </c>
       <c r="S41" t="n">
-        <v>-2410211</v>
+        <v>198442</v>
       </c>
       <c r="T41" t="n">
-        <v>7241921</v>
+        <v>357801</v>
       </c>
       <c r="U41" t="n">
-        <v>85612</v>
+        <v>524834</v>
       </c>
       <c r="V41" t="n">
-        <v>-3265129</v>
+        <v>1194176</v>
       </c>
       <c r="W41" t="n">
-        <v>713743</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>5599979</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>9599254</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>5674613</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>-152075</v>
+        <v>-2898</v>
       </c>
       <c r="AB41" t="n">
-        <v>1422297</v>
+        <v>4464</v>
       </c>
       <c r="AC41" t="n">
-        <v>6143491</v>
+        <v>1880</v>
       </c>
       <c r="AD41" t="n">
-        <v>25366741</v>
+        <v>-11998</v>
       </c>
       <c r="AE41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG41" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AH41" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
@@ -7571,25 +7571,25 @@
         </is>
       </c>
       <c r="AL41" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AM41" t="n">
-        <v>18.75</v>
+        <v>200</v>
       </c>
       <c r="AN41" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AO41" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數剛升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
@@ -7604,17 +7604,17 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能未放大</t>
+          <t>站上5日線、量能溫和放大</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能未放大、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -8143,12 +8143,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1522.TW</t>
+          <t>2408.TW</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8167,28 +8167,28 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>26.75</v>
+        <v>477</v>
       </c>
       <c r="G45" t="n">
-        <v>26.56</v>
+        <v>449.1</v>
       </c>
       <c r="H45" t="n">
-        <v>26.74</v>
+        <v>447.1</v>
       </c>
       <c r="I45" t="n">
-        <v>26.49</v>
+        <v>482.85</v>
       </c>
       <c r="J45" t="n">
-        <v>378425</v>
+        <v>61920419</v>
       </c>
       <c r="K45" t="n">
-        <v>265260</v>
+        <v>43320533</v>
       </c>
       <c r="L45" t="n">
-        <v>27.6</v>
+        <v>537</v>
       </c>
       <c r="M45" t="n">
-        <v>25.4</v>
+        <v>412</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -8196,52 +8196,52 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>195544</v>
+        <v>6389450</v>
       </c>
       <c r="P45" t="n">
-        <v>362265</v>
+        <v>25841504</v>
       </c>
       <c r="Q45" t="n">
-        <v>526714</v>
+        <v>26202701</v>
       </c>
       <c r="R45" t="n">
-        <v>1182178</v>
+        <v>-39784735</v>
       </c>
       <c r="S45" t="n">
-        <v>198442</v>
+        <v>5661474</v>
       </c>
       <c r="T45" t="n">
-        <v>357801</v>
+        <v>22656549</v>
       </c>
       <c r="U45" t="n">
-        <v>524834</v>
+        <v>24948891</v>
       </c>
       <c r="V45" t="n">
-        <v>1194176</v>
+        <v>-30414183</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>623225</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1561532</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>-1589361</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>-12909853</v>
       </c>
       <c r="AA45" t="n">
-        <v>-2898</v>
+        <v>104751</v>
       </c>
       <c r="AB45" t="n">
-        <v>4464</v>
+        <v>1623423</v>
       </c>
       <c r="AC45" t="n">
-        <v>1880</v>
+        <v>2843171</v>
       </c>
       <c r="AD45" t="n">
-        <v>-11998</v>
+        <v>3539301</v>
       </c>
       <c r="AE45" t="n">
         <v>36</v>
@@ -8259,7 +8259,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
@@ -8267,16 +8267,16 @@
         </is>
       </c>
       <c r="AL45" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AM45" t="n">
-        <v>200</v>
+        <v>38.46</v>
       </c>
       <c r="AN45" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO45" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
@@ -8305,12 +8305,12 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -8665,12 +8665,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2408.TW</t>
+          <t>4938.TW</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8689,28 +8689,28 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>477</v>
+        <v>104.5</v>
       </c>
       <c r="G48" t="n">
-        <v>449.1</v>
+        <v>105.2</v>
       </c>
       <c r="H48" t="n">
-        <v>447.1</v>
+        <v>103.31</v>
       </c>
       <c r="I48" t="n">
-        <v>482.85</v>
+        <v>97.63</v>
       </c>
       <c r="J48" t="n">
-        <v>61920419</v>
+        <v>8329981</v>
       </c>
       <c r="K48" t="n">
-        <v>43320533</v>
+        <v>14614082</v>
       </c>
       <c r="L48" t="n">
-        <v>537</v>
+        <v>114</v>
       </c>
       <c r="M48" t="n">
-        <v>412</v>
+        <v>88.7</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -8718,70 +8718,70 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>6389450</v>
+        <v>461441</v>
       </c>
       <c r="P48" t="n">
-        <v>25841504</v>
+        <v>7107175</v>
       </c>
       <c r="Q48" t="n">
-        <v>26202701</v>
+        <v>13720595</v>
       </c>
       <c r="R48" t="n">
-        <v>-39784735</v>
+        <v>31690971</v>
       </c>
       <c r="S48" t="n">
-        <v>5661474</v>
+        <v>631015</v>
       </c>
       <c r="T48" t="n">
-        <v>22656549</v>
+        <v>6250535</v>
       </c>
       <c r="U48" t="n">
-        <v>24948891</v>
+        <v>12600903</v>
       </c>
       <c r="V48" t="n">
-        <v>-30414183</v>
+        <v>35477655</v>
       </c>
       <c r="W48" t="n">
-        <v>623225</v>
+        <v>8000</v>
       </c>
       <c r="X48" t="n">
-        <v>1561532</v>
+        <v>979329</v>
       </c>
       <c r="Y48" t="n">
-        <v>-1589361</v>
+        <v>567329</v>
       </c>
       <c r="Z48" t="n">
-        <v>-12909853</v>
+        <v>-6717406</v>
       </c>
       <c r="AA48" t="n">
-        <v>104751</v>
+        <v>-177574</v>
       </c>
       <c r="AB48" t="n">
-        <v>1623423</v>
+        <v>-122689</v>
       </c>
       <c r="AC48" t="n">
-        <v>2843171</v>
+        <v>552363</v>
       </c>
       <c r="AD48" t="n">
-        <v>3539301</v>
+        <v>2930722</v>
       </c>
       <c r="AE48" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF48" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG48" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="AH48" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
@@ -8789,25 +8789,25 @@
         </is>
       </c>
       <c r="AL48" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>-19.05</v>
+      </c>
+      <c r="AN48" t="n">
         <v>10</v>
       </c>
-      <c r="AM48" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>60</v>
-      </c>
       <c r="AO48" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>DT尚未轉強、5MA乖離尚可、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
@@ -8822,29 +8822,29 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>站上5日線、量能溫和放大</t>
+          <t>跌破5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能溫和放大、法人連續偏買、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4938.TW</t>
+          <t>3005.TW</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8863,28 +8863,28 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>104.5</v>
+        <v>123</v>
       </c>
       <c r="G49" t="n">
-        <v>105.2</v>
+        <v>124.9</v>
       </c>
       <c r="H49" t="n">
-        <v>103.31</v>
+        <v>123.15</v>
       </c>
       <c r="I49" t="n">
-        <v>97.63</v>
+        <v>120.47</v>
       </c>
       <c r="J49" t="n">
-        <v>8329981</v>
+        <v>1752958</v>
       </c>
       <c r="K49" t="n">
-        <v>14614082</v>
+        <v>2520293</v>
       </c>
       <c r="L49" t="n">
-        <v>114</v>
+        <v>127.5</v>
       </c>
       <c r="M49" t="n">
-        <v>88.7</v>
+        <v>116</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -8892,52 +8892,52 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>461441</v>
+        <v>487851</v>
       </c>
       <c r="P49" t="n">
-        <v>7107175</v>
+        <v>1079756</v>
       </c>
       <c r="Q49" t="n">
-        <v>13720595</v>
+        <v>3532666</v>
       </c>
       <c r="R49" t="n">
-        <v>31690971</v>
+        <v>9650122</v>
       </c>
       <c r="S49" t="n">
-        <v>631015</v>
+        <v>493354</v>
       </c>
       <c r="T49" t="n">
-        <v>6250535</v>
+        <v>1015686</v>
       </c>
       <c r="U49" t="n">
-        <v>12600903</v>
+        <v>3233426</v>
       </c>
       <c r="V49" t="n">
-        <v>35477655</v>
+        <v>9171538</v>
       </c>
       <c r="W49" t="n">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="X49" t="n">
-        <v>979329</v>
+        <v>28099</v>
       </c>
       <c r="Y49" t="n">
-        <v>567329</v>
+        <v>32099</v>
       </c>
       <c r="Z49" t="n">
-        <v>-6717406</v>
+        <v>-301415</v>
       </c>
       <c r="AA49" t="n">
-        <v>-177574</v>
+        <v>-8503</v>
       </c>
       <c r="AB49" t="n">
-        <v>-122689</v>
+        <v>35971</v>
       </c>
       <c r="AC49" t="n">
-        <v>552363</v>
+        <v>267141</v>
       </c>
       <c r="AD49" t="n">
-        <v>2930722</v>
+        <v>779999</v>
       </c>
       <c r="AE49" t="n">
         <v>34</v>
@@ -8955,7 +8955,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
@@ -8963,10 +8963,10 @@
         </is>
       </c>
       <c r="AL49" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="AM49" t="n">
-        <v>-19.05</v>
+        <v>-29.17</v>
       </c>
       <c r="AN49" t="n">
         <v>10</v>
@@ -9187,12 +9187,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3005.TW</t>
+          <t>2206.TW</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -9211,28 +9211,28 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>123</v>
+        <v>64</v>
       </c>
       <c r="G51" t="n">
-        <v>124.9</v>
+        <v>63.72</v>
       </c>
       <c r="H51" t="n">
-        <v>123.15</v>
+        <v>64.17</v>
       </c>
       <c r="I51" t="n">
-        <v>120.47</v>
+        <v>63.59</v>
       </c>
       <c r="J51" t="n">
-        <v>1752958</v>
+        <v>296544</v>
       </c>
       <c r="K51" t="n">
-        <v>2520293</v>
+        <v>580853</v>
       </c>
       <c r="L51" t="n">
-        <v>127.5</v>
+        <v>66</v>
       </c>
       <c r="M51" t="n">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -9240,70 +9240,70 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>487851</v>
+        <v>160777</v>
       </c>
       <c r="P51" t="n">
-        <v>1079756</v>
+        <v>5528</v>
       </c>
       <c r="Q51" t="n">
-        <v>3532666</v>
+        <v>184571</v>
       </c>
       <c r="R51" t="n">
-        <v>9650122</v>
+        <v>3008786</v>
       </c>
       <c r="S51" t="n">
-        <v>493354</v>
+        <v>159777</v>
       </c>
       <c r="T51" t="n">
-        <v>1015686</v>
+        <v>-4472</v>
       </c>
       <c r="U51" t="n">
-        <v>3233426</v>
+        <v>176571</v>
       </c>
       <c r="V51" t="n">
-        <v>9171538</v>
+        <v>3055979</v>
       </c>
       <c r="W51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X51" t="n">
         <v>3000</v>
       </c>
-      <c r="X51" t="n">
-        <v>28099</v>
-      </c>
       <c r="Y51" t="n">
-        <v>32099</v>
+        <v>1000</v>
       </c>
       <c r="Z51" t="n">
-        <v>-301415</v>
+        <v>4807</v>
       </c>
       <c r="AA51" t="n">
-        <v>-8503</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>35971</v>
+        <v>7000</v>
       </c>
       <c r="AC51" t="n">
-        <v>267141</v>
+        <v>7000</v>
       </c>
       <c r="AD51" t="n">
-        <v>779999</v>
+        <v>-52000</v>
       </c>
       <c r="AE51" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF51" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AH51" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>48</v>
+        <v>-28</v>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
@@ -9311,25 +9311,25 @@
         </is>
       </c>
       <c r="AL51" t="n">
-        <v>-14</v>
+        <v>60</v>
       </c>
       <c r="AM51" t="n">
-        <v>-29.17</v>
+        <v>214.29</v>
       </c>
       <c r="AN51" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AO51" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、均線多頭排列、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
@@ -9344,29 +9344,29 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>跌破5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、多頭排列、量能未放大、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2206.TW</t>
+          <t>2834.TW</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>臺企銀</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -9385,28 +9385,28 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="G52" t="n">
-        <v>63.72</v>
+        <v>17.94</v>
       </c>
       <c r="H52" t="n">
-        <v>64.17</v>
+        <v>17.88</v>
       </c>
       <c r="I52" t="n">
-        <v>63.59</v>
+        <v>17.71</v>
       </c>
       <c r="J52" t="n">
-        <v>296544</v>
+        <v>15576621</v>
       </c>
       <c r="K52" t="n">
-        <v>580853</v>
+        <v>15799464</v>
       </c>
       <c r="L52" t="n">
-        <v>66</v>
+        <v>18.2</v>
       </c>
       <c r="M52" t="n">
-        <v>62</v>
+        <v>17.25</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -9414,52 +9414,52 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>160777</v>
+        <v>2142586</v>
       </c>
       <c r="P52" t="n">
-        <v>5528</v>
+        <v>-633868</v>
       </c>
       <c r="Q52" t="n">
-        <v>184571</v>
+        <v>5414328</v>
       </c>
       <c r="R52" t="n">
-        <v>3008786</v>
+        <v>-696081</v>
       </c>
       <c r="S52" t="n">
-        <v>159777</v>
+        <v>2044476</v>
       </c>
       <c r="T52" t="n">
-        <v>-4472</v>
+        <v>-892907</v>
       </c>
       <c r="U52" t="n">
-        <v>176571</v>
+        <v>5427927</v>
       </c>
       <c r="V52" t="n">
-        <v>3055979</v>
+        <v>-5985680</v>
       </c>
       <c r="W52" t="n">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="X52" t="n">
-        <v>3000</v>
+        <v>-29542</v>
       </c>
       <c r="Y52" t="n">
-        <v>1000</v>
+        <v>-46542</v>
       </c>
       <c r="Z52" t="n">
-        <v>4807</v>
+        <v>5834344</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>91110</v>
       </c>
       <c r="AB52" t="n">
-        <v>7000</v>
+        <v>288581</v>
       </c>
       <c r="AC52" t="n">
-        <v>7000</v>
+        <v>32943</v>
       </c>
       <c r="AD52" t="n">
-        <v>-52000</v>
+        <v>-544745</v>
       </c>
       <c r="AE52" t="n">
         <v>32</v>
@@ -9468,42 +9468,42 @@
         <v>32</v>
       </c>
       <c r="AG52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AH52" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AL52" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="AN52" t="n">
         <v>70</v>
       </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>-28</v>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AL52" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>214.29</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>45</v>
-      </c>
       <c r="AO52" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數升溫過快</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
@@ -9518,29 +9518,29 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日低點、法人連續偏買、5日法人買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2834.TW</t>
+          <t>2355.TW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>臺企銀</t>
+          <t>敬鵬</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -9559,81 +9559,81 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>18</v>
+        <v>52.5</v>
       </c>
       <c r="G53" t="n">
-        <v>17.94</v>
+        <v>51.85</v>
       </c>
       <c r="H53" t="n">
-        <v>17.88</v>
+        <v>52.17</v>
       </c>
       <c r="I53" t="n">
-        <v>17.71</v>
+        <v>48.42</v>
       </c>
       <c r="J53" t="n">
-        <v>15576621</v>
+        <v>23805071</v>
       </c>
       <c r="K53" t="n">
-        <v>15799464</v>
+        <v>11058329</v>
       </c>
       <c r="L53" t="n">
-        <v>18.2</v>
+        <v>56.3</v>
       </c>
       <c r="M53" t="n">
-        <v>17.25</v>
+        <v>41.25</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>無明顯異常</t>
+          <t>爆量價未漲</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>2142586</v>
+        <v>-4118031</v>
       </c>
       <c r="P53" t="n">
-        <v>-633868</v>
+        <v>494682</v>
       </c>
       <c r="Q53" t="n">
-        <v>5414328</v>
+        <v>716129</v>
       </c>
       <c r="R53" t="n">
-        <v>-696081</v>
+        <v>2238124</v>
       </c>
       <c r="S53" t="n">
-        <v>2044476</v>
+        <v>-4735050</v>
       </c>
       <c r="T53" t="n">
-        <v>-892907</v>
+        <v>-23314</v>
       </c>
       <c r="U53" t="n">
-        <v>5427927</v>
+        <v>433608</v>
       </c>
       <c r="V53" t="n">
-        <v>-5985680</v>
+        <v>1800115</v>
       </c>
       <c r="W53" t="n">
-        <v>7000</v>
+        <v>650000</v>
       </c>
       <c r="X53" t="n">
-        <v>-29542</v>
+        <v>650000</v>
       </c>
       <c r="Y53" t="n">
-        <v>-46542</v>
+        <v>650000</v>
       </c>
       <c r="Z53" t="n">
-        <v>5834344</v>
+        <v>650000</v>
       </c>
       <c r="AA53" t="n">
-        <v>91110</v>
+        <v>-32981</v>
       </c>
       <c r="AB53" t="n">
-        <v>288581</v>
+        <v>-132004</v>
       </c>
       <c r="AC53" t="n">
-        <v>32943</v>
+        <v>-367479</v>
       </c>
       <c r="AD53" t="n">
-        <v>-544745</v>
+        <v>-211991</v>
       </c>
       <c r="AE53" t="n">
         <v>32</v>
@@ -9642,16 +9642,16 @@
         <v>32</v>
       </c>
       <c r="AG53" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH53" t="n">
         <v>50</v>
       </c>
-      <c r="AH53" t="n">
-        <v>30</v>
-      </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="AJ53" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
@@ -9659,25 +9659,25 @@
         </is>
       </c>
       <c r="AL53" t="n">
-        <v>20</v>
+        <v>-4</v>
       </c>
       <c r="AM53" t="n">
-        <v>166.67</v>
+        <v>-11.11</v>
       </c>
       <c r="AN53" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AO53" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數轉弱</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
@@ -9692,17 +9692,17 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點</t>
+          <t>站上5日線、爆量、爆量價未漲</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、接近20日高點、接近20日低點、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -10579,12 +10579,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2355.TW</t>
+          <t>2317.TW</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>敬鵬</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -10603,99 +10603,99 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>52.5</v>
+        <v>248</v>
       </c>
       <c r="G59" t="n">
-        <v>51.85</v>
+        <v>248.4</v>
       </c>
       <c r="H59" t="n">
-        <v>52.17</v>
+        <v>244.95</v>
       </c>
       <c r="I59" t="n">
-        <v>48.42</v>
+        <v>247.6</v>
       </c>
       <c r="J59" t="n">
-        <v>23805071</v>
+        <v>21358260</v>
       </c>
       <c r="K59" t="n">
-        <v>11058329</v>
+        <v>39821779</v>
       </c>
       <c r="L59" t="n">
-        <v>56.3</v>
+        <v>266.5</v>
       </c>
       <c r="M59" t="n">
-        <v>41.25</v>
+        <v>237</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>爆量價未漲</t>
+          <t>無明顯異常</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>-4118031</v>
+        <v>3737414</v>
       </c>
       <c r="P59" t="n">
-        <v>494682</v>
+        <v>22943934</v>
       </c>
       <c r="Q59" t="n">
-        <v>716129</v>
+        <v>52654734</v>
       </c>
       <c r="R59" t="n">
-        <v>2238124</v>
+        <v>60678765</v>
       </c>
       <c r="S59" t="n">
-        <v>-4735050</v>
+        <v>3341501</v>
       </c>
       <c r="T59" t="n">
-        <v>-23314</v>
+        <v>19613071</v>
       </c>
       <c r="U59" t="n">
-        <v>433608</v>
+        <v>51524775</v>
       </c>
       <c r="V59" t="n">
-        <v>1800115</v>
+        <v>52056504</v>
       </c>
       <c r="W59" t="n">
-        <v>650000</v>
+        <v>512127</v>
       </c>
       <c r="X59" t="n">
-        <v>650000</v>
+        <v>1556797</v>
       </c>
       <c r="Y59" t="n">
-        <v>650000</v>
+        <v>1699126</v>
       </c>
       <c r="Z59" t="n">
-        <v>650000</v>
+        <v>5047551</v>
       </c>
       <c r="AA59" t="n">
-        <v>-32981</v>
+        <v>-116214</v>
       </c>
       <c r="AB59" t="n">
-        <v>-132004</v>
+        <v>1774066</v>
       </c>
       <c r="AC59" t="n">
-        <v>-367479</v>
+        <v>-569167</v>
       </c>
       <c r="AD59" t="n">
-        <v>-211991</v>
+        <v>3574710</v>
       </c>
       <c r="AE59" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF59" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG59" t="n">
-        <v>40</v>
+        <v>-5</v>
       </c>
       <c r="AH59" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ59" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
@@ -10703,25 +10703,25 @@
         </is>
       </c>
       <c r="AL59" t="n">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="AM59" t="n">
-        <v>-11.11</v>
+        <v>-31.82</v>
       </c>
       <c r="AN59" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AO59" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能偏強、分數轉弱</t>
+          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
@@ -10736,29 +10736,29 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>站上5日線、爆量、爆量價未漲</t>
+          <t>跌破5日線、黃金交叉、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資投信同步買超</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、爆量、爆量價未漲、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：跌破5日線、黃金交叉、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2317.TW</t>
+          <t>2886.TW</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -10777,28 +10777,28 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>248</v>
+        <v>54.8</v>
       </c>
       <c r="G60" t="n">
-        <v>248.4</v>
+        <v>54.5</v>
       </c>
       <c r="H60" t="n">
-        <v>244.95</v>
+        <v>53.69</v>
       </c>
       <c r="I60" t="n">
-        <v>247.6</v>
+        <v>51.54</v>
       </c>
       <c r="J60" t="n">
-        <v>21358260</v>
+        <v>15397600</v>
       </c>
       <c r="K60" t="n">
-        <v>39821779</v>
+        <v>19024853</v>
       </c>
       <c r="L60" t="n">
-        <v>266.5</v>
+        <v>56</v>
       </c>
       <c r="M60" t="n">
-        <v>237</v>
+        <v>48.35</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -10806,52 +10806,52 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>3737414</v>
+        <v>2550566</v>
       </c>
       <c r="P60" t="n">
-        <v>22943934</v>
+        <v>-1227988</v>
       </c>
       <c r="Q60" t="n">
-        <v>52654734</v>
+        <v>13232583</v>
       </c>
       <c r="R60" t="n">
-        <v>60678765</v>
+        <v>71259592</v>
       </c>
       <c r="S60" t="n">
-        <v>3341501</v>
+        <v>7768271</v>
       </c>
       <c r="T60" t="n">
-        <v>19613071</v>
+        <v>12643922</v>
       </c>
       <c r="U60" t="n">
-        <v>51524775</v>
+        <v>24490438</v>
       </c>
       <c r="V60" t="n">
-        <v>52056504</v>
+        <v>70775517</v>
       </c>
       <c r="W60" t="n">
-        <v>512127</v>
+        <v>-5477941</v>
       </c>
       <c r="X60" t="n">
-        <v>1556797</v>
+        <v>-16012709</v>
       </c>
       <c r="Y60" t="n">
-        <v>1699126</v>
+        <v>-18979474</v>
       </c>
       <c r="Z60" t="n">
-        <v>5047551</v>
+        <v>-24425496</v>
       </c>
       <c r="AA60" t="n">
-        <v>-116214</v>
+        <v>260236</v>
       </c>
       <c r="AB60" t="n">
-        <v>1774066</v>
+        <v>2140799</v>
       </c>
       <c r="AC60" t="n">
-        <v>-569167</v>
+        <v>7721619</v>
       </c>
       <c r="AD60" t="n">
-        <v>3574710</v>
+        <v>24909571</v>
       </c>
       <c r="AE60" t="n">
         <v>30</v>
@@ -10860,16 +10860,16 @@
         <v>30</v>
       </c>
       <c r="AG60" t="n">
-        <v>-5</v>
+        <v>45</v>
       </c>
       <c r="AH60" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
@@ -10877,25 +10877,25 @@
         </is>
       </c>
       <c r="AL60" t="n">
-        <v>-14</v>
+        <v>16</v>
       </c>
       <c r="AM60" t="n">
-        <v>-31.82</v>
+        <v>114.29</v>
       </c>
       <c r="AN60" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO60" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>暫不追價</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>DT尚未轉強、尚未站上5MA、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
@@ -10910,17 +10910,17 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>跌破5日線、黃金交叉、量能未放大、接近20日低點</t>
+          <t>站上5日線、多頭排列、量能未放大</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
+          <t>5日法人明顯買超、外資買投信賣</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>整理觀察：跌破5日線、黃金交叉、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -11449,12 +11449,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2886.TW</t>
+          <t>4766.TW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>南寶</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -11473,28 +11473,28 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>54.8</v>
+        <v>361.5</v>
       </c>
       <c r="G64" t="n">
-        <v>54.5</v>
+        <v>359.6</v>
       </c>
       <c r="H64" t="n">
-        <v>53.69</v>
+        <v>360</v>
       </c>
       <c r="I64" t="n">
-        <v>51.54</v>
+        <v>355.4</v>
       </c>
       <c r="J64" t="n">
-        <v>15397600</v>
+        <v>122386</v>
       </c>
       <c r="K64" t="n">
-        <v>19024853</v>
+        <v>176846</v>
       </c>
       <c r="L64" t="n">
-        <v>56</v>
+        <v>369.5</v>
       </c>
       <c r="M64" t="n">
-        <v>48.35</v>
+        <v>339.5</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -11502,70 +11502,70 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>2550566</v>
+        <v>80379</v>
       </c>
       <c r="P64" t="n">
-        <v>-1227988</v>
+        <v>248435</v>
       </c>
       <c r="Q64" t="n">
-        <v>13232583</v>
+        <v>379527</v>
       </c>
       <c r="R64" t="n">
-        <v>71259592</v>
+        <v>813202</v>
       </c>
       <c r="S64" t="n">
-        <v>7768271</v>
+        <v>80379</v>
       </c>
       <c r="T64" t="n">
-        <v>12643922</v>
+        <v>248804</v>
       </c>
       <c r="U64" t="n">
-        <v>24490438</v>
+        <v>380845</v>
       </c>
       <c r="V64" t="n">
-        <v>70775517</v>
+        <v>882923</v>
       </c>
       <c r="W64" t="n">
-        <v>-5477941</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>-16012709</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>-18979474</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>-24425496</v>
+        <v>-58023</v>
       </c>
       <c r="AA64" t="n">
-        <v>260236</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2140799</v>
+        <v>-369</v>
       </c>
       <c r="AC64" t="n">
-        <v>7721619</v>
+        <v>-1318</v>
       </c>
       <c r="AD64" t="n">
-        <v>24909571</v>
+        <v>-11698</v>
       </c>
       <c r="AE64" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF64" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG64" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="AH64" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
       </c>
       <c r="AJ64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
@@ -11573,25 +11573,25 @@
         </is>
       </c>
       <c r="AL64" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AM64" t="n">
-        <v>114.29</v>
+        <v>75</v>
       </c>
       <c r="AN64" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AO64" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>等待拉回確認</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、均線多頭排列、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
@@ -11606,17 +11606,17 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>站上5日線、多頭排列、量能未放大</t>
+          <t>站上5日線、量能未放大</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、外資買投信賣</t>
+          <t>法人連續偏買、5日法人買超</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、多頭排列、量能未放大、5日法人明顯買超、外資買投信賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
@@ -12493,12 +12493,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4766.TW</t>
+          <t>3293.TWO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>南寶</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -12517,28 +12517,28 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>361.5</v>
+        <v>808</v>
       </c>
       <c r="G70" t="n">
-        <v>359.6</v>
+        <v>794.6</v>
       </c>
       <c r="H70" t="n">
-        <v>360</v>
+        <v>794.7</v>
       </c>
       <c r="I70" t="n">
-        <v>355.4</v>
+        <v>792.75</v>
       </c>
       <c r="J70" t="n">
-        <v>122386</v>
+        <v>1574000</v>
       </c>
       <c r="K70" t="n">
-        <v>176846</v>
+        <v>1282000</v>
       </c>
       <c r="L70" t="n">
-        <v>369.5</v>
+        <v>819</v>
       </c>
       <c r="M70" t="n">
-        <v>339.5</v>
+        <v>766</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
@@ -12546,28 +12546,28 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>80379</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>248435</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>379527</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>813202</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>80379</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>248804</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>380845</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>882923</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
         <v>0</v>
@@ -12579,19 +12579,19 @@
         <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>-58023</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>-369</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>-1318</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>-11698</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="n">
         <v>28</v>
@@ -12600,42 +12600,42 @@
         <v>28</v>
       </c>
       <c r="AG70" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="AH70" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
       </c>
       <c r="AJ70" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AL70" t="n">
         <v>16</v>
       </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="AL70" t="n">
-        <v>12</v>
-      </c>
       <c r="AM70" t="n">
-        <v>75</v>
+        <v>133.33</v>
       </c>
       <c r="AN70" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AO70" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>等待拉回確認</t>
+          <t>進場位置尚可</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
@@ -12650,29 +12650,29 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大</t>
+          <t>站上5日線、黃金交叉、量能溫和放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>法人連續偏買、5日法人買超</t>
+          <t>籌碼中性</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、法人連續偏買、5日法人買超。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3293.TWO</t>
+          <t>2347.TW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -12691,28 +12691,28 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>808</v>
+        <v>102</v>
       </c>
       <c r="G71" t="n">
-        <v>794.6</v>
+        <v>101.1</v>
       </c>
       <c r="H71" t="n">
-        <v>794.7</v>
+        <v>101.35</v>
       </c>
       <c r="I71" t="n">
-        <v>792.75</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>1574000</v>
+        <v>3752247</v>
       </c>
       <c r="K71" t="n">
-        <v>1282000</v>
+        <v>4243109</v>
       </c>
       <c r="L71" t="n">
-        <v>819</v>
+        <v>104</v>
       </c>
       <c r="M71" t="n">
-        <v>766</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -12720,70 +12720,70 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>-542924</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>258976</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>1682548</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>6589207</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>-1641623</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>-713610</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>-1345779</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1218643</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1072000</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>849734</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2250434</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>2796816</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>26699</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>122852</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>777893</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>2573748</v>
       </c>
       <c r="AE71" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF71" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG71" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
       </c>
       <c r="AJ71" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
@@ -12791,25 +12791,25 @@
         </is>
       </c>
       <c r="AL71" t="n">
-        <v>16</v>
+        <v>-20</v>
       </c>
       <c r="AM71" t="n">
-        <v>133.33</v>
+        <v>-43.48</v>
       </c>
       <c r="AN71" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AO71" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>進場位置尚可</t>
+          <t>偏高或條件不足</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、量能溫和放大、分數明顯升溫</t>
+          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
@@ -12824,29 +12824,29 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>站上5日線、黃金交叉、量能溫和放大、接近20日高點</t>
+          <t>站上5日線、量能未放大、接近20日高點</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>籌碼中性</t>
+          <t>5日法人明顯買超、投信買外資賣</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、黃金交叉、量能溫和放大、接近20日高點、籌碼中性。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、量能未放大、接近20日高點、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2347.TW</t>
+          <t>2855.TW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>統一證</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -12865,28 +12865,28 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="G72" t="n">
-        <v>101.1</v>
+        <v>55.42</v>
       </c>
       <c r="H72" t="n">
-        <v>101.35</v>
+        <v>56.48</v>
       </c>
       <c r="I72" t="n">
-        <v>99.04000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="J72" t="n">
-        <v>3752247</v>
+        <v>1770749</v>
       </c>
       <c r="K72" t="n">
-        <v>4243109</v>
+        <v>3030181</v>
       </c>
       <c r="L72" t="n">
-        <v>104</v>
+        <v>60.2</v>
       </c>
       <c r="M72" t="n">
-        <v>94.09999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -12894,52 +12894,52 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>-542924</v>
+        <v>908211</v>
       </c>
       <c r="P72" t="n">
-        <v>258976</v>
+        <v>3770108</v>
       </c>
       <c r="Q72" t="n">
-        <v>1682548</v>
+        <v>6497395</v>
       </c>
       <c r="R72" t="n">
-        <v>6589207</v>
+        <v>6457441</v>
       </c>
       <c r="S72" t="n">
-        <v>-1641623</v>
+        <v>906211</v>
       </c>
       <c r="T72" t="n">
-        <v>-713610</v>
+        <v>3684608</v>
       </c>
       <c r="U72" t="n">
-        <v>-1345779</v>
+        <v>6339895</v>
       </c>
       <c r="V72" t="n">
-        <v>1218643</v>
+        <v>6056090</v>
       </c>
       <c r="W72" t="n">
-        <v>1072000</v>
+        <v>2000</v>
       </c>
       <c r="X72" t="n">
-        <v>849734</v>
+        <v>85500</v>
       </c>
       <c r="Y72" t="n">
-        <v>2250434</v>
+        <v>157500</v>
       </c>
       <c r="Z72" t="n">
-        <v>2796816</v>
+        <v>401351</v>
       </c>
       <c r="AA72" t="n">
-        <v>26699</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>122852</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>777893</v>
+        <v>0</v>
       </c>
       <c r="AD72" t="n">
-        <v>2573748</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
         <v>26</v>
@@ -12948,16 +12948,16 @@
         <v>26</v>
       </c>
       <c r="AG72" t="n">
-        <v>35</v>
+        <v>-15</v>
       </c>
       <c r="AH72" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
       </c>
       <c r="AJ72" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
@@ -12965,25 +12965,25 @@
         </is>
       </c>
       <c r="AL72" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AM72" t="n">
-        <v>-43.48</v>
+        <v>0</v>
       </c>
       <c r="AN72" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AO72" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>偏高或條件不足</t>
+          <t>暫不追價</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>DT尚未轉強、貼近5MA、位於20日區間中上緣、分數轉弱</t>
+          <t>DT尚未轉強、貼近5MA</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
@@ -12998,17 +12998,17 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>站上5日線、量能未放大、接近20日高點</t>
+          <t>站上5日線、空頭排列、量能未放大、接近20日低點</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>5日法人明顯買超、投信買外資賣</t>
+          <t>法人連續偏買、5日法人明顯買超、外資投信同步買超</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>整理觀察：站上5日線、量能未放大、接近20日高點、5日法人明顯買超、投信買外資賣。多空訊號混合，建議降低追價衝動。</t>
+          <t>整理觀察：站上5日線、空頭排列、量能未放大、接近20日低點、法人連續偏買、5日法人明顯買超、外資投信同步買超。多空訊號混合，建議降低追價衝動。</t>
         </is>
       </c>
     </row>
